--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906572F0-9A42-4AD3-8094-A0D75649E288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1D829B-3963-4A7E-AF1D-D21512D4092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="287">
   <si>
     <t>S. No.</t>
   </si>
@@ -560,15 +560,9 @@
     <t>R1, R2, R3</t>
   </si>
   <si>
-    <t>RES SMD 499K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>R4</t>
   </si>
   <si>
-    <t>AC0603FR-07499KL</t>
-  </si>
-  <si>
     <t>RES SMD 20K OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -576,9 +570,6 @@
   </si>
   <si>
     <t>RC0603FR-0720KL</t>
-  </si>
-  <si>
-    <t>499K</t>
   </si>
   <si>
     <t>20K</t>
@@ -684,9 +675,6 @@
     <t>----</t>
   </si>
   <si>
-    <t>C227924</t>
-  </si>
-  <si>
     <t>C105575</t>
   </si>
   <si>
@@ -799,9 +787,6 @@
     <t>SB1, SB2, SB3, SB4, SB5, SB6, SB7, SB8, SB9, SB10, SB11, SB12, SB13, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB21, SB22, SB23, SB24, SB25, SB26, SB27, SB28, SB29, SB30, SB31, SB32, SB33, SB34, SB35, SB36, SB37, SB38, SB39, SB40, SB41, SB42, SB43, SB44, SB45, SB46, SB47, SB48, SB49, SB50, SB70, SB71, SB72</t>
   </si>
   <si>
-    <t>5V Adaptor</t>
-  </si>
-  <si>
     <t>Aliexpress</t>
   </si>
   <si>
@@ -827,6 +812,91 @@
   </si>
   <si>
     <t>Aliexpress Ahipping</t>
+  </si>
+  <si>
+    <t>CAP SMD  2.7pF ±0.25pF 50V NPO 0603</t>
+  </si>
+  <si>
+    <t>C90</t>
+  </si>
+  <si>
+    <t>CC0603CRNPO9BN2R7</t>
+  </si>
+  <si>
+    <t>CAP SMD 4.7pF ±0.1pF 50V NPO 0603</t>
+  </si>
+  <si>
+    <t>C91</t>
+  </si>
+  <si>
+    <t>CC0603BRNPO9BN4R7</t>
+  </si>
+  <si>
+    <t>C282247</t>
+  </si>
+  <si>
+    <t>2.7pF</t>
+  </si>
+  <si>
+    <t>C327022</t>
+  </si>
+  <si>
+    <t>4.7pF</t>
+  </si>
+  <si>
+    <t>IND 700mA 1.6nH ±10% 40mΩ 0603</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>FHW0603UC1N6KST</t>
+  </si>
+  <si>
+    <t>C317978</t>
+  </si>
+  <si>
+    <t>499R</t>
+  </si>
+  <si>
+    <t>RES SMD 499Ω ± 1.00% 0.1W ± 100ppm/℃ 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-07499RL</t>
+  </si>
+  <si>
+    <t>C137714</t>
+  </si>
+  <si>
+    <t>RF ANT 2.4GHZ STAMPED MET SLD</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>PRO-OB-440</t>
+  </si>
+  <si>
+    <t>CONN U.FL RCPT STR 50 OHM SMD</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>U.FL-R-SMT-1(80)</t>
+  </si>
+  <si>
+    <t>Hirose</t>
+  </si>
+  <si>
+    <t>C88374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Abracon LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Need Quotation from custum supplier </t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1284,17 +1354,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1312,17 +1371,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1446,21 +1494,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1470,54 +1503,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1553,62 +1538,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1618,7 +1547,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1701,10 +1630,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1747,9 +1676,6 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1774,16 +1700,16 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1870,7 +1796,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1942,7 +1868,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1951,7 +1877,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1972,58 +1898,22 @@
     <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2053,30 +1943,15 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2084,21 +1959,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2107,21 +1967,12 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2134,7 +1985,57 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2149,228 +2050,145 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2649,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2672,36 +2490,36 @@
     <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.5703125" style="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="169" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
-      <c r="P1" s="178"/>
-      <c r="Q1" s="178"/>
-      <c r="R1" s="178"/>
-      <c r="S1" s="178"/>
-      <c r="T1" s="178"/>
-      <c r="U1" s="178"/>
-      <c r="V1" s="179"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="171"/>
     </row>
     <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2737,8 +2555,8 @@
       <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="202" t="s">
-        <v>259</v>
+      <c r="L2" s="152" t="s">
+        <v>254</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
@@ -2747,7 +2565,7 @@
         <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>11</v>
@@ -2759,10 +2577,10 @@
         <v>46</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="T2" s="202" t="s">
-        <v>258</v>
+        <v>252</v>
+      </c>
+      <c r="T2" s="152" t="s">
+        <v>253</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
@@ -2775,19 +2593,19 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="169" t="s">
+      <c r="D3" s="144" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="78" t="s">
+      <c r="E3" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="77" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="39" t="s">
@@ -2799,7 +2617,7 @@
       <c r="I3" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="77" t="s">
+      <c r="J3" s="76" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="42">
@@ -2808,18 +2626,18 @@
       <c r="L3" s="42">
         <v>100</v>
       </c>
-      <c r="M3" s="79">
+      <c r="M3" s="78">
         <v>4</v>
       </c>
       <c r="N3" s="43">
         <f>M3*5</f>
         <v>20</v>
       </c>
-      <c r="O3" s="201">
+      <c r="O3" s="43">
         <f>M3*20</f>
         <v>80</v>
       </c>
-      <c r="P3" s="80" t="s">
+      <c r="P3" s="79" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="44">
@@ -2832,7 +2650,7 @@
       <c r="S3" s="45">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="T3" s="203">
+      <c r="T3" s="45">
         <f>S3*L3</f>
         <v>1.3599999999999999</v>
       </c>
@@ -2843,63 +2661,63 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="81" t="s">
+      <c r="B4" s="176"/>
+      <c r="C4" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="109" t="s">
+      <c r="D4" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="83" t="s">
+      <c r="E4" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="83" t="s">
+      <c r="F4" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="82" t="s">
+      <c r="J4" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="49">
+      <c r="K4" s="48">
         <v>20</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="48">
         <v>40</v>
       </c>
-      <c r="M4" s="84">
+      <c r="M4" s="83">
         <v>1</v>
       </c>
-      <c r="N4" s="115">
-        <f t="shared" ref="N4:N41" si="0">M4*5</f>
+      <c r="N4" s="114">
+        <f t="shared" ref="N4:N46" si="0">M4*5</f>
         <v>5</v>
       </c>
-      <c r="O4" s="115">
-        <f t="shared" ref="O4:O44" si="1">M4*20</f>
+      <c r="O4" s="114">
+        <f t="shared" ref="O4:O48" si="1">M4*20</f>
         <v>20</v>
       </c>
-      <c r="P4" s="85" t="s">
+      <c r="P4" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4" s="50">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="R4" s="116">
-        <f t="shared" ref="R4:R40" si="2">Q4*K4</f>
+      <c r="R4" s="115">
+        <f t="shared" ref="R4:R45" si="2">Q4*K4</f>
         <v>0.40599999999999997</v>
       </c>
-      <c r="S4" s="116">
+      <c r="S4" s="115">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="T4" s="116">
-        <f t="shared" ref="T4:T44" si="3">S4*L4</f>
+      <c r="T4" s="115">
+        <f t="shared" ref="T4:T45" si="3">S4*L4</f>
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
@@ -2909,62 +2727,62 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="188"/>
-      <c r="C5" s="81" t="s">
+      <c r="B5" s="176"/>
+      <c r="C5" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="168" t="s">
+      <c r="D5" s="143" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="82" t="s">
+      <c r="F5" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="I5" s="48" t="s">
+      <c r="I5" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="82" t="s">
+      <c r="J5" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="48">
         <v>100</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="48">
         <v>400</v>
       </c>
-      <c r="M5" s="84">
+      <c r="M5" s="83">
         <v>19</v>
       </c>
-      <c r="N5" s="115">
+      <c r="N5" s="114">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="O5" s="115">
+      <c r="O5" s="114">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="P5" s="85" t="s">
+      <c r="P5" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="50">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="R5" s="116">
+      <c r="R5" s="115">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="S5" s="116">
+      <c r="S5" s="115">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T5" s="116">
+      <c r="T5" s="115">
         <f t="shared" si="3"/>
         <v>2.8000000000000003</v>
       </c>
@@ -2976,62 +2794,62 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="176"/>
+      <c r="C6" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="109" t="s">
+      <c r="D6" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="I6" s="48" t="s">
+      <c r="I6" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="82" t="s">
+      <c r="J6" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="48">
         <v>100</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="48">
         <v>200</v>
       </c>
-      <c r="M6" s="84">
+      <c r="M6" s="83">
         <v>8</v>
       </c>
-      <c r="N6" s="115">
+      <c r="N6" s="114">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O6" s="115">
+      <c r="O6" s="114">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P6" s="86" t="s">
+      <c r="P6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="51">
+      <c r="Q6" s="50">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="116">
+      <c r="R6" s="115">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="116">
+      <c r="S6" s="115">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="116">
+      <c r="T6" s="115">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
@@ -3043,62 +2861,62 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="188"/>
-      <c r="C7" s="81" t="s">
+      <c r="B7" s="176"/>
+      <c r="C7" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="83" t="s">
+      <c r="E7" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="113" t="s">
+      <c r="F7" s="112" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="H7" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="I7" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="J7" s="82" t="s">
-        <v>201</v>
-      </c>
-      <c r="K7" s="49">
+      <c r="G7" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" s="81" t="s">
+        <v>198</v>
+      </c>
+      <c r="K7" s="48">
         <v>100</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="48">
         <v>100</v>
       </c>
-      <c r="M7" s="84">
+      <c r="M7" s="83">
         <v>1</v>
       </c>
-      <c r="N7" s="115">
+      <c r="N7" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O7" s="115">
+      <c r="O7" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="112" t="s">
+      <c r="P7" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="51">
+      <c r="Q7" s="50">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R7" s="116">
+      <c r="R7" s="115">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S7" s="116">
+      <c r="S7" s="115">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T7" s="116">
+      <c r="T7" s="115">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
@@ -3110,62 +2928,62 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="188"/>
-      <c r="C8" s="81" t="s">
+      <c r="B8" s="176"/>
+      <c r="C8" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="168" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="82" t="s">
+      <c r="D8" s="143" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="82" t="s">
+      <c r="J8" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="49">
+      <c r="K8" s="48">
         <v>150</v>
       </c>
-      <c r="L8" s="49">
+      <c r="L8" s="48">
         <v>600</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="83">
         <v>29</v>
       </c>
-      <c r="N8" s="115">
+      <c r="N8" s="114">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="O8" s="115">
+      <c r="O8" s="114">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="P8" s="86" t="s">
+      <c r="P8" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="51">
+      <c r="Q8" s="50">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="R8" s="116">
+      <c r="R8" s="115">
         <f t="shared" si="2"/>
         <v>1.08</v>
       </c>
-      <c r="S8" s="116">
+      <c r="S8" s="115">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="T8" s="116">
+      <c r="T8" s="115">
         <f t="shared" si="3"/>
         <v>3.4799999999999995</v>
       </c>
@@ -3177,62 +2995,62 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="188"/>
-      <c r="C9" s="81" t="s">
+      <c r="B9" s="176"/>
+      <c r="C9" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="109" t="s">
+      <c r="D9" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="83" t="s">
+      <c r="F9" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="G9" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="52">
         <v>10</v>
       </c>
-      <c r="L9" s="53">
+      <c r="L9" s="52">
         <v>30</v>
       </c>
-      <c r="M9" s="84">
+      <c r="M9" s="83">
         <v>1</v>
       </c>
-      <c r="N9" s="115">
+      <c r="N9" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="115">
+      <c r="O9" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P9" s="86" t="s">
+      <c r="P9" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="51">
+      <c r="Q9" s="50">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="R9" s="116">
+      <c r="R9" s="115">
         <f t="shared" si="2"/>
         <v>0.443</v>
       </c>
-      <c r="S9" s="116">
+      <c r="S9" s="115">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="T9" s="116">
+      <c r="T9" s="115">
         <f t="shared" si="3"/>
         <v>1.1459999999999999</v>
       </c>
@@ -3244,62 +3062,62 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="188"/>
-      <c r="C10" s="81" t="s">
+      <c r="B10" s="176"/>
+      <c r="C10" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="83" t="s">
+      <c r="F10" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="53">
+      <c r="K10" s="52">
         <v>100</v>
       </c>
-      <c r="L10" s="53">
+      <c r="L10" s="52">
         <v>200</v>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="83">
         <v>6</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="114">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="114">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="P10" s="85" t="s">
+      <c r="P10" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="51">
+      <c r="Q10" s="50">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="115">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="115">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="T10" s="116">
+      <c r="T10" s="115">
         <f t="shared" si="3"/>
         <v>0.64</v>
       </c>
@@ -3311,62 +3129,62 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="188"/>
-      <c r="C11" s="81" t="s">
+      <c r="B11" s="176"/>
+      <c r="C11" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="168" t="s">
+      <c r="D11" s="143" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="53" t="s">
+      <c r="G11" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="53">
+      <c r="K11" s="52">
         <v>100</v>
       </c>
-      <c r="L11" s="53">
+      <c r="L11" s="52">
         <v>350</v>
       </c>
-      <c r="M11" s="84">
+      <c r="M11" s="83">
         <v>16</v>
       </c>
-      <c r="N11" s="115">
+      <c r="N11" s="114">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="O11" s="115">
+      <c r="O11" s="114">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="P11" s="85" t="s">
+      <c r="P11" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="51">
+      <c r="Q11" s="50">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="R11" s="116">
+      <c r="R11" s="115">
         <f t="shared" si="2"/>
         <v>1.51</v>
       </c>
-      <c r="S11" s="116">
+      <c r="S11" s="115">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="T11" s="116">
+      <c r="T11" s="115">
         <f t="shared" si="3"/>
         <v>5.2850000000000001</v>
       </c>
@@ -3378,62 +3196,62 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="188"/>
-      <c r="C12" s="81" t="s">
+      <c r="B12" s="176"/>
+      <c r="C12" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="109" t="s">
+      <c r="D12" s="108" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H12" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="I12" s="48" t="s">
+      <c r="H12" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="I12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="82" t="s">
-        <v>203</v>
-      </c>
-      <c r="K12" s="53">
+      <c r="J12" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="K12" s="52">
         <v>50</v>
       </c>
-      <c r="L12" s="53">
+      <c r="L12" s="52">
         <v>50</v>
       </c>
-      <c r="M12" s="84">
+      <c r="M12" s="83">
         <v>1</v>
       </c>
-      <c r="N12" s="115">
+      <c r="N12" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O12" s="115">
+      <c r="O12" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="117" t="s">
+      <c r="P12" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="51">
+      <c r="Q12" s="50">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="R12" s="116">
+      <c r="R12" s="115">
         <f t="shared" si="2"/>
         <v>0.23500000000000001</v>
       </c>
-      <c r="S12" s="116">
+      <c r="S12" s="115">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="T12" s="116">
+      <c r="T12" s="115">
         <f t="shared" si="3"/>
         <v>0.23500000000000001</v>
       </c>
@@ -3445,62 +3263,62 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="188"/>
-      <c r="C13" s="81" t="s">
+      <c r="B13" s="176"/>
+      <c r="C13" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="168" t="s">
+      <c r="D13" s="143" t="s">
         <v>169</v>
       </c>
-      <c r="E13" s="82" t="s">
+      <c r="E13" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="F13" s="100" t="s">
+      <c r="F13" s="99" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="H13" s="47" t="s">
-        <v>204</v>
-      </c>
-      <c r="I13" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="J13" s="82" t="s">
-        <v>205</v>
-      </c>
-      <c r="K13" s="53">
+      <c r="G13" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="J13" s="81" t="s">
+        <v>202</v>
+      </c>
+      <c r="K13" s="52">
         <v>100</v>
       </c>
-      <c r="L13" s="53">
+      <c r="L13" s="52">
         <v>100</v>
       </c>
-      <c r="M13" s="84">
+      <c r="M13" s="83">
         <v>1</v>
       </c>
-      <c r="N13" s="115">
+      <c r="N13" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O13" s="115">
+      <c r="O13" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="117" t="s">
+      <c r="P13" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q13" s="51">
+      <c r="Q13" s="50">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R13" s="116">
+      <c r="R13" s="115">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="S13" s="116">
+      <c r="S13" s="115">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="T13" s="116">
+      <c r="T13" s="115">
         <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
@@ -3512,62 +3330,62 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="188"/>
-      <c r="C14" s="81" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="83" t="s">
+      <c r="B14" s="176"/>
+      <c r="C14" s="80" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="83" t="s">
-        <v>226</v>
-      </c>
-      <c r="G14" s="53" t="s">
+      <c r="F14" s="82" t="s">
+        <v>222</v>
+      </c>
+      <c r="G14" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H14" s="47" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" s="48" t="s">
+      <c r="H14" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="I14" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="82" t="s">
-        <v>234</v>
-      </c>
-      <c r="K14" s="53">
+      <c r="J14" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="K14" s="52">
         <v>100</v>
       </c>
-      <c r="L14" s="53">
+      <c r="L14" s="52">
         <v>100</v>
       </c>
-      <c r="M14" s="84">
+      <c r="M14" s="83">
         <v>1</v>
       </c>
-      <c r="N14" s="115">
+      <c r="N14" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O14" s="115">
+      <c r="O14" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="117" t="s">
+      <c r="P14" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="51">
+      <c r="Q14" s="50">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="R14" s="116">
+      <c r="R14" s="115">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="S14" s="116">
+      <c r="S14" s="115">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="T14" s="116">
+      <c r="T14" s="115">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
@@ -3579,269 +3397,267 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="189"/>
-      <c r="C15" s="128" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="199" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="164" t="s">
+      <c r="B15" s="176"/>
+      <c r="C15" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="108" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="164" t="s">
-        <v>229</v>
-      </c>
-      <c r="G15" s="66" t="s">
+      <c r="F15" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="G15" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="I15" s="68" t="s">
+      <c r="H15" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="K15" s="66">
+      <c r="J15" s="81" t="s">
+        <v>232</v>
+      </c>
+      <c r="K15" s="52">
         <v>50</v>
       </c>
-      <c r="L15" s="66">
+      <c r="L15" s="52">
         <v>50</v>
       </c>
-      <c r="M15" s="97">
+      <c r="M15" s="83">
         <v>2</v>
       </c>
-      <c r="N15" s="70">
+      <c r="N15" s="114">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O15" s="231">
+      <c r="O15" s="114">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="125" t="s">
+      <c r="P15" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="71">
+      <c r="Q15" s="50">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="R15" s="126">
+      <c r="R15" s="115">
         <f t="shared" si="2"/>
         <v>0.255</v>
       </c>
-      <c r="S15" s="126">
+      <c r="S15" s="115">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="T15" s="126">
+      <c r="T15" s="115">
         <f t="shared" si="3"/>
         <v>0.255</v>
       </c>
-      <c r="U15" s="16"/>
-      <c r="V15" s="17"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="15"/>
       <c r="W15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="26.25" thickBot="1">
+    <row r="16" spans="1:23" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="190" t="s">
-        <v>193</v>
-      </c>
-      <c r="C16" s="166" t="s">
-        <v>190</v>
-      </c>
-      <c r="D16" s="133" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" s="121" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="121" t="s">
-        <v>192</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="H16" s="122" t="s">
-        <v>207</v>
-      </c>
-      <c r="I16" s="159" t="s">
-        <v>39</v>
-      </c>
-      <c r="J16" s="121" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="46">
-        <v>10</v>
-      </c>
-      <c r="L16" s="46">
-        <v>30</v>
-      </c>
-      <c r="M16" s="160">
+      <c r="B16" s="176"/>
+      <c r="C16" s="80" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" s="189" t="s">
+        <v>260</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>261</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="81" t="s">
+        <v>266</v>
+      </c>
+      <c r="K16" s="52">
+        <v>50</v>
+      </c>
+      <c r="L16" s="52">
+        <v>50</v>
+      </c>
+      <c r="M16" s="83">
         <v>1</v>
       </c>
-      <c r="N16" s="50">
+      <c r="N16" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O16" s="50">
+      <c r="O16" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="161" t="s">
+      <c r="P16" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="123">
-        <v>6.2600000000000003E-2</v>
-      </c>
-      <c r="R16" s="52">
+      <c r="Q16" s="50">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="R16" s="115">
         <f t="shared" si="2"/>
-        <v>0.626</v>
-      </c>
-      <c r="S16" s="52">
-        <v>6.1699999999999998E-2</v>
-      </c>
-      <c r="T16" s="52">
-        <f t="shared" si="3"/>
-        <v>1.851</v>
-      </c>
-      <c r="U16" s="124"/>
-      <c r="V16" s="127"/>
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="S16" s="115">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="T16" s="115">
+        <f>S16*L16</f>
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="U16" s="14"/>
+      <c r="V16" s="15"/>
       <c r="W16" s="11"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="191"/>
-      <c r="C17" s="167" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="151" t="s">
-        <v>231</v>
-      </c>
-      <c r="E17" s="87" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="87" t="s">
-        <v>232</v>
-      </c>
-      <c r="G17" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="56" t="s">
-        <v>237</v>
-      </c>
-      <c r="I17" s="57" t="s">
+      <c r="B17" s="178"/>
+      <c r="C17" s="122" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" s="191" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="141" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="141" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="I17" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="87" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="55">
-        <v>15</v>
-      </c>
-      <c r="L17" s="55">
-        <v>45</v>
-      </c>
-      <c r="M17" s="162">
-        <v>2</v>
-      </c>
-      <c r="N17" s="129">
+      <c r="J17" s="91" t="s">
+        <v>268</v>
+      </c>
+      <c r="K17" s="65">
+        <v>50</v>
+      </c>
+      <c r="L17" s="65">
+        <v>50</v>
+      </c>
+      <c r="M17" s="96">
+        <v>1</v>
+      </c>
+      <c r="N17" s="69">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O17" s="201">
+        <v>5</v>
+      </c>
+      <c r="O17" s="69">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="P17" s="163" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="58">
-        <v>0.1116</v>
-      </c>
-      <c r="R17" s="130">
+      <c r="Q17" s="70">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="R17" s="121">
         <f t="shared" si="2"/>
-        <v>1.6740000000000002</v>
-      </c>
-      <c r="S17" s="130">
-        <v>0.1116</v>
-      </c>
-      <c r="T17" s="130">
-        <f t="shared" si="3"/>
-        <v>5.0220000000000002</v>
-      </c>
-      <c r="U17" s="30"/>
-      <c r="V17" s="31"/>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="S17" s="121">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="T17" s="121">
+        <f>S17*L17</f>
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="U17" s="16"/>
+      <c r="V17" s="17"/>
       <c r="W17" s="11"/>
     </row>
-    <row r="18" spans="1:23" ht="15.75" thickBot="1">
+    <row r="18" spans="1:23" ht="26.25" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="192" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="76" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="169" t="s">
-        <v>195</v>
-      </c>
-      <c r="E18" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="F18" s="78" t="s">
-        <v>197</v>
+      <c r="B18" s="182" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="201" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="144" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="F18" s="76" t="s">
+        <v>189</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I18" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="77" t="s">
+      <c r="J18" s="76" t="s">
         <v>22</v>
       </c>
       <c r="K18" s="39">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L18" s="39">
-        <v>50</v>
-      </c>
-      <c r="M18" s="79">
+        <v>30</v>
+      </c>
+      <c r="M18" s="78">
         <v>1</v>
       </c>
       <c r="N18" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O18" s="201">
+      <c r="O18" s="43">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="165" t="s">
+      <c r="P18" s="142" t="s">
         <v>16</v>
       </c>
       <c r="Q18" s="44">
-        <v>2.07E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="R18" s="45">
         <f t="shared" si="2"/>
-        <v>1.0349999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="S18" s="45">
-        <v>2.07E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="T18" s="45">
         <f t="shared" si="3"/>
-        <v>1.0349999999999999</v>
+        <v>1.851</v>
       </c>
       <c r="U18" s="12"/>
       <c r="V18" s="13"/>
@@ -3851,949 +3667,949 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="193"/>
-      <c r="C19" s="81" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19" s="109" t="s">
-        <v>239</v>
-      </c>
-      <c r="E19" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="F19" s="83" t="s">
-        <v>240</v>
-      </c>
-      <c r="G19" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="H19" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="I19" s="48" t="s">
+      <c r="B19" s="183"/>
+      <c r="C19" s="202" t="s">
+        <v>226</v>
+      </c>
+      <c r="D19" s="151" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="I19" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="82" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" s="53">
-        <v>20</v>
-      </c>
-      <c r="L19" s="53">
-        <v>50</v>
-      </c>
-      <c r="M19" s="84">
+      <c r="J19" s="91" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="65">
+        <v>15</v>
+      </c>
+      <c r="L19" s="65">
+        <v>45</v>
+      </c>
+      <c r="M19" s="96">
         <v>2</v>
       </c>
-      <c r="N19" s="115">
+      <c r="N19" s="69">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="115">
+      <c r="O19" s="69">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="117" t="s">
+      <c r="P19" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="51">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="R19" s="116">
+      <c r="Q19" s="70">
+        <v>0.1116</v>
+      </c>
+      <c r="R19" s="121">
         <f t="shared" si="2"/>
-        <v>1.4860000000000002</v>
-      </c>
-      <c r="S19" s="116">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="T19" s="116">
+        <v>1.6740000000000002</v>
+      </c>
+      <c r="S19" s="121">
+        <v>0.1116</v>
+      </c>
+      <c r="T19" s="121">
         <f t="shared" si="3"/>
-        <v>3.7150000000000003</v>
-      </c>
-      <c r="U19" s="14"/>
-      <c r="V19" s="15"/>
+        <v>5.0220000000000002</v>
+      </c>
+      <c r="U19" s="16"/>
+      <c r="V19" s="17"/>
       <c r="W19" s="11"/>
     </row>
     <row r="20" spans="1:23" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="194"/>
-      <c r="C20" s="128" t="s">
+      <c r="B20" s="184" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="144" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20" s="77" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>194</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="39">
+        <v>50</v>
+      </c>
+      <c r="L20" s="39">
+        <v>50</v>
+      </c>
+      <c r="M20" s="78">
+        <v>1</v>
+      </c>
+      <c r="N20" s="43">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O20" s="43">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P20" s="142" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="44">
+        <v>2.07E-2</v>
+      </c>
+      <c r="R20" s="45">
+        <f t="shared" si="2"/>
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="S20" s="45">
+        <v>2.07E-2</v>
+      </c>
+      <c r="T20" s="45">
+        <f t="shared" si="3"/>
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="U20" s="12"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="11"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
+      <c r="B21" s="185"/>
+      <c r="C21" s="80" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="108" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" s="82" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="82" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="D20" s="199" t="s">
+      <c r="H21" s="46" t="s">
         <v>242</v>
       </c>
-      <c r="E20" s="164" t="s">
-        <v>243</v>
-      </c>
-      <c r="F20" s="164" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="66" t="s">
-        <v>245</v>
-      </c>
-      <c r="H20" s="67" t="s">
-        <v>247</v>
-      </c>
-      <c r="I20" s="68" t="s">
+      <c r="I21" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="92" t="s">
-        <v>215</v>
-      </c>
-      <c r="K20" s="66">
+      <c r="J21" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="K21" s="52">
         <v>20</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L21" s="52">
         <v>50</v>
       </c>
-      <c r="M20" s="97">
+      <c r="M21" s="83">
         <v>2</v>
       </c>
-      <c r="N20" s="70">
+      <c r="N21" s="114">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O20" s="231">
+      <c r="O21" s="114">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P20" s="125" t="s">
+      <c r="P21" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="71">
+      <c r="Q21" s="50">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="R21" s="115">
+        <f t="shared" si="2"/>
+        <v>1.4860000000000002</v>
+      </c>
+      <c r="S21" s="115">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="T21" s="115">
+        <f t="shared" si="3"/>
+        <v>3.7150000000000003</v>
+      </c>
+      <c r="U21" s="14"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="11"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="185"/>
+      <c r="C22" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="D22" s="108" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="82" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="82" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="52">
+        <v>20</v>
+      </c>
+      <c r="L22" s="52">
+        <v>50</v>
+      </c>
+      <c r="M22" s="83">
+        <v>2</v>
+      </c>
+      <c r="N22" s="114">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="O22" s="114">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="P22" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="50">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R20" s="126">
+      <c r="R22" s="115">
         <f t="shared" si="2"/>
         <v>0.154</v>
       </c>
-      <c r="S20" s="126">
+      <c r="S22" s="115">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T20" s="126">
+      <c r="T22" s="115">
         <f t="shared" si="3"/>
         <v>0.38500000000000001</v>
       </c>
-      <c r="U20" s="16"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="11"/>
-    </row>
-    <row r="21" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A21" s="6">
-        <v>19</v>
-      </c>
-      <c r="B21" s="148" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="233" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="234" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="235" t="s">
+      <c r="U22" s="14"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="11"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="186"/>
+      <c r="C23" s="122" t="s">
+        <v>269</v>
+      </c>
+      <c r="D23" s="191" t="s">
+        <v>270</v>
+      </c>
+      <c r="E23" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="235" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="236" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="236" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="235" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="235" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="235">
-        <v>42</v>
-      </c>
-      <c r="L21" s="235">
-        <v>162</v>
-      </c>
-      <c r="M21" s="237">
-        <v>8</v>
-      </c>
-      <c r="N21" s="237">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="O21" s="237">
-        <f t="shared" si="1"/>
-        <v>160</v>
-      </c>
-      <c r="P21" s="238" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q21" s="239">
-        <v>3.68</v>
-      </c>
-      <c r="R21" s="240">
-        <f t="shared" si="2"/>
-        <v>154.56</v>
-      </c>
-      <c r="S21" s="240">
-        <v>3.68</v>
-      </c>
-      <c r="T21" s="240">
-        <f t="shared" si="3"/>
-        <v>596.16000000000008</v>
-      </c>
-      <c r="U21" s="241" t="s">
-        <v>260</v>
-      </c>
-      <c r="V21" s="242">
-        <v>3.68</v>
-      </c>
-      <c r="W21" s="11"/>
-    </row>
-    <row r="22" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A22" s="6">
-        <v>20</v>
-      </c>
-      <c r="B22" s="243" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="244" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="245" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="246" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="246" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="247" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="248" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="249" t="s">
+      <c r="F23" s="141" t="s">
+        <v>271</v>
+      </c>
+      <c r="G23" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>272</v>
+      </c>
+      <c r="I23" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="250" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="250">
+      <c r="J23" s="91" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="65">
         <v>10</v>
       </c>
-      <c r="L22" s="250">
+      <c r="L23" s="65">
         <v>30</v>
       </c>
-      <c r="M22" s="229">
+      <c r="M23" s="96">
         <v>1</v>
       </c>
-      <c r="N22" s="229">
+      <c r="N23" s="69">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O22" s="229">
+      <c r="O23" s="69">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P22" s="251" t="s">
+      <c r="P23" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="252">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="R22" s="253">
+      <c r="Q23" s="70">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="R23" s="121">
         <f t="shared" si="2"/>
-        <v>0.59</v>
-      </c>
-      <c r="S22" s="253">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="T22" s="253">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="S23" s="121">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="T23" s="121">
         <f t="shared" si="3"/>
-        <v>1.77</v>
-      </c>
-      <c r="U22" s="254"/>
-      <c r="V22" s="255"/>
-      <c r="W22" s="11"/>
-    </row>
-    <row r="23" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A23" s="6">
-        <v>21</v>
-      </c>
-      <c r="B23" s="185" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="89" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="89" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="89" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H23" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="I23" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="K23" s="62">
-        <v>7</v>
-      </c>
-      <c r="L23" s="62">
-        <v>23</v>
-      </c>
-      <c r="M23" s="63">
-        <v>1</v>
-      </c>
-      <c r="N23" s="63">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O23" s="201">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P23" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q23" s="64">
-        <v>0.23949999999999999</v>
-      </c>
-      <c r="R23" s="65">
-        <f>Q23*K23</f>
-        <v>1.6764999999999999</v>
-      </c>
-      <c r="S23" s="65">
-        <v>0.23949999999999999</v>
-      </c>
-      <c r="T23" s="45">
-        <f t="shared" si="3"/>
-        <v>5.5084999999999997</v>
-      </c>
-      <c r="U23" s="18"/>
-      <c r="V23" s="35"/>
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="U23" s="16"/>
+      <c r="V23" s="17"/>
       <c r="W23" s="11"/>
     </row>
     <row r="24" spans="1:23" ht="26.25" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="184"/>
-      <c r="C24" s="95" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="149" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="82" t="s">
+      <c r="B24" s="149" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="203" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="193" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="194" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="82" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="49" t="s">
+      <c r="F24" s="194" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="195" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="195" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="194" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="194" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="49">
-        <v>7</v>
-      </c>
-      <c r="L24" s="49">
-        <v>45</v>
-      </c>
-      <c r="M24" s="115">
-        <v>2</v>
-      </c>
-      <c r="N24" s="115">
+      <c r="K24" s="194">
+        <v>42</v>
+      </c>
+      <c r="L24" s="194">
+        <v>162</v>
+      </c>
+      <c r="M24" s="196">
+        <v>8</v>
+      </c>
+      <c r="N24" s="196">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O24" s="115">
+        <v>40</v>
+      </c>
+      <c r="O24" s="196">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="P24" s="86" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q24" s="51">
-        <v>0.11169999999999999</v>
-      </c>
-      <c r="R24" s="116">
+        <v>160</v>
+      </c>
+      <c r="P24" s="197" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q24" s="198">
+        <v>3.68</v>
+      </c>
+      <c r="R24" s="199">
         <f t="shared" si="2"/>
-        <v>0.78189999999999993</v>
-      </c>
-      <c r="S24" s="116">
-        <v>0.11169999999999999</v>
-      </c>
-      <c r="T24" s="116">
+        <v>154.56</v>
+      </c>
+      <c r="S24" s="199">
+        <v>3.68</v>
+      </c>
+      <c r="T24" s="199">
         <f t="shared" si="3"/>
-        <v>5.0264999999999995</v>
-      </c>
-      <c r="U24" s="14"/>
-      <c r="V24" s="15"/>
+        <v>596.16000000000008</v>
+      </c>
+      <c r="U24" s="200" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="217">
+        <v>3.68</v>
+      </c>
       <c r="W24" s="11"/>
     </row>
     <row r="25" spans="1:23" ht="26.25" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="186"/>
-      <c r="C25" s="91" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="150" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="92" t="s">
+      <c r="B25" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="110" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="188" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="92" t="s">
-        <v>173</v>
-      </c>
-      <c r="G25" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="H25" s="67" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="68" t="s">
+      <c r="F25" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="69">
+      <c r="J25" s="187" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="187">
         <v>10</v>
       </c>
-      <c r="L25" s="69">
-        <v>25</v>
-      </c>
-      <c r="M25" s="70">
+      <c r="L25" s="187">
+        <v>30</v>
+      </c>
+      <c r="M25" s="123">
         <v>1</v>
       </c>
-      <c r="N25" s="70">
+      <c r="N25" s="123">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="231">
+      <c r="O25" s="123">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="136" t="s">
+      <c r="P25" s="192" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="71">
-        <v>9.9099999999999994E-2</v>
-      </c>
-      <c r="R25" s="126">
+      <c r="Q25" s="57">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="R25" s="124">
         <f t="shared" si="2"/>
-        <v>0.99099999999999988</v>
-      </c>
-      <c r="S25" s="126">
-        <v>9.9099999999999994E-2</v>
-      </c>
-      <c r="T25" s="126">
+        <v>0.59</v>
+      </c>
+      <c r="S25" s="124">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="T25" s="124">
         <f t="shared" si="3"/>
-        <v>2.4775</v>
-      </c>
-      <c r="U25" s="16"/>
-      <c r="V25" s="17"/>
+        <v>1.77</v>
+      </c>
+      <c r="U25" s="30"/>
+      <c r="V25" s="31"/>
       <c r="W25" s="11"/>
     </row>
-    <row r="26" spans="1:23" ht="15.75" thickBot="1">
+    <row r="26" spans="1:23" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="184" t="s">
+      <c r="B26" s="177" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="87" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="H26" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="I26" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="61">
+        <v>7</v>
+      </c>
+      <c r="L26" s="61">
         <v>23</v>
       </c>
-      <c r="C26" s="131" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="197" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26" s="121" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="132" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="H26" s="122" t="s">
-        <v>130</v>
-      </c>
-      <c r="I26" s="133" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" s="121" t="s">
-        <v>89</v>
-      </c>
-      <c r="K26" s="134">
-        <v>100</v>
-      </c>
-      <c r="L26" s="134">
-        <v>100</v>
-      </c>
-      <c r="M26" s="134">
-        <v>3</v>
-      </c>
-      <c r="N26" s="50">
+      <c r="M26" s="62">
+        <v>1</v>
+      </c>
+      <c r="N26" s="62">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="O26" s="232">
+        <v>5</v>
+      </c>
+      <c r="O26" s="43">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="P26" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="123">
-        <v>1E-3</v>
-      </c>
-      <c r="R26" s="52">
-        <f t="shared" si="2"/>
-        <v>0.1</v>
-      </c>
-      <c r="S26" s="52">
-        <v>1E-3</v>
-      </c>
-      <c r="T26" s="52">
+      <c r="Q26" s="63">
+        <v>0.23949999999999999</v>
+      </c>
+      <c r="R26" s="64">
+        <f>Q26*K26</f>
+        <v>1.6764999999999999</v>
+      </c>
+      <c r="S26" s="64">
+        <v>0.23949999999999999</v>
+      </c>
+      <c r="T26" s="45">
         <f t="shared" si="3"/>
-        <v>0.1</v>
-      </c>
-      <c r="U26" s="124"/>
-      <c r="V26" s="127"/>
+        <v>5.5084999999999997</v>
+      </c>
+      <c r="U26" s="18"/>
+      <c r="V26" s="35"/>
       <c r="W26" s="11"/>
     </row>
-    <row r="27" spans="1:23" ht="15.75" thickBot="1">
+    <row r="27" spans="1:23" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="95" t="s">
-        <v>175</v>
-      </c>
-      <c r="D27" s="168" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="82" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="82" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="I27" s="109" t="s">
+      <c r="B27" s="176"/>
+      <c r="C27" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="135" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="48">
+        <v>7</v>
+      </c>
+      <c r="L27" s="48">
+        <v>45</v>
+      </c>
+      <c r="M27" s="114">
+        <v>2</v>
+      </c>
+      <c r="N27" s="114">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="O27" s="114">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="J27" s="82" t="s">
-        <v>181</v>
-      </c>
-      <c r="K27" s="110">
-        <v>100</v>
-      </c>
-      <c r="L27" s="110">
-        <v>100</v>
-      </c>
-      <c r="M27" s="110">
-        <v>1</v>
-      </c>
-      <c r="N27" s="115">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O27" s="115">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P27" s="118" t="s">
+      <c r="P27" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="51">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="R27" s="116">
+      <c r="Q27" s="50">
+        <v>0.11169999999999999</v>
+      </c>
+      <c r="R27" s="115">
         <f t="shared" si="2"/>
-        <v>0.26</v>
-      </c>
-      <c r="S27" s="116">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="T27" s="116">
+        <v>0.78189999999999993</v>
+      </c>
+      <c r="S27" s="115">
+        <v>0.11169999999999999</v>
+      </c>
+      <c r="T27" s="115">
         <f t="shared" si="3"/>
-        <v>0.26</v>
+        <v>5.0264999999999995</v>
       </c>
       <c r="U27" s="14"/>
       <c r="V27" s="15"/>
       <c r="W27" s="11"/>
     </row>
-    <row r="28" spans="1:23" ht="15.75" thickBot="1">
+    <row r="28" spans="1:23" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="184"/>
-      <c r="C28" s="95" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="168" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="82" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="82" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="I28" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="82" t="s">
-        <v>182</v>
-      </c>
-      <c r="K28" s="110">
-        <v>100</v>
-      </c>
-      <c r="L28" s="110">
-        <v>100</v>
-      </c>
-      <c r="M28" s="110">
+      <c r="B28" s="178"/>
+      <c r="C28" s="90" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="136" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="91" t="s">
+        <v>173</v>
+      </c>
+      <c r="G28" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="66" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="68">
+        <v>10</v>
+      </c>
+      <c r="L28" s="68">
+        <v>25</v>
+      </c>
+      <c r="M28" s="69">
         <v>1</v>
       </c>
-      <c r="N28" s="115">
+      <c r="N28" s="69">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="115">
+      <c r="O28" s="69">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="118" t="s">
+      <c r="P28" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="51">
-        <v>1.5E-3</v>
-      </c>
-      <c r="R28" s="116">
+      <c r="Q28" s="70">
+        <v>9.9099999999999994E-2</v>
+      </c>
+      <c r="R28" s="121">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="S28" s="116">
-        <v>1.5E-3</v>
-      </c>
-      <c r="T28" s="116">
+        <v>0.99099999999999988</v>
+      </c>
+      <c r="S28" s="121">
+        <v>9.9099999999999994E-2</v>
+      </c>
+      <c r="T28" s="121">
         <f t="shared" si="3"/>
-        <v>0.15</v>
-      </c>
-      <c r="U28" s="14"/>
-      <c r="V28" s="15"/>
+        <v>2.4775</v>
+      </c>
+      <c r="U28" s="16"/>
+      <c r="V28" s="17"/>
       <c r="W28" s="11"/>
     </row>
     <row r="29" spans="1:23" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="184"/>
-      <c r="C29" s="95" t="s">
-        <v>248</v>
-      </c>
-      <c r="D29" s="168" t="s">
-        <v>249</v>
-      </c>
-      <c r="E29" s="82" t="s">
+      <c r="B29" s="177" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="87" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="204" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="82" t="s">
-        <v>250</v>
-      </c>
-      <c r="G29" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="H29" s="47" t="s">
-        <v>251</v>
-      </c>
-      <c r="I29" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="82" t="s">
-        <v>252</v>
-      </c>
-      <c r="K29" s="110">
+      <c r="F29" s="92" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="144" t="s">
+        <v>129</v>
+      </c>
+      <c r="J29" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="205">
         <v>100</v>
       </c>
-      <c r="L29" s="110">
+      <c r="L29" s="205">
         <v>100</v>
       </c>
-      <c r="M29" s="110">
-        <v>4</v>
-      </c>
-      <c r="N29" s="115">
+      <c r="M29" s="205">
+        <v>3</v>
+      </c>
+      <c r="N29" s="43">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="O29" s="115">
+        <v>15</v>
+      </c>
+      <c r="O29" s="43">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="P29" s="118" t="s">
+        <v>60</v>
+      </c>
+      <c r="P29" s="206" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="51">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="R29" s="116">
+      <c r="Q29" s="44">
+        <v>1E-3</v>
+      </c>
+      <c r="R29" s="45">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="S29" s="116">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="T29" s="116">
+        <v>0.1</v>
+      </c>
+      <c r="S29" s="45">
+        <v>1E-3</v>
+      </c>
+      <c r="T29" s="45">
         <f t="shared" si="3"/>
-        <v>0.13</v>
-      </c>
-      <c r="U29" s="14"/>
-      <c r="V29" s="15"/>
+        <v>0.1</v>
+      </c>
+      <c r="U29" s="12"/>
+      <c r="V29" s="13"/>
       <c r="W29" s="11"/>
     </row>
     <row r="30" spans="1:23" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="184"/>
-      <c r="C30" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="198" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="87" t="s">
+      <c r="B30" s="176"/>
+      <c r="C30" s="94" t="s">
+        <v>274</v>
+      </c>
+      <c r="D30" s="190" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="55" t="s">
+      <c r="F30" s="81" t="s">
+        <v>275</v>
+      </c>
+      <c r="G30" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H30" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="I30" s="151" t="s">
+      <c r="H30" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="I30" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="87" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="137">
+      <c r="J30" s="81" t="s">
+        <v>273</v>
+      </c>
+      <c r="K30" s="109">
         <v>100</v>
       </c>
-      <c r="L30" s="137">
+      <c r="L30" s="109">
         <v>100</v>
       </c>
-      <c r="M30" s="137">
+      <c r="M30" s="109">
         <v>1</v>
       </c>
-      <c r="N30" s="129">
+      <c r="N30" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O30" s="232">
+      <c r="O30" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="138" t="s">
+      <c r="P30" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="58">
-        <v>1.4E-3</v>
-      </c>
-      <c r="R30" s="130">
+      <c r="Q30" s="50">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="R30" s="115">
         <f t="shared" si="2"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="S30" s="130">
-        <v>1.4E-3</v>
-      </c>
-      <c r="T30" s="130">
+        <v>0.16</v>
+      </c>
+      <c r="S30" s="115">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="T30" s="115">
         <f t="shared" si="3"/>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="U30" s="30"/>
-      <c r="V30" s="31"/>
+        <v>0.16</v>
+      </c>
+      <c r="U30" s="14"/>
+      <c r="V30" s="15"/>
       <c r="W30" s="11"/>
     </row>
     <row r="31" spans="1:23" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="185" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="E31" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="I31" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="J31" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="K31" s="42">
-        <v>11</v>
-      </c>
-      <c r="L31" s="42">
-        <v>42</v>
-      </c>
-      <c r="M31" s="79">
-        <v>2</v>
-      </c>
-      <c r="N31" s="43">
+      <c r="B31" s="176"/>
+      <c r="C31" s="94" t="s">
+        <v>176</v>
+      </c>
+      <c r="D31" s="143" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="I31" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="K31" s="109">
+        <v>100</v>
+      </c>
+      <c r="L31" s="109">
+        <v>100</v>
+      </c>
+      <c r="M31" s="109">
+        <v>1</v>
+      </c>
+      <c r="N31" s="114">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O31" s="201">
+        <v>5</v>
+      </c>
+      <c r="O31" s="114">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="P31" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="44">
-        <v>0.64739999999999998</v>
-      </c>
-      <c r="R31" s="45">
+      <c r="Q31" s="50">
+        <v>1.5E-3</v>
+      </c>
+      <c r="R31" s="115">
         <f t="shared" si="2"/>
-        <v>7.1213999999999995</v>
-      </c>
-      <c r="S31" s="45">
-        <v>0.4148</v>
-      </c>
-      <c r="T31" s="45">
+        <v>0.15</v>
+      </c>
+      <c r="S31" s="115">
+        <v>1.5E-3</v>
+      </c>
+      <c r="T31" s="115">
         <f t="shared" si="3"/>
-        <v>17.421600000000002</v>
-      </c>
-      <c r="U31" s="12"/>
-      <c r="V31" s="13"/>
+        <v>0.15</v>
+      </c>
+      <c r="U31" s="14"/>
+      <c r="V31" s="15"/>
       <c r="W31" s="11"/>
     </row>
-    <row r="32" spans="1:23" ht="26.25" thickBot="1">
+    <row r="32" spans="1:23" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="184"/>
-      <c r="C32" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="149" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="H32" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" s="48">
-        <v>6</v>
-      </c>
-      <c r="L32" s="48">
-        <v>21</v>
-      </c>
-      <c r="M32" s="84">
-        <v>1</v>
-      </c>
-      <c r="N32" s="115">
+      <c r="B32" s="176"/>
+      <c r="C32" s="94" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="143" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="G32" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="I32" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="K32" s="109">
+        <v>100</v>
+      </c>
+      <c r="L32" s="109">
+        <v>100</v>
+      </c>
+      <c r="M32" s="109">
+        <v>4</v>
+      </c>
+      <c r="N32" s="114">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O32" s="115">
+        <v>20</v>
+      </c>
+      <c r="O32" s="114">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P32" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="P32" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="51">
-        <v>0.39889999999999998</v>
-      </c>
-      <c r="R32" s="116">
+      <c r="Q32" s="50">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="R32" s="115">
         <f t="shared" si="2"/>
-        <v>2.3933999999999997</v>
-      </c>
-      <c r="S32" s="116">
-        <v>0.33829999999999999</v>
-      </c>
-      <c r="T32" s="116">
+        <v>0.13</v>
+      </c>
+      <c r="S32" s="115">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="T32" s="115">
         <f t="shared" si="3"/>
-        <v>7.1042999999999994</v>
+        <v>0.13</v>
       </c>
       <c r="U32" s="14"/>
       <c r="V32" s="15"/>
@@ -4803,204 +4619,202 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="184"/>
-      <c r="C33" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="149" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="82" t="s">
-        <v>98</v>
-      </c>
-      <c r="F33" s="82" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="J33" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="53">
-        <v>6</v>
-      </c>
-      <c r="L33" s="53">
-        <v>21</v>
-      </c>
-      <c r="M33" s="84">
+      <c r="B33" s="178"/>
+      <c r="C33" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="207" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="I33" s="151" t="s">
+        <v>40</v>
+      </c>
+      <c r="J33" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="208">
+        <v>100</v>
+      </c>
+      <c r="L33" s="208">
+        <v>100</v>
+      </c>
+      <c r="M33" s="208">
         <v>1</v>
       </c>
-      <c r="N33" s="115">
+      <c r="N33" s="69">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O33" s="115">
+      <c r="O33" s="69">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P33" s="96" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q33" s="72">
-        <v>8</v>
-      </c>
-      <c r="R33" s="116">
+      <c r="P33" s="209" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q33" s="70">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R33" s="121">
         <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="S33" s="116">
-        <v>8</v>
-      </c>
-      <c r="T33" s="116">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S33" s="121">
+        <v>1.4E-3</v>
+      </c>
+      <c r="T33" s="121">
         <f t="shared" si="3"/>
-        <v>168</v>
-      </c>
-      <c r="U33" s="34"/>
-      <c r="V33" s="32"/>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="U33" s="16"/>
+      <c r="V33" s="17"/>
       <c r="W33" s="11"/>
     </row>
     <row r="34" spans="1:23" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="184"/>
-      <c r="C34" s="101" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="152" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="102" t="s">
-        <v>137</v>
-      </c>
-      <c r="F34" s="102" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="103" t="s">
+      <c r="B34" s="177" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="103" t="s">
+      <c r="H34" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J34" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34" s="102" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="103">
+      <c r="K34" s="42">
         <v>11</v>
       </c>
-      <c r="L34" s="103">
-        <v>41</v>
-      </c>
-      <c r="M34" s="104">
+      <c r="L34" s="42">
+        <v>42</v>
+      </c>
+      <c r="M34" s="78">
         <v>2</v>
       </c>
-      <c r="N34" s="104">
+      <c r="N34" s="43">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="115">
+      <c r="O34" s="43">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="105" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q34" s="119">
-        <v>10.18</v>
-      </c>
-      <c r="R34" s="120">
+      <c r="P34" s="93" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q34" s="44">
+        <v>0.64739999999999998</v>
+      </c>
+      <c r="R34" s="45">
         <f t="shared" si="2"/>
-        <v>111.97999999999999</v>
-      </c>
-      <c r="S34" s="120">
-        <v>10.18</v>
-      </c>
-      <c r="T34" s="116">
+        <v>7.1213999999999995</v>
+      </c>
+      <c r="S34" s="45">
+        <v>0.4148</v>
+      </c>
+      <c r="T34" s="45">
         <f t="shared" si="3"/>
-        <v>417.38</v>
-      </c>
-      <c r="U34" s="106" t="s">
-        <v>260</v>
-      </c>
-      <c r="V34" s="107">
-        <v>10.18</v>
-      </c>
+        <v>17.421600000000002</v>
+      </c>
+      <c r="U34" s="12"/>
+      <c r="V34" s="13"/>
       <c r="W34" s="11"/>
     </row>
-    <row r="35" spans="1:23" ht="15.75" thickBot="1">
+    <row r="35" spans="1:23" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="184"/>
-      <c r="C35" s="95" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="149" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" s="82" t="s">
-        <v>218</v>
-      </c>
-      <c r="F35" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="G35" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="H35" s="53" t="s">
-        <v>220</v>
-      </c>
-      <c r="I35" s="48" t="s">
+      <c r="B35" s="176"/>
+      <c r="C35" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="135" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="I35" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="49" t="s">
+      <c r="J35" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="53">
+      <c r="K35" s="47">
         <v>6</v>
       </c>
-      <c r="L35" s="53">
+      <c r="L35" s="47">
         <v>21</v>
       </c>
-      <c r="M35" s="84">
+      <c r="M35" s="83">
         <v>1</v>
       </c>
-      <c r="N35" s="115">
+      <c r="N35" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="115">
+      <c r="O35" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="108" t="s">
+      <c r="P35" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="51">
-        <v>2.3479000000000001</v>
-      </c>
-      <c r="R35" s="116">
+      <c r="Q35" s="50">
+        <v>0.39889999999999998</v>
+      </c>
+      <c r="R35" s="115">
         <f t="shared" si="2"/>
-        <v>14.087400000000001</v>
-      </c>
-      <c r="S35" s="116">
-        <v>2.3479000000000001</v>
-      </c>
-      <c r="T35" s="116">
+        <v>2.3933999999999997</v>
+      </c>
+      <c r="S35" s="115">
+        <v>0.33829999999999999</v>
+      </c>
+      <c r="T35" s="115">
         <f t="shared" si="3"/>
-        <v>49.305900000000001</v>
-      </c>
-      <c r="U35" s="22"/>
+        <v>7.1042999999999994</v>
+      </c>
+      <c r="U35" s="14"/>
       <c r="V35" s="15"/>
       <c r="W35" s="11"/>
     </row>
@@ -5008,269 +4822,271 @@
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="184"/>
-      <c r="C36" s="95" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="149" t="s">
-        <v>187</v>
-      </c>
-      <c r="E36" s="82" t="s">
-        <v>188</v>
-      </c>
-      <c r="F36" s="82" t="s">
-        <v>189</v>
-      </c>
-      <c r="G36" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="H36" s="53" t="s">
-        <v>222</v>
+      <c r="B36" s="176"/>
+      <c r="C36" s="94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="81" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="52" t="s">
+        <v>22</v>
       </c>
       <c r="I36" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="49" t="s">
+      <c r="J36" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="53">
+      <c r="K36" s="52">
         <v>6</v>
       </c>
-      <c r="L36" s="53">
+      <c r="L36" s="52">
         <v>21</v>
       </c>
-      <c r="M36" s="84">
+      <c r="M36" s="83">
         <v>1</v>
       </c>
-      <c r="N36" s="115">
+      <c r="N36" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="115">
+      <c r="O36" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q36" s="51">
-        <v>0.74660000000000004</v>
-      </c>
-      <c r="R36" s="116">
+      <c r="P36" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q36" s="71">
+        <v>8</v>
+      </c>
+      <c r="R36" s="115">
         <f t="shared" si="2"/>
-        <v>4.4796000000000005</v>
-      </c>
-      <c r="S36" s="116">
-        <v>0.60960000000000003</v>
-      </c>
-      <c r="T36" s="116">
+        <v>48</v>
+      </c>
+      <c r="S36" s="115">
+        <v>8</v>
+      </c>
+      <c r="T36" s="115">
         <f t="shared" si="3"/>
-        <v>12.801600000000001</v>
-      </c>
-      <c r="U36" s="22"/>
-      <c r="V36" s="15"/>
+        <v>168</v>
+      </c>
+      <c r="U36" s="34"/>
+      <c r="V36" s="32"/>
       <c r="W36" s="11"/>
     </row>
-    <row r="37" spans="1:23" ht="26.25" thickBot="1">
+    <row r="37" spans="1:23" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="186"/>
-      <c r="C37" s="91" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="150" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" s="92" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="H37" s="69" t="s">
-        <v>140</v>
-      </c>
-      <c r="I37" s="69" t="s">
+      <c r="B37" s="176"/>
+      <c r="C37" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="137" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="101" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="102" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="69" t="s">
+      <c r="J37" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="66">
+      <c r="K37" s="102">
+        <v>11</v>
+      </c>
+      <c r="L37" s="102">
+        <v>41</v>
+      </c>
+      <c r="M37" s="103">
+        <v>2</v>
+      </c>
+      <c r="N37" s="103">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L37" s="66">
-        <v>30</v>
-      </c>
-      <c r="M37" s="97">
-        <v>1</v>
-      </c>
-      <c r="N37" s="70">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O37" s="231">
+      <c r="O37" s="114">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P37" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q37" s="71">
-        <v>5.3499999999999999E-2</v>
-      </c>
-      <c r="R37" s="126">
+        <v>40</v>
+      </c>
+      <c r="P37" s="104" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q37" s="118">
+        <v>10.18</v>
+      </c>
+      <c r="R37" s="119">
         <f t="shared" si="2"/>
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="S37" s="126">
-        <v>5.3499999999999999E-2</v>
-      </c>
-      <c r="T37" s="126">
+        <v>111.97999999999999</v>
+      </c>
+      <c r="S37" s="119">
+        <v>10.18</v>
+      </c>
+      <c r="T37" s="115">
         <f t="shared" si="3"/>
-        <v>1.605</v>
-      </c>
-      <c r="U37" s="23"/>
-      <c r="V37" s="17"/>
+        <v>417.38</v>
+      </c>
+      <c r="U37" s="105" t="s">
+        <v>255</v>
+      </c>
+      <c r="V37" s="106">
+        <v>10.18</v>
+      </c>
       <c r="W37" s="11"/>
     </row>
     <row r="38" spans="1:23" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="185" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" s="88" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="89" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="93" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="H38" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="I38" s="42" t="s">
+      <c r="B38" s="176"/>
+      <c r="C38" s="94" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="135" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="81" t="s">
+        <v>214</v>
+      </c>
+      <c r="F38" s="81" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>215</v>
+      </c>
+      <c r="H38" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="I38" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="42" t="s">
+      <c r="J38" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="73">
-        <v>50</v>
-      </c>
-      <c r="L38" s="73">
-        <v>50</v>
-      </c>
-      <c r="M38" s="74">
+      <c r="K38" s="52">
+        <v>6</v>
+      </c>
+      <c r="L38" s="52">
+        <v>21</v>
+      </c>
+      <c r="M38" s="83">
         <v>1</v>
       </c>
-      <c r="N38" s="43">
+      <c r="N38" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O38" s="201">
+      <c r="O38" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P38" s="99" t="s">
+      <c r="P38" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="Q38" s="44">
-        <v>1.4E-2</v>
-      </c>
-      <c r="R38" s="45">
+      <c r="Q38" s="50">
+        <v>2.3479000000000001</v>
+      </c>
+      <c r="R38" s="115">
         <f t="shared" si="2"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="S38" s="45">
-        <v>1.4E-2</v>
-      </c>
-      <c r="T38" s="45">
+        <v>14.087400000000001</v>
+      </c>
+      <c r="S38" s="115">
+        <v>2.3479000000000001</v>
+      </c>
+      <c r="T38" s="115">
         <f t="shared" si="3"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="U38" s="24"/>
-      <c r="V38" s="13"/>
+        <v>49.305900000000001</v>
+      </c>
+      <c r="U38" s="22"/>
+      <c r="V38" s="15"/>
       <c r="W38" s="11"/>
     </row>
     <row r="39" spans="1:23" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="184"/>
-      <c r="C39" s="95" t="s">
-        <v>156</v>
-      </c>
-      <c r="D39" s="149" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="82" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="H39" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="I39" s="49" t="s">
+      <c r="B39" s="176"/>
+      <c r="C39" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="135" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="81" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="H39" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="I39" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="49" t="s">
+      <c r="J39" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="49">
+      <c r="K39" s="52">
         <v>6</v>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="52">
         <v>21</v>
       </c>
-      <c r="M39" s="75">
+      <c r="M39" s="83">
         <v>1</v>
       </c>
-      <c r="N39" s="115">
+      <c r="N39" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O39" s="115">
+      <c r="O39" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="108" t="s">
+      <c r="P39" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="Q39" s="72">
-        <v>0.25409999999999999</v>
-      </c>
-      <c r="R39" s="116">
+      <c r="Q39" s="50">
+        <v>0.74660000000000004</v>
+      </c>
+      <c r="R39" s="115">
         <f t="shared" si="2"/>
-        <v>1.5246</v>
-      </c>
-      <c r="S39" s="116">
-        <v>0.21260000000000001</v>
-      </c>
-      <c r="T39" s="116">
+        <v>4.4796000000000005</v>
+      </c>
+      <c r="S39" s="115">
+        <v>0.60960000000000003</v>
+      </c>
+      <c r="T39" s="115">
         <f t="shared" si="3"/>
-        <v>4.4645999999999999</v>
-      </c>
-      <c r="U39" s="28"/>
+        <v>12.801600000000001</v>
+      </c>
+      <c r="U39" s="22"/>
       <c r="V39" s="15"/>
       <c r="W39" s="11"/>
     </row>
@@ -5278,529 +5094,761 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="184"/>
-      <c r="C40" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="149" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="82" t="s">
+      <c r="B40" s="176"/>
+      <c r="C40" s="94" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" s="190" t="s">
+        <v>278</v>
+      </c>
+      <c r="E40" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="G40" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="H40" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="I40" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="J40" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="K40" s="49">
-        <v>50</v>
-      </c>
-      <c r="L40" s="49">
-        <v>50</v>
-      </c>
-      <c r="M40" s="75">
+      <c r="F40" s="81" t="s">
+        <v>279</v>
+      </c>
+      <c r="G40" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="H40" s="52"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="83">
         <v>1</v>
       </c>
-      <c r="N40" s="115">
+      <c r="N40" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="115">
+      <c r="O40" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q40" s="51">
-        <v>1.26E-2</v>
-      </c>
-      <c r="R40" s="116">
-        <f t="shared" si="2"/>
-        <v>0.63</v>
-      </c>
-      <c r="S40" s="116">
-        <v>1.26E-2</v>
-      </c>
-      <c r="T40" s="116">
-        <f t="shared" si="3"/>
-        <v>0.63</v>
-      </c>
-      <c r="U40" s="29"/>
+      <c r="P40" s="107"/>
+      <c r="Q40" s="50"/>
+      <c r="R40" s="115"/>
+      <c r="S40" s="115"/>
+      <c r="T40" s="115"/>
+      <c r="U40" s="22" t="s">
+        <v>286</v>
+      </c>
       <c r="V40" s="15"/>
       <c r="W40" s="11"/>
     </row>
-    <row r="41" spans="1:23" ht="115.5" thickBot="1">
+    <row r="41" spans="1:23" ht="26.25" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="186"/>
-      <c r="C41" s="139" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="140" t="s">
-        <v>253</v>
-      </c>
-      <c r="E41" s="141" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="141" t="s">
-        <v>36</v>
-      </c>
-      <c r="G41" s="142" t="s">
-        <v>145</v>
-      </c>
-      <c r="H41" s="142" t="s">
-        <v>145</v>
-      </c>
-      <c r="I41" s="143" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" s="143" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41" s="143" t="s">
-        <v>145</v>
-      </c>
-      <c r="L41" s="143" t="s">
+      <c r="B41" s="178"/>
+      <c r="C41" s="90" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="136" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="144">
-        <v>53</v>
-      </c>
-      <c r="N41" s="145">
+      <c r="K41" s="65">
+        <v>10</v>
+      </c>
+      <c r="L41" s="65">
+        <v>30</v>
+      </c>
+      <c r="M41" s="96">
+        <v>1</v>
+      </c>
+      <c r="N41" s="69">
         <f t="shared" si="0"/>
-        <v>265</v>
-      </c>
-      <c r="O41" s="231">
+        <v>5</v>
+      </c>
+      <c r="O41" s="69">
         <f t="shared" si="1"/>
-        <v>1060</v>
-      </c>
-      <c r="P41" s="142" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q41" s="143" t="s">
-        <v>40</v>
-      </c>
-      <c r="R41" s="143" t="s">
-        <v>145</v>
-      </c>
-      <c r="S41" s="143" t="s">
-        <v>145</v>
-      </c>
-      <c r="T41" s="143" t="s">
-        <v>145</v>
-      </c>
-      <c r="U41" s="146" t="s">
-        <v>150</v>
-      </c>
-      <c r="V41" s="147"/>
+        <v>20</v>
+      </c>
+      <c r="P41" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q41" s="70">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="R41" s="121">
+        <f t="shared" si="2"/>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="S41" s="121">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="T41" s="121">
+        <f t="shared" si="3"/>
+        <v>1.605</v>
+      </c>
+      <c r="U41" s="23"/>
+      <c r="V41" s="17"/>
       <c r="W41" s="11"/>
     </row>
     <row r="42" spans="1:23" ht="15.75" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="195" t="s">
-        <v>152</v>
-      </c>
-      <c r="C42" s="170" t="s">
-        <v>254</v>
-      </c>
-      <c r="D42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="G42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="H42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="I42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="K42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="L42" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="M42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="N42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="O42" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="P42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="R42" s="153" t="s">
-        <v>40</v>
-      </c>
-      <c r="S42" s="153" t="s">
+      <c r="B42" s="177" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="87" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="I42" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="T42" s="210" t="s">
-        <v>40</v>
-      </c>
-      <c r="U42" s="154" t="s">
-        <v>150</v>
-      </c>
-      <c r="V42" s="155"/>
+      <c r="K42" s="72">
+        <v>50</v>
+      </c>
+      <c r="L42" s="72">
+        <v>50</v>
+      </c>
+      <c r="M42" s="73">
+        <v>1</v>
+      </c>
+      <c r="N42" s="43">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O42" s="43">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P42" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>1.4E-2</v>
+      </c>
+      <c r="R42" s="45">
+        <f t="shared" si="2"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="S42" s="45">
+        <v>1.4E-2</v>
+      </c>
+      <c r="T42" s="45">
+        <f t="shared" si="3"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="U42" s="24"/>
+      <c r="V42" s="13"/>
       <c r="W42" s="11"/>
     </row>
-    <row r="43" spans="1:23" ht="26.25" thickBot="1">
+    <row r="43" spans="1:23" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="204"/>
-      <c r="C43" s="205" t="s">
-        <v>262</v>
-      </c>
-      <c r="D43" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="206" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="206" t="s">
-        <v>261</v>
-      </c>
-      <c r="G43" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="H43" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="I43" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="J43" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="K43" s="206" t="s">
-        <v>145</v>
-      </c>
-      <c r="L43" s="209" t="s">
-        <v>145</v>
-      </c>
-      <c r="M43" s="75">
+      <c r="B43" s="176"/>
+      <c r="C43" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="135" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" s="48" t="s">
+        <v>157</v>
+      </c>
+      <c r="I43" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="48">
+        <v>6</v>
+      </c>
+      <c r="L43" s="48">
+        <v>21</v>
+      </c>
+      <c r="M43" s="74">
         <v>1</v>
       </c>
-      <c r="N43" s="115">
-        <f>M43*5</f>
+      <c r="N43" s="114">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="115">
-        <f>M43*20</f>
-        <v>20</v>
-      </c>
-      <c r="P43" s="213" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q43" s="72">
-        <v>0.2</v>
-      </c>
-      <c r="R43" s="214">
-        <f>Q43*N43</f>
-        <v>1</v>
-      </c>
-      <c r="S43" s="72">
-        <v>0.2</v>
-      </c>
-      <c r="T43" s="52">
-        <f>S43*O43</f>
-        <v>4</v>
-      </c>
-      <c r="U43" s="207"/>
-      <c r="V43" s="208"/>
-      <c r="W43" s="11"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A44" s="19">
-        <v>42</v>
-      </c>
-      <c r="B44" s="196"/>
-      <c r="C44" s="171" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="173" t="s">
-        <v>153</v>
-      </c>
-      <c r="G44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="H44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="I44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="J44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="K44" s="172" t="s">
-        <v>40</v>
-      </c>
-      <c r="L44" s="172" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="156">
-        <v>1</v>
-      </c>
-      <c r="N44" s="156">
-        <f t="shared" ref="N44" si="4">M44*5</f>
-        <v>5</v>
-      </c>
-      <c r="O44" s="231">
+      <c r="O43" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="215" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q44" s="157">
+      <c r="P43" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q43" s="71">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="R43" s="115">
+        <f t="shared" si="2"/>
+        <v>1.5246</v>
+      </c>
+      <c r="S43" s="115">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="T43" s="115">
+        <f t="shared" si="3"/>
+        <v>4.4645999999999999</v>
+      </c>
+      <c r="U43" s="28"/>
+      <c r="V43" s="15"/>
+      <c r="W43" s="11"/>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A44" s="6">
+        <v>42</v>
+      </c>
+      <c r="B44" s="176"/>
+      <c r="C44" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="99" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="H44" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="J44" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="48">
+        <v>50</v>
+      </c>
+      <c r="L44" s="48">
+        <v>50</v>
+      </c>
+      <c r="M44" s="74">
+        <v>1</v>
+      </c>
+      <c r="N44" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O44" s="114">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P44" s="95" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q44" s="50">
+        <v>1.26E-2</v>
+      </c>
+      <c r="R44" s="115">
+        <f t="shared" si="2"/>
+        <v>0.63</v>
+      </c>
+      <c r="S44" s="115">
+        <v>1.26E-2</v>
+      </c>
+      <c r="T44" s="115">
+        <f t="shared" si="3"/>
+        <v>0.63</v>
+      </c>
+      <c r="U44" s="29"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="11"/>
+    </row>
+    <row r="45" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A45" s="6">
+        <v>43</v>
+      </c>
+      <c r="B45" s="176"/>
+      <c r="C45" s="94" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="190" t="s">
+        <v>281</v>
+      </c>
+      <c r="E45" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="81" t="s">
+        <v>282</v>
+      </c>
+      <c r="G45" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="H45" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="J45" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="48">
+        <v>5</v>
+      </c>
+      <c r="L45" s="48">
+        <v>25</v>
+      </c>
+      <c r="M45" s="74">
+        <v>1</v>
+      </c>
+      <c r="N45" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O45" s="114">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P45" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q45" s="50">
+        <v>0.1002</v>
+      </c>
+      <c r="R45" s="115">
+        <f t="shared" si="2"/>
+        <v>0.501</v>
+      </c>
+      <c r="S45" s="115">
+        <v>0.1002</v>
+      </c>
+      <c r="T45" s="115">
+        <f t="shared" si="3"/>
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="U45" s="29"/>
+      <c r="V45" s="15"/>
+      <c r="W45" s="11"/>
+    </row>
+    <row r="46" spans="1:23" ht="115.5" thickBot="1">
+      <c r="A46" s="6">
+        <v>44</v>
+      </c>
+      <c r="B46" s="178"/>
+      <c r="C46" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="127" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="129" t="s">
+        <v>145</v>
+      </c>
+      <c r="H46" s="129" t="s">
+        <v>145</v>
+      </c>
+      <c r="I46" s="130" t="s">
+        <v>40</v>
+      </c>
+      <c r="J46" s="130" t="s">
+        <v>40</v>
+      </c>
+      <c r="K46" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="L46" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="131">
+        <v>53</v>
+      </c>
+      <c r="N46" s="132">
+        <f t="shared" si="0"/>
+        <v>265</v>
+      </c>
+      <c r="O46" s="69">
+        <f t="shared" si="1"/>
+        <v>1060</v>
+      </c>
+      <c r="P46" s="129" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q46" s="130" t="s">
+        <v>40</v>
+      </c>
+      <c r="R46" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="S46" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="T46" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="U46" s="133" t="s">
+        <v>150</v>
+      </c>
+      <c r="V46" s="134"/>
+      <c r="W46" s="11"/>
+    </row>
+    <row r="47" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A47" s="6">
+        <v>45</v>
+      </c>
+      <c r="B47" s="185" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="211" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" s="212" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="212" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="212" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="H47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="I47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="J47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="K47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="L47" s="212" t="s">
+        <v>145</v>
+      </c>
+      <c r="M47" s="210">
+        <v>1</v>
+      </c>
+      <c r="N47" s="49">
+        <f>M47*5</f>
+        <v>5</v>
+      </c>
+      <c r="O47" s="49">
+        <f>M47*20</f>
+        <v>20</v>
+      </c>
+      <c r="P47" s="213" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q47" s="214">
+        <v>0.2</v>
+      </c>
+      <c r="R47" s="215">
+        <f>Q47*N47</f>
+        <v>1</v>
+      </c>
+      <c r="S47" s="214">
+        <v>0.2</v>
+      </c>
+      <c r="T47" s="51">
+        <f>S47*O47</f>
+        <v>4</v>
+      </c>
+      <c r="U47" s="216"/>
+      <c r="V47" s="218"/>
+      <c r="W47" s="11"/>
+    </row>
+    <row r="48" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A48" s="19">
+        <v>46</v>
+      </c>
+      <c r="B48" s="186"/>
+      <c r="C48" s="145" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="147" t="s">
+        <v>153</v>
+      </c>
+      <c r="G48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="J48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="L48" s="146" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="138">
+        <v>1</v>
+      </c>
+      <c r="N48" s="138">
+        <f t="shared" ref="N48" si="4">M48*5</f>
+        <v>5</v>
+      </c>
+      <c r="O48" s="69">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P48" s="155" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q48" s="139">
         <v>3.35</v>
       </c>
-      <c r="R44" s="158">
-        <f>Q44*N44</f>
+      <c r="R48" s="140">
+        <f>Q48*N48</f>
         <v>16.75</v>
       </c>
-      <c r="S44" s="158">
+      <c r="S48" s="140">
         <v>3.35</v>
       </c>
-      <c r="T44" s="230">
-        <f>S44*O44</f>
+      <c r="T48" s="121">
+        <f>S48*O48</f>
         <v>67</v>
       </c>
-      <c r="U44" s="146" t="s">
+      <c r="U48" s="133" t="s">
         <v>150</v>
       </c>
-      <c r="V44" s="174"/>
-      <c r="W44" s="11"/>
-    </row>
-    <row r="45" spans="1:23" ht="15.75">
-      <c r="A45" s="1"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="180" t="s">
+      <c r="V48" s="148"/>
+      <c r="W48" s="11"/>
+    </row>
+    <row r="49" spans="1:23" ht="15.75">
+      <c r="A49" s="1"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="N45" s="181"/>
-      <c r="O45" s="181"/>
-      <c r="P45" s="181"/>
-      <c r="Q45" s="21"/>
-      <c r="R45" s="223">
-        <f>SUM(R3:R44)</f>
-        <v>380.02879999999999</v>
-      </c>
-      <c r="S45" s="223"/>
-      <c r="T45" s="114">
-        <f>SUM(T3:T43)</f>
-        <v>1324.4465000000005</v>
-      </c>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="11"/>
-    </row>
-    <row r="46" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A46" s="1"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="182" t="s">
-        <v>38</v>
-      </c>
-      <c r="N46" s="183"/>
-      <c r="O46" s="183"/>
-      <c r="P46" s="183"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="226">
-        <f>R45/5</f>
-        <v>76.005759999999995</v>
-      </c>
-      <c r="S46" s="226"/>
-      <c r="T46" s="38">
-        <f>T45/20</f>
-        <v>66.222325000000026</v>
-      </c>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="11"/>
-    </row>
-    <row r="47" spans="1:23" ht="15.75">
-      <c r="A47" s="1"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="219" t="s">
-        <v>148</v>
-      </c>
-      <c r="O47" s="220"/>
-      <c r="P47" s="221"/>
-      <c r="Q47" s="222"/>
-      <c r="R47" s="224">
-        <v>3</v>
-      </c>
-      <c r="S47" s="224"/>
-      <c r="T47" s="225">
-        <v>3</v>
-      </c>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="11"/>
-    </row>
-    <row r="48" spans="1:23" ht="15.75">
-      <c r="A48" s="1"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="216" t="s">
-        <v>263</v>
-      </c>
-      <c r="O48" s="217"/>
-      <c r="P48" s="218"/>
-      <c r="Q48" s="212"/>
-      <c r="R48" s="211">
-        <v>22.78</v>
-      </c>
-      <c r="S48" s="211"/>
-      <c r="T48" s="227">
-        <v>90.99</v>
-      </c>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="11"/>
-    </row>
-    <row r="49" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A49" s="1"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="N49" s="175" t="s">
-        <v>43</v>
-      </c>
-      <c r="O49" s="200"/>
-      <c r="P49" s="176"/>
-      <c r="Q49" s="36"/>
-      <c r="R49" s="228">
-        <f>SUM(R46:R48)</f>
-        <v>101.78576</v>
-      </c>
-      <c r="S49" s="228"/>
-      <c r="T49" s="37">
-        <f>SUM(T46:T48)</f>
-        <v>160.21232500000002</v>
-      </c>
-      <c r="V49" s="11"/>
+      <c r="N49" s="173"/>
+      <c r="O49" s="173"/>
+      <c r="P49" s="173"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="157">
+        <f>SUM(R3:R47)</f>
+        <v>365.28580000000005</v>
+      </c>
+      <c r="S49" s="157"/>
+      <c r="T49" s="113">
+        <f>SUM(T3:T47)</f>
+        <v>1330.2895000000003</v>
+      </c>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
       <c r="W49" s="11"/>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" ht="16.5" thickBot="1">
       <c r="A50" s="1"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="G50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
-      <c r="V50" s="11"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="174" t="s">
+        <v>38</v>
+      </c>
+      <c r="N50" s="175"/>
+      <c r="O50" s="175"/>
+      <c r="P50" s="175"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="160">
+        <f>R49/5</f>
+        <v>73.05716000000001</v>
+      </c>
+      <c r="S50" s="160"/>
+      <c r="T50" s="38">
+        <f>T49/20</f>
+        <v>66.514475000000019</v>
+      </c>
+      <c r="U50" s="7"/>
+      <c r="V50" s="7"/>
       <c r="W50" s="11"/>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" ht="15.75">
       <c r="A51" s="1"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="G51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="V51" s="11"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="163" t="s">
+        <v>148</v>
+      </c>
+      <c r="O51" s="164"/>
+      <c r="P51" s="165"/>
+      <c r="Q51" s="156"/>
+      <c r="R51" s="158">
+        <v>3</v>
+      </c>
+      <c r="S51" s="158"/>
+      <c r="T51" s="159">
+        <v>3</v>
+      </c>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
       <c r="W51" s="11"/>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" ht="15.75">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="G52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="V52" s="11"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="179" t="s">
+        <v>258</v>
+      </c>
+      <c r="O52" s="180"/>
+      <c r="P52" s="181"/>
+      <c r="Q52" s="154"/>
+      <c r="R52" s="153">
+        <v>22.78</v>
+      </c>
+      <c r="S52" s="153"/>
+      <c r="T52" s="161">
+        <v>90.99</v>
+      </c>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
       <c r="W52" s="11"/>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:23" ht="16.5" thickBot="1">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="G53" s="2"/>
       <c r="I53" s="2"/>
+      <c r="N53" s="166" t="s">
+        <v>43</v>
+      </c>
+      <c r="O53" s="167"/>
+      <c r="P53" s="168"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="162">
+        <f>SUM(R50:R52)</f>
+        <v>98.837160000000011</v>
+      </c>
+      <c r="S53" s="162"/>
+      <c r="T53" s="37">
+        <f>SUM(T50:T52)</f>
+        <v>160.50447500000001</v>
+      </c>
       <c r="V53" s="11"/>
       <c r="W53" s="11"/>
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="1"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
       <c r="V54" s="11"/>
       <c r="W54" s="11"/>
     </row>
-    <row r="55" spans="1:23" ht="15.75" customHeight="1">
+    <row r="55" spans="1:23">
       <c r="A55" s="1"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="I55" s="2"/>
       <c r="V55" s="11"/>
       <c r="W55" s="11"/>
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="1"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="I56" s="2"/>
       <c r="V56" s="11"/>
       <c r="W56" s="11"/>
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="1"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="I57" s="2"/>
       <c r="V57" s="11"/>
       <c r="W57" s="11"/>
     </row>
@@ -5809,7 +5857,7 @@
       <c r="V58" s="11"/>
       <c r="W58" s="11"/>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="V59" s="11"/>
       <c r="W59" s="11"/>
@@ -5820,32 +5868,52 @@
       <c r="W60" s="11"/>
     </row>
     <row r="61" spans="1:23">
-      <c r="H61" s="9"/>
-      <c r="U61" s="10"/>
+      <c r="A61" s="1"/>
+      <c r="V61" s="11"/>
+      <c r="W61" s="11"/>
     </row>
     <row r="62" spans="1:23">
-      <c r="H62" s="9"/>
-      <c r="U62" s="10"/>
+      <c r="A62" s="1"/>
+      <c r="V62" s="11"/>
+      <c r="W62" s="11"/>
+    </row>
+    <row r="63" spans="1:23">
+      <c r="A63" s="1"/>
+      <c r="V63" s="11"/>
+      <c r="W63" s="11"/>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="A64" s="1"/>
+      <c r="V64" s="11"/>
+      <c r="W64" s="11"/>
+    </row>
+    <row r="65" spans="8:21">
+      <c r="H65" s="9"/>
+      <c r="U65" s="10"/>
+    </row>
+    <row r="66" spans="8:21">
+      <c r="H66" s="9"/>
+      <c r="U66" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N53:P53"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="M45:P45"/>
-    <mergeCell ref="M46:P46"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="B31:B37"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B3:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B20:B23"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="U39">
+  <conditionalFormatting sqref="U43">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -5885,7 +5953,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P10:P20">
+  <conditionalFormatting sqref="P10:P23">
     <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
@@ -5899,7 +5967,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R46:T48">
+  <conditionalFormatting sqref="R50:T52">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5913,7 +5981,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M31:N41 M9:M25 N3:O3 N4:N41 O4:O42 O44 M43:O43">
+  <conditionalFormatting sqref="M34:N46 O48 M9:M28 N3:O46 M47:O47">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -5925,7 +5993,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:O3 M4:N41 O4:O42 O44 M43:O43">
+  <conditionalFormatting sqref="M3:O47 O48">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -5937,21 +6005,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T42:T44 R3:T41">
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41:L41">
+  <conditionalFormatting sqref="K46:L46">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -5965,7 +6019,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44:N44">
+  <conditionalFormatting sqref="M48:N48">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -5977,7 +6031,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44:N44">
+  <conditionalFormatting sqref="M48:N48">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5989,7 +6043,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R44:S44">
+  <conditionalFormatting sqref="R48:S48">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -6003,6 +6057,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="T47:T48 R3:T46">
+    <cfRule type="dataBar" priority="48">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="P3" r:id="rId1" xr:uid="{77E7F02B-CC4A-45E7-B730-3717F029D629}"/>
     <hyperlink ref="P4" r:id="rId2" xr:uid="{422ACB32-99A4-4373-9BBC-0F8302D669E9}"/>
@@ -6012,40 +6080,44 @@
     <hyperlink ref="P9" r:id="rId6" xr:uid="{F5D2937B-2705-425B-A920-F69EE337A9AA}"/>
     <hyperlink ref="P10" r:id="rId7" xr:uid="{23650E7E-1F91-465B-A508-B3E81A5A29DB}"/>
     <hyperlink ref="P11" r:id="rId8" xr:uid="{A3FA0792-9C1C-4B11-8EC7-D8950B40778A}"/>
-    <hyperlink ref="P22" r:id="rId9" xr:uid="{9306F7E1-9FA0-45C1-9226-A5EFFE620B9F}"/>
-    <hyperlink ref="P23" r:id="rId10" xr:uid="{6C2F24FA-F4C6-4765-90C1-BBDF944038A7}"/>
-    <hyperlink ref="P24" r:id="rId11" xr:uid="{834B4123-1D60-4B34-B015-5E7BBC8F47AF}"/>
-    <hyperlink ref="P26" r:id="rId12" xr:uid="{1D1A071F-2A3D-4FA1-937C-5E9315A2DAC9}"/>
-    <hyperlink ref="P30" r:id="rId13" xr:uid="{1ECC2B27-3B6B-4070-A52B-CBF10AA116AF}"/>
-    <hyperlink ref="P31" r:id="rId14" xr:uid="{BFDF2136-290A-40AE-829A-CE2FE24D8034}"/>
-    <hyperlink ref="P32" r:id="rId15" xr:uid="{E71028CE-6136-4648-ABFC-ABDBCFA60DB5}"/>
-    <hyperlink ref="P37" r:id="rId16" xr:uid="{8E22EBA9-5C52-408B-A65B-4F115F1CD0F7}"/>
-    <hyperlink ref="P38" r:id="rId17" xr:uid="{0A7E773D-5A3D-486C-84CA-8D29060909A3}"/>
-    <hyperlink ref="P40" r:id="rId18" xr:uid="{79B90123-86F4-4C7F-BE0B-E5B7C590F601}"/>
-    <hyperlink ref="P21" r:id="rId19" display="Aliexpress" xr:uid="{D571A1A4-A3B8-476C-81AA-A10E0576C945}"/>
-    <hyperlink ref="P39" r:id="rId20" xr:uid="{552B4167-57FF-43F1-B0A5-FDF3A29237A4}"/>
+    <hyperlink ref="P25" r:id="rId9" xr:uid="{9306F7E1-9FA0-45C1-9226-A5EFFE620B9F}"/>
+    <hyperlink ref="P26" r:id="rId10" xr:uid="{6C2F24FA-F4C6-4765-90C1-BBDF944038A7}"/>
+    <hyperlink ref="P27" r:id="rId11" xr:uid="{834B4123-1D60-4B34-B015-5E7BBC8F47AF}"/>
+    <hyperlink ref="P29" r:id="rId12" xr:uid="{1D1A071F-2A3D-4FA1-937C-5E9315A2DAC9}"/>
+    <hyperlink ref="P33" r:id="rId13" xr:uid="{1ECC2B27-3B6B-4070-A52B-CBF10AA116AF}"/>
+    <hyperlink ref="P34" r:id="rId14" xr:uid="{BFDF2136-290A-40AE-829A-CE2FE24D8034}"/>
+    <hyperlink ref="P35" r:id="rId15" xr:uid="{E71028CE-6136-4648-ABFC-ABDBCFA60DB5}"/>
+    <hyperlink ref="P41" r:id="rId16" xr:uid="{8E22EBA9-5C52-408B-A65B-4F115F1CD0F7}"/>
+    <hyperlink ref="P42" r:id="rId17" xr:uid="{0A7E773D-5A3D-486C-84CA-8D29060909A3}"/>
+    <hyperlink ref="P44" r:id="rId18" xr:uid="{79B90123-86F4-4C7F-BE0B-E5B7C590F601}"/>
+    <hyperlink ref="P24" r:id="rId19" display="Aliexpress" xr:uid="{D571A1A4-A3B8-476C-81AA-A10E0576C945}"/>
+    <hyperlink ref="P43" r:id="rId20" xr:uid="{552B4167-57FF-43F1-B0A5-FDF3A29237A4}"/>
     <hyperlink ref="P7" r:id="rId21" xr:uid="{6FBFF76E-B622-4D29-A447-7C6E26828E4F}"/>
     <hyperlink ref="P12" r:id="rId22" xr:uid="{1242BC39-221F-4021-953C-3FCDA7A5753C}"/>
     <hyperlink ref="P13" r:id="rId23" xr:uid="{96270715-E02B-41B7-B021-EDD143E9B86E}"/>
-    <hyperlink ref="P16" r:id="rId24" xr:uid="{9B63197A-770E-4944-B769-AA91C9283ECE}"/>
-    <hyperlink ref="P18" r:id="rId25" xr:uid="{9BCD60A7-30C2-4172-B089-A68B6513C693}"/>
-    <hyperlink ref="P25" r:id="rId26" xr:uid="{B47CC2C3-43E3-4A0C-8766-540A57D9BE72}"/>
-    <hyperlink ref="P27" r:id="rId27" xr:uid="{C514E8E3-59DE-4B44-BBBE-97387454193F}"/>
-    <hyperlink ref="P28" r:id="rId28" xr:uid="{CC730C2B-3995-4162-BE6B-30851128B6A0}"/>
-    <hyperlink ref="P35" r:id="rId29" xr:uid="{9108529D-C5AF-49DE-B1AA-F619710C5B08}"/>
-    <hyperlink ref="P36" r:id="rId30" xr:uid="{31C7B57C-378C-4F81-AADD-6D3587D8A480}"/>
-    <hyperlink ref="P33" r:id="rId31" xr:uid="{600C5A90-1D13-491E-82D2-49A3F9B676E0}"/>
-    <hyperlink ref="P14" r:id="rId32" xr:uid="{44409B7B-710F-4F54-A7F0-477BEA0AFE5F}"/>
-    <hyperlink ref="P15" r:id="rId33" xr:uid="{89198C26-8FB1-4B6B-AE7B-FFAE1D3733A8}"/>
-    <hyperlink ref="P17" r:id="rId34" xr:uid="{EC86EEC1-808E-4C17-B0CB-1E879CDB66DD}"/>
-    <hyperlink ref="P19" r:id="rId35" xr:uid="{2322511E-46DE-4717-9728-D93822E1A6A3}"/>
-    <hyperlink ref="P20" r:id="rId36" xr:uid="{2BCC81E2-819B-49BB-9670-D8361D1C41A8}"/>
-    <hyperlink ref="P29" r:id="rId37" xr:uid="{888359C9-25FD-4ECA-BFAD-B6548ECFC19D}"/>
-    <hyperlink ref="P44" r:id="rId38" xr:uid="{AA0FF76A-81A9-4B84-B70A-22617F6C3440}"/>
-    <hyperlink ref="P43" r:id="rId39" xr:uid="{4800B236-FD98-4B4C-8675-7F9F6549B4BC}"/>
+    <hyperlink ref="P18" r:id="rId24" xr:uid="{9B63197A-770E-4944-B769-AA91C9283ECE}"/>
+    <hyperlink ref="P20" r:id="rId25" xr:uid="{9BCD60A7-30C2-4172-B089-A68B6513C693}"/>
+    <hyperlink ref="P28" r:id="rId26" xr:uid="{B47CC2C3-43E3-4A0C-8766-540A57D9BE72}"/>
+    <hyperlink ref="P31" r:id="rId27" xr:uid="{CC730C2B-3995-4162-BE6B-30851128B6A0}"/>
+    <hyperlink ref="P38" r:id="rId28" xr:uid="{9108529D-C5AF-49DE-B1AA-F619710C5B08}"/>
+    <hyperlink ref="P39" r:id="rId29" xr:uid="{31C7B57C-378C-4F81-AADD-6D3587D8A480}"/>
+    <hyperlink ref="P36" r:id="rId30" xr:uid="{600C5A90-1D13-491E-82D2-49A3F9B676E0}"/>
+    <hyperlink ref="P14" r:id="rId31" xr:uid="{44409B7B-710F-4F54-A7F0-477BEA0AFE5F}"/>
+    <hyperlink ref="P15" r:id="rId32" xr:uid="{89198C26-8FB1-4B6B-AE7B-FFAE1D3733A8}"/>
+    <hyperlink ref="P19" r:id="rId33" xr:uid="{EC86EEC1-808E-4C17-B0CB-1E879CDB66DD}"/>
+    <hyperlink ref="P21" r:id="rId34" xr:uid="{2322511E-46DE-4717-9728-D93822E1A6A3}"/>
+    <hyperlink ref="P22" r:id="rId35" xr:uid="{2BCC81E2-819B-49BB-9670-D8361D1C41A8}"/>
+    <hyperlink ref="P32" r:id="rId36" xr:uid="{888359C9-25FD-4ECA-BFAD-B6548ECFC19D}"/>
+    <hyperlink ref="P48" r:id="rId37" xr:uid="{AA0FF76A-81A9-4B84-B70A-22617F6C3440}"/>
+    <hyperlink ref="P47" r:id="rId38" xr:uid="{4800B236-FD98-4B4C-8675-7F9F6549B4BC}"/>
+    <hyperlink ref="P16" r:id="rId39" xr:uid="{E831E81D-C8A7-439A-9225-793F9ACBC435}"/>
+    <hyperlink ref="P17" r:id="rId40" xr:uid="{87F27C46-519D-4D56-B15F-FD9B1CD47221}"/>
+    <hyperlink ref="P23" r:id="rId41" xr:uid="{0161C0DD-E06A-48BB-800D-73ED423A3AD7}"/>
+    <hyperlink ref="P30" r:id="rId42" xr:uid="{00A7F659-3375-4433-B4AD-F92BAE9ADD19}"/>
+    <hyperlink ref="P45" r:id="rId43" xr:uid="{81929E54-8283-45FE-90B8-1D44758D061E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId40"/>
+  <pageSetup orientation="portrait" r:id="rId44"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6060,7 +6132,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U39</xm:sqref>
+          <xm:sqref>U43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">
@@ -6086,7 +6158,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P10:P20</xm:sqref>
+          <xm:sqref>P10:P23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A8943134-F8F0-4DF3-A9A0-86442E65814B}">
@@ -6099,7 +6171,33 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R46:T48</xm:sqref>
+          <xm:sqref>R50:T52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K46:L46</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{19A41A86-C9BB-4A96-AA11-2BBEAF826782}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>R48:S48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}">
@@ -6112,33 +6210,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T42:T44 R3:T41</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K41:L41</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{19A41A86-C9BB-4A96-AA11-2BBEAF826782}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>R44:S44</xm:sqref>
+          <xm:sqref>T47:T48 R3:T46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1D829B-3963-4A7E-AF1D-D21512D4092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="296">
   <si>
     <t>S. No.</t>
   </si>
@@ -291,9 +290,6 @@
   </si>
   <si>
     <t>RES SMD 10K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>R17</t>
   </si>
   <si>
     <t>RC0603FR-0710KL</t>
@@ -500,18 +496,6 @@
     <t>Custom Supplier</t>
   </si>
   <si>
-    <t>10118194-0001LF</t>
-  </si>
-  <si>
-    <t>USB 2.0 1 5 Female Micro-B SMD USB Connectors ROHS</t>
-  </si>
-  <si>
-    <t>C132563</t>
-  </si>
-  <si>
-    <t>Amphenol ICC</t>
-  </si>
-  <si>
     <t>C3, C5, C7, C9, C11, C13, C15, C17, C27, C29, C53, C55, C70, C72, C76, C78, C85, C#1, C#2</t>
   </si>
   <si>
@@ -897,12 +881,54 @@
   </si>
   <si>
     <t xml:space="preserve">Need Quotation from custum supplier </t>
+  </si>
+  <si>
+    <t>R10,'R17</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>IC PSRAM 64MBIT SPI 133MHZ 8SOIC</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>ESP-PSRAM64H</t>
+  </si>
+  <si>
+    <t>Adafruit Industries</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 6POS 2.54MM</t>
+  </si>
+  <si>
+    <t>Würth Elektronik</t>
+  </si>
+  <si>
+    <t>C37208</t>
+  </si>
+  <si>
+    <t>USB 3.1 1 Surface Mount 6 Female -25℃~+85℃ Type-C SMD USB Connectors ROHS</t>
+  </si>
+  <si>
+    <t>U262-061N-4BVC11</t>
+  </si>
+  <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
+    <t>C2764612</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1547,7 +1573,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2023,6 +2049,99 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2062,15 +2181,21 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2080,116 +2205,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2466,8 +2516,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W66"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2496,30 +2546,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="169" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="171"/>
+      <c r="A1" s="200" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="201"/>
+      <c r="M1" s="201"/>
+      <c r="N1" s="201"/>
+      <c r="O1" s="201"/>
+      <c r="P1" s="201"/>
+      <c r="Q1" s="201"/>
+      <c r="R1" s="201"/>
+      <c r="S1" s="201"/>
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="202"/>
     </row>
     <row r="2" spans="1:23" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2556,7 +2606,7 @@
         <v>47</v>
       </c>
       <c r="L2" s="152" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
@@ -2565,7 +2615,7 @@
         <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>11</v>
@@ -2577,10 +2627,10 @@
         <v>46</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="T2" s="152" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
@@ -2593,14 +2643,14 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="207" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="75" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="144" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E3" s="77" t="s">
         <v>49</v>
@@ -2609,10 +2659,10 @@
         <v>50</v>
       </c>
       <c r="G3" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="40" t="s">
         <v>112</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>113</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>39</v>
@@ -2661,7 +2711,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="176"/>
+      <c r="B4" s="208"/>
       <c r="C4" s="80" t="s">
         <v>21</v>
       </c>
@@ -2675,10 +2725,10 @@
         <v>52</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I4" s="47" t="s">
         <v>39</v>
@@ -2696,11 +2746,11 @@
         <v>1</v>
       </c>
       <c r="N4" s="114">
-        <f t="shared" ref="N4:N46" si="0">M4*5</f>
+        <f t="shared" ref="N4:N48" si="0">M4*5</f>
         <v>5</v>
       </c>
       <c r="O4" s="114">
-        <f t="shared" ref="O4:O48" si="1">M4*20</f>
+        <f t="shared" ref="O4:O50" si="1">M4*20</f>
         <v>20</v>
       </c>
       <c r="P4" s="84" t="s">
@@ -2710,14 +2760,14 @@
         <v>2.0299999999999999E-2</v>
       </c>
       <c r="R4" s="115">
-        <f t="shared" ref="R4:R45" si="2">Q4*K4</f>
+        <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
         <v>0.40599999999999997</v>
       </c>
       <c r="S4" s="115">
         <v>2.0299999999999999E-2</v>
       </c>
       <c r="T4" s="115">
-        <f t="shared" ref="T4:T45" si="3">S4*L4</f>
+        <f t="shared" ref="T4:T47" si="3">S4*L4</f>
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
@@ -2727,12 +2777,12 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="176"/>
+      <c r="B5" s="208"/>
       <c r="C5" s="80" t="s">
         <v>53</v>
       </c>
       <c r="D5" s="143" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E5" s="81" t="s">
         <v>49</v>
@@ -2741,10 +2791,10 @@
         <v>54</v>
       </c>
       <c r="G5" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="46" t="s">
         <v>115</v>
-      </c>
-      <c r="H5" s="46" t="s">
-        <v>116</v>
       </c>
       <c r="I5" s="47" t="s">
         <v>39</v>
@@ -2794,7 +2844,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="176"/>
+      <c r="B6" s="208"/>
       <c r="C6" s="80" t="s">
         <v>55</v>
       </c>
@@ -2808,10 +2858,10 @@
         <v>58</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I6" s="47" t="s">
         <v>39</v>
@@ -2861,30 +2911,30 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="176"/>
+      <c r="B7" s="208"/>
       <c r="C7" s="80" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D7" s="108" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E7" s="82" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F7" s="112" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I7" s="47" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J7" s="81" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K7" s="48">
         <v>100</v>
@@ -2928,12 +2978,12 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="176"/>
+      <c r="B8" s="208"/>
       <c r="C8" s="80" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="143" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E8" s="81" t="s">
         <v>49</v>
@@ -2942,10 +2992,10 @@
         <v>18</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I8" s="47" t="s">
         <v>39</v>
@@ -2995,7 +3045,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="176"/>
+      <c r="B9" s="208"/>
       <c r="C9" s="80" t="s">
         <v>59</v>
       </c>
@@ -3009,10 +3059,10 @@
         <v>61</v>
       </c>
       <c r="G9" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="53" t="s">
         <v>119</v>
-      </c>
-      <c r="H9" s="53" t="s">
-        <v>120</v>
       </c>
       <c r="I9" s="47" t="s">
         <v>39</v>
@@ -3062,7 +3112,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="176"/>
+      <c r="B10" s="208"/>
       <c r="C10" s="80" t="s">
         <v>62</v>
       </c>
@@ -3076,10 +3126,10 @@
         <v>64</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I10" s="47" t="s">
         <v>39</v>
@@ -3129,7 +3179,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="176"/>
+      <c r="B11" s="208"/>
       <c r="C11" s="80" t="s">
         <v>65</v>
       </c>
@@ -3143,10 +3193,10 @@
         <v>67</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I11" s="47" t="s">
         <v>39</v>
@@ -3196,30 +3246,30 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="176"/>
+      <c r="B12" s="208"/>
       <c r="C12" s="80" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D12" s="108" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E12" s="82" t="s">
         <v>49</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I12" s="47" t="s">
         <v>39</v>
       </c>
       <c r="J12" s="81" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K12" s="52">
         <v>50</v>
@@ -3263,30 +3313,30 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="176"/>
+      <c r="B13" s="208"/>
       <c r="C13" s="80" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E13" s="81" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F13" s="99" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G13" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="H13" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="H13" s="46" t="s">
-        <v>201</v>
-      </c>
       <c r="I13" s="47" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J13" s="81" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K13" s="52">
         <v>100</v>
@@ -3330,30 +3380,30 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="176"/>
+      <c r="B14" s="208"/>
       <c r="C14" s="80" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D14" s="108" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E14" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="82" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G14" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I14" s="47" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="81" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K14" s="52">
         <v>100</v>
@@ -3397,30 +3447,30 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="176"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="80" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E15" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="82" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G15" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I15" s="47" t="s">
         <v>39</v>
       </c>
       <c r="J15" s="81" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K15" s="52">
         <v>50</v>
@@ -3464,30 +3514,30 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="176"/>
+      <c r="B16" s="208"/>
       <c r="C16" s="80" t="s">
-        <v>259</v>
-      </c>
-      <c r="D16" s="189" t="s">
-        <v>260</v>
+        <v>254</v>
+      </c>
+      <c r="D16" s="165" t="s">
+        <v>255</v>
       </c>
       <c r="E16" s="82" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="82" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G16" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I16" s="47" t="s">
         <v>40</v>
       </c>
       <c r="J16" s="81" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="K16" s="52">
         <v>50</v>
@@ -3531,30 +3581,30 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="178"/>
+      <c r="B17" s="209"/>
       <c r="C17" s="122" t="s">
-        <v>262</v>
-      </c>
-      <c r="D17" s="191" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="D17" s="166" t="s">
+        <v>258</v>
       </c>
       <c r="E17" s="141" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="141" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G17" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I17" s="67" t="s">
         <v>39</v>
       </c>
       <c r="J17" s="91" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="K17" s="65">
         <v>50</v>
@@ -3598,26 +3648,26 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="182" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="201" t="s">
-        <v>187</v>
+      <c r="B18" s="210" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="176" t="s">
+        <v>182</v>
       </c>
       <c r="D18" s="144" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E18" s="76" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H18" s="40" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I18" s="41" t="s">
         <v>39</v>
@@ -3667,24 +3717,24 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="183"/>
-      <c r="C19" s="202" t="s">
-        <v>226</v>
+      <c r="B19" s="211"/>
+      <c r="C19" s="177" t="s">
+        <v>221</v>
       </c>
       <c r="D19" s="151" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E19" s="91" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="91" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G19" s="65" t="s">
         <v>31</v>
       </c>
       <c r="H19" s="66" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I19" s="67" t="s">
         <v>39</v>
@@ -3734,26 +3784,26 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="184" t="s">
-        <v>195</v>
+      <c r="B20" s="217" t="s">
+        <v>190</v>
       </c>
       <c r="C20" s="75" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D20" s="144" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E20" s="77" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H20" s="40" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>39</v>
@@ -3803,30 +3853,30 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="185"/>
+      <c r="B21" s="215"/>
       <c r="C21" s="80" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D21" s="108" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E21" s="82" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F21" s="82" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="G21" s="52" t="s">
-        <v>241</v>
-      </c>
       <c r="H21" s="46" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I21" s="47" t="s">
         <v>39</v>
       </c>
       <c r="J21" s="81" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K21" s="52">
         <v>20</v>
@@ -3870,30 +3920,30 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="185"/>
+      <c r="B22" s="215"/>
       <c r="C22" s="80" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D22" s="108" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="82" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="H22" s="46" t="s">
         <v>238</v>
-      </c>
-      <c r="E22" s="82" t="s">
-        <v>239</v>
-      </c>
-      <c r="F22" s="82" t="s">
-        <v>240</v>
-      </c>
-      <c r="G22" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>243</v>
       </c>
       <c r="I22" s="47" t="s">
         <v>39</v>
       </c>
       <c r="J22" s="81" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K22" s="52">
         <v>20</v>
@@ -3937,30 +3987,30 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="186"/>
+      <c r="B23" s="216"/>
       <c r="C23" s="122" t="s">
-        <v>269</v>
-      </c>
-      <c r="D23" s="191" t="s">
-        <v>270</v>
+        <v>264</v>
+      </c>
+      <c r="D23" s="166" t="s">
+        <v>265</v>
       </c>
       <c r="E23" s="141" t="s">
         <v>28</v>
       </c>
       <c r="F23" s="141" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G23" s="65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H23" s="66" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I23" s="67" t="s">
         <v>39</v>
       </c>
       <c r="J23" s="91" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K23" s="65">
         <v>10</v>
@@ -4007,68 +4057,68 @@
       <c r="B24" s="149" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="203" t="s">
+      <c r="C24" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="168" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="194" t="s">
+      <c r="E24" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="194" t="s">
+      <c r="F24" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="195" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="195" t="s">
+      <c r="G24" s="170" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="170" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="169" t="s">
         <v>145</v>
       </c>
-      <c r="I24" s="194" t="s">
-        <v>146</v>
-      </c>
-      <c r="J24" s="194" t="s">
+      <c r="J24" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="194">
+      <c r="K24" s="169">
         <v>42</v>
       </c>
-      <c r="L24" s="194">
+      <c r="L24" s="169">
         <v>162</v>
       </c>
-      <c r="M24" s="196">
+      <c r="M24" s="171">
         <v>8</v>
       </c>
-      <c r="N24" s="196">
+      <c r="N24" s="171">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="196">
+      <c r="O24" s="171">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="197" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q24" s="198">
+      <c r="P24" s="172" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q24" s="173">
         <v>3.68</v>
       </c>
-      <c r="R24" s="199">
+      <c r="R24" s="174">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="199">
+      <c r="S24" s="174">
         <v>3.68</v>
       </c>
-      <c r="T24" s="199">
+      <c r="T24" s="174">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="200" t="s">
-        <v>255</v>
-      </c>
-      <c r="V24" s="217">
+      <c r="U24" s="175" t="s">
+        <v>250</v>
+      </c>
+      <c r="V24" s="192">
         <v>3.68</v>
       </c>
       <c r="W24" s="11"/>
@@ -4083,7 +4133,7 @@
       <c r="C25" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="188" t="s">
+      <c r="D25" s="164" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="86" t="s">
@@ -4093,21 +4143,21 @@
         <v>78</v>
       </c>
       <c r="G25" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="55" t="s">
         <v>123</v>
-      </c>
-      <c r="H25" s="55" t="s">
-        <v>124</v>
       </c>
       <c r="I25" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="187" t="s">
+      <c r="J25" s="163" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="187">
+      <c r="K25" s="163">
         <v>10</v>
       </c>
-      <c r="L25" s="187">
+      <c r="L25" s="163">
         <v>30</v>
       </c>
       <c r="M25" s="123">
@@ -4121,7 +4171,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="192" t="s">
+      <c r="P25" s="167" t="s">
         <v>16</v>
       </c>
       <c r="Q25" s="57">
@@ -4146,7 +4196,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="177" t="s">
+      <c r="B26" s="207" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="87" t="s">
@@ -4162,10 +4212,10 @@
         <v>80</v>
       </c>
       <c r="G26" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="59" t="s">
         <v>125</v>
-      </c>
-      <c r="H26" s="59" t="s">
-        <v>126</v>
       </c>
       <c r="I26" s="60" t="s">
         <v>39</v>
@@ -4215,7 +4265,7 @@
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="176"/>
+      <c r="B27" s="208"/>
       <c r="C27" s="94" t="s">
         <v>81</v>
       </c>
@@ -4229,10 +4279,10 @@
         <v>83</v>
       </c>
       <c r="G27" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27" s="46" t="s">
         <v>127</v>
-      </c>
-      <c r="H27" s="46" t="s">
-        <v>128</v>
       </c>
       <c r="I27" s="47" t="s">
         <v>39</v>
@@ -4282,30 +4332,30 @@
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="178"/>
+      <c r="B28" s="209"/>
       <c r="C28" s="90" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D28" s="136" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E28" s="91" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="91" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G28" s="65" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H28" s="66" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I28" s="67" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="68" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K28" s="68">
         <v>10</v>
@@ -4349,14 +4399,14 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="177" t="s">
+      <c r="B29" s="207" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="204" t="s">
-        <v>174</v>
+      <c r="D29" s="179" t="s">
+        <v>169</v>
       </c>
       <c r="E29" s="76" t="s">
         <v>24</v>
@@ -4365,24 +4415,24 @@
         <v>85</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H29" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I29" s="144" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J29" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="K29" s="205">
+        <v>88</v>
+      </c>
+      <c r="K29" s="180">
         <v>100</v>
       </c>
-      <c r="L29" s="205">
+      <c r="L29" s="180">
         <v>100</v>
       </c>
-      <c r="M29" s="205">
+      <c r="M29" s="180">
         <v>3</v>
       </c>
       <c r="N29" s="43">
@@ -4393,7 +4443,7 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="206" t="s">
+      <c r="P29" s="181" t="s">
         <v>16</v>
       </c>
       <c r="Q29" s="44">
@@ -4418,30 +4468,30 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="176"/>
+      <c r="B30" s="208"/>
       <c r="C30" s="94" t="s">
-        <v>274</v>
-      </c>
-      <c r="D30" s="190" t="s">
-        <v>175</v>
+        <v>269</v>
+      </c>
+      <c r="D30" s="226" t="s">
+        <v>170</v>
       </c>
       <c r="E30" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="81" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G30" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I30" s="108" t="s">
         <v>40</v>
       </c>
       <c r="J30" s="81" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="K30" s="109">
         <v>100</v>
@@ -4485,30 +4535,30 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="176"/>
+      <c r="B31" s="208"/>
       <c r="C31" s="94" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D31" s="143" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E31" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="81" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H31" s="46" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I31" s="108" t="s">
         <v>40</v>
       </c>
       <c r="J31" s="81" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K31" s="109">
         <v>100</v>
@@ -4552,30 +4602,30 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="176"/>
+      <c r="B32" s="208"/>
       <c r="C32" s="94" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D32" s="143" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E32" s="81" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="81" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G32" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I32" s="108" t="s">
         <v>40</v>
       </c>
       <c r="J32" s="81" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K32" s="109">
         <v>100</v>
@@ -4619,24 +4669,24 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="178"/>
+      <c r="B33" s="209"/>
       <c r="C33" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="207" t="s">
-        <v>87</v>
+      <c r="D33" s="182" t="s">
+        <v>282</v>
       </c>
       <c r="E33" s="91" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="91" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H33" s="66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I33" s="151" t="s">
         <v>40</v>
@@ -4644,24 +4694,24 @@
       <c r="J33" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="208">
+      <c r="K33" s="183">
         <v>100</v>
       </c>
-      <c r="L33" s="208">
+      <c r="L33" s="183">
         <v>100</v>
       </c>
-      <c r="M33" s="208">
-        <v>1</v>
+      <c r="M33" s="183">
+        <v>2</v>
       </c>
       <c r="N33" s="69">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O33" s="69">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P33" s="209" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="184" t="s">
         <v>16</v>
       </c>
       <c r="Q33" s="70">
@@ -4686,26 +4736,26 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="177" t="s">
-        <v>106</v>
+      <c r="B34" s="207" t="s">
+        <v>105</v>
       </c>
       <c r="C34" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="88" t="s">
+      <c r="E34" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="F34" s="76" t="s">
         <v>92</v>
-      </c>
-      <c r="F34" s="76" t="s">
-        <v>93</v>
       </c>
       <c r="G34" s="39" t="s">
         <v>31</v>
       </c>
       <c r="H34" s="40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I34" s="41" t="s">
         <v>39</v>
@@ -4755,24 +4805,24 @@
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="176"/>
+      <c r="B35" s="208"/>
       <c r="C35" s="94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="135" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="81" t="s">
-        <v>96</v>
-      </c>
       <c r="G35" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="47" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="47" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="47" t="s">
         <v>39</v>
@@ -4822,18 +4872,18 @@
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="176"/>
+      <c r="B36" s="208"/>
       <c r="C36" s="94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36" s="135" t="s">
         <v>29</v>
       </c>
       <c r="E36" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="81" t="s">
         <v>98</v>
-      </c>
-      <c r="F36" s="81" t="s">
-        <v>99</v>
       </c>
       <c r="G36" s="52" t="s">
         <v>31</v>
@@ -4865,7 +4915,7 @@
         <v>20</v>
       </c>
       <c r="P36" s="95" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="71">
         <v>8</v>
@@ -4889,18 +4939,18 @@
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="176"/>
+      <c r="B37" s="208"/>
       <c r="C37" s="100" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="137" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="137" t="s">
+      <c r="E37" s="101" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="101" t="s">
         <v>101</v>
-      </c>
-      <c r="E37" s="101" t="s">
-        <v>137</v>
-      </c>
-      <c r="F37" s="101" t="s">
-        <v>102</v>
       </c>
       <c r="G37" s="102" t="s">
         <v>31</v>
@@ -4932,7 +4982,7 @@
         <v>40</v>
       </c>
       <c r="P37" s="104" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q37" s="118">
         <v>10.18</v>
@@ -4949,7 +4999,7 @@
         <v>417.38</v>
       </c>
       <c r="U37" s="105" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="V37" s="106">
         <v>10.18</v>
@@ -4960,24 +5010,24 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="176"/>
+      <c r="B38" s="208"/>
       <c r="C38" s="94" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D38" s="135" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E38" s="81" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F38" s="81" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H38" s="52" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I38" s="47" t="s">
         <v>39</v>
@@ -5027,24 +5077,24 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="176"/>
+      <c r="B39" s="208"/>
       <c r="C39" s="94" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D39" s="135" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E39" s="81" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F39" s="81" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H39" s="52" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I39" s="47" t="s">
         <v>39</v>
@@ -5094,26 +5144,32 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="176"/>
+      <c r="B40" s="208"/>
       <c r="C40" s="94" t="s">
-        <v>277</v>
-      </c>
-      <c r="D40" s="190" t="s">
-        <v>278</v>
+        <v>272</v>
+      </c>
+      <c r="D40" s="226" t="s">
+        <v>273</v>
       </c>
       <c r="E40" s="81" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="81" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G40" s="52" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H40" s="52"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="52"/>
+      <c r="I40" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="52">
+        <v>6</v>
+      </c>
       <c r="L40" s="52"/>
       <c r="M40" s="83">
         <v>1</v>
@@ -5126,254 +5182,264 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="107"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="115"/>
-      <c r="S40" s="115"/>
-      <c r="T40" s="115"/>
+      <c r="P40" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q40" s="50">
+        <v>1.2</v>
+      </c>
+      <c r="R40" s="115">
+        <f t="shared" si="2"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="S40" s="115">
+        <v>1.2</v>
+      </c>
+      <c r="T40" s="115">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="U40" s="22" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="V40" s="15"/>
       <c r="W40" s="11"/>
     </row>
-    <row r="41" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A41" s="6">
+    <row r="41" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A41" s="6"/>
+      <c r="B41" s="208"/>
+      <c r="C41" s="110" t="s">
+        <v>285</v>
+      </c>
+      <c r="D41" s="221" t="s">
+        <v>283</v>
+      </c>
+      <c r="E41" s="86" t="s">
+        <v>286</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G41" s="54" t="s">
+        <v>288</v>
+      </c>
+      <c r="H41" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="178"/>
-      <c r="C41" s="90" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="E41" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" s="91" t="s">
-        <v>105</v>
-      </c>
-      <c r="G41" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="H41" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="I41" s="68" t="s">
+      <c r="I41" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="68" t="s">
+      <c r="J41" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="65">
+      <c r="K41" s="54">
         <v>10</v>
       </c>
-      <c r="L41" s="65">
+      <c r="L41" s="54">
         <v>30</v>
       </c>
-      <c r="M41" s="96">
+      <c r="M41" s="218">
         <v>1</v>
       </c>
-      <c r="N41" s="69">
+      <c r="N41" s="123">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="69">
+      <c r="O41" s="123">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="97" t="s">
+      <c r="P41" s="225" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q41" s="57">
+        <v>1</v>
+      </c>
+      <c r="R41" s="124">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="S41" s="124">
+        <v>1</v>
+      </c>
+      <c r="T41" s="115">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="U41" s="220"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="11"/>
+    </row>
+    <row r="42" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A42" s="6">
+        <v>39</v>
+      </c>
+      <c r="B42" s="209"/>
+      <c r="C42" s="90" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="136" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="I42" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="65">
+        <v>10</v>
+      </c>
+      <c r="L42" s="65">
+        <v>30</v>
+      </c>
+      <c r="M42" s="96">
+        <v>1</v>
+      </c>
+      <c r="N42" s="69">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O42" s="69">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P42" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="Q41" s="70">
+      <c r="Q42" s="70">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="R41" s="121">
+      <c r="R42" s="121">
         <f t="shared" si="2"/>
         <v>0.53500000000000003</v>
       </c>
-      <c r="S41" s="121">
+      <c r="S42" s="121">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="T41" s="121">
+      <c r="T42" s="121">
         <f t="shared" si="3"/>
         <v>1.605</v>
       </c>
-      <c r="U41" s="23"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="11"/>
-    </row>
-    <row r="42" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A42" s="6">
+      <c r="U42" s="23"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="11"/>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A43" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="177" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="87" t="s">
+      <c r="B43" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="87" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="92" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="88" t="s">
-        <v>41</v>
-      </c>
-      <c r="E42" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="92" t="s">
-        <v>108</v>
-      </c>
-      <c r="G42" s="43" t="s">
+      <c r="G43" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="H43" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="H42" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="I42" s="42" t="s">
+      <c r="I43" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="42" t="s">
+      <c r="J43" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="72">
+      <c r="K43" s="72">
         <v>50</v>
       </c>
-      <c r="L42" s="72">
+      <c r="L43" s="72">
         <v>50</v>
       </c>
-      <c r="M42" s="73">
+      <c r="M43" s="73">
         <v>1</v>
       </c>
-      <c r="N42" s="43">
+      <c r="N43" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="43">
+      <c r="O43" s="43">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="98" t="s">
+      <c r="P43" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="44">
+      <c r="Q43" s="44">
         <v>1.4E-2</v>
       </c>
-      <c r="R42" s="45">
+      <c r="R43" s="45">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="S42" s="45">
+      <c r="S43" s="45">
         <v>1.4E-2</v>
       </c>
-      <c r="T42" s="45">
+      <c r="T43" s="45">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="U42" s="24"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="11"/>
-    </row>
-    <row r="43" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A43" s="6">
+      <c r="U43" s="24"/>
+      <c r="V43" s="13"/>
+      <c r="W43" s="11"/>
+    </row>
+    <row r="44" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A44" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="176"/>
-      <c r="C43" s="94" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="135" t="s">
+      <c r="B44" s="208"/>
+      <c r="C44" s="94" t="s">
+        <v>292</v>
+      </c>
+      <c r="D44" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="E43" s="81" t="s">
+      <c r="E44" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="81" t="s">
-        <v>155</v>
-      </c>
-      <c r="G43" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="H43" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="I43" s="48" t="s">
+      <c r="F44" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="G44" s="48" t="s">
+        <v>294</v>
+      </c>
+      <c r="H44" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" s="48" t="s">
         <v>39</v>
-      </c>
-      <c r="J43" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" s="48">
-        <v>6</v>
-      </c>
-      <c r="L43" s="48">
-        <v>21</v>
-      </c>
-      <c r="M43" s="74">
-        <v>1</v>
-      </c>
-      <c r="N43" s="114">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O43" s="114">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="P43" s="107" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q43" s="71">
-        <v>0.25409999999999999</v>
-      </c>
-      <c r="R43" s="115">
-        <f t="shared" si="2"/>
-        <v>1.5246</v>
-      </c>
-      <c r="S43" s="115">
-        <v>0.21260000000000001</v>
-      </c>
-      <c r="T43" s="115">
-        <f t="shared" si="3"/>
-        <v>4.4645999999999999</v>
-      </c>
-      <c r="U43" s="28"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="11"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A44" s="6">
-        <v>42</v>
-      </c>
-      <c r="B44" s="176"/>
-      <c r="C44" s="94" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="81" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="99" t="s">
-        <v>110</v>
-      </c>
-      <c r="G44" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="H44" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="I44" s="48" t="s">
-        <v>149</v>
       </c>
       <c r="J44" s="48" t="s">
         <v>22</v>
       </c>
       <c r="K44" s="48">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L44" s="48">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M44" s="74">
         <v>1</v>
@@ -5386,61 +5452,61 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="95" t="s">
+      <c r="P44" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="50">
-        <v>1.26E-2</v>
+      <c r="Q44" s="71">
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="R44" s="115">
         <f t="shared" si="2"/>
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S44" s="115">
-        <v>1.26E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="T44" s="115">
         <f t="shared" si="3"/>
-        <v>0.63</v>
-      </c>
-      <c r="U44" s="29"/>
+        <v>1.77</v>
+      </c>
+      <c r="U44" s="28"/>
       <c r="V44" s="15"/>
       <c r="W44" s="11"/>
     </row>
     <row r="45" spans="1:23" ht="15.75" thickBot="1">
       <c r="A45" s="6">
-        <v>43</v>
-      </c>
-      <c r="B45" s="176"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="208"/>
       <c r="C45" s="94" t="s">
-        <v>280</v>
-      </c>
-      <c r="D45" s="190" t="s">
-        <v>281</v>
+        <v>108</v>
+      </c>
+      <c r="D45" s="135" t="s">
+        <v>34</v>
       </c>
       <c r="E45" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="81" t="s">
-        <v>282</v>
+      <c r="F45" s="99" t="s">
+        <v>109</v>
       </c>
       <c r="G45" s="48" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="H45" s="48" t="s">
-        <v>284</v>
+        <v>143</v>
       </c>
       <c r="I45" s="48" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="J45" s="48" t="s">
         <v>22</v>
       </c>
       <c r="K45" s="48">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="L45" s="48">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M45" s="74">
         <v>1</v>
@@ -5453,318 +5519,392 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="107" t="s">
+      <c r="P45" s="95" t="s">
         <v>16</v>
       </c>
       <c r="Q45" s="50">
-        <v>0.1002</v>
+        <v>1.26E-2</v>
       </c>
       <c r="R45" s="115">
         <f t="shared" si="2"/>
-        <v>0.501</v>
+        <v>0.63</v>
       </c>
       <c r="S45" s="115">
-        <v>0.1002</v>
+        <v>1.26E-2</v>
       </c>
       <c r="T45" s="115">
         <f t="shared" si="3"/>
-        <v>2.5049999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="U45" s="29"/>
       <c r="V45" s="15"/>
       <c r="W45" s="11"/>
     </row>
-    <row r="46" spans="1:23" ht="115.5" thickBot="1">
+    <row r="46" spans="1:23" ht="15.75" thickBot="1">
       <c r="A46" s="6">
+        <v>43</v>
+      </c>
+      <c r="B46" s="208"/>
+      <c r="C46" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="D46" s="226" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="81" t="s">
+        <v>277</v>
+      </c>
+      <c r="G46" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="H46" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="I46" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="J46" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="48">
+        <v>5</v>
+      </c>
+      <c r="L46" s="48">
+        <v>25</v>
+      </c>
+      <c r="M46" s="74">
+        <v>1</v>
+      </c>
+      <c r="N46" s="114">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O46" s="114">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P46" s="107" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q46" s="50">
+        <v>0.1002</v>
+      </c>
+      <c r="R46" s="115">
+        <f t="shared" si="2"/>
+        <v>0.501</v>
+      </c>
+      <c r="S46" s="115">
+        <v>0.1002</v>
+      </c>
+      <c r="T46" s="115">
+        <f t="shared" si="3"/>
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="U46" s="29"/>
+      <c r="V46" s="15"/>
+      <c r="W46" s="11"/>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A47" s="6"/>
+      <c r="B47" s="208"/>
+      <c r="C47" s="110" t="s">
+        <v>289</v>
+      </c>
+      <c r="D47" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="E47" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="224">
+        <v>61300611121</v>
+      </c>
+      <c r="G47" s="163" t="s">
+        <v>290</v>
+      </c>
+      <c r="H47" s="163" t="s">
+        <v>291</v>
+      </c>
+      <c r="I47" s="163" t="s">
+        <v>291</v>
+      </c>
+      <c r="J47" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="163">
+        <v>20</v>
+      </c>
+      <c r="L47" s="163">
+        <v>40</v>
+      </c>
+      <c r="M47" s="222">
+        <v>1</v>
+      </c>
+      <c r="N47" s="123">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O47" s="123">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="P47" s="219" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q47" s="57">
+        <v>0.03</v>
+      </c>
+      <c r="R47" s="115">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+      <c r="S47" s="124">
+        <v>0.03</v>
+      </c>
+      <c r="T47" s="115">
+        <f t="shared" si="3"/>
+        <v>1.2</v>
+      </c>
+      <c r="U47" s="223"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="11"/>
+    </row>
+    <row r="48" spans="1:23" ht="115.5" thickBot="1">
+      <c r="A48" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="178"/>
-      <c r="C46" s="126" t="s">
+      <c r="B48" s="209"/>
+      <c r="C48" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="127" t="s">
-        <v>249</v>
-      </c>
-      <c r="E46" s="128" t="s">
+      <c r="D48" s="127" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="128" t="s">
+      <c r="F48" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="G46" s="129" t="s">
-        <v>145</v>
-      </c>
-      <c r="H46" s="129" t="s">
-        <v>145</v>
-      </c>
-      <c r="I46" s="130" t="s">
+      <c r="G48" s="129" t="s">
+        <v>144</v>
+      </c>
+      <c r="H48" s="129"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="130" t="s">
-        <v>40</v>
-      </c>
-      <c r="K46" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="L46" s="130" t="s">
+      <c r="K48" s="130" t="s">
+        <v>144</v>
+      </c>
+      <c r="L48" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="131">
+      <c r="M48" s="131">
         <v>53</v>
       </c>
-      <c r="N46" s="132">
+      <c r="N48" s="132">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O46" s="69">
+      <c r="O48" s="69">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P46" s="129" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q46" s="130" t="s">
+      <c r="P48" s="129" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q48" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="R46" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="S46" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="T46" s="130" t="s">
-        <v>145</v>
-      </c>
-      <c r="U46" s="133" t="s">
-        <v>150</v>
-      </c>
-      <c r="V46" s="134"/>
-      <c r="W46" s="11"/>
-    </row>
-    <row r="47" spans="1:23" ht="26.25" thickBot="1">
-      <c r="A47" s="6">
+      <c r="R48" s="130" t="s">
+        <v>144</v>
+      </c>
+      <c r="S48" s="130" t="s">
+        <v>144</v>
+      </c>
+      <c r="T48" s="130" t="s">
+        <v>144</v>
+      </c>
+      <c r="U48" s="133" t="s">
+        <v>149</v>
+      </c>
+      <c r="V48" s="134"/>
+      <c r="W48" s="11"/>
+    </row>
+    <row r="49" spans="1:23" ht="26.25" thickBot="1">
+      <c r="A49" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="185" t="s">
+      <c r="B49" s="215" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" s="186" t="s">
+        <v>252</v>
+      </c>
+      <c r="D49" s="187" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" s="187" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="187" t="s">
+        <v>251</v>
+      </c>
+      <c r="G49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="H49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="I49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="J49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="K49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="L49" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="M49" s="185">
+        <v>1</v>
+      </c>
+      <c r="N49" s="49">
+        <f>M49*5</f>
+        <v>5</v>
+      </c>
+      <c r="O49" s="49">
+        <f>M49*20</f>
+        <v>20</v>
+      </c>
+      <c r="P49" s="188" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q49" s="189">
+        <v>0.2</v>
+      </c>
+      <c r="R49" s="190">
+        <f>Q49*N49</f>
+        <v>1</v>
+      </c>
+      <c r="S49" s="189">
+        <v>0.2</v>
+      </c>
+      <c r="T49" s="51">
+        <f>S49*O49</f>
+        <v>4</v>
+      </c>
+      <c r="U49" s="191"/>
+      <c r="V49" s="193"/>
+      <c r="W49" s="11"/>
+    </row>
+    <row r="50" spans="1:23" ht="15.75" thickBot="1">
+      <c r="A50" s="19">
+        <v>46</v>
+      </c>
+      <c r="B50" s="216"/>
+      <c r="C50" s="145" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="211" t="s">
-        <v>257</v>
-      </c>
-      <c r="D47" s="212" t="s">
+      <c r="D50" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="E47" s="212" t="s">
+      <c r="E50" s="146" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="212" t="s">
-        <v>256</v>
-      </c>
-      <c r="G47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="H47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="I47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="K47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="L47" s="212" t="s">
-        <v>145</v>
-      </c>
-      <c r="M47" s="210">
+      <c r="F50" s="147" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="J50" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="L50" s="146" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="138">
         <v>1</v>
       </c>
-      <c r="N47" s="49">
-        <f>M47*5</f>
+      <c r="N50" s="138">
+        <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
-      <c r="O47" s="49">
-        <f>M47*20</f>
-        <v>20</v>
-      </c>
-      <c r="P47" s="213" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q47" s="214">
-        <v>0.2</v>
-      </c>
-      <c r="R47" s="215">
-        <f>Q47*N47</f>
-        <v>1</v>
-      </c>
-      <c r="S47" s="214">
-        <v>0.2</v>
-      </c>
-      <c r="T47" s="51">
-        <f>S47*O47</f>
-        <v>4</v>
-      </c>
-      <c r="U47" s="216"/>
-      <c r="V47" s="218"/>
-      <c r="W47" s="11"/>
-    </row>
-    <row r="48" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A48" s="19">
-        <v>46</v>
-      </c>
-      <c r="B48" s="186"/>
-      <c r="C48" s="145" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="F48" s="147" t="s">
-        <v>153</v>
-      </c>
-      <c r="G48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="H48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="I48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="J48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="L48" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" s="138">
-        <v>1</v>
-      </c>
-      <c r="N48" s="138">
-        <f t="shared" ref="N48" si="4">M48*5</f>
-        <v>5</v>
-      </c>
-      <c r="O48" s="69">
+      <c r="O50" s="69">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P48" s="155" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q48" s="139">
+      <c r="P50" s="155" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q50" s="139">
         <v>3.35</v>
       </c>
-      <c r="R48" s="140">
-        <f>Q48*N48</f>
+      <c r="R50" s="140">
+        <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S48" s="140">
+      <c r="S50" s="140">
         <v>3.35</v>
       </c>
-      <c r="T48" s="121">
-        <f>S48*O48</f>
+      <c r="T50" s="121">
+        <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U48" s="133" t="s">
-        <v>150</v>
-      </c>
-      <c r="V48" s="148"/>
-      <c r="W48" s="11"/>
-    </row>
-    <row r="49" spans="1:23" ht="15.75">
-      <c r="A49" s="1"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="172" t="s">
-        <v>37</v>
-      </c>
-      <c r="N49" s="173"/>
-      <c r="O49" s="173"/>
-      <c r="P49" s="173"/>
-      <c r="Q49" s="21"/>
-      <c r="R49" s="157">
-        <f>SUM(R3:R47)</f>
-        <v>365.28580000000005</v>
-      </c>
-      <c r="S49" s="157"/>
-      <c r="T49" s="113">
-        <f>SUM(T3:T47)</f>
-        <v>1330.2895000000003</v>
-      </c>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="11"/>
-    </row>
-    <row r="50" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A50" s="1"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="174" t="s">
-        <v>38</v>
-      </c>
-      <c r="N50" s="175"/>
-      <c r="O50" s="175"/>
-      <c r="P50" s="175"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="160">
-        <f>R49/5</f>
-        <v>73.05716000000001</v>
-      </c>
-      <c r="S50" s="160"/>
-      <c r="T50" s="38">
-        <f>T49/20</f>
-        <v>66.514475000000019</v>
-      </c>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
+      <c r="U50" s="133" t="s">
+        <v>149</v>
+      </c>
+      <c r="V50" s="148"/>
       <c r="W50" s="11"/>
     </row>
     <row r="51" spans="1:23" ht="15.75">
       <c r="A51" s="1"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="33"/>
-      <c r="N51" s="163" t="s">
-        <v>148</v>
-      </c>
-      <c r="O51" s="164"/>
-      <c r="P51" s="165"/>
-      <c r="Q51" s="156"/>
-      <c r="R51" s="158">
-        <v>3</v>
-      </c>
-      <c r="S51" s="158"/>
-      <c r="T51" s="159">
-        <v>3</v>
+      <c r="M51" s="203" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" s="204"/>
+      <c r="O51" s="204"/>
+      <c r="P51" s="204"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="157">
+        <f>SUM(R3:R49)</f>
+        <v>382.15120000000002</v>
+      </c>
+      <c r="S51" s="157"/>
+      <c r="T51" s="113">
+        <f>SUM(T3:T49)</f>
+        <v>1358.7949000000003</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
       <c r="W51" s="11"/>
     </row>
-    <row r="52" spans="1:23" ht="15.75">
+    <row r="52" spans="1:23" ht="16.5" thickBot="1">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -5772,65 +5912,99 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="179" t="s">
-        <v>258</v>
-      </c>
-      <c r="O52" s="180"/>
-      <c r="P52" s="181"/>
-      <c r="Q52" s="154"/>
-      <c r="R52" s="153">
-        <v>22.78</v>
-      </c>
-      <c r="S52" s="153"/>
-      <c r="T52" s="161">
-        <v>90.99</v>
+      <c r="M52" s="205" t="s">
+        <v>38</v>
+      </c>
+      <c r="N52" s="206"/>
+      <c r="O52" s="206"/>
+      <c r="P52" s="206"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="160">
+        <f>R51/5</f>
+        <v>76.430239999999998</v>
+      </c>
+      <c r="S52" s="160"/>
+      <c r="T52" s="38">
+        <f>T51/20</f>
+        <v>67.939745000000016</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="11"/>
     </row>
-    <row r="53" spans="1:23" ht="16.5" thickBot="1">
+    <row r="53" spans="1:23" ht="15.75">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="G53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="N53" s="166" t="s">
-        <v>43</v>
-      </c>
-      <c r="O53" s="167"/>
-      <c r="P53" s="168"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="162">
-        <f>SUM(R50:R52)</f>
-        <v>98.837160000000011</v>
-      </c>
-      <c r="S53" s="162"/>
-      <c r="T53" s="37">
-        <f>SUM(T50:T52)</f>
-        <v>160.50447500000001</v>
-      </c>
-      <c r="V53" s="11"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="33"/>
+      <c r="N53" s="194" t="s">
+        <v>147</v>
+      </c>
+      <c r="O53" s="195"/>
+      <c r="P53" s="196"/>
+      <c r="Q53" s="156"/>
+      <c r="R53" s="158">
+        <v>3</v>
+      </c>
+      <c r="S53" s="158"/>
+      <c r="T53" s="159">
+        <v>3</v>
+      </c>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
       <c r="W53" s="11"/>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" ht="15.75">
       <c r="A54" s="1"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="G54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="V54" s="11"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="212" t="s">
+        <v>253</v>
+      </c>
+      <c r="O54" s="213"/>
+      <c r="P54" s="214"/>
+      <c r="Q54" s="154"/>
+      <c r="R54" s="153">
+        <v>22.78</v>
+      </c>
+      <c r="S54" s="153"/>
+      <c r="T54" s="161">
+        <v>90.99</v>
+      </c>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
       <c r="W54" s="11"/>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" ht="16.5" thickBot="1">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
+      <c r="N55" s="197" t="s">
+        <v>43</v>
+      </c>
+      <c r="O55" s="198"/>
+      <c r="P55" s="199"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="162">
+        <f>SUM(R52:R54)</f>
+        <v>102.21024</v>
+      </c>
+      <c r="S55" s="162"/>
+      <c r="T55" s="37">
+        <f>SUM(T52:T54)</f>
+        <v>161.92974500000003</v>
+      </c>
       <c r="V55" s="11"/>
       <c r="W55" s="11"/>
     </row>
@@ -5840,6 +6014,8 @@
       <c r="D56" s="2"/>
       <c r="G56" s="2"/>
       <c r="I56" s="2"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
       <c r="V56" s="11"/>
       <c r="W56" s="11"/>
     </row>
@@ -5854,11 +6030,19 @@
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="1"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="I58" s="2"/>
       <c r="V58" s="11"/>
       <c r="W58" s="11"/>
     </row>
-    <row r="59" spans="1:23" ht="15.75" customHeight="1">
+    <row r="59" spans="1:23">
       <c r="A59" s="1"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="I59" s="2"/>
       <c r="V59" s="11"/>
       <c r="W59" s="11"/>
     </row>
@@ -5867,7 +6051,7 @@
       <c r="V60" s="11"/>
       <c r="W60" s="11"/>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:23" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
       <c r="V61" s="11"/>
       <c r="W61" s="11"/>
@@ -5887,33 +6071,43 @@
       <c r="V64" s="11"/>
       <c r="W64" s="11"/>
     </row>
-    <row r="65" spans="8:21">
-      <c r="H65" s="9"/>
-      <c r="U65" s="10"/>
-    </row>
-    <row r="66" spans="8:21">
-      <c r="H66" s="9"/>
-      <c r="U66" s="10"/>
+    <row r="65" spans="1:23">
+      <c r="A65" s="1"/>
+      <c r="V65" s="11"/>
+      <c r="W65" s="11"/>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="A66" s="1"/>
+      <c r="V66" s="11"/>
+      <c r="W66" s="11"/>
+    </row>
+    <row r="67" spans="1:23">
+      <c r="H67" s="9"/>
+      <c r="U67" s="10"/>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="H68" s="9"/>
+      <c r="U68" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N51:P51"/>
     <mergeCell ref="N53:P53"/>
+    <mergeCell ref="N55:P55"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="M50:P50"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="M52:P52"/>
     <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B34:B42"/>
+    <mergeCell ref="B43:B48"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="N54:P54"/>
+    <mergeCell ref="B49:B50"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B20:B23"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="U43">
+  <conditionalFormatting sqref="U44">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -5967,7 +6161,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R50:T52">
+  <conditionalFormatting sqref="R52:T54">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -5981,7 +6175,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34:N46 O48 M9:M28 N3:O46 M47:O47">
+  <conditionalFormatting sqref="M34:N48 O50 M9:M28 N3:O48 M49:O49">
     <cfRule type="colorScale" priority="33">
       <colorScale>
         <cfvo type="min"/>
@@ -5993,7 +6187,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:O47 O48">
+  <conditionalFormatting sqref="M3:O49 O50">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
@@ -6005,7 +6199,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K46:L46">
+  <conditionalFormatting sqref="K48:L48">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -6019,7 +6213,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M48:N48">
+  <conditionalFormatting sqref="M50:N50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6031,7 +6225,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M48:N48">
+  <conditionalFormatting sqref="M50:N50">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6043,7 +6237,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R48:S48">
+  <conditionalFormatting sqref="R50:S50">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -6057,7 +6251,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T47:T48 R3:T46">
+  <conditionalFormatting sqref="T49:T50 R3:T48">
     <cfRule type="dataBar" priority="48">
       <dataBar>
         <cfvo type="min"/>
@@ -6072,52 +6266,54 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P3" r:id="rId1" xr:uid="{77E7F02B-CC4A-45E7-B730-3717F029D629}"/>
-    <hyperlink ref="P4" r:id="rId2" xr:uid="{422ACB32-99A4-4373-9BBC-0F8302D669E9}"/>
-    <hyperlink ref="P5" r:id="rId3" xr:uid="{1D3C339F-D2BF-414A-BD64-13F776D76A9F}"/>
-    <hyperlink ref="P6" r:id="rId4" xr:uid="{01BBFB8E-A26B-48C7-AB0F-DF9F65C47B93}"/>
-    <hyperlink ref="P8" r:id="rId5" xr:uid="{83C85DDA-7FBA-4A9B-8C90-61DA15EF09A1}"/>
-    <hyperlink ref="P9" r:id="rId6" xr:uid="{F5D2937B-2705-425B-A920-F69EE337A9AA}"/>
-    <hyperlink ref="P10" r:id="rId7" xr:uid="{23650E7E-1F91-465B-A508-B3E81A5A29DB}"/>
-    <hyperlink ref="P11" r:id="rId8" xr:uid="{A3FA0792-9C1C-4B11-8EC7-D8950B40778A}"/>
-    <hyperlink ref="P25" r:id="rId9" xr:uid="{9306F7E1-9FA0-45C1-9226-A5EFFE620B9F}"/>
-    <hyperlink ref="P26" r:id="rId10" xr:uid="{6C2F24FA-F4C6-4765-90C1-BBDF944038A7}"/>
-    <hyperlink ref="P27" r:id="rId11" xr:uid="{834B4123-1D60-4B34-B015-5E7BBC8F47AF}"/>
-    <hyperlink ref="P29" r:id="rId12" xr:uid="{1D1A071F-2A3D-4FA1-937C-5E9315A2DAC9}"/>
-    <hyperlink ref="P33" r:id="rId13" xr:uid="{1ECC2B27-3B6B-4070-A52B-CBF10AA116AF}"/>
-    <hyperlink ref="P34" r:id="rId14" xr:uid="{BFDF2136-290A-40AE-829A-CE2FE24D8034}"/>
-    <hyperlink ref="P35" r:id="rId15" xr:uid="{E71028CE-6136-4648-ABFC-ABDBCFA60DB5}"/>
-    <hyperlink ref="P41" r:id="rId16" xr:uid="{8E22EBA9-5C52-408B-A65B-4F115F1CD0F7}"/>
-    <hyperlink ref="P42" r:id="rId17" xr:uid="{0A7E773D-5A3D-486C-84CA-8D29060909A3}"/>
-    <hyperlink ref="P44" r:id="rId18" xr:uid="{79B90123-86F4-4C7F-BE0B-E5B7C590F601}"/>
-    <hyperlink ref="P24" r:id="rId19" display="Aliexpress" xr:uid="{D571A1A4-A3B8-476C-81AA-A10E0576C945}"/>
-    <hyperlink ref="P43" r:id="rId20" xr:uid="{552B4167-57FF-43F1-B0A5-FDF3A29237A4}"/>
-    <hyperlink ref="P7" r:id="rId21" xr:uid="{6FBFF76E-B622-4D29-A447-7C6E26828E4F}"/>
-    <hyperlink ref="P12" r:id="rId22" xr:uid="{1242BC39-221F-4021-953C-3FCDA7A5753C}"/>
-    <hyperlink ref="P13" r:id="rId23" xr:uid="{96270715-E02B-41B7-B021-EDD143E9B86E}"/>
-    <hyperlink ref="P18" r:id="rId24" xr:uid="{9B63197A-770E-4944-B769-AA91C9283ECE}"/>
-    <hyperlink ref="P20" r:id="rId25" xr:uid="{9BCD60A7-30C2-4172-B089-A68B6513C693}"/>
-    <hyperlink ref="P28" r:id="rId26" xr:uid="{B47CC2C3-43E3-4A0C-8766-540A57D9BE72}"/>
-    <hyperlink ref="P31" r:id="rId27" xr:uid="{CC730C2B-3995-4162-BE6B-30851128B6A0}"/>
-    <hyperlink ref="P38" r:id="rId28" xr:uid="{9108529D-C5AF-49DE-B1AA-F619710C5B08}"/>
-    <hyperlink ref="P39" r:id="rId29" xr:uid="{31C7B57C-378C-4F81-AADD-6D3587D8A480}"/>
-    <hyperlink ref="P36" r:id="rId30" xr:uid="{600C5A90-1D13-491E-82D2-49A3F9B676E0}"/>
-    <hyperlink ref="P14" r:id="rId31" xr:uid="{44409B7B-710F-4F54-A7F0-477BEA0AFE5F}"/>
-    <hyperlink ref="P15" r:id="rId32" xr:uid="{89198C26-8FB1-4B6B-AE7B-FFAE1D3733A8}"/>
-    <hyperlink ref="P19" r:id="rId33" xr:uid="{EC86EEC1-808E-4C17-B0CB-1E879CDB66DD}"/>
-    <hyperlink ref="P21" r:id="rId34" xr:uid="{2322511E-46DE-4717-9728-D93822E1A6A3}"/>
-    <hyperlink ref="P22" r:id="rId35" xr:uid="{2BCC81E2-819B-49BB-9670-D8361D1C41A8}"/>
-    <hyperlink ref="P32" r:id="rId36" xr:uid="{888359C9-25FD-4ECA-BFAD-B6548ECFC19D}"/>
-    <hyperlink ref="P48" r:id="rId37" xr:uid="{AA0FF76A-81A9-4B84-B70A-22617F6C3440}"/>
-    <hyperlink ref="P47" r:id="rId38" xr:uid="{4800B236-FD98-4B4C-8675-7F9F6549B4BC}"/>
-    <hyperlink ref="P16" r:id="rId39" xr:uid="{E831E81D-C8A7-439A-9225-793F9ACBC435}"/>
-    <hyperlink ref="P17" r:id="rId40" xr:uid="{87F27C46-519D-4D56-B15F-FD9B1CD47221}"/>
-    <hyperlink ref="P23" r:id="rId41" xr:uid="{0161C0DD-E06A-48BB-800D-73ED423A3AD7}"/>
-    <hyperlink ref="P30" r:id="rId42" xr:uid="{00A7F659-3375-4433-B4AD-F92BAE9ADD19}"/>
-    <hyperlink ref="P45" r:id="rId43" xr:uid="{81929E54-8283-45FE-90B8-1D44758D061E}"/>
+    <hyperlink ref="P3" r:id="rId1"/>
+    <hyperlink ref="P4" r:id="rId2"/>
+    <hyperlink ref="P5" r:id="rId3"/>
+    <hyperlink ref="P6" r:id="rId4"/>
+    <hyperlink ref="P8" r:id="rId5"/>
+    <hyperlink ref="P9" r:id="rId6"/>
+    <hyperlink ref="P10" r:id="rId7"/>
+    <hyperlink ref="P11" r:id="rId8"/>
+    <hyperlink ref="P25" r:id="rId9"/>
+    <hyperlink ref="P26" r:id="rId10"/>
+    <hyperlink ref="P27" r:id="rId11"/>
+    <hyperlink ref="P29" r:id="rId12"/>
+    <hyperlink ref="P33" r:id="rId13"/>
+    <hyperlink ref="P34" r:id="rId14"/>
+    <hyperlink ref="P35" r:id="rId15"/>
+    <hyperlink ref="P42" r:id="rId16"/>
+    <hyperlink ref="P43" r:id="rId17"/>
+    <hyperlink ref="P45" r:id="rId18"/>
+    <hyperlink ref="P24" r:id="rId19" display="Aliexpress"/>
+    <hyperlink ref="P44" r:id="rId20"/>
+    <hyperlink ref="P7" r:id="rId21"/>
+    <hyperlink ref="P12" r:id="rId22"/>
+    <hyperlink ref="P13" r:id="rId23"/>
+    <hyperlink ref="P18" r:id="rId24"/>
+    <hyperlink ref="P20" r:id="rId25"/>
+    <hyperlink ref="P28" r:id="rId26"/>
+    <hyperlink ref="P31" r:id="rId27"/>
+    <hyperlink ref="P38" r:id="rId28"/>
+    <hyperlink ref="P39" r:id="rId29"/>
+    <hyperlink ref="P36" r:id="rId30"/>
+    <hyperlink ref="P14" r:id="rId31"/>
+    <hyperlink ref="P15" r:id="rId32"/>
+    <hyperlink ref="P19" r:id="rId33"/>
+    <hyperlink ref="P21" r:id="rId34"/>
+    <hyperlink ref="P22" r:id="rId35"/>
+    <hyperlink ref="P32" r:id="rId36"/>
+    <hyperlink ref="P50" r:id="rId37"/>
+    <hyperlink ref="P49" r:id="rId38"/>
+    <hyperlink ref="P16" r:id="rId39"/>
+    <hyperlink ref="P17" r:id="rId40"/>
+    <hyperlink ref="P23" r:id="rId41"/>
+    <hyperlink ref="P30" r:id="rId42"/>
+    <hyperlink ref="P46" r:id="rId43"/>
+    <hyperlink ref="P41" r:id="rId44"/>
+    <hyperlink ref="P47" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6132,7 +6328,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U43</xm:sqref>
+          <xm:sqref>U44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">
@@ -6171,7 +6367,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R50:T52</xm:sqref>
+          <xm:sqref>R52:T54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{193AFC57-9059-4DAB-9E2A-67F7DD9723ED}">
@@ -6184,7 +6380,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K46:L46</xm:sqref>
+          <xm:sqref>K48:L48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{19A41A86-C9BB-4A96-AA11-2BBEAF826782}">
@@ -6197,7 +6393,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R48:S48</xm:sqref>
+          <xm:sqref>R50:S50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{70CE0387-EDB2-443C-842F-1D5EE6E70AF7}">
@@ -6210,7 +6406,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>T47:T48 R3:T46</xm:sqref>
+          <xm:sqref>T49:T50 R3:T48</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="298">
   <si>
     <t>S. No.</t>
   </si>
@@ -923,18 +923,24 @@
   </si>
   <si>
     <t>C2764612</t>
+  </si>
+  <si>
+    <t>Lesser price?</t>
+  </si>
+  <si>
+    <t>Remarks (Faizan)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,8 +1117,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1155,8 +1168,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1564,6 +1583,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1573,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1622,9 +1702,6 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1662,18 +1739,9 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1738,27 +1806,6 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1831,9 +1878,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1843,9 +1887,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2091,9 +2132,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2142,6 +2180,21 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2214,31 +2267,215 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2517,13 +2754,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5703125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2541,37 +2778,39 @@
     <col min="19" max="19" width="13.5703125" style="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="1"/>
+    <col min="22" max="22" width="32" style="1" customWidth="1"/>
+    <col min="23" max="23" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16.5" thickBot="1">
-      <c r="A1" s="200" t="s">
+    <row r="1" spans="1:24" ht="16.5" thickBot="1">
+      <c r="A1" s="191" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="201"/>
-      <c r="L1" s="201"/>
-      <c r="M1" s="201"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="202"/>
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
+      <c r="M1" s="192"/>
+      <c r="N1" s="192"/>
+      <c r="O1" s="192"/>
+      <c r="P1" s="192"/>
+      <c r="Q1" s="192"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="192"/>
+      <c r="T1" s="192"/>
+      <c r="U1" s="192"/>
+      <c r="V1" s="192"/>
+      <c r="W1" s="193"/>
     </row>
-    <row r="2" spans="1:23" ht="16.5" thickBot="1">
+    <row r="2" spans="1:24" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2605,7 +2844,7 @@
       <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="152" t="s">
+      <c r="L2" s="139" t="s">
         <v>249</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -2629,3253 +2868,3326 @@
       <c r="S2" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="T2" s="152" t="s">
+      <c r="T2" s="139" t="s">
         <v>248</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="139" t="s">
+        <v>297</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75" thickBot="1">
+    <row r="3" spans="1:24" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="144" t="s">
+      <c r="D3" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="77" t="s">
+      <c r="E3" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="76" t="s">
+      <c r="J3" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="42">
+      <c r="K3" s="38">
         <v>40</v>
       </c>
-      <c r="L3" s="42">
+      <c r="L3" s="38">
         <v>100</v>
       </c>
-      <c r="M3" s="78">
+      <c r="M3" s="67">
         <v>4</v>
       </c>
-      <c r="N3" s="43">
+      <c r="N3" s="39">
         <f>M3*5</f>
         <v>20</v>
       </c>
-      <c r="O3" s="43">
+      <c r="O3" s="39">
         <f>M3*20</f>
         <v>80</v>
       </c>
-      <c r="P3" s="79" t="s">
+      <c r="P3" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="44">
+      <c r="Q3" s="40">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="R3" s="45">
+      <c r="R3" s="41">
         <f>Q3*K3</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="S3" s="45">
+      <c r="S3" s="41">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="T3" s="45">
+      <c r="T3" s="41">
         <f>S3*L3</f>
         <v>1.3599999999999999</v>
       </c>
       <c r="U3" s="12"/>
-      <c r="V3" s="13"/>
+      <c r="V3" s="219"/>
+      <c r="W3" s="13"/>
     </row>
-    <row r="4" spans="1:23" ht="15.75" thickBot="1">
+    <row r="4" spans="1:24" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="80" t="s">
+      <c r="B4" s="199"/>
+      <c r="C4" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="81" t="s">
+      <c r="J4" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="48">
+      <c r="K4" s="44">
         <v>20</v>
       </c>
-      <c r="L4" s="48">
+      <c r="L4" s="44">
         <v>40</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="72">
         <v>1</v>
       </c>
-      <c r="N4" s="114">
+      <c r="N4" s="101">
         <f t="shared" ref="N4:N48" si="0">M4*5</f>
         <v>5</v>
       </c>
-      <c r="O4" s="114">
+      <c r="O4" s="101">
         <f t="shared" ref="O4:O50" si="1">M4*20</f>
         <v>20</v>
       </c>
-      <c r="P4" s="84" t="s">
+      <c r="P4" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="50">
+      <c r="Q4" s="46">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="R4" s="115">
+      <c r="R4" s="102">
         <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
         <v>0.40599999999999997</v>
       </c>
-      <c r="S4" s="115">
+      <c r="S4" s="102">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="T4" s="115">
+      <c r="T4" s="102">
         <f t="shared" ref="T4:T47" si="3">S4*L4</f>
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
-      <c r="V4" s="15"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="15"/>
     </row>
-    <row r="5" spans="1:23" ht="39" thickBot="1">
+    <row r="5" spans="1:24" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="80" t="s">
+      <c r="B5" s="199"/>
+      <c r="C5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="143" t="s">
+      <c r="D5" s="130" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="46" t="s">
+      <c r="H5" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I5" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="81" t="s">
+      <c r="J5" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="44">
         <v>100</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="44">
         <v>400</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="72">
         <v>19</v>
       </c>
-      <c r="N5" s="114">
+      <c r="N5" s="101">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="O5" s="114">
+      <c r="O5" s="101">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="P5" s="84" t="s">
+      <c r="P5" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="46">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="R5" s="115">
+      <c r="R5" s="102">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="S5" s="115">
+      <c r="S5" s="102">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T5" s="115">
+      <c r="T5" s="102">
         <f t="shared" si="3"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="U5" s="14"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="11"/>
+      <c r="V5" s="220"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:23" ht="15.75" thickBot="1">
+    <row r="6" spans="1:24" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="208"/>
-      <c r="C6" s="80" t="s">
+      <c r="B6" s="199"/>
+      <c r="C6" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="D6" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="82" t="s">
+      <c r="E6" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="81" t="s">
+      <c r="J6" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="48">
+      <c r="K6" s="44">
         <v>100</v>
       </c>
-      <c r="L6" s="48">
+      <c r="L6" s="44">
         <v>200</v>
       </c>
-      <c r="M6" s="83">
+      <c r="M6" s="72">
         <v>8</v>
       </c>
-      <c r="N6" s="114">
+      <c r="N6" s="101">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O6" s="114">
+      <c r="O6" s="101">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="50">
+      <c r="Q6" s="46">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="115">
+      <c r="R6" s="102">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="115">
+      <c r="S6" s="102">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="115">
+      <c r="T6" s="102">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="U6" s="14"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="11"/>
+      <c r="V6" s="220"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:23" ht="15.75" thickBot="1">
+    <row r="7" spans="1:24" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="208"/>
-      <c r="C7" s="80" t="s">
+      <c r="B7" s="199"/>
+      <c r="C7" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="108" t="s">
+      <c r="D7" s="95" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="112" t="s">
+      <c r="F7" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="47" t="s">
+      <c r="I7" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="J7" s="81" t="s">
+      <c r="J7" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="44">
         <v>100</v>
       </c>
-      <c r="L7" s="48">
+      <c r="L7" s="44">
         <v>100</v>
       </c>
-      <c r="M7" s="83">
+      <c r="M7" s="72">
         <v>1</v>
       </c>
-      <c r="N7" s="114">
+      <c r="N7" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O7" s="114">
+      <c r="O7" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="111" t="s">
+      <c r="P7" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="50">
+      <c r="Q7" s="46">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R7" s="115">
+      <c r="R7" s="102">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S7" s="115">
+      <c r="S7" s="102">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T7" s="115">
+      <c r="T7" s="102">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="11"/>
+      <c r="V7" s="220"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:23" ht="51.75" thickBot="1">
+    <row r="8" spans="1:24" ht="51.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="208"/>
-      <c r="C8" s="80" t="s">
+      <c r="B8" s="199"/>
+      <c r="C8" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="143" t="s">
+      <c r="D8" s="130" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="81" t="s">
+      <c r="J8" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="44">
         <v>150</v>
       </c>
-      <c r="L8" s="48">
+      <c r="L8" s="44">
         <v>600</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="72">
         <v>29</v>
       </c>
-      <c r="N8" s="114">
+      <c r="N8" s="101">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="O8" s="114">
+      <c r="O8" s="101">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="P8" s="85" t="s">
+      <c r="P8" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="50">
+      <c r="Q8" s="46">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="R8" s="115">
+      <c r="R8" s="102">
         <f t="shared" si="2"/>
         <v>1.08</v>
       </c>
-      <c r="S8" s="115">
+      <c r="S8" s="102">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="T8" s="115">
+      <c r="T8" s="102">
         <f t="shared" si="3"/>
         <v>3.4799999999999995</v>
       </c>
-      <c r="U8" s="27"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="11"/>
+      <c r="U8" s="26"/>
+      <c r="V8" s="221"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:23" ht="15.75" thickBot="1">
+    <row r="9" spans="1:24" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="80" t="s">
+      <c r="B9" s="199"/>
+      <c r="C9" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="108" t="s">
+      <c r="D9" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="81" t="s">
+      <c r="J9" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9" s="48">
         <v>10</v>
       </c>
-      <c r="L9" s="52">
+      <c r="L9" s="48">
         <v>30</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="72">
         <v>1</v>
       </c>
-      <c r="N9" s="114">
+      <c r="N9" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="114">
+      <c r="O9" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P9" s="85" t="s">
+      <c r="P9" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="50">
+      <c r="Q9" s="46">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="R9" s="115">
+      <c r="R9" s="102">
         <f t="shared" si="2"/>
         <v>0.443</v>
       </c>
-      <c r="S9" s="115">
+      <c r="S9" s="102">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="T9" s="115">
+      <c r="T9" s="102">
         <f t="shared" si="3"/>
         <v>1.1459999999999999</v>
       </c>
       <c r="U9" s="14"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="11"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="11"/>
     </row>
-    <row r="10" spans="1:23" ht="15.75" thickBot="1">
+    <row r="10" spans="1:24" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="208"/>
-      <c r="C10" s="80" t="s">
+      <c r="B10" s="199"/>
+      <c r="C10" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="108" t="s">
+      <c r="D10" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="82" t="s">
+      <c r="E10" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="81" t="s">
+      <c r="J10" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="52">
+      <c r="K10" s="48">
         <v>100</v>
       </c>
-      <c r="L10" s="52">
+      <c r="L10" s="48">
         <v>200</v>
       </c>
-      <c r="M10" s="83">
+      <c r="M10" s="72">
         <v>6</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="101">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O10" s="114">
+      <c r="O10" s="101">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="P10" s="84" t="s">
+      <c r="P10" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="46">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="102">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="102">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="T10" s="115">
+      <c r="T10" s="102">
         <f t="shared" si="3"/>
         <v>0.64</v>
       </c>
       <c r="U10" s="14"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="11"/>
+      <c r="V10" s="220"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="11"/>
     </row>
-    <row r="11" spans="1:23" ht="26.25" thickBot="1">
+    <row r="11" spans="1:24" ht="26.25" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="208"/>
-      <c r="C11" s="80" t="s">
+      <c r="B11" s="199"/>
+      <c r="C11" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="143" t="s">
+      <c r="D11" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="81" t="s">
+      <c r="E11" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="46" t="s">
+      <c r="H11" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="81" t="s">
+      <c r="J11" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11" s="48">
         <v>100</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11" s="48">
         <v>350</v>
       </c>
-      <c r="M11" s="83">
+      <c r="M11" s="72">
         <v>16</v>
       </c>
-      <c r="N11" s="114">
+      <c r="N11" s="101">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="O11" s="114">
+      <c r="O11" s="101">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="P11" s="84" t="s">
+      <c r="P11" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="50">
+      <c r="Q11" s="46">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="R11" s="115">
+      <c r="R11" s="102">
         <f t="shared" si="2"/>
         <v>1.51</v>
       </c>
-      <c r="S11" s="115">
+      <c r="S11" s="102">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="T11" s="115">
+      <c r="T11" s="102">
         <f t="shared" si="3"/>
         <v>5.2850000000000001</v>
       </c>
       <c r="U11" s="14"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="11"/>
+      <c r="V11" s="220"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="11"/>
     </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1">
+    <row r="12" spans="1:24" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="208"/>
-      <c r="C12" s="80" t="s">
+      <c r="B12" s="199"/>
+      <c r="C12" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="82" t="s">
+      <c r="E12" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="47" t="s">
+      <c r="I12" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="81" t="s">
+      <c r="J12" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="K12" s="52">
+      <c r="K12" s="48">
         <v>50</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12" s="48">
         <v>50</v>
       </c>
-      <c r="M12" s="83">
+      <c r="M12" s="72">
         <v>1</v>
       </c>
-      <c r="N12" s="114">
+      <c r="N12" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O12" s="114">
+      <c r="O12" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="116" t="s">
+      <c r="P12" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="46">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="R12" s="115">
+      <c r="R12" s="102">
         <f t="shared" si="2"/>
         <v>0.23500000000000001</v>
       </c>
-      <c r="S12" s="115">
+      <c r="S12" s="102">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="T12" s="115">
+      <c r="T12" s="102">
         <f t="shared" si="3"/>
         <v>0.23500000000000001</v>
       </c>
       <c r="U12" s="14"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="11"/>
+      <c r="V12" s="220"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="11"/>
     </row>
-    <row r="13" spans="1:23" ht="15.75" thickBot="1">
+    <row r="13" spans="1:24" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="80" t="s">
+      <c r="B13" s="199"/>
+      <c r="C13" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="130" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="81" t="s">
+      <c r="E13" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="F13" s="86" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="52" t="s">
+      <c r="G13" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="J13" s="81" t="s">
+      <c r="J13" s="70" t="s">
         <v>197</v>
       </c>
-      <c r="K13" s="52">
+      <c r="K13" s="48">
         <v>100</v>
       </c>
-      <c r="L13" s="52">
+      <c r="L13" s="48">
         <v>100</v>
       </c>
-      <c r="M13" s="83">
+      <c r="M13" s="72">
         <v>1</v>
       </c>
-      <c r="N13" s="114">
+      <c r="N13" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O13" s="114">
+      <c r="O13" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="116" t="s">
+      <c r="P13" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q13" s="50">
+      <c r="Q13" s="46">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R13" s="115">
+      <c r="R13" s="102">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="S13" s="115">
+      <c r="S13" s="102">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="T13" s="115">
+      <c r="T13" s="102">
         <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
       <c r="U13" s="14"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="11"/>
+      <c r="V13" s="220"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="11"/>
     </row>
-    <row r="14" spans="1:23" ht="15.75" thickBot="1">
+    <row r="14" spans="1:24" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="80" t="s">
+      <c r="B14" s="199"/>
+      <c r="C14" s="69" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="108" t="s">
+      <c r="D14" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G14" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="46" t="s">
+      <c r="H14" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="81" t="s">
+      <c r="J14" s="70" t="s">
         <v>225</v>
       </c>
-      <c r="K14" s="52">
+      <c r="K14" s="48">
         <v>100</v>
       </c>
-      <c r="L14" s="52">
+      <c r="L14" s="48">
         <v>100</v>
       </c>
-      <c r="M14" s="83">
+      <c r="M14" s="72">
         <v>1</v>
       </c>
-      <c r="N14" s="114">
+      <c r="N14" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O14" s="114">
+      <c r="O14" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="116" t="s">
+      <c r="P14" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="50">
+      <c r="Q14" s="46">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="R14" s="115">
+      <c r="R14" s="102">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="S14" s="115">
+      <c r="S14" s="102">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="T14" s="115">
+      <c r="T14" s="102">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="U14" s="14"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="11"/>
+      <c r="V14" s="220"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="11"/>
     </row>
-    <row r="15" spans="1:23" ht="15.75" thickBot="1">
+    <row r="15" spans="1:24" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="208"/>
-      <c r="C15" s="80" t="s">
+      <c r="B15" s="199"/>
+      <c r="C15" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="108" t="s">
+      <c r="D15" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="81" t="s">
+      <c r="J15" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="K15" s="52">
+      <c r="K15" s="48">
         <v>50</v>
       </c>
-      <c r="L15" s="52">
+      <c r="L15" s="48">
         <v>50</v>
       </c>
-      <c r="M15" s="83">
+      <c r="M15" s="72">
         <v>2</v>
       </c>
-      <c r="N15" s="114">
+      <c r="N15" s="101">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O15" s="114">
+      <c r="O15" s="101">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="116" t="s">
+      <c r="P15" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="50">
+      <c r="Q15" s="46">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="R15" s="115">
+      <c r="R15" s="102">
         <f t="shared" si="2"/>
         <v>0.255</v>
       </c>
-      <c r="S15" s="115">
+      <c r="S15" s="102">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="T15" s="115">
+      <c r="T15" s="102">
         <f t="shared" si="3"/>
         <v>0.255</v>
       </c>
       <c r="U15" s="14"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="11"/>
+      <c r="V15" s="220"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="11"/>
     </row>
-    <row r="16" spans="1:23" ht="15.75" thickBot="1">
+    <row r="16" spans="1:24" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="80" t="s">
+      <c r="B16" s="199"/>
+      <c r="C16" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="D16" s="165" t="s">
+      <c r="D16" s="152" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="I16" s="47" t="s">
+      <c r="I16" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="81" t="s">
+      <c r="J16" s="70" t="s">
         <v>261</v>
       </c>
-      <c r="K16" s="52">
+      <c r="K16" s="48">
         <v>50</v>
       </c>
-      <c r="L16" s="52">
+      <c r="L16" s="48">
         <v>50</v>
       </c>
-      <c r="M16" s="83">
+      <c r="M16" s="72">
         <v>1</v>
       </c>
-      <c r="N16" s="114">
+      <c r="N16" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O16" s="114">
+      <c r="O16" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="116" t="s">
+      <c r="P16" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="50">
+      <c r="Q16" s="46">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="R16" s="115">
+      <c r="R16" s="102">
         <f t="shared" si="2"/>
         <v>0.30499999999999999</v>
       </c>
-      <c r="S16" s="115">
+      <c r="S16" s="102">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="T16" s="115">
+      <c r="T16" s="102">
         <f>S16*L16</f>
         <v>0.30499999999999999</v>
       </c>
       <c r="U16" s="14"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="11"/>
+      <c r="V16" s="220"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="11"/>
     </row>
-    <row r="17" spans="1:23" ht="15.75" thickBot="1">
+    <row r="17" spans="1:24" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="209"/>
-      <c r="C17" s="122" t="s">
+      <c r="B17" s="200"/>
+      <c r="C17" s="109" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="166" t="s">
+      <c r="D17" s="153" t="s">
         <v>258</v>
       </c>
-      <c r="E17" s="141" t="s">
+      <c r="E17" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="141" t="s">
+      <c r="F17" s="128" t="s">
         <v>259</v>
       </c>
-      <c r="G17" s="65" t="s">
+      <c r="G17" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="66" t="s">
+      <c r="H17" s="55" t="s">
         <v>262</v>
       </c>
-      <c r="I17" s="67" t="s">
+      <c r="I17" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="91" t="s">
+      <c r="J17" s="79" t="s">
         <v>263</v>
       </c>
-      <c r="K17" s="65">
+      <c r="K17" s="54">
         <v>50</v>
       </c>
-      <c r="L17" s="65">
+      <c r="L17" s="54">
         <v>50</v>
       </c>
-      <c r="M17" s="96">
+      <c r="M17" s="83">
         <v>1</v>
       </c>
-      <c r="N17" s="69">
+      <c r="N17" s="58">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O17" s="69">
+      <c r="O17" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="120" t="s">
+      <c r="P17" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="70">
+      <c r="Q17" s="59">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R17" s="121">
+      <c r="R17" s="108">
         <f t="shared" si="2"/>
         <v>0.38500000000000001</v>
       </c>
-      <c r="S17" s="121">
+      <c r="S17" s="108">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T17" s="121">
+      <c r="T17" s="108">
         <f>S17*L17</f>
         <v>0.38500000000000001</v>
       </c>
       <c r="U17" s="16"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="11"/>
+      <c r="V17" s="222"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="11"/>
     </row>
-    <row r="18" spans="1:23" ht="26.25" thickBot="1">
+    <row r="18" spans="1:24" ht="26.25" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="210" t="s">
+      <c r="B18" s="201" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="176" t="s">
+      <c r="C18" s="163" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="144" t="s">
+      <c r="D18" s="131" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="I18" s="41" t="s">
+      <c r="I18" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="76" t="s">
+      <c r="J18" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="39">
+      <c r="K18" s="35">
         <v>10</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="35">
         <v>30</v>
       </c>
-      <c r="M18" s="78">
+      <c r="M18" s="67">
         <v>1</v>
       </c>
-      <c r="N18" s="43">
+      <c r="N18" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="142" t="s">
+      <c r="P18" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="44">
+      <c r="Q18" s="40">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="R18" s="45">
+      <c r="R18" s="41">
         <f t="shared" si="2"/>
         <v>0.626</v>
       </c>
-      <c r="S18" s="45">
+      <c r="S18" s="41">
         <v>6.1699999999999998E-2</v>
       </c>
-      <c r="T18" s="45">
+      <c r="T18" s="41">
         <f t="shared" si="3"/>
         <v>1.851</v>
       </c>
       <c r="U18" s="12"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="11"/>
+      <c r="V18" s="219"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="11"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75" thickBot="1">
+    <row r="19" spans="1:24" ht="15.75" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="211"/>
-      <c r="C19" s="177" t="s">
+      <c r="B19" s="202"/>
+      <c r="C19" s="209" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="210" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="91" t="s">
+      <c r="F19" s="210" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="65" t="s">
+      <c r="G19" s="211" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="66" t="s">
+      <c r="H19" s="212" t="s">
         <v>228</v>
       </c>
-      <c r="I19" s="67" t="s">
+      <c r="I19" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="91" t="s">
+      <c r="J19" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="211">
         <v>15</v>
       </c>
-      <c r="L19" s="65">
+      <c r="L19" s="211">
         <v>45</v>
       </c>
-      <c r="M19" s="96">
+      <c r="M19" s="213">
         <v>2</v>
       </c>
-      <c r="N19" s="69">
+      <c r="N19" s="213">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="69">
+      <c r="O19" s="213">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="120" t="s">
+      <c r="P19" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="70">
+      <c r="Q19" s="215">
         <v>0.1116</v>
       </c>
-      <c r="R19" s="121">
+      <c r="R19" s="216">
         <f t="shared" si="2"/>
         <v>1.6740000000000002</v>
       </c>
-      <c r="S19" s="121">
+      <c r="S19" s="216">
         <v>0.1116</v>
       </c>
-      <c r="T19" s="121">
+      <c r="T19" s="216">
         <f t="shared" si="3"/>
         <v>5.0220000000000002</v>
       </c>
-      <c r="U19" s="16"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="11"/>
+      <c r="U19" s="232"/>
+      <c r="V19" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W19" s="218"/>
+      <c r="X19" s="11"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75" thickBot="1">
+    <row r="20" spans="1:24" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="217" t="s">
+      <c r="B20" s="208" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="144" t="s">
+      <c r="D20" s="131" t="s">
         <v>187</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="66" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="I20" s="41" t="s">
+      <c r="I20" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="76" t="s">
+      <c r="J20" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="35">
         <v>50</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="35">
         <v>50</v>
       </c>
-      <c r="M20" s="78">
+      <c r="M20" s="67">
         <v>1</v>
       </c>
-      <c r="N20" s="43">
+      <c r="N20" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O20" s="43">
+      <c r="O20" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="142" t="s">
+      <c r="P20" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="44">
+      <c r="Q20" s="40">
         <v>2.07E-2</v>
       </c>
-      <c r="R20" s="45">
+      <c r="R20" s="41">
         <f t="shared" si="2"/>
         <v>1.0349999999999999</v>
       </c>
-      <c r="S20" s="45">
+      <c r="S20" s="41">
         <v>2.07E-2</v>
       </c>
-      <c r="T20" s="45">
+      <c r="T20" s="41">
         <f t="shared" si="3"/>
         <v>1.0349999999999999</v>
       </c>
       <c r="U20" s="12"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="11"/>
+      <c r="V20" s="219"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="11"/>
     </row>
-    <row r="21" spans="1:23" ht="15.75" thickBot="1">
+    <row r="21" spans="1:24" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="215"/>
-      <c r="C21" s="80" t="s">
+      <c r="B21" s="206"/>
+      <c r="C21" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="108" t="s">
+      <c r="D21" s="95" t="s">
         <v>230</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="F21" s="82" t="s">
+      <c r="F21" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="G21" s="52" t="s">
+      <c r="G21" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="I21" s="47" t="s">
+      <c r="I21" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="81" t="s">
+      <c r="J21" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="48">
         <v>20</v>
       </c>
-      <c r="L21" s="52">
+      <c r="L21" s="48">
         <v>50</v>
       </c>
-      <c r="M21" s="83">
+      <c r="M21" s="72">
         <v>2</v>
       </c>
-      <c r="N21" s="114">
+      <c r="N21" s="101">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O21" s="114">
+      <c r="O21" s="101">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="116" t="s">
+      <c r="P21" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="50">
+      <c r="Q21" s="46">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="R21" s="115">
+      <c r="R21" s="102">
         <f t="shared" si="2"/>
         <v>1.4860000000000002</v>
       </c>
-      <c r="S21" s="115">
+      <c r="S21" s="102">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="T21" s="115">
+      <c r="T21" s="102">
         <f t="shared" si="3"/>
         <v>3.7150000000000003</v>
       </c>
       <c r="U21" s="14"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="11"/>
+      <c r="V21" s="220"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="11"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75" thickBot="1">
+    <row r="22" spans="1:24" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="215"/>
-      <c r="C22" s="80" t="s">
+      <c r="B22" s="206"/>
+      <c r="C22" s="69" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="108" t="s">
+      <c r="D22" s="95" t="s">
         <v>233</v>
       </c>
-      <c r="E22" s="82" t="s">
+      <c r="E22" s="71" t="s">
         <v>234</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="71" t="s">
         <v>235</v>
       </c>
-      <c r="G22" s="52" t="s">
+      <c r="G22" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="H22" s="46" t="s">
+      <c r="H22" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="I22" s="47" t="s">
+      <c r="I22" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="81" t="s">
+      <c r="J22" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="K22" s="52">
+      <c r="K22" s="48">
         <v>20</v>
       </c>
-      <c r="L22" s="52">
+      <c r="L22" s="48">
         <v>50</v>
       </c>
-      <c r="M22" s="83">
+      <c r="M22" s="72">
         <v>2</v>
       </c>
-      <c r="N22" s="114">
+      <c r="N22" s="101">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O22" s="114">
+      <c r="O22" s="101">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P22" s="116" t="s">
+      <c r="P22" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="50">
+      <c r="Q22" s="46">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R22" s="115">
+      <c r="R22" s="102">
         <f t="shared" si="2"/>
         <v>0.154</v>
       </c>
-      <c r="S22" s="115">
+      <c r="S22" s="102">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T22" s="115">
+      <c r="T22" s="102">
         <f t="shared" si="3"/>
         <v>0.38500000000000001</v>
       </c>
       <c r="U22" s="14"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="11"/>
+      <c r="V22" s="220"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="11"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" thickBot="1">
+    <row r="23" spans="1:24" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="216"/>
-      <c r="C23" s="122" t="s">
+      <c r="B23" s="207"/>
+      <c r="C23" s="109" t="s">
         <v>264</v>
       </c>
-      <c r="D23" s="166" t="s">
+      <c r="D23" s="153" t="s">
         <v>265</v>
       </c>
-      <c r="E23" s="141" t="s">
+      <c r="E23" s="128" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="141" t="s">
+      <c r="F23" s="128" t="s">
         <v>266</v>
       </c>
-      <c r="G23" s="65" t="s">
+      <c r="G23" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="55" t="s">
         <v>267</v>
       </c>
-      <c r="I23" s="67" t="s">
+      <c r="I23" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="91" t="s">
+      <c r="J23" s="79" t="s">
         <v>207</v>
       </c>
-      <c r="K23" s="65">
+      <c r="K23" s="54">
         <v>10</v>
       </c>
-      <c r="L23" s="65">
+      <c r="L23" s="54">
         <v>30</v>
       </c>
-      <c r="M23" s="96">
+      <c r="M23" s="83">
         <v>1</v>
       </c>
-      <c r="N23" s="69">
+      <c r="N23" s="58">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O23" s="69">
+      <c r="O23" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="120" t="s">
+      <c r="P23" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="70">
+      <c r="Q23" s="59">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="R23" s="121">
+      <c r="R23" s="108">
         <f t="shared" si="2"/>
         <v>0.91600000000000004</v>
       </c>
-      <c r="S23" s="121">
+      <c r="S23" s="108">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="T23" s="121">
+      <c r="T23" s="108">
         <f t="shared" si="3"/>
         <v>2.7480000000000002</v>
       </c>
       <c r="U23" s="16"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="11"/>
+      <c r="V23" s="222"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="11"/>
     </row>
-    <row r="24" spans="1:23" ht="26.25" thickBot="1">
+    <row r="24" spans="1:24" ht="26.25" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="149" t="s">
+      <c r="B24" s="136" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="178" t="s">
+      <c r="C24" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="168" t="s">
+      <c r="D24" s="155" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="169" t="s">
+      <c r="E24" s="156" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="169" t="s">
+      <c r="F24" s="156" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="170" t="s">
+      <c r="G24" s="157" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="170" t="s">
+      <c r="H24" s="157" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="169" t="s">
+      <c r="I24" s="156" t="s">
         <v>145</v>
       </c>
-      <c r="J24" s="169" t="s">
+      <c r="J24" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="169">
+      <c r="K24" s="156">
         <v>42</v>
       </c>
-      <c r="L24" s="169">
+      <c r="L24" s="156">
         <v>162</v>
       </c>
-      <c r="M24" s="171">
+      <c r="M24" s="158">
         <v>8</v>
       </c>
-      <c r="N24" s="171">
+      <c r="N24" s="158">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="171">
+      <c r="O24" s="158">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="172" t="s">
+      <c r="P24" s="159" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="173">
+      <c r="Q24" s="160">
         <v>3.68</v>
       </c>
-      <c r="R24" s="174">
+      <c r="R24" s="161">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="174">
+      <c r="S24" s="161">
         <v>3.68</v>
       </c>
-      <c r="T24" s="174">
+      <c r="T24" s="161">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="175" t="s">
+      <c r="U24" s="162" t="s">
         <v>250</v>
       </c>
-      <c r="V24" s="192">
+      <c r="V24" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W24" s="178">
         <v>3.68</v>
       </c>
-      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
     </row>
-    <row r="25" spans="1:23" ht="26.25" thickBot="1">
+    <row r="25" spans="1:24" ht="26.25" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="150" t="s">
+      <c r="B25" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="110" t="s">
+      <c r="C25" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="164" t="s">
+      <c r="D25" s="151" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="86" t="s">
+      <c r="E25" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="86" t="s">
+      <c r="F25" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="54" t="s">
+      <c r="G25" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="56" t="s">
+      <c r="I25" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="163" t="s">
+      <c r="J25" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="163">
+      <c r="K25" s="150">
         <v>10</v>
       </c>
-      <c r="L25" s="163">
+      <c r="L25" s="150">
         <v>30</v>
       </c>
-      <c r="M25" s="123">
+      <c r="M25" s="110">
         <v>1</v>
       </c>
-      <c r="N25" s="123">
+      <c r="N25" s="110">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="123">
+      <c r="O25" s="110">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="167" t="s">
+      <c r="P25" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="57">
+      <c r="Q25" s="53">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R25" s="124">
+      <c r="R25" s="111">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S25" s="124">
+      <c r="S25" s="111">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="T25" s="124">
+      <c r="T25" s="111">
         <f t="shared" si="3"/>
         <v>1.77</v>
       </c>
-      <c r="U25" s="30"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="11"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="223"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="11"/>
     </row>
-    <row r="26" spans="1:23" ht="26.25" thickBot="1">
+    <row r="26" spans="1:24" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="207" t="s">
+      <c r="B26" s="198" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="87" t="s">
+      <c r="C26" s="233" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="88" t="s">
+      <c r="D26" s="234" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="88" t="s">
+      <c r="E26" s="234" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="88" t="s">
+      <c r="F26" s="234" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="58" t="s">
+      <c r="G26" s="235" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="236" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="I26" s="235" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="61" t="s">
+      <c r="J26" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="61">
+      <c r="K26" s="234">
         <v>7</v>
       </c>
-      <c r="L26" s="61">
+      <c r="L26" s="234">
         <v>23</v>
       </c>
-      <c r="M26" s="62">
+      <c r="M26" s="237">
         <v>1</v>
       </c>
-      <c r="N26" s="62">
+      <c r="N26" s="237">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="43">
+      <c r="O26" s="238">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="89" t="s">
+      <c r="P26" s="239" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="63">
+      <c r="Q26" s="240">
         <v>0.23949999999999999</v>
       </c>
-      <c r="R26" s="64">
+      <c r="R26" s="241">
         <f>Q26*K26</f>
         <v>1.6764999999999999</v>
       </c>
-      <c r="S26" s="64">
+      <c r="S26" s="241">
         <v>0.23949999999999999</v>
       </c>
-      <c r="T26" s="45">
+      <c r="T26" s="242">
         <f t="shared" si="3"/>
         <v>5.5084999999999997</v>
       </c>
-      <c r="U26" s="18"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="11"/>
+      <c r="U26" s="243"/>
+      <c r="V26" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W26" s="244"/>
+      <c r="X26" s="11"/>
     </row>
-    <row r="27" spans="1:23" ht="26.25" thickBot="1">
+    <row r="27" spans="1:24" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="208"/>
-      <c r="C27" s="94" t="s">
+      <c r="B27" s="199"/>
+      <c r="C27" s="245" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="135" t="s">
+      <c r="D27" s="246" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="81" t="s">
+      <c r="E27" s="247" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="81" t="s">
+      <c r="F27" s="247" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="52" t="s">
+      <c r="G27" s="248" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="46" t="s">
+      <c r="H27" s="249" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="47" t="s">
+      <c r="I27" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="48" t="s">
+      <c r="J27" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="48">
+      <c r="K27" s="247">
         <v>7</v>
       </c>
-      <c r="L27" s="48">
+      <c r="L27" s="247">
         <v>45</v>
       </c>
-      <c r="M27" s="114">
+      <c r="M27" s="250">
         <v>2</v>
       </c>
-      <c r="N27" s="114">
+      <c r="N27" s="250">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="114">
+      <c r="O27" s="250">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="85" t="s">
+      <c r="P27" s="251" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="50">
+      <c r="Q27" s="252">
         <v>0.11169999999999999</v>
       </c>
-      <c r="R27" s="115">
+      <c r="R27" s="253">
         <f t="shared" si="2"/>
         <v>0.78189999999999993</v>
       </c>
-      <c r="S27" s="115">
+      <c r="S27" s="253">
         <v>0.11169999999999999</v>
       </c>
-      <c r="T27" s="115">
+      <c r="T27" s="253">
         <f t="shared" si="3"/>
         <v>5.0264999999999995</v>
       </c>
-      <c r="U27" s="14"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="11"/>
+      <c r="U27" s="254"/>
+      <c r="V27" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W27" s="255"/>
+      <c r="X27" s="11"/>
     </row>
-    <row r="28" spans="1:23" ht="26.25" thickBot="1">
+    <row r="28" spans="1:24" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="209"/>
-      <c r="C28" s="90" t="s">
+      <c r="B28" s="200"/>
+      <c r="C28" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="136" t="s">
+      <c r="D28" s="123" t="s">
         <v>167</v>
       </c>
-      <c r="E28" s="91" t="s">
+      <c r="E28" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="91" t="s">
+      <c r="F28" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="65" t="s">
+      <c r="G28" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="H28" s="66" t="s">
+      <c r="H28" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="I28" s="67" t="s">
+      <c r="I28" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="68" t="s">
+      <c r="J28" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="K28" s="68">
+      <c r="K28" s="57">
         <v>10</v>
       </c>
-      <c r="L28" s="68">
+      <c r="L28" s="57">
         <v>25</v>
       </c>
-      <c r="M28" s="69">
+      <c r="M28" s="58">
         <v>1</v>
       </c>
-      <c r="N28" s="69">
+      <c r="N28" s="58">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="69">
+      <c r="O28" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="125" t="s">
+      <c r="P28" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="70">
+      <c r="Q28" s="59">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="R28" s="121">
+      <c r="R28" s="108">
         <f t="shared" si="2"/>
         <v>0.99099999999999988</v>
       </c>
-      <c r="S28" s="121">
+      <c r="S28" s="108">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="T28" s="121">
+      <c r="T28" s="108">
         <f t="shared" si="3"/>
         <v>2.4775</v>
       </c>
       <c r="U28" s="16"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="11"/>
+      <c r="V28" s="222"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="11"/>
     </row>
-    <row r="29" spans="1:23" ht="15.75" thickBot="1">
+    <row r="29" spans="1:24" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="207" t="s">
+      <c r="B29" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="179" t="s">
+      <c r="D29" s="165" t="s">
         <v>169</v>
       </c>
-      <c r="E29" s="76" t="s">
+      <c r="E29" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="92" t="s">
+      <c r="F29" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="39" t="s">
+      <c r="G29" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="144" t="s">
+      <c r="I29" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="76" t="s">
+      <c r="J29" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="180">
+      <c r="K29" s="166">
         <v>100</v>
       </c>
-      <c r="L29" s="180">
+      <c r="L29" s="166">
         <v>100</v>
       </c>
-      <c r="M29" s="180">
+      <c r="M29" s="166">
         <v>3</v>
       </c>
-      <c r="N29" s="43">
+      <c r="N29" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="O29" s="43">
+      <c r="O29" s="39">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="181" t="s">
+      <c r="P29" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="44">
+      <c r="Q29" s="40">
         <v>1E-3</v>
       </c>
-      <c r="R29" s="45">
+      <c r="R29" s="41">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S29" s="45">
+      <c r="S29" s="41">
         <v>1E-3</v>
       </c>
-      <c r="T29" s="45">
+      <c r="T29" s="41">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="U29" s="12"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="11"/>
+      <c r="V29" s="219"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="11"/>
     </row>
-    <row r="30" spans="1:23" ht="15.75" thickBot="1">
+    <row r="30" spans="1:24" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="208"/>
-      <c r="C30" s="94" t="s">
+      <c r="B30" s="199"/>
+      <c r="C30" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="D30" s="226" t="s">
+      <c r="D30" s="184" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="81" t="s">
+      <c r="E30" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="F30" s="70" t="s">
         <v>270</v>
       </c>
-      <c r="G30" s="52" t="s">
+      <c r="G30" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="46" t="s">
+      <c r="H30" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="81" t="s">
+      <c r="J30" s="70" t="s">
         <v>268</v>
       </c>
-      <c r="K30" s="109">
+      <c r="K30" s="96">
         <v>100</v>
       </c>
-      <c r="L30" s="109">
+      <c r="L30" s="96">
         <v>100</v>
       </c>
-      <c r="M30" s="109">
+      <c r="M30" s="96">
         <v>1</v>
       </c>
-      <c r="N30" s="114">
+      <c r="N30" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O30" s="114">
+      <c r="O30" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="117" t="s">
+      <c r="P30" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="50">
+      <c r="Q30" s="46">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R30" s="115">
+      <c r="R30" s="102">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="S30" s="115">
+      <c r="S30" s="102">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="T30" s="115">
+      <c r="T30" s="102">
         <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
       <c r="U30" s="14"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="11"/>
+      <c r="V30" s="220"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="11"/>
     </row>
-    <row r="31" spans="1:23" ht="15.75" thickBot="1">
+    <row r="31" spans="1:24" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="208"/>
-      <c r="C31" s="94" t="s">
+      <c r="B31" s="199"/>
+      <c r="C31" s="81" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="143" t="s">
+      <c r="D31" s="130" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="81" t="s">
+      <c r="E31" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="81" t="s">
+      <c r="F31" s="70" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="52" t="s">
+      <c r="G31" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="46" t="s">
+      <c r="H31" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="I31" s="108" t="s">
+      <c r="I31" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="81" t="s">
+      <c r="J31" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="109">
+      <c r="K31" s="96">
         <v>100</v>
       </c>
-      <c r="L31" s="109">
+      <c r="L31" s="96">
         <v>100</v>
       </c>
-      <c r="M31" s="109">
+      <c r="M31" s="96">
         <v>1</v>
       </c>
-      <c r="N31" s="114">
+      <c r="N31" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O31" s="114">
+      <c r="O31" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P31" s="117" t="s">
+      <c r="P31" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="50">
+      <c r="Q31" s="46">
         <v>1.5E-3</v>
       </c>
-      <c r="R31" s="115">
+      <c r="R31" s="102">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
-      <c r="S31" s="115">
+      <c r="S31" s="102">
         <v>1.5E-3</v>
       </c>
-      <c r="T31" s="115">
+      <c r="T31" s="102">
         <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
       <c r="U31" s="14"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="11"/>
+      <c r="V31" s="220"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="11"/>
     </row>
-    <row r="32" spans="1:23" ht="15.75" thickBot="1">
+    <row r="32" spans="1:24" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="208"/>
-      <c r="C32" s="94" t="s">
+      <c r="B32" s="199"/>
+      <c r="C32" s="81" t="s">
         <v>239</v>
       </c>
-      <c r="D32" s="143" t="s">
+      <c r="D32" s="130" t="s">
         <v>240</v>
       </c>
-      <c r="E32" s="81" t="s">
+      <c r="E32" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="81" t="s">
+      <c r="F32" s="70" t="s">
         <v>241</v>
       </c>
-      <c r="G32" s="52" t="s">
+      <c r="G32" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="46" t="s">
+      <c r="H32" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="I32" s="108" t="s">
+      <c r="I32" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="81" t="s">
+      <c r="J32" s="70" t="s">
         <v>243</v>
       </c>
-      <c r="K32" s="109">
+      <c r="K32" s="96">
         <v>100</v>
       </c>
-      <c r="L32" s="109">
+      <c r="L32" s="96">
         <v>100</v>
       </c>
-      <c r="M32" s="109">
+      <c r="M32" s="96">
         <v>4</v>
       </c>
-      <c r="N32" s="114">
+      <c r="N32" s="101">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="O32" s="114">
+      <c r="O32" s="101">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="P32" s="117" t="s">
+      <c r="P32" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="50">
+      <c r="Q32" s="46">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R32" s="115">
+      <c r="R32" s="102">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S32" s="115">
+      <c r="S32" s="102">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T32" s="115">
+      <c r="T32" s="102">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="U32" s="14"/>
-      <c r="V32" s="15"/>
-      <c r="W32" s="11"/>
+      <c r="V32" s="220"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="11"/>
     </row>
-    <row r="33" spans="1:23" ht="15.75" thickBot="1">
+    <row r="33" spans="1:24" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="209"/>
-      <c r="C33" s="90" t="s">
+      <c r="B33" s="200"/>
+      <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="182" t="s">
+      <c r="D33" s="168" t="s">
         <v>282</v>
       </c>
-      <c r="E33" s="91" t="s">
+      <c r="E33" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="G33" s="65" t="s">
+      <c r="G33" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="66" t="s">
+      <c r="H33" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="151" t="s">
+      <c r="I33" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="91" t="s">
+      <c r="J33" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="183">
+      <c r="K33" s="169">
         <v>100</v>
       </c>
-      <c r="L33" s="183">
+      <c r="L33" s="169">
         <v>100</v>
       </c>
-      <c r="M33" s="183">
+      <c r="M33" s="169">
         <v>2</v>
       </c>
-      <c r="N33" s="69">
+      <c r="N33" s="58">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O33" s="69">
+      <c r="O33" s="58">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="184" t="s">
+      <c r="P33" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="70">
+      <c r="Q33" s="59">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="121">
+      <c r="R33" s="108">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="121">
+      <c r="S33" s="108">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="121">
+      <c r="T33" s="108">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U33" s="16"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="11"/>
+      <c r="V33" s="222"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="11"/>
     </row>
-    <row r="34" spans="1:23" ht="15.75" thickBot="1">
+    <row r="34" spans="1:24" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="207" t="s">
+      <c r="B34" s="198" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="233" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="88" t="s">
+      <c r="D34" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="76" t="s">
+      <c r="E34" s="256" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="76" t="s">
+      <c r="F34" s="256" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="257" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="40" t="s">
+      <c r="H34" s="258" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="41" t="s">
+      <c r="I34" s="257" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="42" t="s">
+      <c r="J34" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="42">
+      <c r="K34" s="256">
         <v>11</v>
       </c>
-      <c r="L34" s="42">
+      <c r="L34" s="256">
         <v>42</v>
       </c>
-      <c r="M34" s="78">
+      <c r="M34" s="238">
         <v>2</v>
       </c>
-      <c r="N34" s="43">
+      <c r="N34" s="238">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="43">
+      <c r="O34" s="238">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="93" t="s">
+      <c r="P34" s="259" t="s">
         <v>16</v>
       </c>
-      <c r="Q34" s="44">
+      <c r="Q34" s="260">
         <v>0.64739999999999998</v>
       </c>
-      <c r="R34" s="45">
+      <c r="R34" s="242">
         <f t="shared" si="2"/>
         <v>7.1213999999999995</v>
       </c>
-      <c r="S34" s="45">
+      <c r="S34" s="242">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="45">
+      <c r="T34" s="242">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="12"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="11"/>
+      <c r="U34" s="261"/>
+      <c r="V34" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W34" s="262"/>
+      <c r="X34" s="11"/>
     </row>
-    <row r="35" spans="1:23" ht="26.25" thickBot="1">
+    <row r="35" spans="1:24" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="208"/>
-      <c r="C35" s="94" t="s">
+      <c r="B35" s="199"/>
+      <c r="C35" s="245" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="135" t="s">
+      <c r="D35" s="246" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="81" t="s">
+      <c r="E35" s="247" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="81" t="s">
+      <c r="F35" s="247" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="47" t="s">
+      <c r="G35" s="248" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="47" t="s">
+      <c r="H35" s="248" t="s">
         <v>134</v>
       </c>
-      <c r="I35" s="47" t="s">
+      <c r="I35" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="48" t="s">
+      <c r="J35" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="47">
+      <c r="K35" s="248">
         <v>6</v>
       </c>
-      <c r="L35" s="47">
+      <c r="L35" s="248">
         <v>21</v>
       </c>
-      <c r="M35" s="83">
+      <c r="M35" s="250">
         <v>1</v>
       </c>
-      <c r="N35" s="114">
+      <c r="N35" s="250">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="114">
+      <c r="O35" s="250">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="85" t="s">
+      <c r="P35" s="251" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="50">
+      <c r="Q35" s="252">
         <v>0.39889999999999998</v>
       </c>
-      <c r="R35" s="115">
+      <c r="R35" s="253">
         <f t="shared" si="2"/>
         <v>2.3933999999999997</v>
       </c>
-      <c r="S35" s="115">
+      <c r="S35" s="253">
         <v>0.33829999999999999</v>
       </c>
-      <c r="T35" s="115">
+      <c r="T35" s="253">
         <f t="shared" si="3"/>
         <v>7.1042999999999994</v>
       </c>
-      <c r="U35" s="14"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="11"/>
+      <c r="U35" s="254"/>
+      <c r="V35" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W35" s="255"/>
+      <c r="X35" s="11"/>
     </row>
-    <row r="36" spans="1:23" ht="15.75" thickBot="1">
+    <row r="36" spans="1:24" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="208"/>
-      <c r="C36" s="94" t="s">
+      <c r="B36" s="199"/>
+      <c r="C36" s="245" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="135" t="s">
+      <c r="D36" s="246" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="81" t="s">
+      <c r="E36" s="247" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="81" t="s">
+      <c r="F36" s="247" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="52" t="s">
+      <c r="G36" s="248" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="52" t="s">
+      <c r="H36" s="248" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="48" t="s">
+      <c r="I36" s="247" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="48" t="s">
+      <c r="J36" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="52">
+      <c r="K36" s="248">
         <v>6</v>
       </c>
-      <c r="L36" s="52">
+      <c r="L36" s="248">
         <v>21</v>
       </c>
-      <c r="M36" s="83">
+      <c r="M36" s="250">
         <v>1</v>
       </c>
-      <c r="N36" s="114">
+      <c r="N36" s="250">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="114">
+      <c r="O36" s="250">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="95" t="s">
+      <c r="P36" s="251" t="s">
         <v>135</v>
       </c>
-      <c r="Q36" s="71">
+      <c r="Q36" s="263">
         <v>8</v>
       </c>
-      <c r="R36" s="115">
+      <c r="R36" s="253">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="115">
+      <c r="S36" s="253">
         <v>8</v>
       </c>
-      <c r="T36" s="115">
+      <c r="T36" s="253">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="34"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="11"/>
+      <c r="U36" s="264"/>
+      <c r="V36" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W36" s="265"/>
+      <c r="X36" s="11"/>
     </row>
-    <row r="37" spans="1:23" ht="15.75" thickBot="1">
+    <row r="37" spans="1:24" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="208"/>
-      <c r="C37" s="100" t="s">
+      <c r="B37" s="199"/>
+      <c r="C37" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="137" t="s">
+      <c r="D37" s="124" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="101" t="s">
+      <c r="E37" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="101" t="s">
+      <c r="F37" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="G37" s="102" t="s">
+      <c r="G37" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="102" t="s">
+      <c r="H37" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="101" t="s">
+      <c r="I37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="101" t="s">
+      <c r="J37" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="102">
+      <c r="K37" s="89">
         <v>11</v>
       </c>
-      <c r="L37" s="102">
+      <c r="L37" s="89">
         <v>41</v>
       </c>
-      <c r="M37" s="103">
+      <c r="M37" s="90">
         <v>2</v>
       </c>
-      <c r="N37" s="103">
+      <c r="N37" s="90">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O37" s="114">
+      <c r="O37" s="101">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P37" s="104" t="s">
+      <c r="P37" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="Q37" s="118">
+      <c r="Q37" s="105">
         <v>10.18</v>
       </c>
-      <c r="R37" s="119">
+      <c r="R37" s="106">
         <f t="shared" si="2"/>
         <v>111.97999999999999</v>
       </c>
-      <c r="S37" s="119">
+      <c r="S37" s="106">
         <v>10.18</v>
       </c>
-      <c r="T37" s="115">
+      <c r="T37" s="102">
         <f t="shared" si="3"/>
         <v>417.38</v>
       </c>
-      <c r="U37" s="105" t="s">
+      <c r="U37" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="V37" s="106">
+      <c r="V37" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W37" s="93">
         <v>10.18</v>
       </c>
-      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
     </row>
-    <row r="38" spans="1:23" ht="15.75" thickBot="1">
+    <row r="38" spans="1:24" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="208"/>
-      <c r="C38" s="94" t="s">
+      <c r="B38" s="199"/>
+      <c r="C38" s="81" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="135" t="s">
+      <c r="D38" s="122" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="81" t="s">
+      <c r="E38" s="70" t="s">
         <v>209</v>
       </c>
-      <c r="F38" s="81" t="s">
+      <c r="F38" s="70" t="s">
         <v>177</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="48" t="s">
         <v>210</v>
       </c>
-      <c r="H38" s="52" t="s">
+      <c r="H38" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="I38" s="47" t="s">
+      <c r="I38" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="48" t="s">
+      <c r="J38" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="52">
+      <c r="K38" s="48">
         <v>6</v>
       </c>
-      <c r="L38" s="52">
+      <c r="L38" s="48">
         <v>21</v>
       </c>
-      <c r="M38" s="83">
+      <c r="M38" s="72">
         <v>1</v>
       </c>
-      <c r="N38" s="114">
+      <c r="N38" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O38" s="114">
+      <c r="O38" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P38" s="107" t="s">
+      <c r="P38" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="Q38" s="50">
+      <c r="Q38" s="46">
         <v>2.3479000000000001</v>
       </c>
-      <c r="R38" s="115">
+      <c r="R38" s="102">
         <f t="shared" si="2"/>
         <v>14.087400000000001</v>
       </c>
-      <c r="S38" s="115">
+      <c r="S38" s="102">
         <v>2.3479000000000001</v>
       </c>
-      <c r="T38" s="115">
+      <c r="T38" s="102">
         <f t="shared" si="3"/>
         <v>49.305900000000001</v>
       </c>
-      <c r="U38" s="22"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="11"/>
+      <c r="U38" s="21"/>
+      <c r="V38" s="224"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="11"/>
     </row>
-    <row r="39" spans="1:23" ht="15.75" thickBot="1">
+    <row r="39" spans="1:24" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="208"/>
-      <c r="C39" s="94" t="s">
+      <c r="B39" s="199"/>
+      <c r="C39" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="135" t="s">
+      <c r="D39" s="122" t="s">
         <v>179</v>
       </c>
-      <c r="E39" s="81" t="s">
+      <c r="E39" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="F39" s="81" t="s">
+      <c r="F39" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="52" t="s">
+      <c r="H39" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="I39" s="47" t="s">
+      <c r="I39" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="48" t="s">
+      <c r="J39" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="52">
+      <c r="K39" s="48">
         <v>6</v>
       </c>
-      <c r="L39" s="52">
+      <c r="L39" s="48">
         <v>21</v>
       </c>
-      <c r="M39" s="83">
+      <c r="M39" s="72">
         <v>1</v>
       </c>
-      <c r="N39" s="114">
+      <c r="N39" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O39" s="114">
+      <c r="O39" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="107" t="s">
+      <c r="P39" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="Q39" s="50">
+      <c r="Q39" s="46">
         <v>0.74660000000000004</v>
       </c>
-      <c r="R39" s="115">
+      <c r="R39" s="102">
         <f t="shared" si="2"/>
         <v>4.4796000000000005</v>
       </c>
-      <c r="S39" s="115">
+      <c r="S39" s="102">
         <v>0.60960000000000003</v>
       </c>
-      <c r="T39" s="115">
+      <c r="T39" s="102">
         <f t="shared" si="3"/>
         <v>12.801600000000001</v>
       </c>
-      <c r="U39" s="22"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="11"/>
+      <c r="U39" s="21"/>
+      <c r="V39" s="224"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="11"/>
     </row>
-    <row r="40" spans="1:23" ht="15.75" thickBot="1">
+    <row r="40" spans="1:24" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="208"/>
-      <c r="C40" s="94" t="s">
+      <c r="B40" s="199"/>
+      <c r="C40" s="245" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="226" t="s">
+      <c r="D40" s="246" t="s">
         <v>273</v>
       </c>
-      <c r="E40" s="81" t="s">
+      <c r="E40" s="247" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="81" t="s">
+      <c r="F40" s="247" t="s">
         <v>274</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="248" t="s">
         <v>280</v>
       </c>
-      <c r="H40" s="52"/>
-      <c r="I40" s="47" t="s">
+      <c r="H40" s="248"/>
+      <c r="I40" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="48" t="s">
+      <c r="J40" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="52">
+      <c r="K40" s="248">
         <v>6</v>
       </c>
-      <c r="L40" s="52"/>
-      <c r="M40" s="83">
+      <c r="L40" s="248"/>
+      <c r="M40" s="250">
         <v>1</v>
       </c>
-      <c r="N40" s="114">
+      <c r="N40" s="250">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="114">
+      <c r="O40" s="250">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="95" t="s">
+      <c r="P40" s="251" t="s">
         <v>153</v>
       </c>
-      <c r="Q40" s="50">
+      <c r="Q40" s="252">
         <v>1.2</v>
       </c>
-      <c r="R40" s="115">
+      <c r="R40" s="253">
         <f t="shared" si="2"/>
         <v>7.1999999999999993</v>
       </c>
-      <c r="S40" s="115">
+      <c r="S40" s="253">
         <v>1.2</v>
       </c>
-      <c r="T40" s="115">
+      <c r="T40" s="253">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U40" s="22" t="s">
+      <c r="U40" s="277" t="s">
         <v>281</v>
       </c>
-      <c r="V40" s="15"/>
-      <c r="W40" s="11"/>
+      <c r="V40" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W40" s="255"/>
+      <c r="X40" s="11"/>
     </row>
-    <row r="41" spans="1:23" ht="15.75" thickBot="1">
+    <row r="41" spans="1:24" ht="15.75" thickBot="1">
       <c r="A41" s="6"/>
-      <c r="B41" s="208"/>
-      <c r="C41" s="110" t="s">
+      <c r="B41" s="199"/>
+      <c r="C41" s="266" t="s">
         <v>285</v>
       </c>
-      <c r="D41" s="221" t="s">
+      <c r="D41" s="267" t="s">
         <v>283</v>
       </c>
-      <c r="E41" s="86" t="s">
+      <c r="E41" s="268" t="s">
         <v>286</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="269" t="s">
         <v>287</v>
       </c>
-      <c r="G41" s="54" t="s">
+      <c r="G41" s="270" t="s">
         <v>288</v>
       </c>
-      <c r="H41" s="54" t="s">
+      <c r="H41" s="270" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="47" t="s">
+      <c r="I41" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="48" t="s">
+      <c r="J41" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="54">
+      <c r="K41" s="270">
         <v>10</v>
       </c>
-      <c r="L41" s="54">
+      <c r="L41" s="270">
         <v>30</v>
       </c>
-      <c r="M41" s="218">
+      <c r="M41" s="271">
         <v>1</v>
       </c>
-      <c r="N41" s="123">
+      <c r="N41" s="271">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="123">
+      <c r="O41" s="271">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="225" t="s">
+      <c r="P41" s="272" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="57">
+      <c r="Q41" s="273">
         <v>1</v>
       </c>
-      <c r="R41" s="124">
+      <c r="R41" s="274">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="124">
+      <c r="S41" s="274">
         <v>1</v>
       </c>
-      <c r="T41" s="115">
+      <c r="T41" s="253">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="220"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="11"/>
+      <c r="U41" s="275"/>
+      <c r="V41" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W41" s="276"/>
+      <c r="X41" s="11"/>
     </row>
-    <row r="42" spans="1:23" ht="26.25" thickBot="1">
+    <row r="42" spans="1:24" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>39</v>
       </c>
-      <c r="B42" s="209"/>
-      <c r="C42" s="90" t="s">
+      <c r="B42" s="200"/>
+      <c r="C42" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="136" t="s">
+      <c r="D42" s="123" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="91" t="s">
+      <c r="E42" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="F42" s="91" t="s">
+      <c r="F42" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="G42" s="68" t="s">
+      <c r="G42" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="H42" s="68" t="s">
+      <c r="H42" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="I42" s="68" t="s">
+      <c r="I42" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="68" t="s">
+      <c r="J42" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="65">
+      <c r="K42" s="54">
         <v>10</v>
       </c>
-      <c r="L42" s="65">
+      <c r="L42" s="54">
         <v>30</v>
       </c>
-      <c r="M42" s="96">
+      <c r="M42" s="83">
         <v>1</v>
       </c>
-      <c r="N42" s="69">
+      <c r="N42" s="58">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="69">
+      <c r="O42" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="97" t="s">
+      <c r="P42" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="70">
+      <c r="Q42" s="59">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="R42" s="121">
+      <c r="R42" s="108">
         <f t="shared" si="2"/>
         <v>0.53500000000000003</v>
       </c>
-      <c r="S42" s="121">
+      <c r="S42" s="108">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="T42" s="121">
+      <c r="T42" s="108">
         <f t="shared" si="3"/>
         <v>1.605</v>
       </c>
-      <c r="U42" s="23"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="11"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="225"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="11"/>
     </row>
-    <row r="43" spans="1:23" ht="15.75" thickBot="1">
+    <row r="43" spans="1:24" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>40</v>
       </c>
-      <c r="B43" s="207" t="s">
+      <c r="B43" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="87" t="s">
+      <c r="C43" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="88" t="s">
+      <c r="D43" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="76" t="s">
+      <c r="E43" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="92" t="s">
+      <c r="F43" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="43" t="s">
+      <c r="G43" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H43" s="43" t="s">
+      <c r="H43" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="I43" s="42" t="s">
+      <c r="I43" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="J43" s="42" t="s">
+      <c r="J43" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="72">
+      <c r="K43" s="61">
         <v>50</v>
       </c>
-      <c r="L43" s="72">
+      <c r="L43" s="61">
         <v>50</v>
       </c>
-      <c r="M43" s="73">
+      <c r="M43" s="62">
         <v>1</v>
       </c>
-      <c r="N43" s="43">
+      <c r="N43" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="43">
+      <c r="O43" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P43" s="98" t="s">
+      <c r="P43" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="44">
+      <c r="Q43" s="40">
         <v>1.4E-2</v>
       </c>
-      <c r="R43" s="45">
+      <c r="R43" s="41">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="S43" s="45">
+      <c r="S43" s="41">
         <v>1.4E-2</v>
       </c>
-      <c r="T43" s="45">
+      <c r="T43" s="41">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="U43" s="24"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="11"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="226"/>
+      <c r="W43" s="13"/>
+      <c r="X43" s="11"/>
     </row>
-    <row r="44" spans="1:23" ht="26.25" thickBot="1">
+    <row r="44" spans="1:24" ht="26.25" thickBot="1">
       <c r="A44" s="6">
         <v>41</v>
       </c>
-      <c r="B44" s="208"/>
-      <c r="C44" s="94" t="s">
+      <c r="B44" s="199"/>
+      <c r="C44" s="81" t="s">
         <v>292</v>
       </c>
-      <c r="D44" s="135" t="s">
+      <c r="D44" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="76" t="s">
+      <c r="E44" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="81" t="s">
+      <c r="F44" s="70" t="s">
         <v>293</v>
       </c>
-      <c r="G44" s="48" t="s">
+      <c r="G44" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="H44" s="48" t="s">
+      <c r="H44" s="44" t="s">
         <v>295</v>
       </c>
-      <c r="I44" s="48" t="s">
+      <c r="I44" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="J44" s="48" t="s">
+      <c r="J44" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="48">
+      <c r="K44" s="44">
         <v>10</v>
       </c>
-      <c r="L44" s="48">
+      <c r="L44" s="44">
         <v>30</v>
       </c>
-      <c r="M44" s="74">
+      <c r="M44" s="63">
         <v>1</v>
       </c>
-      <c r="N44" s="114">
+      <c r="N44" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O44" s="114">
+      <c r="O44" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="107" t="s">
+      <c r="P44" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="71">
+      <c r="Q44" s="60">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R44" s="115">
+      <c r="R44" s="102">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S44" s="115">
+      <c r="S44" s="102">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="T44" s="115">
+      <c r="T44" s="102">
         <f t="shared" si="3"/>
         <v>1.77</v>
       </c>
-      <c r="U44" s="28"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="11"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="227"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="11"/>
     </row>
-    <row r="45" spans="1:23" ht="15.75" thickBot="1">
+    <row r="45" spans="1:24" ht="15.75" thickBot="1">
       <c r="A45" s="6">
         <v>42</v>
       </c>
-      <c r="B45" s="208"/>
-      <c r="C45" s="94" t="s">
+      <c r="B45" s="199"/>
+      <c r="C45" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="135" t="s">
+      <c r="D45" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="81" t="s">
+      <c r="E45" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="99" t="s">
+      <c r="F45" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="G45" s="48" t="s">
+      <c r="G45" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="48" t="s">
+      <c r="H45" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="I45" s="48" t="s">
+      <c r="I45" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="J45" s="48" t="s">
+      <c r="J45" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="48">
+      <c r="K45" s="44">
         <v>50</v>
       </c>
-      <c r="L45" s="48">
+      <c r="L45" s="44">
         <v>50</v>
       </c>
-      <c r="M45" s="74">
+      <c r="M45" s="63">
         <v>1</v>
       </c>
-      <c r="N45" s="114">
+      <c r="N45" s="101">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O45" s="114">
+      <c r="O45" s="101">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="95" t="s">
+      <c r="P45" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="50">
+      <c r="Q45" s="46">
         <v>1.26E-2</v>
       </c>
-      <c r="R45" s="115">
+      <c r="R45" s="102">
         <f t="shared" si="2"/>
         <v>0.63</v>
       </c>
-      <c r="S45" s="115">
+      <c r="S45" s="102">
         <v>1.26E-2</v>
       </c>
-      <c r="T45" s="115">
+      <c r="T45" s="102">
         <f t="shared" si="3"/>
         <v>0.63</v>
       </c>
-      <c r="U45" s="29"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="11"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="228"/>
+      <c r="W45" s="15"/>
+      <c r="X45" s="11"/>
     </row>
-    <row r="46" spans="1:23" ht="15.75" thickBot="1">
+    <row r="46" spans="1:24" ht="15.75" thickBot="1">
       <c r="A46" s="6">
         <v>43</v>
       </c>
-      <c r="B46" s="208"/>
-      <c r="C46" s="94" t="s">
+      <c r="B46" s="199"/>
+      <c r="C46" s="245" t="s">
         <v>275</v>
       </c>
-      <c r="D46" s="226" t="s">
+      <c r="D46" s="246" t="s">
         <v>276</v>
       </c>
-      <c r="E46" s="81" t="s">
+      <c r="E46" s="247" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="81" t="s">
+      <c r="F46" s="247" t="s">
         <v>277</v>
       </c>
-      <c r="G46" s="48" t="s">
+      <c r="G46" s="247" t="s">
         <v>278</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="247" t="s">
         <v>279</v>
       </c>
-      <c r="I46" s="48" t="s">
+      <c r="I46" s="247" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="48" t="s">
+      <c r="J46" s="247" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="48">
+      <c r="K46" s="247">
         <v>5</v>
       </c>
-      <c r="L46" s="48">
+      <c r="L46" s="247">
         <v>25</v>
       </c>
-      <c r="M46" s="74">
+      <c r="M46" s="250">
         <v>1</v>
       </c>
-      <c r="N46" s="114">
+      <c r="N46" s="250">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="114">
+      <c r="O46" s="250">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="107" t="s">
+      <c r="P46" s="278" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="50">
+      <c r="Q46" s="252">
         <v>0.1002</v>
       </c>
-      <c r="R46" s="115">
+      <c r="R46" s="253">
         <f t="shared" si="2"/>
         <v>0.501</v>
       </c>
-      <c r="S46" s="115">
+      <c r="S46" s="253">
         <v>0.1002</v>
       </c>
-      <c r="T46" s="115">
+      <c r="T46" s="253">
         <f t="shared" si="3"/>
         <v>2.5049999999999999</v>
       </c>
-      <c r="U46" s="29"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="11"/>
+      <c r="U46" s="279"/>
+      <c r="V46" s="217" t="s">
+        <v>296</v>
+      </c>
+      <c r="W46" s="255"/>
+      <c r="X46" s="11"/>
     </row>
-    <row r="47" spans="1:23" ht="15.75" thickBot="1">
+    <row r="47" spans="1:24" ht="15.75" thickBot="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="208"/>
-      <c r="C47" s="110" t="s">
+      <c r="B47" s="199"/>
+      <c r="C47" s="97" t="s">
         <v>289</v>
       </c>
-      <c r="D47" s="86" t="s">
+      <c r="D47" s="75" t="s">
         <v>284</v>
       </c>
-      <c r="E47" s="81" t="s">
+      <c r="E47" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="224">
+      <c r="F47" s="183">
         <v>61300611121</v>
       </c>
-      <c r="G47" s="163" t="s">
+      <c r="G47" s="150" t="s">
         <v>290</v>
       </c>
-      <c r="H47" s="163" t="s">
+      <c r="H47" s="150" t="s">
         <v>291</v>
       </c>
-      <c r="I47" s="163" t="s">
+      <c r="I47" s="150" t="s">
         <v>291</v>
       </c>
-      <c r="J47" s="48" t="s">
+      <c r="J47" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="163">
+      <c r="K47" s="150">
         <v>20</v>
       </c>
-      <c r="L47" s="163">
+      <c r="L47" s="150">
         <v>40</v>
       </c>
-      <c r="M47" s="222">
+      <c r="M47" s="181">
         <v>1</v>
       </c>
-      <c r="N47" s="123">
+      <c r="N47" s="110">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="123">
+      <c r="O47" s="110">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="219" t="s">
+      <c r="P47" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="57">
+      <c r="Q47" s="53">
         <v>0.03</v>
       </c>
-      <c r="R47" s="115">
+      <c r="R47" s="102">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="S47" s="124">
+      <c r="S47" s="111">
         <v>0.03</v>
       </c>
-      <c r="T47" s="115">
+      <c r="T47" s="102">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="U47" s="223"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="11"/>
+      <c r="U47" s="182"/>
+      <c r="V47" s="229"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="11"/>
     </row>
-    <row r="48" spans="1:23" ht="115.5" thickBot="1">
+    <row r="48" spans="1:24" ht="115.5" thickBot="1">
       <c r="A48" s="6">
         <v>44</v>
       </c>
-      <c r="B48" s="209"/>
-      <c r="C48" s="126" t="s">
+      <c r="B48" s="200"/>
+      <c r="C48" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="127" t="s">
+      <c r="D48" s="114" t="s">
         <v>244</v>
       </c>
-      <c r="E48" s="128" t="s">
+      <c r="E48" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="128" t="s">
+      <c r="F48" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="129" t="s">
+      <c r="G48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="H48" s="129"/>
-      <c r="I48" s="130"/>
-      <c r="J48" s="130" t="s">
+      <c r="H48" s="116"/>
+      <c r="I48" s="117"/>
+      <c r="J48" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="130" t="s">
+      <c r="K48" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="L48" s="130" t="s">
+      <c r="L48" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="131">
+      <c r="M48" s="118">
         <v>53</v>
       </c>
-      <c r="N48" s="132">
+      <c r="N48" s="119">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O48" s="69">
+      <c r="O48" s="58">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="129" t="s">
+      <c r="P48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="Q48" s="130" t="s">
+      <c r="Q48" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="130" t="s">
+      <c r="R48" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="S48" s="130" t="s">
+      <c r="S48" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="T48" s="130" t="s">
+      <c r="T48" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="U48" s="133" t="s">
+      <c r="U48" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="V48" s="134"/>
-      <c r="W48" s="11"/>
+      <c r="V48" s="230"/>
+      <c r="W48" s="121"/>
+      <c r="X48" s="11"/>
     </row>
-    <row r="49" spans="1:23" ht="26.25" thickBot="1">
+    <row r="49" spans="1:24" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>45</v>
       </c>
-      <c r="B49" s="215" t="s">
+      <c r="B49" s="206" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="186" t="s">
+      <c r="C49" s="172" t="s">
         <v>252</v>
       </c>
-      <c r="D49" s="187" t="s">
+      <c r="D49" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="187" t="s">
+      <c r="E49" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="187" t="s">
+      <c r="F49" s="173" t="s">
         <v>251</v>
       </c>
-      <c r="G49" s="187" t="s">
+      <c r="G49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="H49" s="187" t="s">
+      <c r="H49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="I49" s="187" t="s">
+      <c r="I49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="187" t="s">
+      <c r="J49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="K49" s="187" t="s">
+      <c r="K49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="187" t="s">
+      <c r="L49" s="173" t="s">
         <v>144</v>
       </c>
-      <c r="M49" s="185">
+      <c r="M49" s="171">
         <v>1</v>
       </c>
-      <c r="N49" s="49">
+      <c r="N49" s="45">
         <f>M49*5</f>
         <v>5</v>
       </c>
-      <c r="O49" s="49">
+      <c r="O49" s="45">
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="188" t="s">
+      <c r="P49" s="174" t="s">
         <v>245</v>
       </c>
-      <c r="Q49" s="189">
+      <c r="Q49" s="175">
         <v>0.2</v>
       </c>
-      <c r="R49" s="190">
+      <c r="R49" s="176">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="189">
+      <c r="S49" s="175">
         <v>0.2</v>
       </c>
-      <c r="T49" s="51">
+      <c r="T49" s="47">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="191"/>
-      <c r="V49" s="193"/>
-      <c r="W49" s="11"/>
+      <c r="U49" s="177"/>
+      <c r="V49" s="231"/>
+      <c r="W49" s="179"/>
+      <c r="X49" s="11"/>
     </row>
-    <row r="50" spans="1:23" ht="15.75" thickBot="1">
-      <c r="A50" s="19">
+    <row r="50" spans="1:24" ht="15.75" thickBot="1">
+      <c r="A50" s="18">
         <v>46</v>
       </c>
-      <c r="B50" s="216"/>
-      <c r="C50" s="145" t="s">
+      <c r="B50" s="207"/>
+      <c r="C50" s="132" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="146" t="s">
+      <c r="D50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="146" t="s">
+      <c r="E50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="147" t="s">
+      <c r="F50" s="134" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="146" t="s">
+      <c r="G50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="146" t="s">
+      <c r="H50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="146" t="s">
+      <c r="I50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="146" t="s">
+      <c r="J50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="146" t="s">
+      <c r="K50" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="146" t="s">
+      <c r="L50" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="138">
+      <c r="M50" s="125">
         <v>1</v>
       </c>
-      <c r="N50" s="138">
+      <c r="N50" s="125">
         <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
-      <c r="O50" s="69">
+      <c r="O50" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="155" t="s">
+      <c r="P50" s="142" t="s">
         <v>245</v>
       </c>
-      <c r="Q50" s="139">
+      <c r="Q50" s="126">
         <v>3.35</v>
       </c>
-      <c r="R50" s="140">
+      <c r="R50" s="127">
         <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="140">
+      <c r="S50" s="127">
         <v>3.35</v>
       </c>
-      <c r="T50" s="121">
+      <c r="T50" s="108">
         <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U50" s="133" t="s">
+      <c r="U50" s="120" t="s">
         <v>149</v>
       </c>
-      <c r="V50" s="148"/>
-      <c r="W50" s="11"/>
+      <c r="V50" s="230"/>
+      <c r="W50" s="135"/>
+      <c r="X50" s="11"/>
     </row>
-    <row r="51" spans="1:23" ht="15.75">
+    <row r="51" spans="1:24" ht="15.75">
       <c r="A51" s="1"/>
-      <c r="C51" s="25"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="8"/>
       <c r="E51" s="7"/>
       <c r="G51" s="7"/>
@@ -5884,27 +6196,28 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="203" t="s">
+      <c r="M51" s="194" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="204"/>
-      <c r="O51" s="204"/>
-      <c r="P51" s="204"/>
-      <c r="Q51" s="21"/>
-      <c r="R51" s="157">
+      <c r="N51" s="195"/>
+      <c r="O51" s="195"/>
+      <c r="P51" s="195"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="144">
         <f>SUM(R3:R49)</f>
         <v>382.15120000000002</v>
       </c>
-      <c r="S51" s="157"/>
-      <c r="T51" s="113">
+      <c r="S51" s="144"/>
+      <c r="T51" s="100">
         <f>SUM(T3:T49)</f>
         <v>1358.7949000000003</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
-      <c r="W51" s="11"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="11"/>
     </row>
-    <row r="52" spans="1:23" ht="16.5" thickBot="1">
+    <row r="52" spans="1:24" ht="16.5" thickBot="1">
       <c r="A52" s="1"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -5912,27 +6225,28 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="205" t="s">
+      <c r="M52" s="196" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="206"/>
-      <c r="O52" s="206"/>
-      <c r="P52" s="206"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="160">
+      <c r="N52" s="197"/>
+      <c r="O52" s="197"/>
+      <c r="P52" s="197"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="147">
         <f>R51/5</f>
         <v>76.430239999999998</v>
       </c>
-      <c r="S52" s="160"/>
-      <c r="T52" s="38">
+      <c r="S52" s="147"/>
+      <c r="T52" s="34">
         <f>T51/20</f>
         <v>67.939745000000016</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
-      <c r="W52" s="11"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="11"/>
     </row>
-    <row r="53" spans="1:23" ht="15.75">
+    <row r="53" spans="1:24" ht="15.75">
       <c r="A53" s="1"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -5940,25 +6254,26 @@
       <c r="I53" s="2"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="33"/>
-      <c r="N53" s="194" t="s">
+      <c r="M53" s="31"/>
+      <c r="N53" s="185" t="s">
         <v>147</v>
       </c>
-      <c r="O53" s="195"/>
-      <c r="P53" s="196"/>
-      <c r="Q53" s="156"/>
-      <c r="R53" s="158">
+      <c r="O53" s="186"/>
+      <c r="P53" s="187"/>
+      <c r="Q53" s="143"/>
+      <c r="R53" s="145">
         <v>3</v>
       </c>
-      <c r="S53" s="158"/>
-      <c r="T53" s="159">
+      <c r="S53" s="145"/>
+      <c r="T53" s="146">
         <v>3</v>
       </c>
       <c r="U53" s="7"/>
       <c r="V53" s="7"/>
-      <c r="W53" s="11"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="11"/>
     </row>
-    <row r="54" spans="1:23" ht="15.75">
+    <row r="54" spans="1:24" ht="15.75">
       <c r="A54" s="1"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -5966,134 +6281,137 @@
       <c r="I54" s="2"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="212" t="s">
+      <c r="M54" s="31"/>
+      <c r="N54" s="203" t="s">
         <v>253</v>
       </c>
-      <c r="O54" s="213"/>
-      <c r="P54" s="214"/>
-      <c r="Q54" s="154"/>
-      <c r="R54" s="153">
+      <c r="O54" s="204"/>
+      <c r="P54" s="205"/>
+      <c r="Q54" s="141"/>
+      <c r="R54" s="140">
         <v>22.78</v>
       </c>
-      <c r="S54" s="153"/>
-      <c r="T54" s="161">
+      <c r="S54" s="140"/>
+      <c r="T54" s="148">
         <v>90.99</v>
       </c>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
-      <c r="W54" s="11"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="11"/>
     </row>
-    <row r="55" spans="1:23" ht="16.5" thickBot="1">
+    <row r="55" spans="1:24" ht="16.5" thickBot="1">
       <c r="A55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="197" t="s">
+      <c r="N55" s="188" t="s">
         <v>43</v>
       </c>
-      <c r="O55" s="198"/>
-      <c r="P55" s="199"/>
-      <c r="Q55" s="36"/>
-      <c r="R55" s="162">
+      <c r="O55" s="189"/>
+      <c r="P55" s="190"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="149">
         <f>SUM(R52:R54)</f>
         <v>102.21024</v>
       </c>
-      <c r="S55" s="162"/>
-      <c r="T55" s="37">
+      <c r="S55" s="149"/>
+      <c r="T55" s="33">
         <f>SUM(T52:T54)</f>
         <v>161.92974500000003</v>
       </c>
-      <c r="V55" s="11"/>
       <c r="W55" s="11"/>
+      <c r="X55" s="11"/>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:24">
       <c r="A56" s="1"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="G56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="V56" s="11"/>
+      <c r="N56" s="19"/>
+      <c r="O56" s="19"/>
       <c r="W56" s="11"/>
+      <c r="X56" s="11"/>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:24">
       <c r="A57" s="1"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="G57" s="2"/>
       <c r="I57" s="2"/>
-      <c r="V57" s="11"/>
       <c r="W57" s="11"/>
+      <c r="X57" s="11"/>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:24">
       <c r="A58" s="1"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="G58" s="2"/>
       <c r="I58" s="2"/>
-      <c r="V58" s="11"/>
       <c r="W58" s="11"/>
+      <c r="X58" s="11"/>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:24">
       <c r="A59" s="1"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="G59" s="2"/>
       <c r="I59" s="2"/>
-      <c r="V59" s="11"/>
       <c r="W59" s="11"/>
+      <c r="X59" s="11"/>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:24">
       <c r="A60" s="1"/>
-      <c r="V60" s="11"/>
       <c r="W60" s="11"/>
+      <c r="X60" s="11"/>
     </row>
-    <row r="61" spans="1:23" ht="15.75" customHeight="1">
+    <row r="61" spans="1:24" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="V61" s="11"/>
       <c r="W61" s="11"/>
+      <c r="X61" s="11"/>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:24">
       <c r="A62" s="1"/>
-      <c r="V62" s="11"/>
       <c r="W62" s="11"/>
+      <c r="X62" s="11"/>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:24">
       <c r="A63" s="1"/>
-      <c r="V63" s="11"/>
       <c r="W63" s="11"/>
+      <c r="X63" s="11"/>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:24">
       <c r="A64" s="1"/>
-      <c r="V64" s="11"/>
       <c r="W64" s="11"/>
+      <c r="X64" s="11"/>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:24">
       <c r="A65" s="1"/>
-      <c r="V65" s="11"/>
       <c r="W65" s="11"/>
+      <c r="X65" s="11"/>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:24">
       <c r="A66" s="1"/>
-      <c r="V66" s="11"/>
       <c r="W66" s="11"/>
+      <c r="X66" s="11"/>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:24">
       <c r="H67" s="9"/>
       <c r="U67" s="10"/>
+      <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:24">
       <c r="H68" s="9"/>
       <c r="U68" s="10"/>
+      <c r="V68" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="N53:P53"/>
     <mergeCell ref="N55:P55"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:W1"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="B29:B33"/>
@@ -6107,7 +6425,7 @@
     <mergeCell ref="B20:B23"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="U44">
+  <conditionalFormatting sqref="U44:V44">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -6328,7 +6646,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>U44</xm:sqref>
+          <xm:sqref>U44:V44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{73D72061-44BE-43BF-B86A-016273A3FADD}">

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="298">
   <si>
     <t>S. No.</t>
   </si>
@@ -720,9 +720,6 @@
     <t>33nF</t>
   </si>
   <si>
-    <t>C48260</t>
-  </si>
-  <si>
     <t>FIXED IND 3.3NH 1A 120 MOHM SMD</t>
   </si>
   <si>
@@ -929,12 +926,15 @@
   </si>
   <si>
     <t>Remarks (Faizan)</t>
+  </si>
+  <si>
+    <t>Supplier / Hanson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -1125,7 +1125,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,6 +1174,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="36">
     <border>
@@ -1653,7 +1659,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="280">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1959,9 +1965,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2194,78 +2197,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2477,6 +2408,84 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2784,31 +2793,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickBot="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="261" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="193"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
+      <c r="K1" s="262"/>
+      <c r="L1" s="262"/>
+      <c r="M1" s="262"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="262"/>
+      <c r="P1" s="262"/>
+      <c r="Q1" s="262"/>
+      <c r="R1" s="262"/>
+      <c r="S1" s="262"/>
+      <c r="T1" s="262"/>
+      <c r="U1" s="262"/>
+      <c r="V1" s="262"/>
+      <c r="W1" s="263"/>
     </row>
     <row r="2" spans="1:24" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2844,8 +2853,8 @@
       <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="139" t="s">
-        <v>249</v>
+      <c r="L2" s="138" t="s">
+        <v>248</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
@@ -2854,7 +2863,7 @@
         <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>11</v>
@@ -2866,16 +2875,16 @@
         <v>46</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="T2" s="138" t="s">
         <v>247</v>
-      </c>
-      <c r="T2" s="139" t="s">
-        <v>248</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="139" t="s">
-        <v>297</v>
+      <c r="V2" s="138" t="s">
+        <v>296</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>13</v>
@@ -2885,13 +2894,13 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="268" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="131" t="s">
+      <c r="D3" s="130" t="s">
         <v>159</v>
       </c>
       <c r="E3" s="66" t="s">
@@ -2947,14 +2956,14 @@
         <v>1.3599999999999999</v>
       </c>
       <c r="U3" s="12"/>
-      <c r="V3" s="219"/>
+      <c r="V3" s="194"/>
       <c r="W3" s="13"/>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="199"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="69" t="s">
         <v>21</v>
       </c>
@@ -3014,18 +3023,18 @@
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
-      <c r="V4" s="220"/>
+      <c r="V4" s="195"/>
       <c r="W4" s="15"/>
     </row>
     <row r="5" spans="1:24" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="199"/>
+      <c r="B5" s="269"/>
       <c r="C5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="130" t="s">
+      <c r="D5" s="129" t="s">
         <v>154</v>
       </c>
       <c r="E5" s="70" t="s">
@@ -3081,7 +3090,7 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="U5" s="14"/>
-      <c r="V5" s="220"/>
+      <c r="V5" s="195"/>
       <c r="W5" s="15"/>
       <c r="X5" s="11"/>
     </row>
@@ -3089,7 +3098,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="199"/>
+      <c r="B6" s="269"/>
       <c r="C6" s="69" t="s">
         <v>55</v>
       </c>
@@ -3149,7 +3158,7 @@
         <v>0.67999999999999994</v>
       </c>
       <c r="U6" s="14"/>
-      <c r="V6" s="220"/>
+      <c r="V6" s="195"/>
       <c r="W6" s="15"/>
       <c r="X6" s="11"/>
     </row>
@@ -3157,7 +3166,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="199"/>
+      <c r="B7" s="269"/>
       <c r="C7" s="69" t="s">
         <v>155</v>
       </c>
@@ -3217,7 +3226,7 @@
         <v>0.13</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="220"/>
+      <c r="V7" s="195"/>
       <c r="W7" s="15"/>
       <c r="X7" s="11"/>
     </row>
@@ -3225,11 +3234,11 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="199"/>
+      <c r="B8" s="269"/>
       <c r="C8" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="130" t="s">
+      <c r="D8" s="129" t="s">
         <v>214</v>
       </c>
       <c r="E8" s="70" t="s">
@@ -3285,7 +3294,7 @@
         <v>3.4799999999999995</v>
       </c>
       <c r="U8" s="26"/>
-      <c r="V8" s="221"/>
+      <c r="V8" s="196"/>
       <c r="W8" s="15"/>
       <c r="X8" s="11"/>
     </row>
@@ -3293,7 +3302,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="199"/>
+      <c r="B9" s="269"/>
       <c r="C9" s="69" t="s">
         <v>59</v>
       </c>
@@ -3353,7 +3362,7 @@
         <v>1.1459999999999999</v>
       </c>
       <c r="U9" s="14"/>
-      <c r="V9" s="220"/>
+      <c r="V9" s="195"/>
       <c r="W9" s="15"/>
       <c r="X9" s="11"/>
     </row>
@@ -3361,7 +3370,7 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="199"/>
+      <c r="B10" s="269"/>
       <c r="C10" s="69" t="s">
         <v>62</v>
       </c>
@@ -3421,7 +3430,7 @@
         <v>0.64</v>
       </c>
       <c r="U10" s="14"/>
-      <c r="V10" s="220"/>
+      <c r="V10" s="195"/>
       <c r="W10" s="15"/>
       <c r="X10" s="11"/>
     </row>
@@ -3429,11 +3438,11 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="199"/>
+      <c r="B11" s="269"/>
       <c r="C11" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="130" t="s">
+      <c r="D11" s="129" t="s">
         <v>66</v>
       </c>
       <c r="E11" s="70" t="s">
@@ -3489,7 +3498,7 @@
         <v>5.2850000000000001</v>
       </c>
       <c r="U11" s="14"/>
-      <c r="V11" s="220"/>
+      <c r="V11" s="195"/>
       <c r="W11" s="15"/>
       <c r="X11" s="11"/>
     </row>
@@ -3497,7 +3506,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="199"/>
+      <c r="B12" s="269"/>
       <c r="C12" s="69" t="s">
         <v>160</v>
       </c>
@@ -3557,7 +3566,7 @@
         <v>0.23500000000000001</v>
       </c>
       <c r="U12" s="14"/>
-      <c r="V12" s="220"/>
+      <c r="V12" s="195"/>
       <c r="W12" s="15"/>
       <c r="X12" s="11"/>
     </row>
@@ -3565,11 +3574,11 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="199"/>
+      <c r="B13" s="269"/>
       <c r="C13" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="130" t="s">
+      <c r="D13" s="129" t="s">
         <v>164</v>
       </c>
       <c r="E13" s="70" t="s">
@@ -3625,7 +3634,7 @@
         <v>0.11</v>
       </c>
       <c r="U13" s="14"/>
-      <c r="V13" s="220"/>
+      <c r="V13" s="195"/>
       <c r="W13" s="15"/>
       <c r="X13" s="11"/>
     </row>
@@ -3633,7 +3642,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="199"/>
+      <c r="B14" s="269"/>
       <c r="C14" s="69" t="s">
         <v>215</v>
       </c>
@@ -3693,7 +3702,7 @@
         <v>0.37</v>
       </c>
       <c r="U14" s="14"/>
-      <c r="V14" s="220"/>
+      <c r="V14" s="195"/>
       <c r="W14" s="15"/>
       <c r="X14" s="11"/>
     </row>
@@ -3701,7 +3710,7 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="199"/>
+      <c r="B15" s="269"/>
       <c r="C15" s="69" t="s">
         <v>218</v>
       </c>
@@ -3761,7 +3770,7 @@
         <v>0.255</v>
       </c>
       <c r="U15" s="14"/>
-      <c r="V15" s="220"/>
+      <c r="V15" s="195"/>
       <c r="W15" s="15"/>
       <c r="X15" s="11"/>
     </row>
@@ -3769,30 +3778,30 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="199"/>
+      <c r="B16" s="269"/>
       <c r="C16" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" s="151" t="s">
         <v>254</v>
-      </c>
-      <c r="D16" s="152" t="s">
-        <v>255</v>
       </c>
       <c r="E16" s="71" t="s">
         <v>49</v>
       </c>
       <c r="F16" s="71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G16" s="48" t="s">
         <v>114</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I16" s="43" t="s">
         <v>40</v>
       </c>
       <c r="J16" s="70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K16" s="48">
         <v>50</v>
@@ -3829,7 +3838,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="U16" s="14"/>
-      <c r="V16" s="220"/>
+      <c r="V16" s="195"/>
       <c r="W16" s="15"/>
       <c r="X16" s="11"/>
     </row>
@@ -3837,30 +3846,30 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="200"/>
-      <c r="C17" s="109" t="s">
+      <c r="B17" s="270"/>
+      <c r="C17" s="108" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="152" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="153" t="s">
+      <c r="E17" s="127" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="127" t="s">
         <v>258</v>
-      </c>
-      <c r="E17" s="128" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="128" t="s">
-        <v>259</v>
       </c>
       <c r="G17" s="54" t="s">
         <v>114</v>
       </c>
       <c r="H17" s="55" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I17" s="56" t="s">
         <v>39</v>
       </c>
       <c r="J17" s="79" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K17" s="54">
         <v>50</v>
@@ -3879,25 +3888,25 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="107" t="s">
+      <c r="P17" s="106" t="s">
         <v>16</v>
       </c>
       <c r="Q17" s="59">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R17" s="108">
+      <c r="R17" s="107">
         <f t="shared" si="2"/>
         <v>0.38500000000000001</v>
       </c>
-      <c r="S17" s="108">
+      <c r="S17" s="107">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T17" s="108">
+      <c r="T17" s="107">
         <f>S17*L17</f>
         <v>0.38500000000000001</v>
       </c>
       <c r="U17" s="16"/>
-      <c r="V17" s="222"/>
+      <c r="V17" s="197"/>
       <c r="W17" s="17"/>
       <c r="X17" s="11"/>
     </row>
@@ -3905,13 +3914,13 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="201" t="s">
+      <c r="B18" s="271" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="163" t="s">
+      <c r="C18" s="162" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="131" t="s">
+      <c r="D18" s="130" t="s">
         <v>183</v>
       </c>
       <c r="E18" s="65" t="s">
@@ -3949,7 +3958,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="129" t="s">
+      <c r="P18" s="128" t="s">
         <v>16</v>
       </c>
       <c r="Q18" s="40">
@@ -3967,7 +3976,7 @@
         <v>1.851</v>
       </c>
       <c r="U18" s="12"/>
-      <c r="V18" s="219"/>
+      <c r="V18" s="194"/>
       <c r="W18" s="13"/>
       <c r="X18" s="11"/>
     </row>
@@ -3975,83 +3984,83 @@
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="202"/>
-      <c r="C19" s="209" t="s">
+      <c r="B19" s="272"/>
+      <c r="C19" s="184" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="210" t="s">
+      <c r="D19" s="185" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="210" t="s">
+      <c r="E19" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="210" t="s">
+      <c r="F19" s="185" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="211" t="s">
+      <c r="G19" s="186" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="212" t="s">
-        <v>228</v>
-      </c>
-      <c r="I19" s="211" t="s">
+      <c r="H19" s="187">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="I19" s="186" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="210" t="s">
+      <c r="J19" s="185" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="211">
-        <v>15</v>
-      </c>
-      <c r="L19" s="211">
-        <v>45</v>
-      </c>
-      <c r="M19" s="213">
+      <c r="K19" s="186">
+        <v>10</v>
+      </c>
+      <c r="L19" s="186">
+        <v>50</v>
+      </c>
+      <c r="M19" s="188">
         <v>2</v>
       </c>
-      <c r="N19" s="213">
+      <c r="N19" s="188">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="213">
+      <c r="O19" s="188">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="214" t="s">
+      <c r="P19" s="189" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="215">
-        <v>0.1116</v>
-      </c>
-      <c r="R19" s="216">
+      <c r="Q19" s="190">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="R19" s="191">
         <f t="shared" si="2"/>
-        <v>1.6740000000000002</v>
-      </c>
-      <c r="S19" s="216">
-        <v>0.1116</v>
-      </c>
-      <c r="T19" s="216">
+        <v>0.39399999999999996</v>
+      </c>
+      <c r="S19" s="191">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="T19" s="191">
         <f t="shared" si="3"/>
-        <v>5.0220000000000002</v>
-      </c>
-      <c r="U19" s="232"/>
-      <c r="V19" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W19" s="218"/>
+        <v>1.97</v>
+      </c>
+      <c r="U19" s="207"/>
+      <c r="V19" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W19" s="193"/>
       <c r="X19" s="11"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="208" t="s">
+      <c r="B20" s="278" t="s">
         <v>190</v>
       </c>
       <c r="C20" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="131" t="s">
+      <c r="D20" s="130" t="s">
         <v>187</v>
       </c>
       <c r="E20" s="66" t="s">
@@ -4089,7 +4098,7 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="129" t="s">
+      <c r="P20" s="128" t="s">
         <v>16</v>
       </c>
       <c r="Q20" s="40">
@@ -4107,7 +4116,7 @@
         <v>1.0349999999999999</v>
       </c>
       <c r="U20" s="12"/>
-      <c r="V20" s="219"/>
+      <c r="V20" s="194"/>
       <c r="W20" s="13"/>
       <c r="X20" s="11"/>
     </row>
@@ -4115,24 +4124,24 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="206"/>
+      <c r="B21" s="276"/>
       <c r="C21" s="69" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="95" t="s">
         <v>229</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>230</v>
       </c>
       <c r="E21" s="71" t="s">
         <v>188</v>
       </c>
       <c r="F21" s="71" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G21" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="H21" s="42" t="s">
         <v>236</v>
-      </c>
-      <c r="H21" s="42" t="s">
-        <v>237</v>
       </c>
       <c r="I21" s="43" t="s">
         <v>39</v>
@@ -4175,7 +4184,7 @@
         <v>3.7150000000000003</v>
       </c>
       <c r="U21" s="14"/>
-      <c r="V21" s="220"/>
+      <c r="V21" s="195"/>
       <c r="W21" s="15"/>
       <c r="X21" s="11"/>
     </row>
@@ -4183,24 +4192,24 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="206"/>
+      <c r="B22" s="276"/>
       <c r="C22" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" s="95" t="s">
         <v>232</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="E22" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="E22" s="71" t="s">
+      <c r="F22" s="71" t="s">
         <v>234</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="G22" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="G22" s="48" t="s">
-        <v>236</v>
-      </c>
       <c r="H22" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I22" s="43" t="s">
         <v>39</v>
@@ -4243,7 +4252,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="U22" s="14"/>
-      <c r="V22" s="220"/>
+      <c r="V22" s="195"/>
       <c r="W22" s="15"/>
       <c r="X22" s="11"/>
     </row>
@@ -4251,24 +4260,24 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="207"/>
-      <c r="C23" s="109" t="s">
+      <c r="B23" s="277"/>
+      <c r="C23" s="108" t="s">
+        <v>263</v>
+      </c>
+      <c r="D23" s="152" t="s">
         <v>264</v>
       </c>
-      <c r="D23" s="153" t="s">
+      <c r="E23" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="127" t="s">
         <v>265</v>
-      </c>
-      <c r="E23" s="128" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="128" t="s">
-        <v>266</v>
       </c>
       <c r="G23" s="54" t="s">
         <v>130</v>
       </c>
       <c r="H23" s="55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I23" s="56" t="s">
         <v>39</v>
@@ -4293,25 +4302,25 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="107" t="s">
+      <c r="P23" s="106" t="s">
         <v>16</v>
       </c>
       <c r="Q23" s="59">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="R23" s="108">
+      <c r="R23" s="107">
         <f t="shared" si="2"/>
         <v>0.91600000000000004</v>
       </c>
-      <c r="S23" s="108">
+      <c r="S23" s="107">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="T23" s="108">
+      <c r="T23" s="107">
         <f t="shared" si="3"/>
         <v>2.7480000000000002</v>
       </c>
       <c r="U23" s="16"/>
-      <c r="V23" s="222"/>
+      <c r="V23" s="197"/>
       <c r="W23" s="17"/>
       <c r="X23" s="11"/>
     </row>
@@ -4319,74 +4328,74 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="164" t="s">
+      <c r="C24" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="155" t="s">
+      <c r="D24" s="154" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="156" t="s">
+      <c r="E24" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="156" t="s">
+      <c r="F24" s="155" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="157" t="s">
+      <c r="G24" s="156" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="157" t="s">
+      <c r="H24" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="156" t="s">
+      <c r="I24" s="155" t="s">
         <v>145</v>
       </c>
-      <c r="J24" s="156" t="s">
+      <c r="J24" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="156">
+      <c r="K24" s="155">
         <v>42</v>
       </c>
-      <c r="L24" s="156">
+      <c r="L24" s="155">
         <v>162</v>
       </c>
-      <c r="M24" s="158">
+      <c r="M24" s="157">
         <v>8</v>
       </c>
-      <c r="N24" s="158">
+      <c r="N24" s="157">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="158">
+      <c r="O24" s="157">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="159" t="s">
+      <c r="P24" s="158" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="160">
+      <c r="Q24" s="159">
         <v>3.68</v>
       </c>
-      <c r="R24" s="161">
+      <c r="R24" s="160">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="161">
+      <c r="S24" s="160">
         <v>3.68</v>
       </c>
-      <c r="T24" s="161">
+      <c r="T24" s="160">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="162" t="s">
-        <v>250</v>
-      </c>
-      <c r="V24" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W24" s="178">
+      <c r="U24" s="161" t="s">
+        <v>249</v>
+      </c>
+      <c r="V24" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W24" s="177">
         <v>3.68</v>
       </c>
       <c r="X24" s="11"/>
@@ -4395,13 +4404,13 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="136" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="151" t="s">
+      <c r="D25" s="150" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="75" t="s">
@@ -4419,45 +4428,45 @@
       <c r="I25" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="150" t="s">
+      <c r="J25" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="150">
+      <c r="K25" s="149">
         <v>10</v>
       </c>
-      <c r="L25" s="150">
+      <c r="L25" s="149">
         <v>30</v>
       </c>
-      <c r="M25" s="110">
+      <c r="M25" s="109">
         <v>1</v>
       </c>
-      <c r="N25" s="110">
+      <c r="N25" s="109">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="110">
+      <c r="O25" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="154" t="s">
+      <c r="P25" s="153" t="s">
         <v>16</v>
       </c>
       <c r="Q25" s="53">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R25" s="111">
+      <c r="R25" s="110">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S25" s="111">
+      <c r="S25" s="110">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="T25" s="111">
+      <c r="T25" s="110">
         <f t="shared" si="3"/>
         <v>1.77</v>
       </c>
       <c r="U25" s="29"/>
-      <c r="V25" s="223"/>
+      <c r="V25" s="198"/>
       <c r="W25" s="30"/>
       <c r="X25" s="11"/>
     </row>
@@ -4465,153 +4474,153 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="198" t="s">
+      <c r="B26" s="268" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="233" t="s">
+      <c r="C26" s="208" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="234" t="s">
+      <c r="D26" s="209" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="234" t="s">
+      <c r="E26" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="234" t="s">
+      <c r="F26" s="209" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="235" t="s">
+      <c r="G26" s="210" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="236" t="s">
+      <c r="H26" s="211" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="235" t="s">
+      <c r="I26" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="234" t="s">
+      <c r="J26" s="209" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="234">
+      <c r="K26" s="209">
         <v>7</v>
       </c>
-      <c r="L26" s="234">
+      <c r="L26" s="209">
         <v>23</v>
       </c>
-      <c r="M26" s="237">
+      <c r="M26" s="212">
         <v>1</v>
       </c>
-      <c r="N26" s="237">
+      <c r="N26" s="212">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="238">
+      <c r="O26" s="213">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="239" t="s">
+      <c r="P26" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="240">
+      <c r="Q26" s="215">
         <v>0.23949999999999999</v>
       </c>
-      <c r="R26" s="241">
+      <c r="R26" s="216">
         <f>Q26*K26</f>
         <v>1.6764999999999999</v>
       </c>
-      <c r="S26" s="241">
+      <c r="S26" s="216">
         <v>0.23949999999999999</v>
       </c>
-      <c r="T26" s="242">
+      <c r="T26" s="217">
         <f t="shared" si="3"/>
         <v>5.5084999999999997</v>
       </c>
-      <c r="U26" s="243"/>
-      <c r="V26" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W26" s="244"/>
+      <c r="U26" s="218"/>
+      <c r="V26" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W26" s="219"/>
       <c r="X26" s="11"/>
     </row>
     <row r="27" spans="1:24" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="199"/>
-      <c r="C27" s="245" t="s">
+      <c r="B27" s="269"/>
+      <c r="C27" s="220" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="246" t="s">
+      <c r="D27" s="221" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="247" t="s">
+      <c r="E27" s="222" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="247" t="s">
+      <c r="F27" s="222" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="248" t="s">
+      <c r="G27" s="223" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="249" t="s">
+      <c r="H27" s="224" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="248" t="s">
+      <c r="I27" s="223" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="247" t="s">
+      <c r="J27" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="247">
+      <c r="K27" s="222">
         <v>7</v>
       </c>
-      <c r="L27" s="247">
+      <c r="L27" s="222">
         <v>45</v>
       </c>
-      <c r="M27" s="250">
+      <c r="M27" s="225">
         <v>2</v>
       </c>
-      <c r="N27" s="250">
+      <c r="N27" s="225">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="250">
+      <c r="O27" s="225">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="251" t="s">
+      <c r="P27" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="252">
+      <c r="Q27" s="227">
         <v>0.11169999999999999</v>
       </c>
-      <c r="R27" s="253">
+      <c r="R27" s="228">
         <f t="shared" si="2"/>
         <v>0.78189999999999993</v>
       </c>
-      <c r="S27" s="253">
+      <c r="S27" s="228">
         <v>0.11169999999999999</v>
       </c>
-      <c r="T27" s="253">
+      <c r="T27" s="228">
         <f t="shared" si="3"/>
         <v>5.0264999999999995</v>
       </c>
-      <c r="U27" s="254"/>
-      <c r="V27" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W27" s="255"/>
+      <c r="U27" s="229"/>
+      <c r="V27" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W27" s="230"/>
       <c r="X27" s="11"/>
     </row>
     <row r="28" spans="1:24" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="200"/>
+      <c r="B28" s="270"/>
       <c r="C28" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="123" t="s">
+      <c r="D28" s="122" t="s">
         <v>167</v>
       </c>
       <c r="E28" s="79" t="s">
@@ -4649,25 +4658,25 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="112" t="s">
+      <c r="P28" s="111" t="s">
         <v>16</v>
       </c>
       <c r="Q28" s="59">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="R28" s="108">
+      <c r="R28" s="107">
         <f t="shared" si="2"/>
         <v>0.99099999999999988</v>
       </c>
-      <c r="S28" s="108">
+      <c r="S28" s="107">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="T28" s="108">
+      <c r="T28" s="107">
         <f t="shared" si="3"/>
         <v>2.4775</v>
       </c>
       <c r="U28" s="16"/>
-      <c r="V28" s="222"/>
+      <c r="V28" s="197"/>
       <c r="W28" s="17"/>
       <c r="X28" s="11"/>
     </row>
@@ -4675,13 +4684,13 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="198" t="s">
+      <c r="B29" s="268" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="165" t="s">
+      <c r="D29" s="164" t="s">
         <v>169</v>
       </c>
       <c r="E29" s="65" t="s">
@@ -4696,19 +4705,19 @@
       <c r="H29" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="131" t="s">
+      <c r="I29" s="130" t="s">
         <v>128</v>
       </c>
       <c r="J29" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="166">
+      <c r="K29" s="165">
         <v>100</v>
       </c>
-      <c r="L29" s="166">
+      <c r="L29" s="165">
         <v>100</v>
       </c>
-      <c r="M29" s="166">
+      <c r="M29" s="165">
         <v>3</v>
       </c>
       <c r="N29" s="39">
@@ -4719,7 +4728,7 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="167" t="s">
+      <c r="P29" s="166" t="s">
         <v>16</v>
       </c>
       <c r="Q29" s="40">
@@ -4737,7 +4746,7 @@
         <v>0.1</v>
       </c>
       <c r="U29" s="12"/>
-      <c r="V29" s="219"/>
+      <c r="V29" s="194"/>
       <c r="W29" s="13"/>
       <c r="X29" s="11"/>
     </row>
@@ -4745,30 +4754,30 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="199"/>
+      <c r="B30" s="269"/>
       <c r="C30" s="81" t="s">
-        <v>269</v>
-      </c>
-      <c r="D30" s="184" t="s">
+        <v>268</v>
+      </c>
+      <c r="D30" s="183" t="s">
         <v>170</v>
       </c>
       <c r="E30" s="70" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="70" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G30" s="48" t="s">
         <v>114</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I30" s="95" t="s">
         <v>40</v>
       </c>
       <c r="J30" s="70" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K30" s="96">
         <v>100</v>
@@ -4805,7 +4814,7 @@
         <v>0.16</v>
       </c>
       <c r="U30" s="14"/>
-      <c r="V30" s="220"/>
+      <c r="V30" s="195"/>
       <c r="W30" s="15"/>
       <c r="X30" s="11"/>
     </row>
@@ -4813,11 +4822,11 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="199"/>
+      <c r="B31" s="269"/>
       <c r="C31" s="81" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="130" t="s">
+      <c r="D31" s="129" t="s">
         <v>172</v>
       </c>
       <c r="E31" s="70" t="s">
@@ -4873,7 +4882,7 @@
         <v>0.15</v>
       </c>
       <c r="U31" s="14"/>
-      <c r="V31" s="220"/>
+      <c r="V31" s="195"/>
       <c r="W31" s="15"/>
       <c r="X31" s="11"/>
     </row>
@@ -4881,30 +4890,30 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="199"/>
+      <c r="B32" s="269"/>
       <c r="C32" s="81" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" s="129" t="s">
         <v>239</v>
-      </c>
-      <c r="D32" s="130" t="s">
-        <v>240</v>
       </c>
       <c r="E32" s="70" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G32" s="48" t="s">
         <v>114</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I32" s="95" t="s">
         <v>40</v>
       </c>
       <c r="J32" s="70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K32" s="96">
         <v>100</v>
@@ -4941,7 +4950,7 @@
         <v>0.13</v>
       </c>
       <c r="U32" s="14"/>
-      <c r="V32" s="220"/>
+      <c r="V32" s="195"/>
       <c r="W32" s="15"/>
       <c r="X32" s="11"/>
     </row>
@@ -4949,12 +4958,12 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="200"/>
+      <c r="B33" s="270"/>
       <c r="C33" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="168" t="s">
-        <v>282</v>
+      <c r="D33" s="167" t="s">
+        <v>281</v>
       </c>
       <c r="E33" s="79" t="s">
         <v>24</v>
@@ -4968,19 +4977,19 @@
       <c r="H33" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="138" t="s">
+      <c r="I33" s="137" t="s">
         <v>40</v>
       </c>
       <c r="J33" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="169">
+      <c r="K33" s="168">
         <v>100</v>
       </c>
-      <c r="L33" s="169">
+      <c r="L33" s="168">
         <v>100</v>
       </c>
-      <c r="M33" s="169">
+      <c r="M33" s="168">
         <v>2</v>
       </c>
       <c r="N33" s="58">
@@ -4991,25 +5000,25 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="170" t="s">
+      <c r="P33" s="169" t="s">
         <v>16</v>
       </c>
       <c r="Q33" s="59">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="108">
+      <c r="R33" s="107">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="108">
+      <c r="S33" s="107">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="108">
+      <c r="T33" s="107">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U33" s="16"/>
-      <c r="V33" s="222"/>
+      <c r="V33" s="197"/>
       <c r="W33" s="17"/>
       <c r="X33" s="11"/>
     </row>
@@ -5017,223 +5026,223 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="198" t="s">
+      <c r="B34" s="268" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="233" t="s">
+      <c r="C34" s="208" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="234" t="s">
+      <c r="D34" s="209" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="256" t="s">
+      <c r="E34" s="231" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="256" t="s">
+      <c r="F34" s="231" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="257" t="s">
+      <c r="G34" s="232" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="258" t="s">
+      <c r="H34" s="233" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="257" t="s">
+      <c r="I34" s="232" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="256" t="s">
+      <c r="J34" s="231" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="256">
+      <c r="K34" s="231">
         <v>11</v>
       </c>
-      <c r="L34" s="256">
+      <c r="L34" s="231">
         <v>42</v>
       </c>
-      <c r="M34" s="238">
+      <c r="M34" s="213">
         <v>2</v>
       </c>
-      <c r="N34" s="238">
+      <c r="N34" s="213">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="238">
+      <c r="O34" s="213">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="259" t="s">
+      <c r="P34" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="Q34" s="260">
+      <c r="Q34" s="235">
         <v>0.64739999999999998</v>
       </c>
-      <c r="R34" s="242">
+      <c r="R34" s="217">
         <f t="shared" si="2"/>
         <v>7.1213999999999995</v>
       </c>
-      <c r="S34" s="242">
+      <c r="S34" s="217">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="242">
+      <c r="T34" s="217">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="261"/>
-      <c r="V34" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W34" s="262"/>
+      <c r="U34" s="236"/>
+      <c r="V34" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W34" s="237"/>
       <c r="X34" s="11"/>
     </row>
     <row r="35" spans="1:24" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="199"/>
-      <c r="C35" s="245" t="s">
+      <c r="B35" s="269"/>
+      <c r="C35" s="220" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="246" t="s">
+      <c r="D35" s="221" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="247" t="s">
+      <c r="E35" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="247" t="s">
+      <c r="F35" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="248" t="s">
+      <c r="G35" s="223" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="248" t="s">
+      <c r="H35" s="223" t="s">
         <v>134</v>
       </c>
-      <c r="I35" s="248" t="s">
+      <c r="I35" s="223" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="247" t="s">
+      <c r="J35" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="248">
+      <c r="K35" s="223">
         <v>6</v>
       </c>
-      <c r="L35" s="248">
+      <c r="L35" s="223">
         <v>21</v>
       </c>
-      <c r="M35" s="250">
+      <c r="M35" s="225">
         <v>1</v>
       </c>
-      <c r="N35" s="250">
+      <c r="N35" s="225">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="250">
+      <c r="O35" s="225">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="251" t="s">
+      <c r="P35" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="252">
+      <c r="Q35" s="227">
         <v>0.39889999999999998</v>
       </c>
-      <c r="R35" s="253">
+      <c r="R35" s="228">
         <f t="shared" si="2"/>
         <v>2.3933999999999997</v>
       </c>
-      <c r="S35" s="253">
+      <c r="S35" s="228">
         <v>0.33829999999999999</v>
       </c>
-      <c r="T35" s="253">
+      <c r="T35" s="228">
         <f t="shared" si="3"/>
         <v>7.1042999999999994</v>
       </c>
-      <c r="U35" s="254"/>
-      <c r="V35" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W35" s="255"/>
+      <c r="U35" s="229"/>
+      <c r="V35" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W35" s="230"/>
       <c r="X35" s="11"/>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="199"/>
-      <c r="C36" s="245" t="s">
+      <c r="B36" s="269"/>
+      <c r="C36" s="220" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="246" t="s">
+      <c r="D36" s="221" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="247" t="s">
+      <c r="E36" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="247" t="s">
+      <c r="F36" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="248" t="s">
+      <c r="G36" s="223" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="248" t="s">
+      <c r="H36" s="223" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="247" t="s">
+      <c r="I36" s="222" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="247" t="s">
+      <c r="J36" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="248">
+      <c r="K36" s="223">
         <v>6</v>
       </c>
-      <c r="L36" s="248">
+      <c r="L36" s="223">
         <v>21</v>
       </c>
-      <c r="M36" s="250">
+      <c r="M36" s="225">
         <v>1</v>
       </c>
-      <c r="N36" s="250">
+      <c r="N36" s="225">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="250">
+      <c r="O36" s="225">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="251" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q36" s="263">
+      <c r="P36" s="226" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q36" s="238">
         <v>8</v>
       </c>
-      <c r="R36" s="253">
+      <c r="R36" s="228">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="253">
+      <c r="S36" s="228">
         <v>8</v>
       </c>
-      <c r="T36" s="253">
+      <c r="T36" s="228">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="264"/>
-      <c r="V36" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W36" s="265"/>
+      <c r="U36" s="239"/>
+      <c r="V36" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W36" s="240"/>
       <c r="X36" s="11"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="199"/>
+      <c r="B37" s="269"/>
       <c r="C37" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="124" t="s">
+      <c r="D37" s="123" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="88" t="s">
@@ -5274,25 +5283,25 @@
       <c r="P37" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="Q37" s="105">
-        <v>10.18</v>
-      </c>
-      <c r="R37" s="106">
+      <c r="Q37" s="279">
+        <v>4.76</v>
+      </c>
+      <c r="R37" s="105">
         <f t="shared" si="2"/>
-        <v>111.97999999999999</v>
-      </c>
-      <c r="S37" s="106">
-        <v>10.18</v>
-      </c>
-      <c r="T37" s="102">
+        <v>52.36</v>
+      </c>
+      <c r="S37" s="105">
+        <v>4.76</v>
+      </c>
+      <c r="T37" s="280">
         <f t="shared" si="3"/>
-        <v>417.38</v>
+        <v>195.16</v>
       </c>
       <c r="U37" s="92" t="s">
-        <v>250</v>
-      </c>
-      <c r="V37" s="217" t="s">
-        <v>296</v>
+        <v>297</v>
+      </c>
+      <c r="V37" s="192" t="s">
+        <v>295</v>
       </c>
       <c r="W37" s="93">
         <v>10.18</v>
@@ -5303,11 +5312,11 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="199"/>
+      <c r="B38" s="269"/>
       <c r="C38" s="81" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="122" t="s">
+      <c r="D38" s="121" t="s">
         <v>176</v>
       </c>
       <c r="E38" s="70" t="s">
@@ -5363,7 +5372,7 @@
         <v>49.305900000000001</v>
       </c>
       <c r="U38" s="21"/>
-      <c r="V38" s="224"/>
+      <c r="V38" s="199"/>
       <c r="W38" s="15"/>
       <c r="X38" s="11"/>
     </row>
@@ -5371,11 +5380,11 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="199"/>
+      <c r="B39" s="269"/>
       <c r="C39" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="122" t="s">
+      <c r="D39" s="121" t="s">
         <v>179</v>
       </c>
       <c r="E39" s="70" t="s">
@@ -5431,7 +5440,7 @@
         <v>12.801600000000001</v>
       </c>
       <c r="U39" s="21"/>
-      <c r="V39" s="224"/>
+      <c r="V39" s="199"/>
       <c r="W39" s="15"/>
       <c r="X39" s="11"/>
     </row>
@@ -5439,147 +5448,149 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="199"/>
-      <c r="C40" s="245" t="s">
+      <c r="B40" s="269"/>
+      <c r="C40" s="220" t="s">
+        <v>271</v>
+      </c>
+      <c r="D40" s="221" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="246" t="s">
+      <c r="E40" s="222" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="222" t="s">
         <v>273</v>
       </c>
-      <c r="E40" s="247" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="247" t="s">
-        <v>274</v>
-      </c>
-      <c r="G40" s="248" t="s">
-        <v>280</v>
-      </c>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248" t="s">
+      <c r="G40" s="223" t="s">
+        <v>279</v>
+      </c>
+      <c r="H40" s="223"/>
+      <c r="I40" s="223" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="247" t="s">
+      <c r="J40" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="248">
+      <c r="K40" s="223">
         <v>6</v>
       </c>
-      <c r="L40" s="248"/>
-      <c r="M40" s="250">
+      <c r="L40" s="223">
+        <v>22</v>
+      </c>
+      <c r="M40" s="225">
         <v>1</v>
       </c>
-      <c r="N40" s="250">
+      <c r="N40" s="225">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="250">
+      <c r="O40" s="225">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="251" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q40" s="252">
-        <v>1.2</v>
-      </c>
-      <c r="R40" s="253">
+      <c r="P40" s="253" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q40" s="227">
+        <v>0.8</v>
+      </c>
+      <c r="R40" s="228">
         <f t="shared" si="2"/>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="S40" s="253">
-        <v>1.2</v>
-      </c>
-      <c r="T40" s="253">
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="S40" s="228">
+        <v>0.8</v>
+      </c>
+      <c r="T40" s="228">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="277" t="s">
-        <v>281</v>
-      </c>
-      <c r="V40" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W40" s="255"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="U40" s="252" t="s">
+        <v>280</v>
+      </c>
+      <c r="V40" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W40" s="230"/>
       <c r="X40" s="11"/>
     </row>
     <row r="41" spans="1:24" ht="15.75" thickBot="1">
       <c r="A41" s="6"/>
-      <c r="B41" s="199"/>
-      <c r="C41" s="266" t="s">
+      <c r="B41" s="269"/>
+      <c r="C41" s="241" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="242" t="s">
+        <v>282</v>
+      </c>
+      <c r="E41" s="243" t="s">
         <v>285</v>
       </c>
-      <c r="D41" s="267" t="s">
-        <v>283</v>
-      </c>
-      <c r="E41" s="268" t="s">
+      <c r="F41" s="244" t="s">
         <v>286</v>
       </c>
-      <c r="F41" s="269" t="s">
+      <c r="G41" s="245" t="s">
         <v>287</v>
       </c>
-      <c r="G41" s="270" t="s">
-        <v>288</v>
-      </c>
-      <c r="H41" s="270" t="s">
+      <c r="H41" s="245" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="248" t="s">
+      <c r="I41" s="223" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="247" t="s">
+      <c r="J41" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="270">
+      <c r="K41" s="245">
         <v>10</v>
       </c>
-      <c r="L41" s="270">
+      <c r="L41" s="245">
         <v>30</v>
       </c>
-      <c r="M41" s="271">
+      <c r="M41" s="246">
         <v>1</v>
       </c>
-      <c r="N41" s="271">
+      <c r="N41" s="246">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="271">
+      <c r="O41" s="246">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="272" t="s">
+      <c r="P41" s="247" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="273">
+      <c r="Q41" s="248">
         <v>1</v>
       </c>
-      <c r="R41" s="274">
+      <c r="R41" s="249">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="274">
+      <c r="S41" s="249">
         <v>1</v>
       </c>
-      <c r="T41" s="253">
+      <c r="T41" s="228">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="275"/>
-      <c r="V41" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W41" s="276"/>
+      <c r="U41" s="250"/>
+      <c r="V41" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W41" s="251"/>
       <c r="X41" s="11"/>
     </row>
     <row r="42" spans="1:24" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>39</v>
       </c>
-      <c r="B42" s="200"/>
+      <c r="B42" s="270"/>
       <c r="C42" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="123" t="s">
+      <c r="D42" s="122" t="s">
         <v>103</v>
       </c>
       <c r="E42" s="79" t="s">
@@ -5623,19 +5634,19 @@
       <c r="Q42" s="59">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="R42" s="108">
+      <c r="R42" s="107">
         <f t="shared" si="2"/>
         <v>0.53500000000000003</v>
       </c>
-      <c r="S42" s="108">
+      <c r="S42" s="107">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="T42" s="108">
+      <c r="T42" s="107">
         <f t="shared" si="3"/>
         <v>1.605</v>
       </c>
       <c r="U42" s="22"/>
-      <c r="V42" s="225"/>
+      <c r="V42" s="200"/>
       <c r="W42" s="17"/>
       <c r="X42" s="11"/>
     </row>
@@ -5643,7 +5654,7 @@
       <c r="A43" s="6">
         <v>40</v>
       </c>
-      <c r="B43" s="198" t="s">
+      <c r="B43" s="268" t="s">
         <v>110</v>
       </c>
       <c r="C43" s="76" t="s">
@@ -5705,7 +5716,7 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="U43" s="23"/>
-      <c r="V43" s="226"/>
+      <c r="V43" s="201"/>
       <c r="W43" s="13"/>
       <c r="X43" s="11"/>
     </row>
@@ -5713,24 +5724,24 @@
       <c r="A44" s="6">
         <v>41</v>
       </c>
-      <c r="B44" s="199"/>
+      <c r="B44" s="269"/>
       <c r="C44" s="81" t="s">
-        <v>292</v>
-      </c>
-      <c r="D44" s="122" t="s">
+        <v>291</v>
+      </c>
+      <c r="D44" s="121" t="s">
         <v>42</v>
       </c>
       <c r="E44" s="65" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="70" t="s">
+        <v>292</v>
+      </c>
+      <c r="G44" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="H44" s="44" t="s">
         <v>294</v>
-      </c>
-      <c r="H44" s="44" t="s">
-        <v>295</v>
       </c>
       <c r="I44" s="44" t="s">
         <v>39</v>
@@ -5773,7 +5784,7 @@
         <v>1.77</v>
       </c>
       <c r="U44" s="27"/>
-      <c r="V44" s="227"/>
+      <c r="V44" s="202"/>
       <c r="W44" s="15"/>
       <c r="X44" s="11"/>
     </row>
@@ -5781,11 +5792,11 @@
       <c r="A45" s="6">
         <v>42</v>
       </c>
-      <c r="B45" s="199"/>
+      <c r="B45" s="269"/>
       <c r="C45" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="122" t="s">
+      <c r="D45" s="121" t="s">
         <v>34</v>
       </c>
       <c r="E45" s="70" t="s">
@@ -5841,7 +5852,7 @@
         <v>0.63</v>
       </c>
       <c r="U45" s="28"/>
-      <c r="V45" s="228"/>
+      <c r="V45" s="203"/>
       <c r="W45" s="15"/>
       <c r="X45" s="11"/>
     </row>
@@ -5849,117 +5860,117 @@
       <c r="A46" s="6">
         <v>43</v>
       </c>
-      <c r="B46" s="199"/>
-      <c r="C46" s="245" t="s">
+      <c r="B46" s="269"/>
+      <c r="C46" s="220" t="s">
+        <v>274</v>
+      </c>
+      <c r="D46" s="221" t="s">
         <v>275</v>
       </c>
-      <c r="D46" s="246" t="s">
+      <c r="E46" s="222" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="222" t="s">
         <v>276</v>
       </c>
-      <c r="E46" s="247" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="247" t="s">
+      <c r="G46" s="222" t="s">
         <v>277</v>
       </c>
-      <c r="G46" s="247" t="s">
+      <c r="H46" s="222" t="s">
         <v>278</v>
       </c>
-      <c r="H46" s="247" t="s">
-        <v>279</v>
-      </c>
-      <c r="I46" s="247" t="s">
+      <c r="I46" s="222" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="247" t="s">
+      <c r="J46" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="247">
+      <c r="K46" s="222">
         <v>5</v>
       </c>
-      <c r="L46" s="247">
+      <c r="L46" s="222">
         <v>25</v>
       </c>
-      <c r="M46" s="250">
+      <c r="M46" s="225">
         <v>1</v>
       </c>
-      <c r="N46" s="250">
+      <c r="N46" s="225">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="250">
+      <c r="O46" s="225">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="278" t="s">
+      <c r="P46" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="252">
+      <c r="Q46" s="227">
         <v>0.1002</v>
       </c>
-      <c r="R46" s="253">
+      <c r="R46" s="228">
         <f t="shared" si="2"/>
         <v>0.501</v>
       </c>
-      <c r="S46" s="253">
+      <c r="S46" s="228">
         <v>0.1002</v>
       </c>
-      <c r="T46" s="253">
+      <c r="T46" s="228">
         <f t="shared" si="3"/>
         <v>2.5049999999999999</v>
       </c>
-      <c r="U46" s="279"/>
-      <c r="V46" s="217" t="s">
-        <v>296</v>
-      </c>
-      <c r="W46" s="255"/>
+      <c r="U46" s="254"/>
+      <c r="V46" s="192" t="s">
+        <v>295</v>
+      </c>
+      <c r="W46" s="230"/>
       <c r="X46" s="11"/>
     </row>
     <row r="47" spans="1:24" ht="15.75" thickBot="1">
       <c r="A47" s="6"/>
-      <c r="B47" s="199"/>
+      <c r="B47" s="269"/>
       <c r="C47" s="97" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D47" s="75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E47" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="183">
+      <c r="F47" s="182">
         <v>61300611121</v>
       </c>
-      <c r="G47" s="150" t="s">
+      <c r="G47" s="149" t="s">
+        <v>289</v>
+      </c>
+      <c r="H47" s="149" t="s">
         <v>290</v>
       </c>
-      <c r="H47" s="150" t="s">
-        <v>291</v>
-      </c>
-      <c r="I47" s="150" t="s">
-        <v>291</v>
+      <c r="I47" s="149" t="s">
+        <v>290</v>
       </c>
       <c r="J47" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="150">
+      <c r="K47" s="149">
         <v>20</v>
       </c>
-      <c r="L47" s="150">
+      <c r="L47" s="149">
         <v>40</v>
       </c>
-      <c r="M47" s="181">
+      <c r="M47" s="180">
         <v>1</v>
       </c>
-      <c r="N47" s="110">
+      <c r="N47" s="109">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="110">
+      <c r="O47" s="109">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="180" t="s">
+      <c r="P47" s="179" t="s">
         <v>16</v>
       </c>
       <c r="Q47" s="53">
@@ -5969,15 +5980,15 @@
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="S47" s="111">
+      <c r="S47" s="110">
         <v>0.03</v>
       </c>
       <c r="T47" s="102">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="U47" s="182"/>
-      <c r="V47" s="229"/>
+      <c r="U47" s="181"/>
+      <c r="V47" s="204"/>
       <c r="W47" s="30"/>
       <c r="X47" s="11"/>
     </row>
@@ -5985,37 +5996,37 @@
       <c r="A48" s="6">
         <v>44</v>
       </c>
-      <c r="B48" s="200"/>
-      <c r="C48" s="113" t="s">
+      <c r="B48" s="270"/>
+      <c r="C48" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="114" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="115" t="s">
+      <c r="D48" s="113" t="s">
+        <v>243</v>
+      </c>
+      <c r="E48" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="115" t="s">
+      <c r="F48" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="116" t="s">
+      <c r="G48" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="H48" s="116"/>
-      <c r="I48" s="117"/>
-      <c r="J48" s="117" t="s">
+      <c r="H48" s="115"/>
+      <c r="I48" s="116"/>
+      <c r="J48" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="117" t="s">
+      <c r="K48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="L48" s="117" t="s">
+      <c r="L48" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="118">
+      <c r="M48" s="117">
         <v>53</v>
       </c>
-      <c r="N48" s="119">
+      <c r="N48" s="118">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
@@ -6023,66 +6034,66 @@
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="116" t="s">
+      <c r="P48" s="115" t="s">
         <v>144</v>
       </c>
-      <c r="Q48" s="117" t="s">
+      <c r="Q48" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="117" t="s">
+      <c r="R48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="S48" s="117" t="s">
+      <c r="S48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="T48" s="117" t="s">
+      <c r="T48" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="U48" s="120" t="s">
+      <c r="U48" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="V48" s="230"/>
-      <c r="W48" s="121"/>
+      <c r="V48" s="205"/>
+      <c r="W48" s="120"/>
       <c r="X48" s="11"/>
     </row>
     <row r="49" spans="1:24" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>45</v>
       </c>
-      <c r="B49" s="206" t="s">
+      <c r="B49" s="276" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="172" t="s">
-        <v>252</v>
-      </c>
-      <c r="D49" s="173" t="s">
+      <c r="C49" s="171" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="173" t="s">
+      <c r="E49" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="173" t="s">
-        <v>251</v>
-      </c>
-      <c r="G49" s="173" t="s">
+      <c r="F49" s="172" t="s">
+        <v>250</v>
+      </c>
+      <c r="G49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="H49" s="173" t="s">
+      <c r="H49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="I49" s="173" t="s">
+      <c r="I49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="173" t="s">
+      <c r="J49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="K49" s="173" t="s">
+      <c r="K49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="173" t="s">
+      <c r="L49" s="172" t="s">
         <v>144</v>
       </c>
-      <c r="M49" s="171">
+      <c r="M49" s="170">
         <v>1</v>
       </c>
       <c r="N49" s="45">
@@ -6093,67 +6104,67 @@
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="174" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q49" s="175">
+      <c r="P49" s="173" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q49" s="174">
         <v>0.2</v>
       </c>
-      <c r="R49" s="176">
+      <c r="R49" s="175">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="175">
+      <c r="S49" s="174">
         <v>0.2</v>
       </c>
       <c r="T49" s="47">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="177"/>
-      <c r="V49" s="231"/>
-      <c r="W49" s="179"/>
+      <c r="U49" s="176"/>
+      <c r="V49" s="206"/>
+      <c r="W49" s="178"/>
       <c r="X49" s="11"/>
     </row>
     <row r="50" spans="1:24" ht="15.75" thickBot="1">
       <c r="A50" s="18">
         <v>46</v>
       </c>
-      <c r="B50" s="207"/>
-      <c r="C50" s="132" t="s">
+      <c r="B50" s="277"/>
+      <c r="C50" s="131" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="133" t="s">
+      <c r="D50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="133" t="s">
+      <c r="E50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="134" t="s">
+      <c r="F50" s="133" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="133" t="s">
+      <c r="G50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="133" t="s">
+      <c r="H50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="133" t="s">
+      <c r="I50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="133" t="s">
+      <c r="J50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="133" t="s">
+      <c r="K50" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="133" t="s">
+      <c r="L50" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="125">
+      <c r="M50" s="124">
         <v>1</v>
       </c>
-      <c r="N50" s="125">
+      <c r="N50" s="124">
         <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
@@ -6161,28 +6172,28 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="142" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q50" s="126">
+      <c r="P50" s="141" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q50" s="125">
         <v>3.35</v>
       </c>
-      <c r="R50" s="127">
+      <c r="R50" s="126">
         <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="127">
+      <c r="S50" s="126">
         <v>3.35</v>
       </c>
-      <c r="T50" s="108">
+      <c r="T50" s="107">
         <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U50" s="120" t="s">
+      <c r="U50" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="V50" s="230"/>
-      <c r="W50" s="135"/>
+      <c r="V50" s="205"/>
+      <c r="W50" s="134"/>
       <c r="X50" s="11"/>
     </row>
     <row r="51" spans="1:24" ht="15.75">
@@ -6196,21 +6207,21 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="194" t="s">
+      <c r="M51" s="264" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="195"/>
-      <c r="O51" s="195"/>
-      <c r="P51" s="195"/>
+      <c r="N51" s="265"/>
+      <c r="O51" s="265"/>
+      <c r="P51" s="265"/>
       <c r="Q51" s="20"/>
-      <c r="R51" s="144">
+      <c r="R51" s="143">
         <f>SUM(R3:R49)</f>
-        <v>382.15120000000002</v>
-      </c>
-      <c r="S51" s="144"/>
+        <v>318.85120000000001</v>
+      </c>
+      <c r="S51" s="143"/>
       <c r="T51" s="100">
         <f>SUM(T3:T49)</f>
-        <v>1358.7949000000003</v>
+        <v>1151.1229000000003</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -6225,21 +6236,21 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="196" t="s">
+      <c r="M52" s="266" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="197"/>
-      <c r="O52" s="197"/>
-      <c r="P52" s="197"/>
+      <c r="N52" s="267"/>
+      <c r="O52" s="267"/>
+      <c r="P52" s="267"/>
       <c r="Q52" s="32"/>
-      <c r="R52" s="147">
+      <c r="R52" s="146">
         <f>R51/5</f>
-        <v>76.430239999999998</v>
-      </c>
-      <c r="S52" s="147"/>
+        <v>63.770240000000001</v>
+      </c>
+      <c r="S52" s="146"/>
       <c r="T52" s="34">
         <f>T51/20</f>
-        <v>67.939745000000016</v>
+        <v>57.556145000000015</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
@@ -6255,17 +6266,17 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="31"/>
-      <c r="N53" s="185" t="s">
+      <c r="N53" s="255" t="s">
         <v>147</v>
       </c>
-      <c r="O53" s="186"/>
-      <c r="P53" s="187"/>
-      <c r="Q53" s="143"/>
-      <c r="R53" s="145">
+      <c r="O53" s="256"/>
+      <c r="P53" s="257"/>
+      <c r="Q53" s="142"/>
+      <c r="R53" s="144">
         <v>3</v>
       </c>
-      <c r="S53" s="145"/>
-      <c r="T53" s="146">
+      <c r="S53" s="144"/>
+      <c r="T53" s="145">
         <v>3</v>
       </c>
       <c r="U53" s="7"/>
@@ -6282,17 +6293,17 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="31"/>
-      <c r="N54" s="203" t="s">
-        <v>253</v>
-      </c>
-      <c r="O54" s="204"/>
-      <c r="P54" s="205"/>
-      <c r="Q54" s="141"/>
-      <c r="R54" s="140">
+      <c r="N54" s="273" t="s">
+        <v>252</v>
+      </c>
+      <c r="O54" s="274"/>
+      <c r="P54" s="275"/>
+      <c r="Q54" s="140"/>
+      <c r="R54" s="139">
         <v>22.78</v>
       </c>
-      <c r="S54" s="140"/>
-      <c r="T54" s="148">
+      <c r="S54" s="139"/>
+      <c r="T54" s="147">
         <v>90.99</v>
       </c>
       <c r="U54" s="7"/>
@@ -6306,20 +6317,20 @@
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="188" t="s">
+      <c r="N55" s="258" t="s">
         <v>43</v>
       </c>
-      <c r="O55" s="189"/>
-      <c r="P55" s="190"/>
+      <c r="O55" s="259"/>
+      <c r="P55" s="260"/>
       <c r="Q55" s="32"/>
-      <c r="R55" s="149">
+      <c r="R55" s="148">
         <f>SUM(R52:R54)</f>
-        <v>102.21024</v>
-      </c>
-      <c r="S55" s="149"/>
+        <v>89.550240000000002</v>
+      </c>
+      <c r="S55" s="148"/>
       <c r="T55" s="33">
         <f>SUM(T52:T54)</f>
-        <v>161.92974500000003</v>
+        <v>151.54614500000002</v>
       </c>
       <c r="W55" s="11"/>
       <c r="X55" s="11"/>
@@ -6613,22 +6624,22 @@
     <hyperlink ref="P31" r:id="rId27"/>
     <hyperlink ref="P38" r:id="rId28"/>
     <hyperlink ref="P39" r:id="rId29"/>
-    <hyperlink ref="P36" r:id="rId30"/>
-    <hyperlink ref="P14" r:id="rId31"/>
-    <hyperlink ref="P15" r:id="rId32"/>
-    <hyperlink ref="P19" r:id="rId33"/>
-    <hyperlink ref="P21" r:id="rId34"/>
-    <hyperlink ref="P22" r:id="rId35"/>
-    <hyperlink ref="P32" r:id="rId36"/>
-    <hyperlink ref="P50" r:id="rId37"/>
-    <hyperlink ref="P49" r:id="rId38"/>
-    <hyperlink ref="P16" r:id="rId39"/>
-    <hyperlink ref="P17" r:id="rId40"/>
-    <hyperlink ref="P23" r:id="rId41"/>
-    <hyperlink ref="P30" r:id="rId42"/>
-    <hyperlink ref="P46" r:id="rId43"/>
-    <hyperlink ref="P41" r:id="rId44"/>
-    <hyperlink ref="P47" r:id="rId45"/>
+    <hyperlink ref="P14" r:id="rId30"/>
+    <hyperlink ref="P15" r:id="rId31"/>
+    <hyperlink ref="P21" r:id="rId32"/>
+    <hyperlink ref="P22" r:id="rId33"/>
+    <hyperlink ref="P32" r:id="rId34"/>
+    <hyperlink ref="P50" r:id="rId35"/>
+    <hyperlink ref="P49" r:id="rId36"/>
+    <hyperlink ref="P16" r:id="rId37"/>
+    <hyperlink ref="P17" r:id="rId38"/>
+    <hyperlink ref="P23" r:id="rId39"/>
+    <hyperlink ref="P30" r:id="rId40"/>
+    <hyperlink ref="P46" r:id="rId41"/>
+    <hyperlink ref="P41" r:id="rId42"/>
+    <hyperlink ref="P47" r:id="rId43"/>
+    <hyperlink ref="P19" r:id="rId44"/>
+    <hyperlink ref="P40" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId46"/>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A7FEB7-865A-46B7-8958-519D1F77BB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="298">
   <si>
     <t>S. No.</t>
   </si>
@@ -934,13 +935,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,6 +1125,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1659,7 +1675,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="279">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1708,9 +1724,6 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1929,9 +1942,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2213,9 +2223,6 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2223,9 +2230,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2355,9 +2359,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2409,6 +2410,12 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2481,10 +2488,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2762,14 +2772,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.5703125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2793,31 +2803,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickBot="1">
-      <c r="A1" s="261" t="s">
+      <c r="A1" s="258" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
-      <c r="J1" s="262"/>
-      <c r="K1" s="262"/>
-      <c r="L1" s="262"/>
-      <c r="M1" s="262"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="262"/>
-      <c r="P1" s="262"/>
-      <c r="Q1" s="262"/>
-      <c r="R1" s="262"/>
-      <c r="S1" s="262"/>
-      <c r="T1" s="262"/>
-      <c r="U1" s="262"/>
-      <c r="V1" s="262"/>
-      <c r="W1" s="263"/>
+      <c r="B1" s="259"/>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="259"/>
+      <c r="F1" s="259"/>
+      <c r="G1" s="259"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
+      <c r="J1" s="259"/>
+      <c r="K1" s="259"/>
+      <c r="L1" s="259"/>
+      <c r="M1" s="259"/>
+      <c r="N1" s="259"/>
+      <c r="O1" s="259"/>
+      <c r="P1" s="259"/>
+      <c r="Q1" s="259"/>
+      <c r="R1" s="259"/>
+      <c r="S1" s="259"/>
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="260"/>
     </row>
     <row r="2" spans="1:24" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2853,7 +2863,7 @@
       <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="138" t="s">
+      <c r="L2" s="136" t="s">
         <v>248</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -2877,13 +2887,13 @@
       <c r="S2" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="T2" s="138" t="s">
+      <c r="T2" s="136" t="s">
         <v>247</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="138" t="s">
+      <c r="V2" s="136" t="s">
         <v>296</v>
       </c>
       <c r="W2" s="5" t="s">
@@ -2894,203 +2904,203 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="268" t="s">
+      <c r="B3" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="128" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="65" t="s">
+      <c r="J3" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="37">
         <v>40</v>
       </c>
-      <c r="L3" s="38">
+      <c r="L3" s="37">
         <v>100</v>
       </c>
-      <c r="M3" s="67">
+      <c r="M3" s="66">
         <v>4</v>
       </c>
-      <c r="N3" s="39">
+      <c r="N3" s="38">
         <f>M3*5</f>
         <v>20</v>
       </c>
-      <c r="O3" s="39">
+      <c r="O3" s="38">
         <f>M3*20</f>
         <v>80</v>
       </c>
-      <c r="P3" s="68" t="s">
+      <c r="P3" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="40">
+      <c r="Q3" s="39">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="R3" s="41">
+      <c r="R3" s="40">
         <f>Q3*K3</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="S3" s="41">
+      <c r="S3" s="40">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="T3" s="41">
+      <c r="T3" s="40">
         <f>S3*L3</f>
         <v>1.3599999999999999</v>
       </c>
       <c r="U3" s="12"/>
-      <c r="V3" s="194"/>
+      <c r="V3" s="190"/>
       <c r="W3" s="13"/>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="269"/>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="266"/>
+      <c r="C4" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="43" t="s">
+      <c r="I4" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="70" t="s">
+      <c r="J4" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="43">
         <v>20</v>
       </c>
-      <c r="L4" s="44">
+      <c r="L4" s="43">
         <v>40</v>
       </c>
-      <c r="M4" s="72">
+      <c r="M4" s="71">
         <v>1</v>
       </c>
-      <c r="N4" s="101">
+      <c r="N4" s="99">
         <f t="shared" ref="N4:N48" si="0">M4*5</f>
         <v>5</v>
       </c>
-      <c r="O4" s="101">
+      <c r="O4" s="99">
         <f t="shared" ref="O4:O50" si="1">M4*20</f>
         <v>20</v>
       </c>
-      <c r="P4" s="73" t="s">
+      <c r="P4" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="45">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="R4" s="102">
+      <c r="R4" s="100">
         <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
         <v>0.40599999999999997</v>
       </c>
-      <c r="S4" s="102">
+      <c r="S4" s="100">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="T4" s="102">
+      <c r="T4" s="100">
         <f t="shared" ref="T4:T47" si="3">S4*L4</f>
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
-      <c r="V4" s="195"/>
+      <c r="V4" s="191"/>
       <c r="W4" s="15"/>
     </row>
     <row r="5" spans="1:24" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="269"/>
-      <c r="C5" s="69" t="s">
+      <c r="B5" s="266"/>
+      <c r="C5" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="129" t="s">
+      <c r="D5" s="127" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="I5" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="70" t="s">
+      <c r="J5" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="43">
         <v>100</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="43">
         <v>400</v>
       </c>
-      <c r="M5" s="72">
+      <c r="M5" s="71">
         <v>19</v>
       </c>
-      <c r="N5" s="101">
+      <c r="N5" s="99">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="O5" s="101">
+      <c r="O5" s="99">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="P5" s="73" t="s">
+      <c r="P5" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="45">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="R5" s="102">
+      <c r="R5" s="100">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="S5" s="102">
+      <c r="S5" s="100">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="T5" s="102">
+      <c r="T5" s="100">
         <f t="shared" si="3"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="U5" s="14"/>
-      <c r="V5" s="195"/>
+      <c r="V5" s="191"/>
       <c r="W5" s="15"/>
       <c r="X5" s="11"/>
     </row>
@@ -3098,67 +3108,67 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="269"/>
-      <c r="C6" s="69" t="s">
+      <c r="B6" s="266"/>
+      <c r="C6" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="95" t="s">
+      <c r="D6" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="71" t="s">
+      <c r="E6" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="70" t="s">
+      <c r="J6" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="43">
         <v>100</v>
       </c>
-      <c r="L6" s="44">
+      <c r="L6" s="43">
         <v>200</v>
       </c>
-      <c r="M6" s="72">
+      <c r="M6" s="71">
         <v>8</v>
       </c>
-      <c r="N6" s="101">
+      <c r="N6" s="99">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O6" s="101">
+      <c r="O6" s="99">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P6" s="74" t="s">
+      <c r="P6" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="45">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="102">
+      <c r="R6" s="100">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="102">
+      <c r="S6" s="100">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="102">
+      <c r="T6" s="100">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="U6" s="14"/>
-      <c r="V6" s="195"/>
+      <c r="V6" s="191"/>
       <c r="W6" s="15"/>
       <c r="X6" s="11"/>
     </row>
@@ -3166,67 +3176,67 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="269"/>
-      <c r="C7" s="69" t="s">
+      <c r="B7" s="266"/>
+      <c r="C7" s="68" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="D7" s="93" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="99" t="s">
+      <c r="F7" s="97" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="43" t="s">
+      <c r="I7" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="J7" s="70" t="s">
+      <c r="J7" s="69" t="s">
         <v>193</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="43">
         <v>100</v>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="43">
         <v>100</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="71">
         <v>1</v>
       </c>
-      <c r="N7" s="101">
+      <c r="N7" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O7" s="101">
+      <c r="O7" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="98" t="s">
+      <c r="P7" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="45">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R7" s="102">
+      <c r="R7" s="100">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S7" s="102">
+      <c r="S7" s="100">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T7" s="102">
+      <c r="T7" s="100">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="195"/>
+      <c r="V7" s="191"/>
       <c r="W7" s="15"/>
       <c r="X7" s="11"/>
     </row>
@@ -3234,67 +3244,67 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="269"/>
-      <c r="C8" s="69" t="s">
+      <c r="B8" s="266"/>
+      <c r="C8" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="129" t="s">
+      <c r="D8" s="127" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="70" t="s">
+      <c r="J8" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="43">
         <v>150</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="43">
         <v>600</v>
       </c>
-      <c r="M8" s="72">
+      <c r="M8" s="71">
         <v>29</v>
       </c>
-      <c r="N8" s="101">
+      <c r="N8" s="99">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="O8" s="101">
+      <c r="O8" s="99">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="P8" s="74" t="s">
+      <c r="P8" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="45">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="R8" s="102">
+      <c r="R8" s="100">
         <f t="shared" si="2"/>
         <v>1.08</v>
       </c>
-      <c r="S8" s="102">
+      <c r="S8" s="100">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="T8" s="102">
+      <c r="T8" s="100">
         <f t="shared" si="3"/>
         <v>3.4799999999999995</v>
       </c>
-      <c r="U8" s="26"/>
-      <c r="V8" s="196"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="192"/>
       <c r="W8" s="15"/>
       <c r="X8" s="11"/>
     </row>
@@ -3302,67 +3312,67 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="269"/>
-      <c r="C9" s="69" t="s">
+      <c r="B9" s="266"/>
+      <c r="C9" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="49" t="s">
+      <c r="H9" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="I9" s="43" t="s">
+      <c r="I9" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="70" t="s">
+      <c r="J9" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="47">
         <v>10</v>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="47">
         <v>30</v>
       </c>
-      <c r="M9" s="72">
+      <c r="M9" s="71">
         <v>1</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P9" s="74" t="s">
+      <c r="P9" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="46">
+      <c r="Q9" s="45">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="100">
         <f t="shared" si="2"/>
         <v>0.443</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="100">
         <v>3.8199999999999998E-2</v>
       </c>
-      <c r="T9" s="102">
+      <c r="T9" s="100">
         <f t="shared" si="3"/>
         <v>1.1459999999999999</v>
       </c>
       <c r="U9" s="14"/>
-      <c r="V9" s="195"/>
+      <c r="V9" s="191"/>
       <c r="W9" s="15"/>
       <c r="X9" s="11"/>
     </row>
@@ -3370,67 +3380,67 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="269"/>
-      <c r="C10" s="69" t="s">
+      <c r="B10" s="266"/>
+      <c r="C10" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="43" t="s">
+      <c r="I10" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="70" t="s">
+      <c r="J10" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="48">
+      <c r="K10" s="47">
         <v>100</v>
       </c>
-      <c r="L10" s="48">
+      <c r="L10" s="47">
         <v>200</v>
       </c>
-      <c r="M10" s="72">
+      <c r="M10" s="71">
         <v>6</v>
       </c>
-      <c r="N10" s="101">
+      <c r="N10" s="99">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="99">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="P10" s="73" t="s">
+      <c r="P10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="46">
+      <c r="Q10" s="45">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="R10" s="102">
+      <c r="R10" s="100">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="100">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="T10" s="102">
+      <c r="T10" s="100">
         <f t="shared" si="3"/>
         <v>0.64</v>
       </c>
       <c r="U10" s="14"/>
-      <c r="V10" s="195"/>
+      <c r="V10" s="191"/>
       <c r="W10" s="15"/>
       <c r="X10" s="11"/>
     </row>
@@ -3438,67 +3448,67 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="269"/>
-      <c r="C11" s="69" t="s">
+      <c r="B11" s="266"/>
+      <c r="C11" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="129" t="s">
+      <c r="D11" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="70" t="s">
+      <c r="E11" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="43" t="s">
+      <c r="I11" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="70" t="s">
+      <c r="J11" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="48">
+      <c r="K11" s="47">
         <v>100</v>
       </c>
-      <c r="L11" s="48">
+      <c r="L11" s="47">
         <v>350</v>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="71">
         <v>16</v>
       </c>
-      <c r="N11" s="101">
+      <c r="N11" s="99">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="O11" s="101">
+      <c r="O11" s="99">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="P11" s="73" t="s">
+      <c r="P11" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="45">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="R11" s="102">
+      <c r="R11" s="100">
         <f t="shared" si="2"/>
         <v>1.51</v>
       </c>
-      <c r="S11" s="102">
+      <c r="S11" s="100">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="T11" s="102">
+      <c r="T11" s="100">
         <f t="shared" si="3"/>
         <v>5.2850000000000001</v>
       </c>
       <c r="U11" s="14"/>
-      <c r="V11" s="195"/>
+      <c r="V11" s="191"/>
       <c r="W11" s="15"/>
       <c r="X11" s="11"/>
     </row>
@@ -3506,67 +3516,67 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="269"/>
-      <c r="C12" s="69" t="s">
+      <c r="B12" s="266"/>
+      <c r="C12" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="70" t="s">
+      <c r="J12" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="K12" s="48">
+      <c r="K12" s="47">
         <v>50</v>
       </c>
-      <c r="L12" s="48">
+      <c r="L12" s="47">
         <v>50</v>
       </c>
-      <c r="M12" s="72">
+      <c r="M12" s="71">
         <v>1</v>
       </c>
-      <c r="N12" s="101">
+      <c r="N12" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O12" s="101">
+      <c r="O12" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="103" t="s">
+      <c r="P12" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="45">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="R12" s="102">
+      <c r="R12" s="100">
         <f t="shared" si="2"/>
         <v>0.23500000000000001</v>
       </c>
-      <c r="S12" s="102">
+      <c r="S12" s="100">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="T12" s="102">
+      <c r="T12" s="100">
         <f t="shared" si="3"/>
         <v>0.23500000000000001</v>
       </c>
       <c r="U12" s="14"/>
-      <c r="V12" s="195"/>
+      <c r="V12" s="191"/>
       <c r="W12" s="15"/>
       <c r="X12" s="11"/>
     </row>
@@ -3574,67 +3584,67 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="269"/>
-      <c r="C13" s="69" t="s">
+      <c r="B13" s="266"/>
+      <c r="C13" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="129" t="s">
+      <c r="D13" s="127" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="70" t="s">
+      <c r="E13" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="J13" s="70" t="s">
+      <c r="J13" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="47">
         <v>100</v>
       </c>
-      <c r="L13" s="48">
+      <c r="L13" s="47">
         <v>100</v>
       </c>
-      <c r="M13" s="72">
+      <c r="M13" s="71">
         <v>1</v>
       </c>
-      <c r="N13" s="101">
+      <c r="N13" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O13" s="101">
+      <c r="O13" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="103" t="s">
+      <c r="P13" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q13" s="46">
+      <c r="Q13" s="45">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R13" s="102">
+      <c r="R13" s="100">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="S13" s="102">
+      <c r="S13" s="100">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="T13" s="102">
+      <c r="T13" s="100">
         <f t="shared" si="3"/>
         <v>0.11</v>
       </c>
       <c r="U13" s="14"/>
-      <c r="V13" s="195"/>
+      <c r="V13" s="191"/>
       <c r="W13" s="15"/>
       <c r="X13" s="11"/>
     </row>
@@ -3642,67 +3652,67 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="269"/>
-      <c r="C14" s="69" t="s">
+      <c r="B14" s="266"/>
+      <c r="C14" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="93" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="I14" s="43" t="s">
+      <c r="I14" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="70" t="s">
+      <c r="J14" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="47">
         <v>100</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="47">
         <v>100</v>
       </c>
-      <c r="M14" s="72">
+      <c r="M14" s="71">
         <v>1</v>
       </c>
-      <c r="N14" s="101">
+      <c r="N14" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O14" s="101">
+      <c r="O14" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="103" t="s">
+      <c r="P14" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="46">
+      <c r="Q14" s="45">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="R14" s="102">
+      <c r="R14" s="100">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
-      <c r="S14" s="102">
+      <c r="S14" s="100">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="T14" s="102">
+      <c r="T14" s="100">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="U14" s="14"/>
-      <c r="V14" s="195"/>
+      <c r="V14" s="191"/>
       <c r="W14" s="15"/>
       <c r="X14" s="11"/>
     </row>
@@ -3710,67 +3720,67 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="269"/>
-      <c r="C15" s="69" t="s">
+      <c r="B15" s="266"/>
+      <c r="C15" s="68" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="I15" s="43" t="s">
+      <c r="I15" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J15" s="70" t="s">
+      <c r="J15" s="69" t="s">
         <v>227</v>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="47">
         <v>50</v>
       </c>
-      <c r="L15" s="48">
+      <c r="L15" s="47">
         <v>50</v>
       </c>
-      <c r="M15" s="72">
+      <c r="M15" s="71">
         <v>2</v>
       </c>
-      <c r="N15" s="101">
+      <c r="N15" s="99">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O15" s="101">
+      <c r="O15" s="99">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="103" t="s">
+      <c r="P15" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="46">
+      <c r="Q15" s="45">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="R15" s="102">
+      <c r="R15" s="100">
         <f t="shared" si="2"/>
         <v>0.255</v>
       </c>
-      <c r="S15" s="102">
+      <c r="S15" s="100">
         <v>5.1000000000000004E-3</v>
       </c>
-      <c r="T15" s="102">
+      <c r="T15" s="100">
         <f t="shared" si="3"/>
         <v>0.255</v>
       </c>
       <c r="U15" s="14"/>
-      <c r="V15" s="195"/>
+      <c r="V15" s="191"/>
       <c r="W15" s="15"/>
       <c r="X15" s="11"/>
     </row>
@@ -3778,67 +3788,67 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="269"/>
-      <c r="C16" s="69" t="s">
+      <c r="B16" s="266"/>
+      <c r="C16" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="D16" s="151" t="s">
+      <c r="D16" s="149" t="s">
         <v>254</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="70" t="s">
         <v>255</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="I16" s="43" t="s">
+      <c r="I16" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="70" t="s">
+      <c r="J16" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="47">
         <v>50</v>
       </c>
-      <c r="L16" s="48">
+      <c r="L16" s="47">
         <v>50</v>
       </c>
-      <c r="M16" s="72">
+      <c r="M16" s="71">
         <v>1</v>
       </c>
-      <c r="N16" s="101">
+      <c r="N16" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O16" s="101">
+      <c r="O16" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="103" t="s">
+      <c r="P16" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="46">
+      <c r="Q16" s="45">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="R16" s="102">
+      <c r="R16" s="100">
         <f t="shared" si="2"/>
         <v>0.30499999999999999</v>
       </c>
-      <c r="S16" s="102">
+      <c r="S16" s="100">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="T16" s="102">
+      <c r="T16" s="100">
         <f>S16*L16</f>
         <v>0.30499999999999999</v>
       </c>
       <c r="U16" s="14"/>
-      <c r="V16" s="195"/>
+      <c r="V16" s="191"/>
       <c r="W16" s="15"/>
       <c r="X16" s="11"/>
     </row>
@@ -3846,67 +3856,67 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="270"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="267"/>
+      <c r="C17" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="D17" s="152" t="s">
+      <c r="D17" s="150" t="s">
         <v>257</v>
       </c>
-      <c r="E17" s="127" t="s">
+      <c r="E17" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="127" t="s">
+      <c r="F17" s="125" t="s">
         <v>258</v>
       </c>
-      <c r="G17" s="54" t="s">
+      <c r="G17" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="79" t="s">
+      <c r="J17" s="78" t="s">
         <v>262</v>
       </c>
-      <c r="K17" s="54">
+      <c r="K17" s="53">
         <v>50</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="53">
         <v>50</v>
       </c>
-      <c r="M17" s="83">
+      <c r="M17" s="82">
         <v>1</v>
       </c>
-      <c r="N17" s="58">
+      <c r="N17" s="57">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O17" s="58">
+      <c r="O17" s="57">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="106" t="s">
+      <c r="P17" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="58">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R17" s="107">
+      <c r="R17" s="105">
         <f t="shared" si="2"/>
         <v>0.38500000000000001</v>
       </c>
-      <c r="S17" s="107">
+      <c r="S17" s="105">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T17" s="107">
+      <c r="T17" s="105">
         <f>S17*L17</f>
         <v>0.38500000000000001</v>
       </c>
       <c r="U17" s="16"/>
-      <c r="V17" s="197"/>
+      <c r="V17" s="193"/>
       <c r="W17" s="17"/>
       <c r="X17" s="11"/>
     </row>
@@ -3914,209 +3924,211 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="271" t="s">
+      <c r="B18" s="268" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="162" t="s">
+      <c r="C18" s="160" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="130" t="s">
+      <c r="D18" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="H18" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="I18" s="37" t="s">
+      <c r="I18" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="65" t="s">
+      <c r="J18" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="34">
         <v>10</v>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="34">
         <v>30</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="66">
         <v>1</v>
       </c>
-      <c r="N18" s="39">
+      <c r="N18" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O18" s="39">
+      <c r="O18" s="38">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="128" t="s">
+      <c r="P18" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="40">
+      <c r="Q18" s="39">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="R18" s="41">
+      <c r="R18" s="40">
         <f t="shared" si="2"/>
         <v>0.626</v>
       </c>
-      <c r="S18" s="41">
+      <c r="S18" s="40">
         <v>6.1699999999999998E-2</v>
       </c>
-      <c r="T18" s="41">
+      <c r="T18" s="40">
         <f t="shared" si="3"/>
         <v>1.851</v>
       </c>
       <c r="U18" s="12"/>
-      <c r="V18" s="194"/>
+      <c r="V18" s="190"/>
       <c r="W18" s="13"/>
       <c r="X18" s="11"/>
     </row>
-    <row r="19" spans="1:24" ht="15.75" thickBot="1">
+    <row r="19" spans="1:24" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="272"/>
-      <c r="C19" s="184" t="s">
+      <c r="B19" s="269"/>
+      <c r="C19" s="182" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="185" t="s">
+      <c r="D19" s="183" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="185" t="s">
+      <c r="E19" s="183" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="185" t="s">
+      <c r="F19" s="183" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="186" t="s">
+      <c r="G19" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="187">
+      <c r="H19" s="185">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="I19" s="186" t="s">
+      <c r="I19" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="185" t="s">
+      <c r="J19" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="186">
+      <c r="K19" s="184">
         <v>10</v>
       </c>
-      <c r="L19" s="186">
+      <c r="L19" s="184">
         <v>50</v>
       </c>
-      <c r="M19" s="188">
+      <c r="M19" s="186">
         <v>2</v>
       </c>
-      <c r="N19" s="188">
+      <c r="N19" s="186">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="188">
+      <c r="O19" s="186">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="189" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q19" s="190">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="R19" s="191">
+      <c r="P19" s="278" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q19" s="187">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="R19" s="188">
         <f t="shared" si="2"/>
-        <v>0.39399999999999996</v>
-      </c>
-      <c r="S19" s="191">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="T19" s="191">
+        <v>2.38</v>
+      </c>
+      <c r="S19" s="188">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="T19" s="188">
         <f t="shared" si="3"/>
-        <v>1.97</v>
-      </c>
-      <c r="U19" s="207"/>
-      <c r="V19" s="192" t="s">
+        <v>11.899999999999999</v>
+      </c>
+      <c r="U19" s="203"/>
+      <c r="V19" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W19" s="193"/>
+      <c r="W19" s="276" t="s">
+        <v>135</v>
+      </c>
       <c r="X19" s="11"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="278" t="s">
+      <c r="B20" s="275" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="130" t="s">
+      <c r="D20" s="128" t="s">
         <v>187</v>
       </c>
-      <c r="E20" s="66" t="s">
+      <c r="E20" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="F20" s="66" t="s">
+      <c r="F20" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="36" t="s">
+      <c r="H20" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="I20" s="37" t="s">
+      <c r="I20" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="65" t="s">
+      <c r="J20" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="34">
         <v>50</v>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="34">
         <v>50</v>
       </c>
-      <c r="M20" s="67">
+      <c r="M20" s="66">
         <v>1</v>
       </c>
-      <c r="N20" s="39">
+      <c r="N20" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O20" s="39">
+      <c r="O20" s="38">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="128" t="s">
+      <c r="P20" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="40">
+      <c r="Q20" s="39">
         <v>2.07E-2</v>
       </c>
-      <c r="R20" s="41">
+      <c r="R20" s="40">
         <f t="shared" si="2"/>
         <v>1.0349999999999999</v>
       </c>
-      <c r="S20" s="41">
+      <c r="S20" s="40">
         <v>2.07E-2</v>
       </c>
-      <c r="T20" s="41">
+      <c r="T20" s="40">
         <f t="shared" si="3"/>
         <v>1.0349999999999999</v>
       </c>
       <c r="U20" s="12"/>
-      <c r="V20" s="194"/>
+      <c r="V20" s="190"/>
       <c r="W20" s="13"/>
       <c r="X20" s="11"/>
     </row>
@@ -4124,67 +4136,67 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="276"/>
-      <c r="C21" s="69" t="s">
+      <c r="B21" s="273"/>
+      <c r="C21" s="68" t="s">
         <v>228</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="93" t="s">
         <v>229</v>
       </c>
-      <c r="E21" s="71" t="s">
+      <c r="E21" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="F21" s="71" t="s">
+      <c r="F21" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="70" t="s">
+      <c r="J21" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="47">
         <v>20</v>
       </c>
-      <c r="L21" s="48">
+      <c r="L21" s="47">
         <v>50</v>
       </c>
-      <c r="M21" s="72">
+      <c r="M21" s="71">
         <v>2</v>
       </c>
-      <c r="N21" s="101">
+      <c r="N21" s="99">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O21" s="101">
+      <c r="O21" s="99">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="103" t="s">
+      <c r="P21" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q21" s="46">
+      <c r="Q21" s="45">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="R21" s="102">
+      <c r="R21" s="100">
         <f t="shared" si="2"/>
         <v>1.4860000000000002</v>
       </c>
-      <c r="S21" s="102">
+      <c r="S21" s="100">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="T21" s="102">
+      <c r="T21" s="100">
         <f t="shared" si="3"/>
         <v>3.7150000000000003</v>
       </c>
       <c r="U21" s="14"/>
-      <c r="V21" s="195"/>
+      <c r="V21" s="191"/>
       <c r="W21" s="15"/>
       <c r="X21" s="11"/>
     </row>
@@ -4192,67 +4204,67 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="276"/>
-      <c r="C22" s="69" t="s">
+      <c r="B22" s="273"/>
+      <c r="C22" s="68" t="s">
         <v>231</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="93" t="s">
         <v>232</v>
       </c>
-      <c r="E22" s="71" t="s">
+      <c r="E22" s="70" t="s">
         <v>233</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="70" t="s">
         <v>234</v>
       </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="H22" s="42" t="s">
+      <c r="H22" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="I22" s="43" t="s">
+      <c r="I22" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="70" t="s">
+      <c r="J22" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="47">
         <v>20</v>
       </c>
-      <c r="L22" s="48">
+      <c r="L22" s="47">
         <v>50</v>
       </c>
-      <c r="M22" s="72">
+      <c r="M22" s="71">
         <v>2</v>
       </c>
-      <c r="N22" s="101">
+      <c r="N22" s="99">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O22" s="101">
+      <c r="O22" s="99">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P22" s="103" t="s">
+      <c r="P22" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="46">
+      <c r="Q22" s="45">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="R22" s="102">
+      <c r="R22" s="100">
         <f t="shared" si="2"/>
         <v>0.154</v>
       </c>
-      <c r="S22" s="102">
+      <c r="S22" s="100">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="T22" s="102">
+      <c r="T22" s="100">
         <f t="shared" si="3"/>
         <v>0.38500000000000001</v>
       </c>
       <c r="U22" s="14"/>
-      <c r="V22" s="195"/>
+      <c r="V22" s="191"/>
       <c r="W22" s="15"/>
       <c r="X22" s="11"/>
     </row>
@@ -4260,67 +4272,67 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="277"/>
-      <c r="C23" s="108" t="s">
+      <c r="B23" s="274"/>
+      <c r="C23" s="106" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="152" t="s">
+      <c r="D23" s="150" t="s">
         <v>264</v>
       </c>
-      <c r="E23" s="127" t="s">
+      <c r="E23" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="127" t="s">
+      <c r="F23" s="125" t="s">
         <v>265</v>
       </c>
-      <c r="G23" s="54" t="s">
+      <c r="G23" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="55" t="s">
+      <c r="H23" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="I23" s="56" t="s">
+      <c r="I23" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="79" t="s">
+      <c r="J23" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="K23" s="54">
+      <c r="K23" s="53">
         <v>10</v>
       </c>
-      <c r="L23" s="54">
+      <c r="L23" s="53">
         <v>30</v>
       </c>
-      <c r="M23" s="83">
+      <c r="M23" s="82">
         <v>1</v>
       </c>
-      <c r="N23" s="58">
+      <c r="N23" s="57">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O23" s="58">
+      <c r="O23" s="57">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="106" t="s">
+      <c r="P23" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="59">
+      <c r="Q23" s="58">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="R23" s="107">
+      <c r="R23" s="105">
         <f t="shared" si="2"/>
         <v>0.91600000000000004</v>
       </c>
-      <c r="S23" s="107">
+      <c r="S23" s="105">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="T23" s="107">
+      <c r="T23" s="105">
         <f t="shared" si="3"/>
         <v>2.7480000000000002</v>
       </c>
       <c r="U23" s="16"/>
-      <c r="V23" s="197"/>
+      <c r="V23" s="193"/>
       <c r="W23" s="17"/>
       <c r="X23" s="11"/>
     </row>
@@ -4328,74 +4340,74 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="163" t="s">
+      <c r="C24" s="161" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="154" t="s">
+      <c r="D24" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="155" t="s">
+      <c r="E24" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="155" t="s">
+      <c r="F24" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="156" t="s">
+      <c r="G24" s="154" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="156" t="s">
+      <c r="H24" s="154" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="155" t="s">
+      <c r="I24" s="153" t="s">
         <v>145</v>
       </c>
-      <c r="J24" s="155" t="s">
+      <c r="J24" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="155">
+      <c r="K24" s="153">
         <v>42</v>
       </c>
-      <c r="L24" s="155">
+      <c r="L24" s="153">
         <v>162</v>
       </c>
-      <c r="M24" s="157">
+      <c r="M24" s="155">
         <v>8</v>
       </c>
-      <c r="N24" s="157">
+      <c r="N24" s="155">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="157">
+      <c r="O24" s="155">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="158" t="s">
+      <c r="P24" s="156" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="159">
+      <c r="Q24" s="157">
         <v>3.68</v>
       </c>
-      <c r="R24" s="160">
+      <c r="R24" s="158">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="160">
+      <c r="S24" s="158">
         <v>3.68</v>
       </c>
-      <c r="T24" s="160">
+      <c r="T24" s="158">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="161" t="s">
+      <c r="U24" s="159" t="s">
         <v>249</v>
       </c>
-      <c r="V24" s="192" t="s">
+      <c r="V24" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W24" s="177">
+      <c r="W24" s="175">
         <v>3.68</v>
       </c>
       <c r="X24" s="11"/>
@@ -4404,279 +4416,279 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="136" t="s">
+      <c r="B25" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="97" t="s">
+      <c r="C25" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="150" t="s">
+      <c r="D25" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="75" t="s">
+      <c r="F25" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="50" t="s">
+      <c r="G25" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H25" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="52" t="s">
+      <c r="I25" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="149" t="s">
+      <c r="J25" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="149">
+      <c r="K25" s="147">
         <v>10</v>
       </c>
-      <c r="L25" s="149">
+      <c r="L25" s="147">
         <v>30</v>
       </c>
-      <c r="M25" s="109">
+      <c r="M25" s="107">
         <v>1</v>
       </c>
-      <c r="N25" s="109">
+      <c r="N25" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="109">
+      <c r="O25" s="107">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="153" t="s">
+      <c r="P25" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="53">
+      <c r="Q25" s="52">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R25" s="110">
+      <c r="R25" s="108">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S25" s="110">
+      <c r="S25" s="108">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="T25" s="110">
+      <c r="T25" s="108">
         <f t="shared" si="3"/>
         <v>1.77</v>
       </c>
-      <c r="U25" s="29"/>
-      <c r="V25" s="198"/>
-      <c r="W25" s="30"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="194"/>
+      <c r="W25" s="29"/>
       <c r="X25" s="11"/>
     </row>
     <row r="26" spans="1:24" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="268" t="s">
+      <c r="B26" s="265" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="204" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="209" t="s">
+      <c r="D26" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="209" t="s">
+      <c r="E26" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="209" t="s">
+      <c r="F26" s="205" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="210" t="s">
+      <c r="G26" s="206" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="211" t="s">
+      <c r="H26" s="207" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="210" t="s">
+      <c r="I26" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="209" t="s">
+      <c r="J26" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="209">
+      <c r="K26" s="205">
         <v>7</v>
       </c>
-      <c r="L26" s="209">
+      <c r="L26" s="205">
         <v>23</v>
       </c>
-      <c r="M26" s="212">
+      <c r="M26" s="208">
         <v>1</v>
       </c>
-      <c r="N26" s="212">
+      <c r="N26" s="208">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="213">
+      <c r="O26" s="209">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="214" t="s">
+      <c r="P26" s="210" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="215">
+      <c r="Q26" s="211">
         <v>0.23949999999999999</v>
       </c>
-      <c r="R26" s="216">
+      <c r="R26" s="212">
         <f>Q26*K26</f>
         <v>1.6764999999999999</v>
       </c>
-      <c r="S26" s="216">
+      <c r="S26" s="212">
         <v>0.23949999999999999</v>
       </c>
-      <c r="T26" s="217">
+      <c r="T26" s="213">
         <f t="shared" si="3"/>
         <v>5.5084999999999997</v>
       </c>
-      <c r="U26" s="218"/>
-      <c r="V26" s="192" t="s">
+      <c r="U26" s="214"/>
+      <c r="V26" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W26" s="219"/>
+      <c r="W26" s="215"/>
       <c r="X26" s="11"/>
     </row>
     <row r="27" spans="1:24" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="269"/>
-      <c r="C27" s="220" t="s">
+      <c r="B27" s="266"/>
+      <c r="C27" s="216" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="221" t="s">
+      <c r="D27" s="217" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="222" t="s">
+      <c r="E27" s="218" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="222" t="s">
+      <c r="F27" s="218" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="223" t="s">
+      <c r="G27" s="219" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="224" t="s">
+      <c r="H27" s="220" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="223" t="s">
+      <c r="I27" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="222" t="s">
+      <c r="J27" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="222">
+      <c r="K27" s="218">
         <v>7</v>
       </c>
-      <c r="L27" s="222">
+      <c r="L27" s="218">
         <v>45</v>
       </c>
-      <c r="M27" s="225">
+      <c r="M27" s="221">
         <v>2</v>
       </c>
-      <c r="N27" s="225">
+      <c r="N27" s="221">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="225">
+      <c r="O27" s="221">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="226" t="s">
+      <c r="P27" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="227">
+      <c r="Q27" s="223">
         <v>0.11169999999999999</v>
       </c>
-      <c r="R27" s="228">
+      <c r="R27" s="224">
         <f t="shared" si="2"/>
         <v>0.78189999999999993</v>
       </c>
-      <c r="S27" s="228">
+      <c r="S27" s="224">
         <v>0.11169999999999999</v>
       </c>
-      <c r="T27" s="228">
+      <c r="T27" s="224">
         <f t="shared" si="3"/>
         <v>5.0264999999999995</v>
       </c>
-      <c r="U27" s="229"/>
-      <c r="V27" s="192" t="s">
+      <c r="U27" s="225"/>
+      <c r="V27" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W27" s="230"/>
+      <c r="W27" s="226"/>
       <c r="X27" s="11"/>
     </row>
     <row r="28" spans="1:24" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="270"/>
-      <c r="C28" s="78" t="s">
+      <c r="B28" s="267"/>
+      <c r="C28" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="122" t="s">
+      <c r="D28" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="E28" s="79" t="s">
+      <c r="E28" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="79" t="s">
+      <c r="F28" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="54" t="s">
+      <c r="G28" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="I28" s="56" t="s">
+      <c r="I28" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="J28" s="57" t="s">
+      <c r="J28" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="K28" s="57">
+      <c r="K28" s="56">
         <v>10</v>
       </c>
-      <c r="L28" s="57">
+      <c r="L28" s="56">
         <v>25</v>
       </c>
-      <c r="M28" s="58">
+      <c r="M28" s="57">
         <v>1</v>
       </c>
-      <c r="N28" s="58">
+      <c r="N28" s="57">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="58">
+      <c r="O28" s="57">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="111" t="s">
+      <c r="P28" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="59">
+      <c r="Q28" s="58">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="R28" s="107">
+      <c r="R28" s="105">
         <f t="shared" si="2"/>
         <v>0.99099999999999988</v>
       </c>
-      <c r="S28" s="107">
+      <c r="S28" s="105">
         <v>9.9099999999999994E-2</v>
       </c>
-      <c r="T28" s="107">
+      <c r="T28" s="105">
         <f t="shared" si="3"/>
         <v>2.4775</v>
       </c>
       <c r="U28" s="16"/>
-      <c r="V28" s="197"/>
+      <c r="V28" s="193"/>
       <c r="W28" s="17"/>
       <c r="X28" s="11"/>
     </row>
@@ -4684,69 +4696,69 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="268" t="s">
+      <c r="B29" s="265" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="76" t="s">
+      <c r="C29" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="164" t="s">
+      <c r="D29" s="162" t="s">
         <v>169</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="80" t="s">
+      <c r="F29" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="36" t="s">
+      <c r="H29" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="130" t="s">
+      <c r="I29" s="128" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="65" t="s">
+      <c r="J29" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="165">
+      <c r="K29" s="163">
         <v>100</v>
       </c>
-      <c r="L29" s="165">
+      <c r="L29" s="163">
         <v>100</v>
       </c>
-      <c r="M29" s="165">
+      <c r="M29" s="163">
         <v>3</v>
       </c>
-      <c r="N29" s="39">
+      <c r="N29" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="O29" s="39">
+      <c r="O29" s="38">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="166" t="s">
+      <c r="P29" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="40">
+      <c r="Q29" s="39">
         <v>1E-3</v>
       </c>
-      <c r="R29" s="41">
+      <c r="R29" s="40">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S29" s="41">
+      <c r="S29" s="40">
         <v>1E-3</v>
       </c>
-      <c r="T29" s="41">
+      <c r="T29" s="40">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="U29" s="12"/>
-      <c r="V29" s="194"/>
+      <c r="V29" s="190"/>
       <c r="W29" s="13"/>
       <c r="X29" s="11"/>
     </row>
@@ -4754,67 +4766,67 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="269"/>
-      <c r="C30" s="81" t="s">
+      <c r="B30" s="266"/>
+      <c r="C30" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="D30" s="183" t="s">
+      <c r="D30" s="181" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="70" t="s">
+      <c r="E30" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="70" t="s">
+      <c r="F30" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="G30" s="48" t="s">
+      <c r="G30" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H30" s="42" t="s">
+      <c r="H30" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="I30" s="95" t="s">
+      <c r="I30" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="70" t="s">
+      <c r="J30" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="K30" s="96">
+      <c r="K30" s="94">
         <v>100</v>
       </c>
-      <c r="L30" s="96">
+      <c r="L30" s="94">
         <v>100</v>
       </c>
-      <c r="M30" s="96">
+      <c r="M30" s="94">
         <v>1</v>
       </c>
-      <c r="N30" s="101">
+      <c r="N30" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O30" s="101">
+      <c r="O30" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="104" t="s">
+      <c r="P30" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="46">
+      <c r="Q30" s="45">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="R30" s="102">
+      <c r="R30" s="100">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="S30" s="102">
+      <c r="S30" s="100">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="T30" s="102">
+      <c r="T30" s="100">
         <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
       <c r="U30" s="14"/>
-      <c r="V30" s="195"/>
+      <c r="V30" s="191"/>
       <c r="W30" s="15"/>
       <c r="X30" s="11"/>
     </row>
@@ -4822,67 +4834,67 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="269"/>
-      <c r="C31" s="81" t="s">
+      <c r="B31" s="266"/>
+      <c r="C31" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="129" t="s">
+      <c r="D31" s="127" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="70" t="s">
+      <c r="E31" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="69" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="48" t="s">
+      <c r="G31" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="42" t="s">
+      <c r="H31" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="I31" s="95" t="s">
+      <c r="I31" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="70" t="s">
+      <c r="J31" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="96">
+      <c r="K31" s="94">
         <v>100</v>
       </c>
-      <c r="L31" s="96">
+      <c r="L31" s="94">
         <v>100</v>
       </c>
-      <c r="M31" s="96">
+      <c r="M31" s="94">
         <v>1</v>
       </c>
-      <c r="N31" s="101">
+      <c r="N31" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O31" s="101">
+      <c r="O31" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P31" s="104" t="s">
+      <c r="P31" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="46">
+      <c r="Q31" s="45">
         <v>1.5E-3</v>
       </c>
-      <c r="R31" s="102">
+      <c r="R31" s="100">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
-      <c r="S31" s="102">
+      <c r="S31" s="100">
         <v>1.5E-3</v>
       </c>
-      <c r="T31" s="102">
+      <c r="T31" s="100">
         <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
       <c r="U31" s="14"/>
-      <c r="V31" s="195"/>
+      <c r="V31" s="191"/>
       <c r="W31" s="15"/>
       <c r="X31" s="11"/>
     </row>
@@ -4890,67 +4902,67 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="269"/>
-      <c r="C32" s="81" t="s">
+      <c r="B32" s="266"/>
+      <c r="C32" s="80" t="s">
         <v>238</v>
       </c>
-      <c r="D32" s="129" t="s">
+      <c r="D32" s="127" t="s">
         <v>239</v>
       </c>
-      <c r="E32" s="70" t="s">
+      <c r="E32" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="69" t="s">
         <v>240</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="I32" s="95" t="s">
+      <c r="I32" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="J32" s="70" t="s">
+      <c r="J32" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="K32" s="96">
+      <c r="K32" s="94">
         <v>100</v>
       </c>
-      <c r="L32" s="96">
+      <c r="L32" s="94">
         <v>100</v>
       </c>
-      <c r="M32" s="96">
+      <c r="M32" s="94">
         <v>4</v>
       </c>
-      <c r="N32" s="101">
+      <c r="N32" s="99">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="O32" s="101">
+      <c r="O32" s="99">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="P32" s="104" t="s">
+      <c r="P32" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="46">
+      <c r="Q32" s="45">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R32" s="102">
+      <c r="R32" s="100">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="S32" s="102">
+      <c r="S32" s="100">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T32" s="102">
+      <c r="T32" s="100">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
       <c r="U32" s="14"/>
-      <c r="V32" s="195"/>
+      <c r="V32" s="191"/>
       <c r="W32" s="15"/>
       <c r="X32" s="11"/>
     </row>
@@ -4958,353 +4970,355 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="270"/>
-      <c r="C33" s="78" t="s">
+      <c r="B33" s="267"/>
+      <c r="C33" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="167" t="s">
+      <c r="D33" s="165" t="s">
         <v>281</v>
       </c>
-      <c r="E33" s="79" t="s">
+      <c r="E33" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="79" t="s">
+      <c r="F33" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="G33" s="54" t="s">
+      <c r="G33" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="55" t="s">
+      <c r="H33" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="137" t="s">
+      <c r="I33" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="79" t="s">
+      <c r="J33" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="168">
+      <c r="K33" s="166">
         <v>100</v>
       </c>
-      <c r="L33" s="168">
+      <c r="L33" s="166">
         <v>100</v>
       </c>
-      <c r="M33" s="168">
+      <c r="M33" s="166">
         <v>2</v>
       </c>
-      <c r="N33" s="58">
+      <c r="N33" s="57">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O33" s="58">
+      <c r="O33" s="57">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="169" t="s">
+      <c r="P33" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="59">
+      <c r="Q33" s="58">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="107">
+      <c r="R33" s="105">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="107">
+      <c r="S33" s="105">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="107">
+      <c r="T33" s="105">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U33" s="16"/>
-      <c r="V33" s="197"/>
+      <c r="V33" s="193"/>
       <c r="W33" s="17"/>
       <c r="X33" s="11"/>
     </row>
-    <row r="34" spans="1:24" ht="15.75" thickBot="1">
+    <row r="34" spans="1:24" ht="16.5" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="268" t="s">
+      <c r="B34" s="265" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="208" t="s">
+      <c r="C34" s="204" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="209" t="s">
+      <c r="D34" s="205" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="231" t="s">
+      <c r="E34" s="227" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="231" t="s">
+      <c r="F34" s="227" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="232" t="s">
+      <c r="G34" s="228" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="233" t="s">
+      <c r="H34" s="229" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="232" t="s">
+      <c r="I34" s="228" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="231" t="s">
+      <c r="J34" s="227" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="231">
+      <c r="K34" s="227">
         <v>11</v>
       </c>
-      <c r="L34" s="231">
+      <c r="L34" s="227">
         <v>42</v>
       </c>
-      <c r="M34" s="213">
+      <c r="M34" s="209">
         <v>2</v>
       </c>
-      <c r="N34" s="213">
+      <c r="N34" s="209">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="213">
+      <c r="O34" s="209">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="234" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q34" s="235">
-        <v>0.64739999999999998</v>
-      </c>
-      <c r="R34" s="217">
+      <c r="P34" s="230" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q34" s="231">
+        <v>0.318</v>
+      </c>
+      <c r="R34" s="213">
         <f t="shared" si="2"/>
-        <v>7.1213999999999995</v>
-      </c>
-      <c r="S34" s="217">
+        <v>3.4980000000000002</v>
+      </c>
+      <c r="S34" s="213">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="217">
+      <c r="T34" s="213">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="236"/>
-      <c r="V34" s="192" t="s">
+      <c r="U34" s="232"/>
+      <c r="V34" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W34" s="237"/>
+      <c r="W34" s="277" t="s">
+        <v>135</v>
+      </c>
       <c r="X34" s="11"/>
     </row>
     <row r="35" spans="1:24" ht="26.25" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="269"/>
-      <c r="C35" s="220" t="s">
+      <c r="B35" s="266"/>
+      <c r="C35" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="221" t="s">
+      <c r="D35" s="217" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="222" t="s">
+      <c r="E35" s="218" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="222" t="s">
+      <c r="F35" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="223" t="s">
+      <c r="G35" s="219" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="223" t="s">
+      <c r="H35" s="219" t="s">
         <v>134</v>
       </c>
-      <c r="I35" s="223" t="s">
+      <c r="I35" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="222" t="s">
+      <c r="J35" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="223">
+      <c r="K35" s="219">
         <v>6</v>
       </c>
-      <c r="L35" s="223">
+      <c r="L35" s="219">
         <v>21</v>
       </c>
-      <c r="M35" s="225">
+      <c r="M35" s="221">
         <v>1</v>
       </c>
-      <c r="N35" s="225">
+      <c r="N35" s="221">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="225">
+      <c r="O35" s="221">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="226" t="s">
+      <c r="P35" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="227">
+      <c r="Q35" s="223">
         <v>0.39889999999999998</v>
       </c>
-      <c r="R35" s="228">
+      <c r="R35" s="224">
         <f t="shared" si="2"/>
         <v>2.3933999999999997</v>
       </c>
-      <c r="S35" s="228">
+      <c r="S35" s="224">
         <v>0.33829999999999999</v>
       </c>
-      <c r="T35" s="228">
+      <c r="T35" s="224">
         <f t="shared" si="3"/>
         <v>7.1042999999999994</v>
       </c>
-      <c r="U35" s="229"/>
-      <c r="V35" s="192" t="s">
+      <c r="U35" s="225"/>
+      <c r="V35" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W35" s="230"/>
+      <c r="W35" s="226"/>
       <c r="X35" s="11"/>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="269"/>
-      <c r="C36" s="220" t="s">
+      <c r="B36" s="266"/>
+      <c r="C36" s="216" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="221" t="s">
+      <c r="D36" s="217" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="222" t="s">
+      <c r="E36" s="218" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="222" t="s">
+      <c r="F36" s="218" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="223" t="s">
+      <c r="G36" s="219" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="223" t="s">
+      <c r="H36" s="219" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="222" t="s">
+      <c r="I36" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="222" t="s">
+      <c r="J36" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="223">
+      <c r="K36" s="219">
         <v>6</v>
       </c>
-      <c r="L36" s="223">
+      <c r="L36" s="219">
         <v>21</v>
       </c>
-      <c r="M36" s="225">
+      <c r="M36" s="221">
         <v>1</v>
       </c>
-      <c r="N36" s="225">
+      <c r="N36" s="221">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="225">
+      <c r="O36" s="221">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="226" t="s">
+      <c r="P36" s="222" t="s">
         <v>153</v>
       </c>
-      <c r="Q36" s="238">
+      <c r="Q36" s="233">
         <v>8</v>
       </c>
-      <c r="R36" s="228">
+      <c r="R36" s="224">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="228">
+      <c r="S36" s="224">
         <v>8</v>
       </c>
-      <c r="T36" s="228">
+      <c r="T36" s="224">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="239"/>
-      <c r="V36" s="192" t="s">
+      <c r="U36" s="234"/>
+      <c r="V36" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W36" s="240"/>
+      <c r="W36" s="235"/>
       <c r="X36" s="11"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="269"/>
-      <c r="C37" s="87" t="s">
+      <c r="B37" s="266"/>
+      <c r="C37" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="123" t="s">
+      <c r="D37" s="121" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="88" t="s">
+      <c r="E37" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="88" t="s">
+      <c r="F37" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="G37" s="89" t="s">
+      <c r="G37" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="89" t="s">
+      <c r="H37" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="88" t="s">
+      <c r="I37" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="88" t="s">
+      <c r="J37" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="89">
+      <c r="K37" s="88">
         <v>11</v>
       </c>
-      <c r="L37" s="89">
+      <c r="L37" s="88">
         <v>41</v>
       </c>
-      <c r="M37" s="90">
+      <c r="M37" s="89">
         <v>2</v>
       </c>
-      <c r="N37" s="90">
+      <c r="N37" s="89">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O37" s="101">
+      <c r="O37" s="99">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P37" s="91" t="s">
+      <c r="P37" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="Q37" s="279">
+      <c r="Q37" s="250">
         <v>4.76</v>
       </c>
-      <c r="R37" s="105">
+      <c r="R37" s="103">
         <f t="shared" si="2"/>
         <v>52.36</v>
       </c>
-      <c r="S37" s="105">
+      <c r="S37" s="103">
         <v>4.76</v>
       </c>
-      <c r="T37" s="280">
+      <c r="T37" s="251">
         <f t="shared" si="3"/>
         <v>195.16</v>
       </c>
-      <c r="U37" s="92" t="s">
+      <c r="U37" s="91" t="s">
         <v>297</v>
       </c>
-      <c r="V37" s="192" t="s">
+      <c r="V37" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W37" s="93">
-        <v>10.18</v>
+      <c r="W37" s="250">
+        <v>4.76</v>
       </c>
       <c r="X37" s="11"/>
     </row>
@@ -5312,67 +5326,67 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="269"/>
-      <c r="C38" s="81" t="s">
+      <c r="B38" s="266"/>
+      <c r="C38" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="121" t="s">
+      <c r="D38" s="119" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="70" t="s">
+      <c r="E38" s="69" t="s">
         <v>209</v>
       </c>
-      <c r="F38" s="70" t="s">
+      <c r="F38" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="H38" s="48" t="s">
+      <c r="H38" s="47" t="s">
         <v>211</v>
       </c>
-      <c r="I38" s="43" t="s">
+      <c r="I38" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="44" t="s">
+      <c r="J38" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="48">
+      <c r="K38" s="47">
         <v>6</v>
       </c>
-      <c r="L38" s="48">
+      <c r="L38" s="47">
         <v>21</v>
       </c>
-      <c r="M38" s="72">
+      <c r="M38" s="71">
         <v>1</v>
       </c>
-      <c r="N38" s="101">
+      <c r="N38" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O38" s="101">
+      <c r="O38" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P38" s="94" t="s">
+      <c r="P38" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q38" s="46">
+      <c r="Q38" s="45">
         <v>2.3479000000000001</v>
       </c>
-      <c r="R38" s="102">
+      <c r="R38" s="100">
         <f t="shared" si="2"/>
         <v>14.087400000000001</v>
       </c>
-      <c r="S38" s="102">
+      <c r="S38" s="100">
         <v>2.3479000000000001</v>
       </c>
-      <c r="T38" s="102">
+      <c r="T38" s="100">
         <f t="shared" si="3"/>
         <v>49.305900000000001</v>
       </c>
-      <c r="U38" s="21"/>
-      <c r="V38" s="199"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="195"/>
       <c r="W38" s="15"/>
       <c r="X38" s="11"/>
     </row>
@@ -5380,67 +5394,67 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="269"/>
-      <c r="C39" s="81" t="s">
+      <c r="B39" s="266"/>
+      <c r="C39" s="80" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="121" t="s">
+      <c r="D39" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E39" s="70" t="s">
+      <c r="E39" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="F39" s="70" t="s">
+      <c r="F39" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="G39" s="48" t="s">
+      <c r="G39" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="48" t="s">
+      <c r="H39" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="I39" s="43" t="s">
+      <c r="I39" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="44" t="s">
+      <c r="J39" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="48">
+      <c r="K39" s="47">
         <v>6</v>
       </c>
-      <c r="L39" s="48">
+      <c r="L39" s="47">
         <v>21</v>
       </c>
-      <c r="M39" s="72">
+      <c r="M39" s="71">
         <v>1</v>
       </c>
-      <c r="N39" s="101">
+      <c r="N39" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O39" s="101">
+      <c r="O39" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="94" t="s">
+      <c r="P39" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q39" s="46">
+      <c r="Q39" s="45">
         <v>0.74660000000000004</v>
       </c>
-      <c r="R39" s="102">
+      <c r="R39" s="100">
         <f t="shared" si="2"/>
         <v>4.4796000000000005</v>
       </c>
-      <c r="S39" s="102">
+      <c r="S39" s="100">
         <v>0.60960000000000003</v>
       </c>
-      <c r="T39" s="102">
+      <c r="T39" s="100">
         <f t="shared" si="3"/>
         <v>12.801600000000001</v>
       </c>
-      <c r="U39" s="21"/>
-      <c r="V39" s="199"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="195"/>
       <c r="W39" s="15"/>
       <c r="X39" s="11"/>
     </row>
@@ -5448,757 +5462,761 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="269"/>
-      <c r="C40" s="220" t="s">
+      <c r="B40" s="266"/>
+      <c r="C40" s="216" t="s">
         <v>271</v>
       </c>
-      <c r="D40" s="221" t="s">
+      <c r="D40" s="217" t="s">
         <v>272</v>
       </c>
-      <c r="E40" s="222" t="s">
+      <c r="E40" s="218" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="222" t="s">
+      <c r="F40" s="218" t="s">
         <v>273</v>
       </c>
-      <c r="G40" s="223" t="s">
+      <c r="G40" s="219" t="s">
         <v>279</v>
       </c>
-      <c r="H40" s="223"/>
-      <c r="I40" s="223" t="s">
+      <c r="H40" s="219"/>
+      <c r="I40" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="222" t="s">
+      <c r="J40" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="223">
+      <c r="K40" s="219">
         <v>6</v>
       </c>
-      <c r="L40" s="223">
+      <c r="L40" s="219">
         <v>22</v>
       </c>
-      <c r="M40" s="225">
+      <c r="M40" s="221">
         <v>1</v>
       </c>
-      <c r="N40" s="225">
+      <c r="N40" s="221">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="225">
+      <c r="O40" s="221">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="253" t="s">
+      <c r="P40" s="248" t="s">
         <v>244</v>
       </c>
-      <c r="Q40" s="227">
+      <c r="Q40" s="223">
         <v>0.8</v>
       </c>
-      <c r="R40" s="228">
+      <c r="R40" s="224">
         <f t="shared" si="2"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S40" s="228">
+      <c r="S40" s="224">
         <v>0.8</v>
       </c>
-      <c r="T40" s="228">
+      <c r="T40" s="224">
         <f t="shared" si="3"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="U40" s="252" t="s">
+      <c r="U40" s="247" t="s">
         <v>280</v>
       </c>
-      <c r="V40" s="192" t="s">
+      <c r="V40" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W40" s="230"/>
+      <c r="W40" s="226"/>
       <c r="X40" s="11"/>
     </row>
     <row r="41" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="269"/>
-      <c r="C41" s="241" t="s">
+      <c r="A41" s="6">
+        <v>39</v>
+      </c>
+      <c r="B41" s="266"/>
+      <c r="C41" s="236" t="s">
         <v>284</v>
       </c>
-      <c r="D41" s="242" t="s">
+      <c r="D41" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="E41" s="243" t="s">
+      <c r="E41" s="238" t="s">
         <v>285</v>
       </c>
-      <c r="F41" s="244" t="s">
+      <c r="F41" s="239" t="s">
         <v>286</v>
       </c>
-      <c r="G41" s="245" t="s">
+      <c r="G41" s="240" t="s">
         <v>287</v>
       </c>
-      <c r="H41" s="245" t="s">
+      <c r="H41" s="240" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="223" t="s">
+      <c r="I41" s="219" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="222" t="s">
+      <c r="J41" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="245">
+      <c r="K41" s="240">
         <v>10</v>
       </c>
-      <c r="L41" s="245">
+      <c r="L41" s="240">
         <v>30</v>
       </c>
-      <c r="M41" s="246">
+      <c r="M41" s="241">
         <v>1</v>
       </c>
-      <c r="N41" s="246">
+      <c r="N41" s="241">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="246">
+      <c r="O41" s="241">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="247" t="s">
+      <c r="P41" s="242" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="248">
+      <c r="Q41" s="243">
         <v>1</v>
       </c>
-      <c r="R41" s="249">
+      <c r="R41" s="244">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="249">
+      <c r="S41" s="244">
         <v>1</v>
       </c>
-      <c r="T41" s="228">
+      <c r="T41" s="224">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="250"/>
-      <c r="V41" s="192" t="s">
+      <c r="U41" s="245"/>
+      <c r="V41" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W41" s="251"/>
+      <c r="W41" s="246"/>
       <c r="X41" s="11"/>
     </row>
     <row r="42" spans="1:24" ht="26.25" thickBot="1">
       <c r="A42" s="6">
+        <v>40</v>
+      </c>
+      <c r="B42" s="267"/>
+      <c r="C42" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="I42" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="270"/>
-      <c r="C42" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" s="122" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="G42" s="57" t="s">
-        <v>138</v>
-      </c>
-      <c r="H42" s="57" t="s">
-        <v>139</v>
-      </c>
-      <c r="I42" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="J42" s="57" t="s">
+      <c r="J42" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="54">
+      <c r="K42" s="53">
         <v>10</v>
       </c>
-      <c r="L42" s="54">
+      <c r="L42" s="53">
         <v>30</v>
       </c>
-      <c r="M42" s="83">
+      <c r="M42" s="82">
         <v>1</v>
       </c>
-      <c r="N42" s="58">
+      <c r="N42" s="57">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="58">
+      <c r="O42" s="57">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="84" t="s">
+      <c r="P42" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="59">
+      <c r="Q42" s="58">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="R42" s="107">
+      <c r="R42" s="105">
         <f t="shared" si="2"/>
         <v>0.53500000000000003</v>
       </c>
-      <c r="S42" s="107">
+      <c r="S42" s="105">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="T42" s="107">
+      <c r="T42" s="105">
         <f t="shared" si="3"/>
         <v>1.605</v>
       </c>
-      <c r="U42" s="22"/>
-      <c r="V42" s="200"/>
+      <c r="U42" s="21"/>
+      <c r="V42" s="196"/>
       <c r="W42" s="17"/>
       <c r="X42" s="11"/>
     </row>
     <row r="43" spans="1:24" ht="15.75" thickBot="1">
       <c r="A43" s="6">
-        <v>40</v>
-      </c>
-      <c r="B43" s="268" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="265" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="77" t="s">
+      <c r="D43" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="80" t="s">
+      <c r="F43" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="39" t="s">
+      <c r="G43" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="H43" s="39" t="s">
+      <c r="H43" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="I43" s="38" t="s">
+      <c r="I43" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="J43" s="38" t="s">
+      <c r="J43" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="61">
+      <c r="K43" s="60">
         <v>50</v>
       </c>
-      <c r="L43" s="61">
+      <c r="L43" s="60">
         <v>50</v>
       </c>
-      <c r="M43" s="62">
+      <c r="M43" s="61">
         <v>1</v>
       </c>
-      <c r="N43" s="39">
+      <c r="N43" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="39">
+      <c r="O43" s="38">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P43" s="85" t="s">
+      <c r="P43" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="40">
+      <c r="Q43" s="39">
         <v>1.4E-2</v>
       </c>
-      <c r="R43" s="41">
+      <c r="R43" s="40">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="S43" s="41">
+      <c r="S43" s="40">
         <v>1.4E-2</v>
       </c>
-      <c r="T43" s="41">
+      <c r="T43" s="40">
         <f t="shared" si="3"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="U43" s="23"/>
-      <c r="V43" s="201"/>
+      <c r="U43" s="22"/>
+      <c r="V43" s="197"/>
       <c r="W43" s="13"/>
       <c r="X43" s="11"/>
     </row>
     <row r="44" spans="1:24" ht="26.25" thickBot="1">
       <c r="A44" s="6">
-        <v>41</v>
-      </c>
-      <c r="B44" s="269"/>
-      <c r="C44" s="81" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="266"/>
+      <c r="C44" s="80" t="s">
         <v>291</v>
       </c>
-      <c r="D44" s="121" t="s">
+      <c r="D44" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="70" t="s">
+      <c r="F44" s="69" t="s">
         <v>292</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="H44" s="44" t="s">
+      <c r="H44" s="43" t="s">
         <v>294</v>
       </c>
-      <c r="I44" s="44" t="s">
+      <c r="I44" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J44" s="44" t="s">
+      <c r="J44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="44">
+      <c r="K44" s="43">
         <v>10</v>
       </c>
-      <c r="L44" s="44">
+      <c r="L44" s="43">
         <v>30</v>
       </c>
-      <c r="M44" s="63">
+      <c r="M44" s="62">
         <v>1</v>
       </c>
-      <c r="N44" s="101">
+      <c r="N44" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O44" s="101">
+      <c r="O44" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="94" t="s">
+      <c r="P44" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="60">
+      <c r="Q44" s="59">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="R44" s="102">
+      <c r="R44" s="100">
         <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
-      <c r="S44" s="102">
+      <c r="S44" s="100">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="T44" s="102">
+      <c r="T44" s="100">
         <f t="shared" si="3"/>
         <v>1.77</v>
       </c>
-      <c r="U44" s="27"/>
-      <c r="V44" s="202"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="198"/>
       <c r="W44" s="15"/>
       <c r="X44" s="11"/>
     </row>
     <row r="45" spans="1:24" ht="15.75" thickBot="1">
       <c r="A45" s="6">
-        <v>42</v>
-      </c>
-      <c r="B45" s="269"/>
-      <c r="C45" s="81" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="266"/>
+      <c r="C45" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="121" t="s">
+      <c r="D45" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="70" t="s">
+      <c r="E45" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="86" t="s">
+      <c r="F45" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G45" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="I45" s="44" t="s">
+      <c r="I45" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="J45" s="44" t="s">
+      <c r="J45" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="44">
+      <c r="K45" s="43">
         <v>50</v>
       </c>
-      <c r="L45" s="44">
+      <c r="L45" s="43">
         <v>50</v>
       </c>
-      <c r="M45" s="63">
+      <c r="M45" s="62">
         <v>1</v>
       </c>
-      <c r="N45" s="101">
+      <c r="N45" s="99">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O45" s="101">
+      <c r="O45" s="99">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="82" t="s">
+      <c r="P45" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="46">
+      <c r="Q45" s="45">
         <v>1.26E-2</v>
       </c>
-      <c r="R45" s="102">
+      <c r="R45" s="100">
         <f t="shared" si="2"/>
         <v>0.63</v>
       </c>
-      <c r="S45" s="102">
+      <c r="S45" s="100">
         <v>1.26E-2</v>
       </c>
-      <c r="T45" s="102">
+      <c r="T45" s="100">
         <f t="shared" si="3"/>
         <v>0.63</v>
       </c>
-      <c r="U45" s="28"/>
-      <c r="V45" s="203"/>
+      <c r="U45" s="27"/>
+      <c r="V45" s="199"/>
       <c r="W45" s="15"/>
       <c r="X45" s="11"/>
     </row>
     <row r="46" spans="1:24" ht="15.75" thickBot="1">
       <c r="A46" s="6">
-        <v>43</v>
-      </c>
-      <c r="B46" s="269"/>
-      <c r="C46" s="220" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="266"/>
+      <c r="C46" s="216" t="s">
         <v>274</v>
       </c>
-      <c r="D46" s="221" t="s">
+      <c r="D46" s="217" t="s">
         <v>275</v>
       </c>
-      <c r="E46" s="222" t="s">
+      <c r="E46" s="218" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="222" t="s">
+      <c r="F46" s="218" t="s">
         <v>276</v>
       </c>
-      <c r="G46" s="222" t="s">
+      <c r="G46" s="218" t="s">
         <v>277</v>
       </c>
-      <c r="H46" s="222" t="s">
+      <c r="H46" s="218" t="s">
         <v>278</v>
       </c>
-      <c r="I46" s="222" t="s">
+      <c r="I46" s="218" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="222" t="s">
+      <c r="J46" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="222">
+      <c r="K46" s="218">
         <v>5</v>
       </c>
-      <c r="L46" s="222">
+      <c r="L46" s="218">
         <v>25</v>
       </c>
-      <c r="M46" s="225">
+      <c r="M46" s="221">
         <v>1</v>
       </c>
-      <c r="N46" s="225">
+      <c r="N46" s="221">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="225">
+      <c r="O46" s="221">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="253" t="s">
+      <c r="P46" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="227">
+      <c r="Q46" s="223">
         <v>0.1002</v>
       </c>
-      <c r="R46" s="228">
+      <c r="R46" s="224">
         <f t="shared" si="2"/>
         <v>0.501</v>
       </c>
-      <c r="S46" s="228">
+      <c r="S46" s="224">
         <v>0.1002</v>
       </c>
-      <c r="T46" s="228">
+      <c r="T46" s="224">
         <f t="shared" si="3"/>
         <v>2.5049999999999999</v>
       </c>
-      <c r="U46" s="254"/>
-      <c r="V46" s="192" t="s">
+      <c r="U46" s="249"/>
+      <c r="V46" s="189" t="s">
         <v>295</v>
       </c>
-      <c r="W46" s="230"/>
+      <c r="W46" s="226"/>
       <c r="X46" s="11"/>
     </row>
     <row r="47" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="269"/>
-      <c r="C47" s="97" t="s">
+      <c r="A47" s="6">
+        <v>45</v>
+      </c>
+      <c r="B47" s="266"/>
+      <c r="C47" s="95" t="s">
         <v>288</v>
       </c>
-      <c r="D47" s="75" t="s">
+      <c r="D47" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="E47" s="70" t="s">
+      <c r="E47" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="182">
+      <c r="F47" s="180">
         <v>61300611121</v>
       </c>
-      <c r="G47" s="149" t="s">
+      <c r="G47" s="147" t="s">
         <v>289</v>
       </c>
-      <c r="H47" s="149" t="s">
+      <c r="H47" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="I47" s="149" t="s">
+      <c r="I47" s="147" t="s">
         <v>290</v>
       </c>
-      <c r="J47" s="44" t="s">
+      <c r="J47" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="149">
+      <c r="K47" s="147">
         <v>20</v>
       </c>
-      <c r="L47" s="149">
+      <c r="L47" s="147">
         <v>40</v>
       </c>
-      <c r="M47" s="180">
+      <c r="M47" s="178">
         <v>1</v>
       </c>
-      <c r="N47" s="109">
+      <c r="N47" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="109">
+      <c r="O47" s="107">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="179" t="s">
+      <c r="P47" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="53">
+      <c r="Q47" s="52">
         <v>0.03</v>
       </c>
-      <c r="R47" s="102">
+      <c r="R47" s="100">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="S47" s="110">
+      <c r="S47" s="108">
         <v>0.03</v>
       </c>
-      <c r="T47" s="102">
+      <c r="T47" s="100">
         <f t="shared" si="3"/>
         <v>1.2</v>
       </c>
-      <c r="U47" s="181"/>
-      <c r="V47" s="204"/>
-      <c r="W47" s="30"/>
+      <c r="U47" s="179"/>
+      <c r="V47" s="200"/>
+      <c r="W47" s="29"/>
       <c r="X47" s="11"/>
     </row>
     <row r="48" spans="1:24" ht="115.5" thickBot="1">
       <c r="A48" s="6">
-        <v>44</v>
-      </c>
-      <c r="B48" s="270"/>
-      <c r="C48" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="267"/>
+      <c r="C48" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="113" t="s">
+      <c r="D48" s="111" t="s">
         <v>243</v>
       </c>
-      <c r="E48" s="114" t="s">
+      <c r="E48" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="114" t="s">
+      <c r="F48" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="115" t="s">
+      <c r="G48" s="113" t="s">
         <v>144</v>
       </c>
-      <c r="H48" s="115"/>
-      <c r="I48" s="116"/>
-      <c r="J48" s="116" t="s">
+      <c r="H48" s="113"/>
+      <c r="I48" s="114"/>
+      <c r="J48" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="116" t="s">
+      <c r="K48" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="L48" s="116" t="s">
+      <c r="L48" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="117">
+      <c r="M48" s="115">
         <v>53</v>
       </c>
-      <c r="N48" s="118">
+      <c r="N48" s="116">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O48" s="58">
+      <c r="O48" s="57">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="115" t="s">
+      <c r="P48" s="113" t="s">
         <v>144</v>
       </c>
-      <c r="Q48" s="116" t="s">
+      <c r="Q48" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="116" t="s">
+      <c r="R48" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="S48" s="116" t="s">
+      <c r="S48" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="T48" s="116" t="s">
+      <c r="T48" s="114" t="s">
         <v>144</v>
       </c>
-      <c r="U48" s="119" t="s">
+      <c r="U48" s="117" t="s">
         <v>149</v>
       </c>
-      <c r="V48" s="205"/>
-      <c r="W48" s="120"/>
+      <c r="V48" s="201"/>
+      <c r="W48" s="118"/>
       <c r="X48" s="11"/>
     </row>
     <row r="49" spans="1:24" ht="26.25" thickBot="1">
       <c r="A49" s="6">
-        <v>45</v>
-      </c>
-      <c r="B49" s="276" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="273" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="171" t="s">
+      <c r="C49" s="169" t="s">
         <v>251</v>
       </c>
-      <c r="D49" s="172" t="s">
+      <c r="D49" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="172" t="s">
+      <c r="E49" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="172" t="s">
+      <c r="F49" s="170" t="s">
         <v>250</v>
       </c>
-      <c r="G49" s="172" t="s">
+      <c r="G49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="H49" s="172" t="s">
+      <c r="H49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="I49" s="172" t="s">
+      <c r="I49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="172" t="s">
+      <c r="J49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="K49" s="172" t="s">
+      <c r="K49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="172" t="s">
+      <c r="L49" s="170" t="s">
         <v>144</v>
       </c>
-      <c r="M49" s="170">
+      <c r="M49" s="168">
         <v>1</v>
       </c>
-      <c r="N49" s="45">
+      <c r="N49" s="44">
         <f>M49*5</f>
         <v>5</v>
       </c>
-      <c r="O49" s="45">
+      <c r="O49" s="44">
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="173" t="s">
+      <c r="P49" s="171" t="s">
         <v>244</v>
       </c>
-      <c r="Q49" s="174">
+      <c r="Q49" s="172">
         <v>0.2</v>
       </c>
-      <c r="R49" s="175">
+      <c r="R49" s="173">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="174">
+      <c r="S49" s="172">
         <v>0.2</v>
       </c>
-      <c r="T49" s="47">
+      <c r="T49" s="46">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="176"/>
-      <c r="V49" s="206"/>
-      <c r="W49" s="178"/>
+      <c r="U49" s="174"/>
+      <c r="V49" s="202"/>
+      <c r="W49" s="176"/>
       <c r="X49" s="11"/>
     </row>
     <row r="50" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A50" s="18">
-        <v>46</v>
-      </c>
-      <c r="B50" s="277"/>
-      <c r="C50" s="131" t="s">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="274"/>
+      <c r="C50" s="129" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="132" t="s">
+      <c r="D50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="132" t="s">
+      <c r="E50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="133" t="s">
+      <c r="F50" s="131" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="132" t="s">
+      <c r="G50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="132" t="s">
+      <c r="H50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="132" t="s">
+      <c r="I50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="132" t="s">
+      <c r="J50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="132" t="s">
+      <c r="K50" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="132" t="s">
+      <c r="L50" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="124">
+      <c r="M50" s="122">
         <v>1</v>
       </c>
-      <c r="N50" s="124">
+      <c r="N50" s="122">
         <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
-      <c r="O50" s="58">
+      <c r="O50" s="57">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="141" t="s">
+      <c r="P50" s="139" t="s">
         <v>244</v>
       </c>
-      <c r="Q50" s="125">
+      <c r="Q50" s="123">
         <v>3.35</v>
       </c>
-      <c r="R50" s="126">
+      <c r="R50" s="124">
         <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="126">
+      <c r="S50" s="124">
         <v>3.35</v>
       </c>
-      <c r="T50" s="107">
+      <c r="T50" s="105">
         <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U50" s="119" t="s">
+      <c r="U50" s="117" t="s">
         <v>149</v>
       </c>
-      <c r="V50" s="205"/>
-      <c r="W50" s="134"/>
+      <c r="V50" s="201"/>
+      <c r="W50" s="132"/>
       <c r="X50" s="11"/>
     </row>
     <row r="51" spans="1:24" ht="15.75">
       <c r="A51" s="1"/>
-      <c r="C51" s="24"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="8"/>
       <c r="E51" s="7"/>
       <c r="G51" s="7"/>
@@ -6207,21 +6225,21 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="264" t="s">
+      <c r="M51" s="261" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="265"/>
-      <c r="O51" s="265"/>
-      <c r="P51" s="265"/>
-      <c r="Q51" s="20"/>
-      <c r="R51" s="143">
+      <c r="N51" s="262"/>
+      <c r="O51" s="262"/>
+      <c r="P51" s="262"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="141">
         <f>SUM(R3:R49)</f>
-        <v>318.85120000000001</v>
-      </c>
-      <c r="S51" s="143"/>
-      <c r="T51" s="100">
+        <v>317.21379999999999</v>
+      </c>
+      <c r="S51" s="141"/>
+      <c r="T51" s="98">
         <f>SUM(T3:T49)</f>
-        <v>1151.1229000000003</v>
+        <v>1161.0529000000004</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -6236,21 +6254,21 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="266" t="s">
+      <c r="M52" s="263" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="267"/>
-      <c r="O52" s="267"/>
-      <c r="P52" s="267"/>
-      <c r="Q52" s="32"/>
-      <c r="R52" s="146">
+      <c r="N52" s="264"/>
+      <c r="O52" s="264"/>
+      <c r="P52" s="264"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="144">
         <f>R51/5</f>
-        <v>63.770240000000001</v>
-      </c>
-      <c r="S52" s="146"/>
-      <c r="T52" s="34">
+        <v>63.44276</v>
+      </c>
+      <c r="S52" s="144"/>
+      <c r="T52" s="33">
         <f>T51/20</f>
-        <v>57.556145000000015</v>
+        <v>58.05264500000002</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
@@ -6265,18 +6283,18 @@
       <c r="I53" s="2"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="255" t="s">
+      <c r="M53" s="30"/>
+      <c r="N53" s="252" t="s">
         <v>147</v>
       </c>
-      <c r="O53" s="256"/>
-      <c r="P53" s="257"/>
-      <c r="Q53" s="142"/>
-      <c r="R53" s="144">
+      <c r="O53" s="253"/>
+      <c r="P53" s="254"/>
+      <c r="Q53" s="140"/>
+      <c r="R53" s="142">
         <v>3</v>
       </c>
-      <c r="S53" s="144"/>
-      <c r="T53" s="145">
+      <c r="S53" s="142"/>
+      <c r="T53" s="143">
         <v>3</v>
       </c>
       <c r="U53" s="7"/>
@@ -6292,18 +6310,18 @@
       <c r="I54" s="2"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="273" t="s">
+      <c r="M54" s="30"/>
+      <c r="N54" s="270" t="s">
         <v>252</v>
       </c>
-      <c r="O54" s="274"/>
-      <c r="P54" s="275"/>
-      <c r="Q54" s="140"/>
-      <c r="R54" s="139">
+      <c r="O54" s="271"/>
+      <c r="P54" s="272"/>
+      <c r="Q54" s="138"/>
+      <c r="R54" s="137">
         <v>22.78</v>
       </c>
-      <c r="S54" s="139"/>
-      <c r="T54" s="147">
+      <c r="S54" s="137"/>
+      <c r="T54" s="145">
         <v>90.99</v>
       </c>
       <c r="U54" s="7"/>
@@ -6317,20 +6335,20 @@
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="258" t="s">
+      <c r="N55" s="255" t="s">
         <v>43</v>
       </c>
-      <c r="O55" s="259"/>
-      <c r="P55" s="260"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="148">
+      <c r="O55" s="256"/>
+      <c r="P55" s="257"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="146">
         <f>SUM(R52:R54)</f>
-        <v>89.550240000000002</v>
-      </c>
-      <c r="S55" s="148"/>
-      <c r="T55" s="33">
+        <v>89.222759999999994</v>
+      </c>
+      <c r="S55" s="146"/>
+      <c r="T55" s="32">
         <f>SUM(T52:T54)</f>
-        <v>151.54614500000002</v>
+        <v>152.04264500000002</v>
       </c>
       <c r="W55" s="11"/>
       <c r="X55" s="11"/>
@@ -6341,8 +6359,8 @@
       <c r="D56" s="2"/>
       <c r="G56" s="2"/>
       <c r="I56" s="2"/>
-      <c r="N56" s="19"/>
-      <c r="O56" s="19"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
       <c r="W56" s="11"/>
       <c r="X56" s="11"/>
     </row>
@@ -6595,54 +6613,53 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="P3" r:id="rId1"/>
-    <hyperlink ref="P4" r:id="rId2"/>
-    <hyperlink ref="P5" r:id="rId3"/>
-    <hyperlink ref="P6" r:id="rId4"/>
-    <hyperlink ref="P8" r:id="rId5"/>
-    <hyperlink ref="P9" r:id="rId6"/>
-    <hyperlink ref="P10" r:id="rId7"/>
-    <hyperlink ref="P11" r:id="rId8"/>
-    <hyperlink ref="P25" r:id="rId9"/>
-    <hyperlink ref="P26" r:id="rId10"/>
-    <hyperlink ref="P27" r:id="rId11"/>
-    <hyperlink ref="P29" r:id="rId12"/>
-    <hyperlink ref="P33" r:id="rId13"/>
-    <hyperlink ref="P34" r:id="rId14"/>
-    <hyperlink ref="P35" r:id="rId15"/>
-    <hyperlink ref="P42" r:id="rId16"/>
-    <hyperlink ref="P43" r:id="rId17"/>
-    <hyperlink ref="P45" r:id="rId18"/>
-    <hyperlink ref="P24" r:id="rId19" display="Aliexpress"/>
-    <hyperlink ref="P44" r:id="rId20"/>
-    <hyperlink ref="P7" r:id="rId21"/>
-    <hyperlink ref="P12" r:id="rId22"/>
-    <hyperlink ref="P13" r:id="rId23"/>
-    <hyperlink ref="P18" r:id="rId24"/>
-    <hyperlink ref="P20" r:id="rId25"/>
-    <hyperlink ref="P28" r:id="rId26"/>
-    <hyperlink ref="P31" r:id="rId27"/>
-    <hyperlink ref="P38" r:id="rId28"/>
-    <hyperlink ref="P39" r:id="rId29"/>
-    <hyperlink ref="P14" r:id="rId30"/>
-    <hyperlink ref="P15" r:id="rId31"/>
-    <hyperlink ref="P21" r:id="rId32"/>
-    <hyperlink ref="P22" r:id="rId33"/>
-    <hyperlink ref="P32" r:id="rId34"/>
-    <hyperlink ref="P50" r:id="rId35"/>
-    <hyperlink ref="P49" r:id="rId36"/>
-    <hyperlink ref="P16" r:id="rId37"/>
-    <hyperlink ref="P17" r:id="rId38"/>
-    <hyperlink ref="P23" r:id="rId39"/>
-    <hyperlink ref="P30" r:id="rId40"/>
-    <hyperlink ref="P46" r:id="rId41"/>
-    <hyperlink ref="P41" r:id="rId42"/>
-    <hyperlink ref="P47" r:id="rId43"/>
-    <hyperlink ref="P19" r:id="rId44"/>
-    <hyperlink ref="P40" r:id="rId45"/>
+    <hyperlink ref="P3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="P5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="P8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="P9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="P10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="P11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P25" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="P26" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P27" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="P29" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="P33" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="P35" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="P42" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="P43" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="P45" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P24" r:id="rId18" display="Aliexpress" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="P44" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="P7" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="P12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="P13" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="P18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="P20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="P28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="P31" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="P38" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="P39" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="P14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="P15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="P21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="P22" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P32" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="P50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="P49" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="P16" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="P17" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="P23" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="P30" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="P46" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="P41" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="P47" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="P19" r:id="rId43" display="LCSC" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="P40" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId46"/>
+  <pageSetup orientation="portrait" r:id="rId45"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
+++ b/Deliverables/BOM/eSpark-BOM-v2.0 Boards).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A7FEB7-865A-46B7-8958-519D1F77BB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7609CEB5-BC85-493C-96EF-DDF0A1355F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="298">
   <si>
     <t>S. No.</t>
   </si>
@@ -629,10 +629,6 @@
     <t>3.3nF</t>
   </si>
   <si>
-    <t xml:space="preserve">SOD-323
-</t>
-  </si>
-  <si>
     <t>C78439</t>
   </si>
   <si>
@@ -745,9 +741,6 @@
     <t xml:space="preserve">Murata </t>
   </si>
   <si>
-    <t>C162552</t>
-  </si>
-  <si>
     <t>C77105</t>
   </si>
   <si>
@@ -930,6 +923,12 @@
   </si>
   <si>
     <t>Supplier / Hanson</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>Chipmall</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1540,12 +1539,112 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1561,108 +1660,17 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1675,7 +1683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1731,9 +1739,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1834,9 +1839,6 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1915,9 +1917,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1993,9 +1992,6 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2026,9 +2022,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2065,12 +2058,6 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2115,39 +2102,6 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2166,148 +2120,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2341,24 +2156,6 @@
     <xf numFmtId="165" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2368,55 +2165,290 @@
     <xf numFmtId="165" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="29" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2464,37 +2496,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2779,7 +2802,7 @@
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="47.5703125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2803,31 +2826,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16.5" thickBot="1">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="266" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="259"/>
-      <c r="C1" s="259"/>
-      <c r="D1" s="259"/>
-      <c r="E1" s="259"/>
-      <c r="F1" s="259"/>
-      <c r="G1" s="259"/>
-      <c r="H1" s="259"/>
-      <c r="I1" s="259"/>
-      <c r="J1" s="259"/>
-      <c r="K1" s="259"/>
-      <c r="L1" s="259"/>
-      <c r="M1" s="259"/>
-      <c r="N1" s="259"/>
-      <c r="O1" s="259"/>
-      <c r="P1" s="259"/>
-      <c r="Q1" s="259"/>
-      <c r="R1" s="259"/>
-      <c r="S1" s="259"/>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="260"/>
+      <c r="B1" s="267"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+      <c r="F1" s="267"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="267"/>
+      <c r="J1" s="267"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="267"/>
+      <c r="M1" s="267"/>
+      <c r="N1" s="267"/>
+      <c r="O1" s="267"/>
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="267"/>
+      <c r="T1" s="267"/>
+      <c r="U1" s="267"/>
+      <c r="V1" s="267"/>
+      <c r="W1" s="268"/>
     </row>
     <row r="2" spans="1:24" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2863,8 +2886,8 @@
       <c r="K2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="136" t="s">
-        <v>248</v>
+      <c r="L2" s="129" t="s">
+        <v>246</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
@@ -2873,7 +2896,7 @@
         <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>11</v>
@@ -2885,16 +2908,16 @@
         <v>46</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="T2" s="136" t="s">
-        <v>247</v>
+        <v>244</v>
+      </c>
+      <c r="T2" s="129" t="s">
+        <v>245</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="136" t="s">
-        <v>296</v>
+      <c r="V2" s="129" t="s">
+        <v>294</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>13</v>
@@ -2904,203 +2927,203 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="265" t="s">
+      <c r="B3" s="273" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="128" t="s">
+      <c r="D3" s="123" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="37">
+      <c r="K3" s="36">
         <v>40</v>
       </c>
-      <c r="L3" s="37">
+      <c r="L3" s="36">
         <v>100</v>
       </c>
-      <c r="M3" s="66">
+      <c r="M3" s="64">
         <v>4</v>
       </c>
-      <c r="N3" s="38">
+      <c r="N3" s="37">
         <f>M3*5</f>
         <v>20</v>
       </c>
-      <c r="O3" s="38">
+      <c r="O3" s="37">
         <f>M3*20</f>
         <v>80</v>
       </c>
-      <c r="P3" s="67" t="s">
+      <c r="P3" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="39">
+      <c r="Q3" s="38">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="R3" s="40">
+      <c r="R3" s="39">
         <f>Q3*K3</f>
         <v>0.54399999999999993</v>
       </c>
-      <c r="S3" s="40">
+      <c r="S3" s="39">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="T3" s="40">
+      <c r="T3" s="39">
         <f>S3*L3</f>
         <v>1.3599999999999999</v>
       </c>
       <c r="U3" s="12"/>
-      <c r="V3" s="190"/>
+      <c r="V3" s="12"/>
       <c r="W3" s="13"/>
     </row>
     <row r="4" spans="1:24" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="266"/>
-      <c r="C4" s="68" t="s">
+      <c r="B4" s="274"/>
+      <c r="C4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="69" t="s">
+      <c r="J4" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="43">
+      <c r="K4" s="42">
         <v>20</v>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="42">
         <v>40</v>
       </c>
-      <c r="M4" s="71">
+      <c r="M4" s="69">
         <v>1</v>
       </c>
-      <c r="N4" s="99">
+      <c r="N4" s="96">
         <f t="shared" ref="N4:N48" si="0">M4*5</f>
         <v>5</v>
       </c>
-      <c r="O4" s="99">
+      <c r="O4" s="96">
         <f t="shared" ref="O4:O50" si="1">M4*20</f>
         <v>20</v>
       </c>
-      <c r="P4" s="72" t="s">
+      <c r="P4" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="45">
+      <c r="Q4" s="44">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="R4" s="100">
+      <c r="R4" s="97">
         <f t="shared" ref="R4:R47" si="2">Q4*K4</f>
         <v>0.40599999999999997</v>
       </c>
-      <c r="S4" s="100">
+      <c r="S4" s="97">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="T4" s="100">
+      <c r="T4" s="97">
         <f t="shared" ref="T4:T47" si="3">S4*L4</f>
         <v>0.81199999999999994</v>
       </c>
       <c r="U4" s="14"/>
-      <c r="V4" s="191"/>
+      <c r="V4" s="14"/>
       <c r="W4" s="15"/>
     </row>
     <row r="5" spans="1:24" ht="39" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="266"/>
-      <c r="C5" s="68" t="s">
+      <c r="B5" s="274"/>
+      <c r="C5" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="127" t="s">
+      <c r="D5" s="122" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="42">
         <v>100</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="42">
         <v>400</v>
       </c>
-      <c r="M5" s="71">
+      <c r="M5" s="69">
         <v>19</v>
       </c>
-      <c r="N5" s="99">
+      <c r="N5" s="96">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="O5" s="99">
+      <c r="O5" s="96">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="P5" s="72" t="s">
+      <c r="P5" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="45">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="R5" s="100">
+      <c r="Q5" s="44">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R5" s="97">
         <f t="shared" si="2"/>
-        <v>0.73</v>
-      </c>
-      <c r="S5" s="100">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="T5" s="100">
+        <v>0.71000000000000008</v>
+      </c>
+      <c r="S5" s="97">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="T5" s="97">
         <f t="shared" si="3"/>
-        <v>2.8000000000000003</v>
+        <v>2.8400000000000003</v>
       </c>
       <c r="U5" s="14"/>
-      <c r="V5" s="191"/>
+      <c r="V5" s="14"/>
       <c r="W5" s="15"/>
       <c r="X5" s="11"/>
     </row>
@@ -3108,67 +3131,67 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="266"/>
-      <c r="C6" s="68" t="s">
+      <c r="B6" s="274"/>
+      <c r="C6" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="93" t="s">
+      <c r="D6" s="90" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="42">
         <v>100</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="42">
         <v>200</v>
       </c>
-      <c r="M6" s="71">
+      <c r="M6" s="69">
         <v>8</v>
       </c>
-      <c r="N6" s="99">
+      <c r="N6" s="96">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O6" s="99">
+      <c r="O6" s="96">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P6" s="73" t="s">
+      <c r="P6" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="45">
+      <c r="Q6" s="44">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="R6" s="100">
+      <c r="R6" s="97">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
-      <c r="S6" s="100">
+      <c r="S6" s="97">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="T6" s="100">
+      <c r="T6" s="97">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
       <c r="U6" s="14"/>
-      <c r="V6" s="191"/>
+      <c r="V6" s="14"/>
       <c r="W6" s="15"/>
       <c r="X6" s="11"/>
     </row>
@@ -3176,67 +3199,67 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="266"/>
-      <c r="C7" s="68" t="s">
+      <c r="B7" s="274"/>
+      <c r="C7" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="93" t="s">
+      <c r="D7" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="68" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="97" t="s">
+      <c r="F7" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="46" t="s">
         <v>191</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="40" t="s">
         <v>192</v>
       </c>
-      <c r="I7" s="42" t="s">
-        <v>201</v>
-      </c>
-      <c r="J7" s="69" t="s">
+      <c r="I7" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="J7" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="K7" s="43">
+      <c r="K7" s="42">
         <v>100</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="42">
         <v>100</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="69">
         <v>1</v>
       </c>
-      <c r="N7" s="99">
+      <c r="N7" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O7" s="99">
+      <c r="O7" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P7" s="96" t="s">
+      <c r="P7" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="45">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="R7" s="100">
+      <c r="Q7" s="44">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R7" s="97">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="S7" s="100">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="T7" s="100">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S7" s="97">
+        <v>1.4E-3</v>
+      </c>
+      <c r="T7" s="97">
         <f t="shared" si="3"/>
-        <v>0.13</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="U7" s="14"/>
-      <c r="V7" s="191"/>
+      <c r="V7" s="14"/>
       <c r="W7" s="15"/>
       <c r="X7" s="11"/>
     </row>
@@ -3244,67 +3267,67 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="266"/>
-      <c r="C8" s="68" t="s">
+      <c r="B8" s="274"/>
+      <c r="C8" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="127" t="s">
-        <v>214</v>
-      </c>
-      <c r="E8" s="69" t="s">
+      <c r="D8" s="122" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="69" t="s">
+      <c r="J8" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="42">
         <v>150</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="42">
         <v>600</v>
       </c>
-      <c r="M8" s="71">
+      <c r="M8" s="69">
         <v>29</v>
       </c>
-      <c r="N8" s="99">
+      <c r="N8" s="96">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="O8" s="99">
+      <c r="O8" s="96">
         <f t="shared" si="1"/>
         <v>580</v>
       </c>
-      <c r="P8" s="73" t="s">
+      <c r="P8" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="45">
-        <v>7.1999999999999998E-3</v>
-      </c>
-      <c r="R8" s="100">
+      <c r="Q8" s="44">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="R8" s="97">
         <f t="shared" si="2"/>
-        <v>1.08</v>
-      </c>
-      <c r="S8" s="100">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="T8" s="100">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="S8" s="97">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="T8" s="97">
         <f t="shared" si="3"/>
-        <v>3.4799999999999995</v>
-      </c>
-      <c r="U8" s="25"/>
-      <c r="V8" s="192"/>
+        <v>3.6</v>
+      </c>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
       <c r="W8" s="15"/>
       <c r="X8" s="11"/>
     </row>
@@ -3312,67 +3335,67 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="266"/>
-      <c r="C9" s="68" t="s">
+      <c r="B9" s="274"/>
+      <c r="C9" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="47" t="s">
+      <c r="G9" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="69" t="s">
+      <c r="J9" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="46">
         <v>10</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="46">
         <v>30</v>
       </c>
-      <c r="M9" s="71">
+      <c r="M9" s="69">
         <v>1</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P9" s="73" t="s">
+      <c r="P9" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="45">
-        <v>4.4299999999999999E-2</v>
-      </c>
-      <c r="R9" s="100">
+      <c r="Q9" s="44">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="R9" s="97">
         <f t="shared" si="2"/>
-        <v>0.443</v>
-      </c>
-      <c r="S9" s="100">
-        <v>3.8199999999999998E-2</v>
-      </c>
-      <c r="T9" s="100">
+        <v>0.37</v>
+      </c>
+      <c r="S9" s="97">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="T9" s="97">
         <f t="shared" si="3"/>
-        <v>1.1459999999999999</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="U9" s="14"/>
-      <c r="V9" s="191"/>
+      <c r="V9" s="14"/>
       <c r="W9" s="15"/>
       <c r="X9" s="11"/>
     </row>
@@ -3380,67 +3403,67 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="266"/>
-      <c r="C10" s="68" t="s">
+      <c r="B10" s="274"/>
+      <c r="C10" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="93" t="s">
+      <c r="D10" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="47" t="s">
+      <c r="G10" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="69" t="s">
+      <c r="J10" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="46">
         <v>100</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="46">
         <v>200</v>
       </c>
-      <c r="M10" s="71">
+      <c r="M10" s="69">
         <v>6</v>
       </c>
-      <c r="N10" s="99">
+      <c r="N10" s="96">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="96">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="P10" s="72" t="s">
+      <c r="P10" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="Q10" s="45">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="R10" s="100">
+      <c r="Q10" s="44">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="R10" s="97">
         <f t="shared" si="2"/>
-        <v>0.32</v>
-      </c>
-      <c r="S10" s="100">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="T10" s="100">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="S10" s="97">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="T10" s="97">
         <f t="shared" si="3"/>
-        <v>0.64</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="U10" s="14"/>
-      <c r="V10" s="191"/>
+      <c r="V10" s="14"/>
       <c r="W10" s="15"/>
       <c r="X10" s="11"/>
     </row>
@@ -3448,67 +3471,67 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="266"/>
-      <c r="C11" s="68" t="s">
+      <c r="B11" s="274"/>
+      <c r="C11" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="42" t="s">
+      <c r="I11" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="69" t="s">
+      <c r="J11" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="46">
         <v>100</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="46">
         <v>350</v>
       </c>
-      <c r="M11" s="71">
+      <c r="M11" s="69">
         <v>16</v>
       </c>
-      <c r="N11" s="99">
+      <c r="N11" s="96">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="O11" s="99">
+      <c r="O11" s="96">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="P11" s="72" t="s">
+      <c r="P11" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="45">
-        <v>1.5100000000000001E-2</v>
-      </c>
-      <c r="R11" s="100">
+      <c r="Q11" s="44">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="R11" s="97">
         <f t="shared" si="2"/>
-        <v>1.51</v>
-      </c>
-      <c r="S11" s="100">
-        <v>1.5100000000000001E-2</v>
-      </c>
-      <c r="T11" s="100">
+        <v>1.5599999999999998</v>
+      </c>
+      <c r="S11" s="97">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="T11" s="97">
         <f t="shared" si="3"/>
-        <v>5.2850000000000001</v>
+        <v>5.46</v>
       </c>
       <c r="U11" s="14"/>
-      <c r="V11" s="191"/>
+      <c r="V11" s="14"/>
       <c r="W11" s="15"/>
       <c r="X11" s="11"/>
     </row>
@@ -3516,67 +3539,67 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="266"/>
-      <c r="C12" s="68" t="s">
+      <c r="B12" s="274"/>
+      <c r="C12" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="93" t="s">
+      <c r="D12" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="69" t="s">
+      <c r="J12" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="46">
         <v>50</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="46">
         <v>50</v>
       </c>
-      <c r="M12" s="71">
+      <c r="M12" s="69">
         <v>1</v>
       </c>
-      <c r="N12" s="99">
+      <c r="N12" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O12" s="99">
+      <c r="O12" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P12" s="101" t="s">
+      <c r="P12" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="45">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="R12" s="100">
+      <c r="Q12" s="44">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="R12" s="97">
         <f t="shared" si="2"/>
-        <v>0.23500000000000001</v>
-      </c>
-      <c r="S12" s="100">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="T12" s="100">
+        <v>0.245</v>
+      </c>
+      <c r="S12" s="97">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="T12" s="97">
         <f t="shared" si="3"/>
-        <v>0.23500000000000001</v>
+        <v>0.245</v>
       </c>
       <c r="U12" s="14"/>
-      <c r="V12" s="191"/>
+      <c r="V12" s="14"/>
       <c r="W12" s="15"/>
       <c r="X12" s="11"/>
     </row>
@@ -3584,67 +3607,67 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="266"/>
-      <c r="C13" s="68" t="s">
+      <c r="B13" s="274"/>
+      <c r="C13" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="122" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="69" t="s">
+      <c r="E13" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="85" t="s">
+      <c r="F13" s="82" t="s">
         <v>165</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="46" t="s">
         <v>191</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="I13" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="J13" s="69" t="s">
+      <c r="I13" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="J13" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="46">
         <v>100</v>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="46">
         <v>100</v>
       </c>
-      <c r="M13" s="71">
+      <c r="M13" s="69">
         <v>1</v>
       </c>
-      <c r="N13" s="99">
+      <c r="N13" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O13" s="99">
+      <c r="O13" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P13" s="101" t="s">
+      <c r="P13" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q13" s="45">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="R13" s="100">
+      <c r="Q13" s="44">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="R13" s="97">
         <f t="shared" si="2"/>
-        <v>0.11</v>
-      </c>
-      <c r="S13" s="100">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="T13" s="100">
+        <v>0.13</v>
+      </c>
+      <c r="S13" s="97">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="T13" s="97">
         <f t="shared" si="3"/>
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="U13" s="14"/>
-      <c r="V13" s="191"/>
+      <c r="V13" s="14"/>
       <c r="W13" s="15"/>
       <c r="X13" s="11"/>
     </row>
@@ -3652,67 +3675,67 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="266"/>
-      <c r="C14" s="68" t="s">
+      <c r="B14" s="274"/>
+      <c r="C14" s="66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="D14" s="93" t="s">
+      <c r="E14" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="68" t="s">
         <v>216</v>
       </c>
-      <c r="E14" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="G14" s="47" t="s">
+      <c r="G14" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="67" t="s">
         <v>224</v>
       </c>
-      <c r="I14" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="K14" s="47">
+      <c r="K14" s="46">
         <v>100</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="46">
         <v>100</v>
       </c>
-      <c r="M14" s="71">
+      <c r="M14" s="69">
         <v>1</v>
       </c>
-      <c r="N14" s="99">
+      <c r="N14" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P14" s="101" t="s">
+      <c r="P14" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="45">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="R14" s="100">
+      <c r="Q14" s="44">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="R14" s="97">
         <f t="shared" si="2"/>
-        <v>0.37</v>
-      </c>
-      <c r="S14" s="100">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="T14" s="100">
+        <v>0.38999999999999996</v>
+      </c>
+      <c r="S14" s="97">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="T14" s="97">
         <f t="shared" si="3"/>
-        <v>0.37</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="U14" s="14"/>
-      <c r="V14" s="191"/>
+      <c r="V14" s="14"/>
       <c r="W14" s="15"/>
       <c r="X14" s="11"/>
     </row>
@@ -3720,67 +3743,67 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="266"/>
-      <c r="C15" s="68" t="s">
+      <c r="B15" s="274"/>
+      <c r="C15" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="90" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="93" t="s">
+      <c r="E15" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="I15" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="69" t="s">
-        <v>227</v>
-      </c>
-      <c r="K15" s="47">
+      <c r="K15" s="46">
         <v>50</v>
       </c>
-      <c r="L15" s="47">
+      <c r="L15" s="46">
         <v>50</v>
       </c>
-      <c r="M15" s="71">
+      <c r="M15" s="69">
         <v>2</v>
       </c>
-      <c r="N15" s="99">
+      <c r="N15" s="96">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O15" s="99">
+      <c r="O15" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P15" s="101" t="s">
+      <c r="P15" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="45">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="R15" s="100">
+      <c r="Q15" s="44">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="R15" s="97">
         <f t="shared" si="2"/>
-        <v>0.255</v>
-      </c>
-      <c r="S15" s="100">
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="T15" s="100">
+        <v>0.27</v>
+      </c>
+      <c r="S15" s="97">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="T15" s="97">
         <f t="shared" si="3"/>
-        <v>0.255</v>
+        <v>0.27</v>
       </c>
       <c r="U15" s="14"/>
-      <c r="V15" s="191"/>
+      <c r="V15" s="14"/>
       <c r="W15" s="15"/>
       <c r="X15" s="11"/>
     </row>
@@ -3788,67 +3811,67 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="266"/>
-      <c r="C16" s="68" t="s">
+      <c r="B16" s="274"/>
+      <c r="C16" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" s="142" t="s">
+        <v>252</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="D16" s="149" t="s">
-        <v>254</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="70" t="s">
-        <v>255</v>
-      </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="I16" s="42" t="s">
+      <c r="H16" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="I16" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="K16" s="47">
+      <c r="J16" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="K16" s="46">
         <v>50</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="46">
         <v>50</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="69">
         <v>1</v>
       </c>
-      <c r="N16" s="99">
+      <c r="N16" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O16" s="99">
+      <c r="O16" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P16" s="101" t="s">
+      <c r="P16" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q16" s="45">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="R16" s="100">
+      <c r="Q16" s="44">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="R16" s="97">
         <f t="shared" si="2"/>
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="S16" s="100">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="T16" s="100">
+        <v>0.32</v>
+      </c>
+      <c r="S16" s="97">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="T16" s="97">
         <f>S16*L16</f>
-        <v>0.30499999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="U16" s="14"/>
-      <c r="V16" s="191"/>
+      <c r="V16" s="14"/>
       <c r="W16" s="15"/>
       <c r="X16" s="11"/>
     </row>
@@ -3856,67 +3879,67 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="267"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="275"/>
+      <c r="C17" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" s="143" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" s="120" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="120" t="s">
         <v>256</v>
       </c>
-      <c r="D17" s="150" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="125" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="125" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="54" t="s">
-        <v>261</v>
-      </c>
-      <c r="I17" s="55" t="s">
+      <c r="H17" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="78" t="s">
-        <v>262</v>
-      </c>
-      <c r="K17" s="53">
+      <c r="J17" s="76" t="s">
+        <v>260</v>
+      </c>
+      <c r="K17" s="52">
         <v>50</v>
       </c>
-      <c r="L17" s="53">
+      <c r="L17" s="52">
         <v>50</v>
       </c>
-      <c r="M17" s="82">
+      <c r="M17" s="80">
         <v>1</v>
       </c>
-      <c r="N17" s="57">
+      <c r="N17" s="55">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O17" s="57">
+      <c r="O17" s="55">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P17" s="104" t="s">
+      <c r="P17" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q17" s="58">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="R17" s="105">
+      <c r="Q17" s="56">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="R17" s="102">
         <f t="shared" si="2"/>
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="S17" s="105">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="T17" s="105">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="S17" s="102">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="T17" s="102">
         <f>S17*L17</f>
-        <v>0.38500000000000001</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="U17" s="16"/>
-      <c r="V17" s="193"/>
+      <c r="V17" s="16"/>
       <c r="W17" s="17"/>
       <c r="X17" s="11"/>
     </row>
@@ -3924,140 +3947,140 @@
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="268" t="s">
+      <c r="B18" s="276" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="160" t="s">
+      <c r="C18" s="237" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="128" t="s">
+      <c r="D18" s="185" t="s">
         <v>183</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="186" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="187" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" s="188" t="s">
+        <v>199</v>
+      </c>
+      <c r="H18" s="189" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="190" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="64" t="s">
+      <c r="J18" s="187" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="34">
+      <c r="K18" s="188">
         <v>10</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="188">
         <v>30</v>
       </c>
-      <c r="M18" s="66">
+      <c r="M18" s="191">
         <v>1</v>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O18" s="38">
+      <c r="O18" s="43">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P18" s="126" t="s">
+      <c r="P18" s="192" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="39">
-        <v>6.2600000000000003E-2</v>
-      </c>
-      <c r="R18" s="40">
+      <c r="Q18" s="193">
+        <v>6.9699999999999998E-2</v>
+      </c>
+      <c r="R18" s="45">
         <f t="shared" si="2"/>
-        <v>0.626</v>
-      </c>
-      <c r="S18" s="40">
-        <v>6.1699999999999998E-2</v>
-      </c>
-      <c r="T18" s="40">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="S18" s="45">
+        <v>6.9699999999999998E-2</v>
+      </c>
+      <c r="T18" s="45">
         <f t="shared" si="3"/>
-        <v>1.851</v>
-      </c>
-      <c r="U18" s="12"/>
-      <c r="V18" s="190"/>
-      <c r="W18" s="13"/>
+        <v>2.0909999999999997</v>
+      </c>
+      <c r="U18" s="194"/>
+      <c r="V18" s="194"/>
+      <c r="W18" s="253"/>
       <c r="X18" s="11"/>
     </row>
     <row r="19" spans="1:24" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="269"/>
-      <c r="C19" s="182" t="s">
+      <c r="B19" s="277"/>
+      <c r="C19" s="238" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="165" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="183" t="s">
+      <c r="E19" s="165" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="165" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="183" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="183" t="s">
-        <v>223</v>
-      </c>
-      <c r="G19" s="184" t="s">
+      <c r="G19" s="166" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="185">
+      <c r="H19" s="195">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="I19" s="184" t="s">
+      <c r="I19" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="183" t="s">
+      <c r="J19" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="184">
+      <c r="K19" s="166">
         <v>10</v>
       </c>
-      <c r="L19" s="184">
+      <c r="L19" s="166">
         <v>50</v>
       </c>
-      <c r="M19" s="186">
+      <c r="M19" s="167">
         <v>2</v>
       </c>
-      <c r="N19" s="186">
+      <c r="N19" s="167">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O19" s="186">
+      <c r="O19" s="167">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P19" s="278" t="s">
+      <c r="P19" s="196" t="s">
         <v>135</v>
       </c>
-      <c r="Q19" s="187">
+      <c r="Q19" s="168">
         <v>0.23799999999999999</v>
       </c>
-      <c r="R19" s="188">
+      <c r="R19" s="169">
         <f t="shared" si="2"/>
         <v>2.38</v>
       </c>
-      <c r="S19" s="188">
+      <c r="S19" s="169">
         <v>0.23799999999999999</v>
       </c>
-      <c r="T19" s="188">
+      <c r="T19" s="169">
         <f t="shared" si="3"/>
         <v>11.899999999999999</v>
       </c>
-      <c r="U19" s="203"/>
-      <c r="V19" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W19" s="276" t="s">
+      <c r="U19" s="197"/>
+      <c r="V19" s="198" t="s">
+        <v>293</v>
+      </c>
+      <c r="W19" s="254" t="s">
         <v>135</v>
       </c>
       <c r="X19" s="11"/>
@@ -4066,69 +4089,69 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="275" t="s">
+      <c r="B20" s="281" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="D20" s="128" t="s">
+      <c r="D20" s="123" t="s">
         <v>187</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="F20" s="65" t="s">
+      <c r="F20" s="63" t="s">
         <v>189</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="H20" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="I20" s="36" t="s">
+      <c r="I20" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="J20" s="64" t="s">
+      <c r="J20" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="33">
         <v>50</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="33">
         <v>50</v>
       </c>
-      <c r="M20" s="66">
+      <c r="M20" s="64">
         <v>1</v>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O20" s="38">
+      <c r="O20" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P20" s="126" t="s">
+      <c r="P20" s="121" t="s">
         <v>16</v>
       </c>
-      <c r="Q20" s="39">
-        <v>2.07E-2</v>
-      </c>
-      <c r="R20" s="40">
+      <c r="Q20" s="38">
+        <v>2.12E-2</v>
+      </c>
+      <c r="R20" s="39">
         <f t="shared" si="2"/>
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="S20" s="40">
-        <v>2.07E-2</v>
-      </c>
-      <c r="T20" s="40">
+        <v>1.06</v>
+      </c>
+      <c r="S20" s="39">
+        <v>2.12E-2</v>
+      </c>
+      <c r="T20" s="39">
         <f t="shared" si="3"/>
-        <v>1.0349999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="U20" s="12"/>
-      <c r="V20" s="190"/>
+      <c r="V20" s="12"/>
       <c r="W20" s="13"/>
       <c r="X20" s="11"/>
     </row>
@@ -4136,67 +4159,67 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="273"/>
-      <c r="C21" s="68" t="s">
+      <c r="B21" s="283"/>
+      <c r="C21" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="D21" s="93" t="s">
+      <c r="E21" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="68" t="s">
         <v>229</v>
       </c>
-      <c r="E21" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="70" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>235</v>
+      <c r="G21" s="46" t="s">
+        <v>234</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="I21" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="69" t="s">
-        <v>207</v>
-      </c>
-      <c r="K21" s="47">
-        <v>20</v>
-      </c>
-      <c r="L21" s="47">
-        <v>50</v>
-      </c>
-      <c r="M21" s="71">
+      <c r="J21" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" s="46">
+        <v>12</v>
+      </c>
+      <c r="L21" s="46">
+        <v>45</v>
+      </c>
+      <c r="M21" s="69">
         <v>2</v>
       </c>
-      <c r="N21" s="99">
+      <c r="N21" s="96">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O21" s="99">
+      <c r="O21" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P21" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q21" s="45">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="R21" s="100">
+      <c r="P21" s="98" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q21" s="44">
+        <v>0.11208</v>
+      </c>
+      <c r="R21" s="97">
         <f t="shared" si="2"/>
-        <v>1.4860000000000002</v>
-      </c>
-      <c r="S21" s="100">
-        <v>7.4300000000000005E-2</v>
-      </c>
-      <c r="T21" s="100">
+        <v>1.3449599999999999</v>
+      </c>
+      <c r="S21" s="97">
+        <v>0.11208</v>
+      </c>
+      <c r="T21" s="97">
         <f t="shared" si="3"/>
-        <v>3.7150000000000003</v>
-      </c>
-      <c r="U21" s="14"/>
-      <c r="V21" s="191"/>
+        <v>5.0435999999999996</v>
+      </c>
+      <c r="U21" s="20"/>
+      <c r="V21" s="14"/>
       <c r="W21" s="15"/>
       <c r="X21" s="11"/>
     </row>
@@ -4204,67 +4227,67 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="273"/>
-      <c r="C22" s="68" t="s">
+      <c r="B22" s="283"/>
+      <c r="C22" s="66" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="D22" s="93" t="s">
+      <c r="E22" s="68" t="s">
         <v>232</v>
       </c>
-      <c r="E22" s="70" t="s">
+      <c r="F22" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="F22" s="70" t="s">
+      <c r="G22" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="H22" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="H22" s="41" t="s">
-        <v>237</v>
-      </c>
-      <c r="I22" s="42" t="s">
+      <c r="I22" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="69" t="s">
-        <v>207</v>
-      </c>
-      <c r="K22" s="47">
-        <v>20</v>
-      </c>
-      <c r="L22" s="47">
+      <c r="J22" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="K22" s="46">
         <v>50</v>
       </c>
-      <c r="M22" s="71">
+      <c r="L22" s="46">
+        <v>50</v>
+      </c>
+      <c r="M22" s="69">
         <v>2</v>
       </c>
-      <c r="N22" s="99">
+      <c r="N22" s="96">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O22" s="99">
+      <c r="O22" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P22" s="101" t="s">
+      <c r="P22" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="45">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="R22" s="100">
+      <c r="Q22" s="44">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="R22" s="97">
         <f t="shared" si="2"/>
-        <v>0.154</v>
-      </c>
-      <c r="S22" s="100">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="T22" s="100">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="S22" s="97">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="T22" s="97">
         <f t="shared" si="3"/>
-        <v>0.38500000000000001</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="U22" s="14"/>
-      <c r="V22" s="191"/>
+      <c r="V22" s="14"/>
       <c r="W22" s="15"/>
       <c r="X22" s="11"/>
     </row>
@@ -4272,67 +4295,67 @@
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="274"/>
-      <c r="C23" s="106" t="s">
+      <c r="B23" s="282"/>
+      <c r="C23" s="103" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" s="143" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="120" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" s="120" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="150" t="s">
+      <c r="G23" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="E23" s="125" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="125" t="s">
-        <v>265</v>
-      </c>
-      <c r="G23" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23" s="54" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="55" t="s">
+      <c r="I23" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="J23" s="78" t="s">
-        <v>207</v>
-      </c>
-      <c r="K23" s="53">
+      <c r="J23" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" s="52">
         <v>10</v>
       </c>
-      <c r="L23" s="53">
+      <c r="L23" s="52">
         <v>30</v>
       </c>
-      <c r="M23" s="82">
+      <c r="M23" s="80">
         <v>1</v>
       </c>
-      <c r="N23" s="57">
+      <c r="N23" s="55">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O23" s="57">
+      <c r="O23" s="55">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P23" s="104" t="s">
+      <c r="P23" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="Q23" s="58">
-        <v>9.1600000000000001E-2</v>
-      </c>
-      <c r="R23" s="105">
+      <c r="Q23" s="56">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="R23" s="102">
         <f t="shared" si="2"/>
-        <v>0.91600000000000004</v>
-      </c>
-      <c r="S23" s="105">
-        <v>9.1600000000000001E-2</v>
-      </c>
-      <c r="T23" s="105">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="S23" s="102">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="T23" s="102">
         <f t="shared" si="3"/>
-        <v>2.7480000000000002</v>
+        <v>1.353</v>
       </c>
       <c r="U23" s="16"/>
-      <c r="V23" s="193"/>
+      <c r="V23" s="16"/>
       <c r="W23" s="17"/>
       <c r="X23" s="11"/>
     </row>
@@ -4340,74 +4363,74 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="133" t="s">
+      <c r="B24" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="161" t="s">
+      <c r="C24" s="239" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="152" t="s">
+      <c r="D24" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="153" t="s">
+      <c r="E24" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="153" t="s">
+      <c r="F24" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="154" t="s">
+      <c r="G24" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="154" t="s">
+      <c r="H24" s="211" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="153" t="s">
+      <c r="I24" s="210" t="s">
         <v>145</v>
       </c>
-      <c r="J24" s="153" t="s">
+      <c r="J24" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="153">
+      <c r="K24" s="210">
         <v>42</v>
       </c>
-      <c r="L24" s="153">
+      <c r="L24" s="210">
         <v>162</v>
       </c>
-      <c r="M24" s="155">
+      <c r="M24" s="212">
         <v>8</v>
       </c>
-      <c r="N24" s="155">
+      <c r="N24" s="212">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="O24" s="155">
+      <c r="O24" s="212">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="P24" s="156" t="s">
+      <c r="P24" s="213" t="s">
         <v>153</v>
       </c>
-      <c r="Q24" s="157">
+      <c r="Q24" s="214">
         <v>3.68</v>
       </c>
-      <c r="R24" s="158">
+      <c r="R24" s="215">
         <f t="shared" si="2"/>
         <v>154.56</v>
       </c>
-      <c r="S24" s="158">
+      <c r="S24" s="215">
         <v>3.68</v>
       </c>
-      <c r="T24" s="158">
+      <c r="T24" s="215">
         <f t="shared" si="3"/>
         <v>596.16000000000008</v>
       </c>
-      <c r="U24" s="159" t="s">
-        <v>249</v>
-      </c>
-      <c r="V24" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W24" s="175">
+      <c r="U24" s="216" t="s">
+        <v>247</v>
+      </c>
+      <c r="V24" s="217" t="s">
+        <v>293</v>
+      </c>
+      <c r="W24" s="255">
         <v>3.68</v>
       </c>
       <c r="X24" s="11"/>
@@ -4416,349 +4439,349 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="134" t="s">
+      <c r="B25" s="242" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="148" t="s">
+      <c r="D25" s="225" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="74" t="s">
+      <c r="E25" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="74" t="s">
+      <c r="F25" s="226" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="227" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="228" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="229" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="147" t="s">
+      <c r="J25" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="147">
+      <c r="K25" s="230">
         <v>10</v>
       </c>
-      <c r="L25" s="147">
+      <c r="L25" s="230">
         <v>30</v>
       </c>
-      <c r="M25" s="107">
+      <c r="M25" s="231">
         <v>1</v>
       </c>
-      <c r="N25" s="107">
+      <c r="N25" s="231">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O25" s="107">
+      <c r="O25" s="231">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P25" s="151" t="s">
+      <c r="P25" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="52">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="R25" s="108">
+      <c r="Q25" s="233">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="R25" s="234">
         <f t="shared" si="2"/>
-        <v>0.59</v>
-      </c>
-      <c r="S25" s="108">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="T25" s="108">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="S25" s="234">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="T25" s="234">
         <f t="shared" si="3"/>
-        <v>1.77</v>
-      </c>
-      <c r="U25" s="28"/>
-      <c r="V25" s="194"/>
-      <c r="W25" s="29"/>
+        <v>1.7910000000000001</v>
+      </c>
+      <c r="U25" s="235"/>
+      <c r="V25" s="235"/>
+      <c r="W25" s="236"/>
       <c r="X25" s="11"/>
     </row>
     <row r="26" spans="1:24" ht="26.25" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="265" t="s">
+      <c r="B26" s="274" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="204" t="s">
+      <c r="C26" s="241" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="205" t="s">
+      <c r="D26" s="201" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="205" t="s">
+      <c r="E26" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="205" t="s">
+      <c r="F26" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="206" t="s">
+      <c r="G26" s="218" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="207" t="s">
+      <c r="H26" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="I26" s="206" t="s">
+      <c r="I26" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="J26" s="205" t="s">
+      <c r="J26" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="205">
+      <c r="K26" s="201">
         <v>7</v>
       </c>
-      <c r="L26" s="205">
-        <v>23</v>
-      </c>
-      <c r="M26" s="208">
+      <c r="L26" s="201">
+        <v>22</v>
+      </c>
+      <c r="M26" s="220">
         <v>1</v>
       </c>
-      <c r="N26" s="208">
+      <c r="N26" s="220">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O26" s="209">
+      <c r="O26" s="205">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P26" s="210" t="s">
+      <c r="P26" s="221" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="211">
-        <v>0.23949999999999999</v>
-      </c>
-      <c r="R26" s="212">
+      <c r="Q26" s="222">
+        <v>0.21840000000000001</v>
+      </c>
+      <c r="R26" s="223">
         <f>Q26*K26</f>
-        <v>1.6764999999999999</v>
-      </c>
-      <c r="S26" s="212">
-        <v>0.23949999999999999</v>
-      </c>
-      <c r="T26" s="213">
+        <v>1.5288000000000002</v>
+      </c>
+      <c r="S26" s="223">
+        <v>0.1774</v>
+      </c>
+      <c r="T26" s="208">
         <f t="shared" si="3"/>
-        <v>5.5084999999999997</v>
-      </c>
-      <c r="U26" s="214"/>
-      <c r="V26" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W26" s="215"/>
+        <v>3.9028</v>
+      </c>
+      <c r="U26" s="224"/>
+      <c r="V26" s="199" t="s">
+        <v>293</v>
+      </c>
+      <c r="W26" s="256"/>
       <c r="X26" s="11"/>
     </row>
     <row r="27" spans="1:24" ht="26.25" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="266"/>
-      <c r="C27" s="216" t="s">
+      <c r="B27" s="274"/>
+      <c r="C27" s="151" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="217" t="s">
+      <c r="D27" s="152" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="218" t="s">
+      <c r="E27" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="218" t="s">
+      <c r="F27" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="219" t="s">
+      <c r="G27" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="H27" s="220" t="s">
+      <c r="H27" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="219" t="s">
+      <c r="I27" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="218" t="s">
+      <c r="J27" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K27" s="218">
-        <v>7</v>
-      </c>
-      <c r="L27" s="218">
+      <c r="K27" s="153">
+        <v>15</v>
+      </c>
+      <c r="L27" s="153">
         <v>45</v>
       </c>
-      <c r="M27" s="221">
+      <c r="M27" s="156">
         <v>2</v>
       </c>
-      <c r="N27" s="221">
+      <c r="N27" s="156">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O27" s="221">
+      <c r="O27" s="156">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P27" s="222" t="s">
+      <c r="P27" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="Q27" s="223">
-        <v>0.11169999999999999</v>
-      </c>
-      <c r="R27" s="224">
+      <c r="Q27" s="158">
+        <v>0.1085</v>
+      </c>
+      <c r="R27" s="159">
         <f t="shared" si="2"/>
-        <v>0.78189999999999993</v>
-      </c>
-      <c r="S27" s="224">
-        <v>0.11169999999999999</v>
-      </c>
-      <c r="T27" s="224">
+        <v>1.6274999999999999</v>
+      </c>
+      <c r="S27" s="159">
+        <v>0.1085</v>
+      </c>
+      <c r="T27" s="159">
         <f t="shared" si="3"/>
-        <v>5.0264999999999995</v>
-      </c>
-      <c r="U27" s="225"/>
-      <c r="V27" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W27" s="226"/>
+        <v>4.8825000000000003</v>
+      </c>
+      <c r="U27" s="160"/>
+      <c r="V27" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W27" s="161"/>
       <c r="X27" s="11"/>
     </row>
     <row r="28" spans="1:24" ht="26.25" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="267"/>
-      <c r="C28" s="77" t="s">
+      <c r="B28" s="274"/>
+      <c r="C28" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="D28" s="120" t="s">
+      <c r="D28" s="141" t="s">
         <v>167</v>
       </c>
-      <c r="E28" s="78" t="s">
+      <c r="E28" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="78" t="s">
+      <c r="F28" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="53" t="s">
+      <c r="G28" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="H28" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="H28" s="54" t="s">
+      <c r="I28" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="I28" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="J28" s="56" t="s">
-        <v>207</v>
-      </c>
-      <c r="K28" s="56">
+      <c r="K28" s="140">
         <v>10</v>
       </c>
-      <c r="L28" s="56">
+      <c r="L28" s="140">
         <v>25</v>
       </c>
-      <c r="M28" s="57">
+      <c r="M28" s="104">
         <v>1</v>
       </c>
-      <c r="N28" s="57">
+      <c r="N28" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O28" s="57">
+      <c r="O28" s="104">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P28" s="109" t="s">
+      <c r="P28" s="200" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="58">
-        <v>9.9099999999999994E-2</v>
+      <c r="Q28" s="51">
+        <v>9.6199999999999994E-2</v>
       </c>
       <c r="R28" s="105">
         <f t="shared" si="2"/>
-        <v>0.99099999999999988</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="S28" s="105">
-        <v>9.9099999999999994E-2</v>
+        <v>9.6199999999999994E-2</v>
       </c>
       <c r="T28" s="105">
         <f t="shared" si="3"/>
-        <v>2.4775</v>
-      </c>
-      <c r="U28" s="16"/>
-      <c r="V28" s="193"/>
-      <c r="W28" s="17"/>
+        <v>2.4049999999999998</v>
+      </c>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="28"/>
       <c r="X28" s="11"/>
     </row>
     <row r="29" spans="1:24" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="265" t="s">
+      <c r="B29" s="273" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="75" t="s">
+      <c r="C29" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="162" t="s">
+      <c r="D29" s="144" t="s">
         <v>169</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="79" t="s">
+      <c r="F29" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="34" t="s">
+      <c r="G29" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="128" t="s">
+      <c r="I29" s="123" t="s">
         <v>128</v>
       </c>
-      <c r="J29" s="64" t="s">
+      <c r="J29" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="K29" s="163">
+      <c r="K29" s="145">
         <v>100</v>
       </c>
-      <c r="L29" s="163">
+      <c r="L29" s="145">
         <v>100</v>
       </c>
-      <c r="M29" s="163">
+      <c r="M29" s="145">
         <v>3</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="O29" s="38">
+      <c r="O29" s="37">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="P29" s="164" t="s">
+      <c r="P29" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="Q29" s="39">
+      <c r="Q29" s="38">
         <v>1E-3</v>
       </c>
-      <c r="R29" s="40">
+      <c r="R29" s="39">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="S29" s="40">
+      <c r="S29" s="39">
         <v>1E-3</v>
       </c>
-      <c r="T29" s="40">
+      <c r="T29" s="39">
         <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
       <c r="U29" s="12"/>
-      <c r="V29" s="190"/>
+      <c r="V29" s="12"/>
       <c r="W29" s="13"/>
       <c r="X29" s="11"/>
     </row>
@@ -4766,67 +4789,67 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="266"/>
-      <c r="C30" s="80" t="s">
+      <c r="B30" s="274"/>
+      <c r="C30" s="78" t="s">
+        <v>266</v>
+      </c>
+      <c r="D30" s="150" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="67" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="H30" s="40" t="s">
         <v>268</v>
       </c>
-      <c r="D30" s="181" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="H30" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="I30" s="93" t="s">
+      <c r="I30" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="K30" s="94">
+      <c r="J30" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="K30" s="91">
         <v>100</v>
       </c>
-      <c r="L30" s="94">
+      <c r="L30" s="91">
         <v>100</v>
       </c>
-      <c r="M30" s="94">
+      <c r="M30" s="91">
         <v>1</v>
       </c>
-      <c r="N30" s="99">
+      <c r="N30" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O30" s="99">
+      <c r="O30" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P30" s="102" t="s">
+      <c r="P30" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="Q30" s="45">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="R30" s="100">
+      <c r="Q30" s="44">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="R30" s="97">
         <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-      <c r="S30" s="100">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="T30" s="100">
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="S30" s="97">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="T30" s="97">
         <f t="shared" si="3"/>
-        <v>0.16</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="U30" s="14"/>
-      <c r="V30" s="191"/>
+      <c r="V30" s="14"/>
       <c r="W30" s="15"/>
       <c r="X30" s="11"/>
     </row>
@@ -4834,67 +4857,67 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="266"/>
-      <c r="C31" s="80" t="s">
+      <c r="B31" s="274"/>
+      <c r="C31" s="78" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="127" t="s">
+      <c r="D31" s="122" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="69" t="s">
+      <c r="E31" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="F31" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="47" t="s">
+      <c r="G31" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="I31" s="93" t="s">
+      <c r="H31" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="I31" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="J31" s="69" t="s">
+      <c r="J31" s="67" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="94">
+      <c r="K31" s="91">
         <v>100</v>
       </c>
-      <c r="L31" s="94">
+      <c r="L31" s="91">
         <v>100</v>
       </c>
-      <c r="M31" s="94">
+      <c r="M31" s="91">
         <v>1</v>
       </c>
-      <c r="N31" s="99">
+      <c r="N31" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O31" s="99">
+      <c r="O31" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P31" s="102" t="s">
+      <c r="P31" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="45">
-        <v>1.5E-3</v>
-      </c>
-      <c r="R31" s="100">
+      <c r="Q31" s="44">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="R31" s="97">
         <f t="shared" si="2"/>
-        <v>0.15</v>
-      </c>
-      <c r="S31" s="100">
-        <v>1.5E-3</v>
-      </c>
-      <c r="T31" s="100">
+        <v>0.16</v>
+      </c>
+      <c r="S31" s="97">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="T31" s="97">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="U31" s="14"/>
-      <c r="V31" s="191"/>
+      <c r="V31" s="14"/>
       <c r="W31" s="15"/>
       <c r="X31" s="11"/>
     </row>
@@ -4902,67 +4925,67 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="266"/>
-      <c r="C32" s="80" t="s">
+      <c r="B32" s="274"/>
+      <c r="C32" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="D32" s="122" t="s">
+        <v>237</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="D32" s="127" t="s">
+      <c r="G32" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="E32" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="69" t="s">
+      <c r="I32" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="67" t="s">
         <v>240</v>
       </c>
-      <c r="G32" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="H32" s="41" t="s">
-        <v>241</v>
-      </c>
-      <c r="I32" s="93" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="K32" s="94">
+      <c r="K32" s="91">
         <v>100</v>
       </c>
-      <c r="L32" s="94">
+      <c r="L32" s="91">
         <v>100</v>
       </c>
-      <c r="M32" s="94">
+      <c r="M32" s="91">
         <v>4</v>
       </c>
-      <c r="N32" s="99">
+      <c r="N32" s="96">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="O32" s="99">
+      <c r="O32" s="96">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="P32" s="102" t="s">
+      <c r="P32" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="Q32" s="45">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="R32" s="100">
+      <c r="Q32" s="44">
+        <v>1.4E-3</v>
+      </c>
+      <c r="R32" s="97">
         <f t="shared" si="2"/>
-        <v>0.13</v>
-      </c>
-      <c r="S32" s="100">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="T32" s="100">
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="S32" s="97">
+        <v>1.4E-3</v>
+      </c>
+      <c r="T32" s="97">
         <f t="shared" si="3"/>
-        <v>0.13</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="U32" s="14"/>
-      <c r="V32" s="191"/>
+      <c r="V32" s="14"/>
       <c r="W32" s="15"/>
       <c r="X32" s="11"/>
     </row>
@@ -4970,67 +4993,67 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="267"/>
-      <c r="C33" s="77" t="s">
+      <c r="B33" s="275"/>
+      <c r="C33" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="165" t="s">
-        <v>281</v>
-      </c>
-      <c r="E33" s="78" t="s">
+      <c r="D33" s="147" t="s">
+        <v>279</v>
+      </c>
+      <c r="E33" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="78" t="s">
+      <c r="F33" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="54" t="s">
+      <c r="H33" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="135" t="s">
+      <c r="I33" s="128" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="78" t="s">
+      <c r="J33" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="166">
+      <c r="K33" s="148">
         <v>100</v>
       </c>
-      <c r="L33" s="166">
+      <c r="L33" s="148">
         <v>100</v>
       </c>
-      <c r="M33" s="166">
+      <c r="M33" s="148">
         <v>2</v>
       </c>
-      <c r="N33" s="57">
+      <c r="N33" s="55">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O33" s="57">
+      <c r="O33" s="55">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P33" s="167" t="s">
+      <c r="P33" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="58">
+      <c r="Q33" s="56">
         <v>1.4E-3</v>
       </c>
-      <c r="R33" s="105">
+      <c r="R33" s="102">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="S33" s="105">
+      <c r="S33" s="102">
         <v>1.4E-3</v>
       </c>
-      <c r="T33" s="105">
+      <c r="T33" s="102">
         <f t="shared" si="3"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="U33" s="16"/>
-      <c r="V33" s="193"/>
+      <c r="V33" s="16"/>
       <c r="W33" s="17"/>
       <c r="X33" s="11"/>
     </row>
@@ -5038,72 +5061,72 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="265" t="s">
+      <c r="B34" s="274" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="204" t="s">
+      <c r="C34" s="241" t="s">
         <v>89</v>
       </c>
-      <c r="D34" s="205" t="s">
+      <c r="D34" s="201" t="s">
         <v>90</v>
       </c>
-      <c r="E34" s="227" t="s">
+      <c r="E34" s="202" t="s">
         <v>91</v>
       </c>
-      <c r="F34" s="227" t="s">
+      <c r="F34" s="202" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="228" t="s">
+      <c r="G34" s="203" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="229" t="s">
+      <c r="H34" s="204" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="228" t="s">
+      <c r="I34" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="J34" s="227" t="s">
+      <c r="J34" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="227">
+      <c r="K34" s="202">
         <v>11</v>
       </c>
-      <c r="L34" s="227">
+      <c r="L34" s="202">
         <v>42</v>
       </c>
-      <c r="M34" s="209">
+      <c r="M34" s="205">
         <v>2</v>
       </c>
-      <c r="N34" s="209">
+      <c r="N34" s="205">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O34" s="209">
+      <c r="O34" s="205">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P34" s="230" t="s">
+      <c r="P34" s="206" t="s">
         <v>135</v>
       </c>
-      <c r="Q34" s="231">
+      <c r="Q34" s="207">
         <v>0.318</v>
       </c>
-      <c r="R34" s="213">
+      <c r="R34" s="208">
         <f t="shared" si="2"/>
         <v>3.4980000000000002</v>
       </c>
-      <c r="S34" s="213">
+      <c r="S34" s="208">
         <v>0.4148</v>
       </c>
-      <c r="T34" s="213">
+      <c r="T34" s="208">
         <f t="shared" si="3"/>
         <v>17.421600000000002</v>
       </c>
-      <c r="U34" s="232"/>
-      <c r="V34" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W34" s="277" t="s">
+      <c r="U34" s="199"/>
+      <c r="V34" s="199" t="s">
+        <v>293</v>
+      </c>
+      <c r="W34" s="257" t="s">
         <v>135</v>
       </c>
       <c r="X34" s="11"/>
@@ -5112,212 +5135,212 @@
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="266"/>
-      <c r="C35" s="216" t="s">
+      <c r="B35" s="274"/>
+      <c r="C35" s="151" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="217" t="s">
+      <c r="D35" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="218" t="s">
+      <c r="E35" s="153" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="218" t="s">
+      <c r="F35" s="153" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="219" t="s">
+      <c r="G35" s="154" t="s">
         <v>133</v>
       </c>
-      <c r="H35" s="219" t="s">
+      <c r="H35" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="I35" s="219" t="s">
+      <c r="I35" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="J35" s="218" t="s">
+      <c r="J35" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="219">
+      <c r="K35" s="154">
         <v>6</v>
       </c>
-      <c r="L35" s="219">
+      <c r="L35" s="154">
         <v>21</v>
       </c>
-      <c r="M35" s="221">
+      <c r="M35" s="156">
         <v>1</v>
       </c>
-      <c r="N35" s="221">
+      <c r="N35" s="156">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O35" s="221">
+      <c r="O35" s="156">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P35" s="222" t="s">
+      <c r="P35" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="Q35" s="223">
-        <v>0.39889999999999998</v>
-      </c>
-      <c r="R35" s="224">
+      <c r="Q35" s="158">
+        <v>0.40610000000000002</v>
+      </c>
+      <c r="R35" s="159">
         <f t="shared" si="2"/>
-        <v>2.3933999999999997</v>
-      </c>
-      <c r="S35" s="224">
-        <v>0.33829999999999999</v>
-      </c>
-      <c r="T35" s="224">
+        <v>2.4366000000000003</v>
+      </c>
+      <c r="S35" s="159">
+        <v>0.3528</v>
+      </c>
+      <c r="T35" s="159">
         <f t="shared" si="3"/>
-        <v>7.1042999999999994</v>
-      </c>
-      <c r="U35" s="225"/>
-      <c r="V35" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W35" s="226"/>
+        <v>7.4088000000000003</v>
+      </c>
+      <c r="U35" s="160"/>
+      <c r="V35" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W35" s="161"/>
       <c r="X35" s="11"/>
     </row>
     <row r="36" spans="1:24" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="266"/>
-      <c r="C36" s="216" t="s">
+      <c r="B36" s="274"/>
+      <c r="C36" s="151" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="217" t="s">
+      <c r="D36" s="152" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="218" t="s">
+      <c r="E36" s="153" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F36" s="153" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="219" t="s">
+      <c r="G36" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="219" t="s">
+      <c r="H36" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="218" t="s">
+      <c r="I36" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="218" t="s">
+      <c r="J36" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K36" s="219">
+      <c r="K36" s="154">
         <v>6</v>
       </c>
-      <c r="L36" s="219">
+      <c r="L36" s="154">
         <v>21</v>
       </c>
-      <c r="M36" s="221">
+      <c r="M36" s="156">
         <v>1</v>
       </c>
-      <c r="N36" s="221">
+      <c r="N36" s="156">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O36" s="221">
+      <c r="O36" s="156">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P36" s="222" t="s">
+      <c r="P36" s="157" t="s">
         <v>153</v>
       </c>
-      <c r="Q36" s="233">
+      <c r="Q36" s="162">
         <v>8</v>
       </c>
-      <c r="R36" s="224">
+      <c r="R36" s="159">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="S36" s="224">
+      <c r="S36" s="159">
         <v>8</v>
       </c>
-      <c r="T36" s="224">
+      <c r="T36" s="159">
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="U36" s="234"/>
-      <c r="V36" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W36" s="235"/>
+      <c r="U36" s="163"/>
+      <c r="V36" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W36" s="164"/>
       <c r="X36" s="11"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="266"/>
-      <c r="C37" s="86" t="s">
+      <c r="B37" s="274"/>
+      <c r="C37" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="121" t="s">
+      <c r="D37" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="87" t="s">
+      <c r="E37" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="87" t="s">
+      <c r="F37" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="G37" s="88" t="s">
+      <c r="G37" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="88" t="s">
+      <c r="H37" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="87" t="s">
+      <c r="I37" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="87" t="s">
+      <c r="J37" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="88">
+      <c r="K37" s="85">
         <v>11</v>
       </c>
-      <c r="L37" s="88">
+      <c r="L37" s="85">
         <v>41</v>
       </c>
-      <c r="M37" s="89">
+      <c r="M37" s="86">
         <v>2</v>
       </c>
-      <c r="N37" s="89">
+      <c r="N37" s="86">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O37" s="99">
+      <c r="O37" s="96">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="P37" s="90" t="s">
+      <c r="P37" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="Q37" s="250">
+      <c r="Q37" s="172">
         <v>4.76</v>
       </c>
-      <c r="R37" s="103">
+      <c r="R37" s="100">
         <f t="shared" si="2"/>
         <v>52.36</v>
       </c>
-      <c r="S37" s="103">
+      <c r="S37" s="100">
         <v>4.76</v>
       </c>
-      <c r="T37" s="251">
+      <c r="T37" s="173">
         <f t="shared" si="3"/>
         <v>195.16</v>
       </c>
-      <c r="U37" s="91" t="s">
-        <v>297</v>
-      </c>
-      <c r="V37" s="189" t="s">
+      <c r="U37" s="88" t="s">
         <v>295</v>
       </c>
-      <c r="W37" s="250">
+      <c r="V37" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W37" s="258">
         <v>4.76</v>
       </c>
       <c r="X37" s="11"/>
@@ -5326,67 +5349,67 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="266"/>
-      <c r="C38" s="80" t="s">
+      <c r="B38" s="274"/>
+      <c r="C38" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="119" t="s">
+      <c r="D38" s="115" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="69" t="s">
+      <c r="E38" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="F38" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="F38" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="G38" s="47" t="s">
+      <c r="H38" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="H38" s="47" t="s">
-        <v>211</v>
-      </c>
-      <c r="I38" s="42" t="s">
+      <c r="I38" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J38" s="43" t="s">
+      <c r="J38" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="47">
+      <c r="K38" s="46">
         <v>6</v>
       </c>
-      <c r="L38" s="47">
+      <c r="L38" s="46">
         <v>21</v>
       </c>
-      <c r="M38" s="71">
+      <c r="M38" s="69">
         <v>1</v>
       </c>
-      <c r="N38" s="99">
+      <c r="N38" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O38" s="99">
+      <c r="O38" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P38" s="92" t="s">
+      <c r="P38" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q38" s="45">
-        <v>2.3479000000000001</v>
-      </c>
-      <c r="R38" s="100">
+      <c r="Q38" s="44">
+        <v>2.3496999999999999</v>
+      </c>
+      <c r="R38" s="97">
         <f t="shared" si="2"/>
-        <v>14.087400000000001</v>
-      </c>
-      <c r="S38" s="100">
-        <v>2.3479000000000001</v>
-      </c>
-      <c r="T38" s="100">
+        <v>14.098199999999999</v>
+      </c>
+      <c r="S38" s="97">
+        <v>2.3496999999999999</v>
+      </c>
+      <c r="T38" s="97">
         <f t="shared" si="3"/>
-        <v>49.305900000000001</v>
+        <v>49.343699999999998</v>
       </c>
       <c r="U38" s="20"/>
-      <c r="V38" s="195"/>
+      <c r="V38" s="20"/>
       <c r="W38" s="15"/>
       <c r="X38" s="11"/>
     </row>
@@ -5394,67 +5417,67 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="266"/>
-      <c r="C39" s="80" t="s">
+      <c r="B39" s="274"/>
+      <c r="C39" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="D39" s="119" t="s">
+      <c r="D39" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="E39" s="69" t="s">
+      <c r="E39" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="F39" s="69" t="s">
+      <c r="F39" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="G39" s="47" t="s">
+      <c r="G39" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="H39" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="47" t="s">
-        <v>213</v>
-      </c>
-      <c r="I39" s="42" t="s">
+      <c r="I39" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="43" t="s">
+      <c r="J39" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="47">
+      <c r="K39" s="46">
         <v>6</v>
       </c>
-      <c r="L39" s="47">
+      <c r="L39" s="46">
         <v>21</v>
       </c>
-      <c r="M39" s="71">
+      <c r="M39" s="69">
         <v>1</v>
       </c>
-      <c r="N39" s="99">
+      <c r="N39" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O39" s="99">
+      <c r="O39" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P39" s="92" t="s">
+      <c r="P39" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q39" s="45">
-        <v>0.74660000000000004</v>
-      </c>
-      <c r="R39" s="100">
+      <c r="Q39" s="44">
+        <v>0.6492</v>
+      </c>
+      <c r="R39" s="97">
         <f t="shared" si="2"/>
-        <v>4.4796000000000005</v>
-      </c>
-      <c r="S39" s="100">
-        <v>0.60960000000000003</v>
-      </c>
-      <c r="T39" s="100">
+        <v>3.8952</v>
+      </c>
+      <c r="S39" s="97">
+        <v>0.5464</v>
+      </c>
+      <c r="T39" s="97">
         <f t="shared" si="3"/>
-        <v>12.801600000000001</v>
+        <v>11.474399999999999</v>
       </c>
       <c r="U39" s="20"/>
-      <c r="V39" s="195"/>
+      <c r="V39" s="20"/>
       <c r="W39" s="15"/>
       <c r="X39" s="11"/>
     </row>
@@ -5462,277 +5485,277 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="266"/>
-      <c r="C40" s="216" t="s">
+      <c r="B40" s="274"/>
+      <c r="C40" s="151" t="s">
+        <v>269</v>
+      </c>
+      <c r="D40" s="152" t="s">
+        <v>270</v>
+      </c>
+      <c r="E40" s="153" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="153" t="s">
         <v>271</v>
       </c>
-      <c r="D40" s="217" t="s">
-        <v>272</v>
-      </c>
-      <c r="E40" s="218" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="218" t="s">
-        <v>273</v>
-      </c>
-      <c r="G40" s="219" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219" t="s">
+      <c r="G40" s="154" t="s">
+        <v>277</v>
+      </c>
+      <c r="H40" s="154"/>
+      <c r="I40" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="218" t="s">
+      <c r="J40" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="219">
+      <c r="K40" s="154">
         <v>6</v>
       </c>
-      <c r="L40" s="219">
+      <c r="L40" s="154">
         <v>22</v>
       </c>
-      <c r="M40" s="221">
+      <c r="M40" s="156">
         <v>1</v>
       </c>
-      <c r="N40" s="221">
+      <c r="N40" s="156">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O40" s="221">
+      <c r="O40" s="156">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P40" s="248" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q40" s="223">
+      <c r="P40" s="171" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q40" s="158">
         <v>0.8</v>
       </c>
-      <c r="R40" s="224">
+      <c r="R40" s="159">
         <f t="shared" si="2"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S40" s="224">
+      <c r="S40" s="159">
         <v>0.8</v>
       </c>
-      <c r="T40" s="224">
+      <c r="T40" s="159">
         <f t="shared" si="3"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="U40" s="247" t="s">
-        <v>280</v>
-      </c>
-      <c r="V40" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W40" s="226"/>
+      <c r="U40" s="170" t="s">
+        <v>278</v>
+      </c>
+      <c r="V40" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W40" s="161"/>
       <c r="X40" s="11"/>
     </row>
     <row r="41" spans="1:24" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="266"/>
-      <c r="C41" s="236" t="s">
+      <c r="B41" s="274"/>
+      <c r="C41" s="151" t="s">
+        <v>282</v>
+      </c>
+      <c r="D41" s="152" t="s">
+        <v>280</v>
+      </c>
+      <c r="E41" s="153" t="s">
+        <v>283</v>
+      </c>
+      <c r="F41" s="181" t="s">
         <v>284</v>
       </c>
-      <c r="D41" s="237" t="s">
-        <v>282</v>
-      </c>
-      <c r="E41" s="238" t="s">
+      <c r="G41" s="154" t="s">
         <v>285</v>
       </c>
-      <c r="F41" s="239" t="s">
-        <v>286</v>
-      </c>
-      <c r="G41" s="240" t="s">
-        <v>287</v>
-      </c>
-      <c r="H41" s="240" t="s">
+      <c r="H41" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="I41" s="219" t="s">
+      <c r="I41" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="218" t="s">
+      <c r="J41" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="240">
+      <c r="K41" s="154">
         <v>10</v>
       </c>
-      <c r="L41" s="240">
+      <c r="L41" s="154">
         <v>30</v>
       </c>
-      <c r="M41" s="241">
+      <c r="M41" s="156">
         <v>1</v>
       </c>
-      <c r="N41" s="241">
+      <c r="N41" s="156">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O41" s="241">
+      <c r="O41" s="156">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P41" s="242" t="s">
+      <c r="P41" s="157" t="s">
         <v>135</v>
       </c>
-      <c r="Q41" s="243">
+      <c r="Q41" s="158">
         <v>1</v>
       </c>
-      <c r="R41" s="244">
+      <c r="R41" s="159">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S41" s="244">
+      <c r="S41" s="159">
         <v>1</v>
       </c>
-      <c r="T41" s="224">
+      <c r="T41" s="159">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="U41" s="245"/>
-      <c r="V41" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W41" s="246"/>
+      <c r="U41" s="182"/>
+      <c r="V41" s="160" t="s">
+        <v>293</v>
+      </c>
+      <c r="W41" s="161"/>
       <c r="X41" s="11"/>
     </row>
     <row r="42" spans="1:24" ht="26.25" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="267"/>
-      <c r="C42" s="77" t="s">
+      <c r="B42" s="274"/>
+      <c r="C42" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="D42" s="120" t="s">
+      <c r="D42" s="141" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="78" t="s">
+      <c r="E42" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="F42" s="78" t="s">
+      <c r="F42" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="G42" s="56" t="s">
+      <c r="G42" s="140" t="s">
         <v>138</v>
       </c>
-      <c r="H42" s="56" t="s">
+      <c r="H42" s="140" t="s">
         <v>139</v>
       </c>
-      <c r="I42" s="56" t="s">
+      <c r="I42" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="J42" s="56" t="s">
+      <c r="J42" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="53">
+      <c r="K42" s="48">
         <v>10</v>
       </c>
-      <c r="L42" s="53">
+      <c r="L42" s="48">
         <v>30</v>
       </c>
-      <c r="M42" s="82">
+      <c r="M42" s="243">
         <v>1</v>
       </c>
-      <c r="N42" s="57">
+      <c r="N42" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O42" s="57">
+      <c r="O42" s="104">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P42" s="83" t="s">
+      <c r="P42" s="244" t="s">
         <v>16</v>
       </c>
-      <c r="Q42" s="58">
-        <v>5.3499999999999999E-2</v>
+      <c r="Q42" s="51">
+        <v>5.6099999999999997E-2</v>
       </c>
       <c r="R42" s="105">
         <f t="shared" si="2"/>
-        <v>0.53500000000000003</v>
+        <v>0.56099999999999994</v>
       </c>
       <c r="S42" s="105">
-        <v>5.3499999999999999E-2</v>
+        <v>5.6099999999999997E-2</v>
       </c>
       <c r="T42" s="105">
         <f t="shared" si="3"/>
-        <v>1.605</v>
-      </c>
-      <c r="U42" s="21"/>
-      <c r="V42" s="196"/>
-      <c r="W42" s="17"/>
+        <v>1.6829999999999998</v>
+      </c>
+      <c r="U42" s="245"/>
+      <c r="V42" s="245"/>
+      <c r="W42" s="28"/>
       <c r="X42" s="11"/>
     </row>
     <row r="43" spans="1:24" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="265" t="s">
+      <c r="B43" s="273" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="76" t="s">
+      <c r="D43" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="79" t="s">
+      <c r="F43" s="77" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="38" t="s">
+      <c r="G43" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="H43" s="38" t="s">
+      <c r="H43" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="I43" s="37" t="s">
+      <c r="I43" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="J43" s="37" t="s">
+      <c r="J43" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="60">
+      <c r="K43" s="58">
         <v>50</v>
       </c>
-      <c r="L43" s="60">
+      <c r="L43" s="58">
         <v>50</v>
       </c>
-      <c r="M43" s="61">
+      <c r="M43" s="59">
         <v>1</v>
       </c>
-      <c r="N43" s="38">
+      <c r="N43" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O43" s="38">
+      <c r="O43" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P43" s="84" t="s">
+      <c r="P43" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="39">
-        <v>1.4E-2</v>
-      </c>
-      <c r="R43" s="40">
+      <c r="Q43" s="38">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="R43" s="39">
         <f t="shared" si="2"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="S43" s="40">
-        <v>1.4E-2</v>
-      </c>
-      <c r="T43" s="40">
+        <v>0.72500000000000009</v>
+      </c>
+      <c r="S43" s="39">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="T43" s="39">
         <f t="shared" si="3"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="U43" s="22"/>
-      <c r="V43" s="197"/>
+        <v>0.72500000000000009</v>
+      </c>
+      <c r="U43" s="21"/>
+      <c r="V43" s="21"/>
       <c r="W43" s="13"/>
       <c r="X43" s="11"/>
     </row>
@@ -5740,67 +5763,67 @@
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="266"/>
-      <c r="C44" s="80" t="s">
+      <c r="B44" s="274"/>
+      <c r="C44" s="78" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" s="115" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="G44" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="D44" s="119" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="F44" s="69" t="s">
+      <c r="H44" s="42" t="s">
         <v>292</v>
       </c>
-      <c r="G44" s="43" t="s">
-        <v>293</v>
-      </c>
-      <c r="H44" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="I44" s="43" t="s">
+      <c r="I44" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J44" s="43" t="s">
+      <c r="J44" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="43">
+      <c r="K44" s="42">
         <v>10</v>
       </c>
-      <c r="L44" s="43">
+      <c r="L44" s="42">
         <v>30</v>
       </c>
-      <c r="M44" s="62">
+      <c r="M44" s="60">
         <v>1</v>
       </c>
-      <c r="N44" s="99">
+      <c r="N44" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O44" s="99">
+      <c r="O44" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P44" s="92" t="s">
+      <c r="P44" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q44" s="59">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="R44" s="100">
+      <c r="Q44" s="57">
+        <v>6.2E-2</v>
+      </c>
+      <c r="R44" s="97">
         <f t="shared" si="2"/>
-        <v>0.59</v>
-      </c>
-      <c r="S44" s="100">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="T44" s="100">
+        <v>0.62</v>
+      </c>
+      <c r="S44" s="97">
+        <v>6.2E-2</v>
+      </c>
+      <c r="T44" s="97">
         <f t="shared" si="3"/>
-        <v>1.77</v>
-      </c>
-      <c r="U44" s="26"/>
-      <c r="V44" s="198"/>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="U44" s="25"/>
+      <c r="V44" s="25"/>
       <c r="W44" s="15"/>
       <c r="X44" s="11"/>
     </row>
@@ -5808,67 +5831,67 @@
       <c r="A45" s="6">
         <v>43</v>
       </c>
-      <c r="B45" s="266"/>
-      <c r="C45" s="80" t="s">
+      <c r="B45" s="274"/>
+      <c r="C45" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="119" t="s">
+      <c r="D45" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="69" t="s">
+      <c r="E45" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="85" t="s">
+      <c r="F45" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="G45" s="43" t="s">
+      <c r="G45" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="H45" s="43" t="s">
+      <c r="H45" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="I45" s="43" t="s">
+      <c r="I45" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="J45" s="43" t="s">
+      <c r="J45" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="43">
+      <c r="K45" s="42">
         <v>50</v>
       </c>
-      <c r="L45" s="43">
+      <c r="L45" s="42">
         <v>50</v>
       </c>
-      <c r="M45" s="62">
+      <c r="M45" s="60">
         <v>1</v>
       </c>
-      <c r="N45" s="99">
+      <c r="N45" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O45" s="99">
+      <c r="O45" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P45" s="81" t="s">
+      <c r="P45" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="Q45" s="45">
-        <v>1.26E-2</v>
-      </c>
-      <c r="R45" s="100">
+      <c r="Q45" s="44">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R45" s="97">
         <f t="shared" si="2"/>
-        <v>0.63</v>
-      </c>
-      <c r="S45" s="100">
-        <v>1.26E-2</v>
-      </c>
-      <c r="T45" s="100">
+        <v>0.65</v>
+      </c>
+      <c r="S45" s="97">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="T45" s="97">
         <f t="shared" si="3"/>
-        <v>0.63</v>
-      </c>
-      <c r="U45" s="27"/>
-      <c r="V45" s="199"/>
+        <v>0.65</v>
+      </c>
+      <c r="U45" s="26"/>
+      <c r="V45" s="26"/>
       <c r="W45" s="15"/>
       <c r="X45" s="11"/>
     </row>
@@ -5876,347 +5899,345 @@
       <c r="A46" s="6">
         <v>44</v>
       </c>
-      <c r="B46" s="266"/>
-      <c r="C46" s="216" t="s">
+      <c r="B46" s="274"/>
+      <c r="C46" s="175" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="122" t="s">
+        <v>273</v>
+      </c>
+      <c r="E46" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="D46" s="217" t="s">
+      <c r="G46" s="90" t="s">
         <v>275</v>
       </c>
-      <c r="E46" s="218" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="218" t="s">
+      <c r="H46" s="90" t="s">
         <v>276</v>
       </c>
-      <c r="G46" s="218" t="s">
-        <v>277</v>
-      </c>
-      <c r="H46" s="218" t="s">
-        <v>278</v>
-      </c>
-      <c r="I46" s="218" t="s">
+      <c r="I46" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="J46" s="218" t="s">
+      <c r="J46" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="218">
+      <c r="K46" s="90">
         <v>5</v>
       </c>
-      <c r="L46" s="218">
+      <c r="L46" s="90">
         <v>25</v>
       </c>
-      <c r="M46" s="221">
+      <c r="M46" s="47">
         <v>1</v>
       </c>
-      <c r="N46" s="221">
+      <c r="N46" s="47">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O46" s="221">
+      <c r="O46" s="47">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P46" s="248" t="s">
+      <c r="P46" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="Q46" s="223">
-        <v>0.1002</v>
-      </c>
-      <c r="R46" s="224">
+      <c r="Q46" s="177">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="R46" s="178">
         <f t="shared" si="2"/>
-        <v>0.501</v>
-      </c>
-      <c r="S46" s="224">
-        <v>0.1002</v>
-      </c>
-      <c r="T46" s="224">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="S46" s="178">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="T46" s="178">
         <f t="shared" si="3"/>
-        <v>2.5049999999999999</v>
-      </c>
-      <c r="U46" s="249"/>
-      <c r="V46" s="189" t="s">
-        <v>295</v>
-      </c>
-      <c r="W46" s="226"/>
+        <v>2.34</v>
+      </c>
+      <c r="U46" s="179"/>
+      <c r="V46" s="183"/>
+      <c r="W46" s="180"/>
       <c r="X46" s="11"/>
     </row>
     <row r="47" spans="1:24" ht="15.75" thickBot="1">
       <c r="A47" s="6">
         <v>45</v>
       </c>
-      <c r="B47" s="266"/>
-      <c r="C47" s="95" t="s">
+      <c r="B47" s="274"/>
+      <c r="C47" s="78" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="E47" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="184">
+        <v>61300611121</v>
+      </c>
+      <c r="G47" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="H47" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="D47" s="74" t="s">
-        <v>283</v>
-      </c>
-      <c r="E47" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="180">
-        <v>61300611121</v>
-      </c>
-      <c r="G47" s="147" t="s">
-        <v>289</v>
-      </c>
-      <c r="H47" s="147" t="s">
-        <v>290</v>
-      </c>
-      <c r="I47" s="147" t="s">
-        <v>290</v>
-      </c>
-      <c r="J47" s="43" t="s">
+      <c r="I47" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="J47" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="K47" s="147">
+      <c r="K47" s="42">
         <v>20</v>
       </c>
-      <c r="L47" s="147">
+      <c r="L47" s="42">
         <v>40</v>
       </c>
-      <c r="M47" s="178">
+      <c r="M47" s="60">
         <v>1</v>
       </c>
-      <c r="N47" s="107">
+      <c r="N47" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O47" s="107">
+      <c r="O47" s="96">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P47" s="177" t="s">
+      <c r="P47" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Q47" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="R47" s="100">
+      <c r="Q47" s="44">
+        <v>3.09E-2</v>
+      </c>
+      <c r="R47" s="97">
         <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-      <c r="S47" s="108">
-        <v>0.03</v>
-      </c>
-      <c r="T47" s="100">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="S47" s="97">
+        <v>3.09E-2</v>
+      </c>
+      <c r="T47" s="97">
         <f t="shared" si="3"/>
-        <v>1.2</v>
-      </c>
-      <c r="U47" s="179"/>
-      <c r="V47" s="200"/>
-      <c r="W47" s="29"/>
+        <v>1.236</v>
+      </c>
+      <c r="U47" s="26"/>
+      <c r="V47" s="26"/>
+      <c r="W47" s="15"/>
       <c r="X47" s="11"/>
     </row>
     <row r="48" spans="1:24" ht="115.5" thickBot="1">
       <c r="A48" s="6">
         <v>46</v>
       </c>
-      <c r="B48" s="267"/>
-      <c r="C48" s="110" t="s">
+      <c r="B48" s="275"/>
+      <c r="C48" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="D48" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="E48" s="112" t="s">
+      <c r="D48" s="107" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="112" t="s">
+      <c r="F48" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="G48" s="113" t="s">
+      <c r="G48" s="109" t="s">
         <v>144</v>
       </c>
-      <c r="H48" s="113"/>
-      <c r="I48" s="114"/>
-      <c r="J48" s="114" t="s">
+      <c r="H48" s="109"/>
+      <c r="I48" s="110"/>
+      <c r="J48" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="K48" s="114" t="s">
+      <c r="K48" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="L48" s="114" t="s">
+      <c r="L48" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="115">
+      <c r="M48" s="111">
         <v>53</v>
       </c>
-      <c r="N48" s="116">
+      <c r="N48" s="112">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-      <c r="O48" s="57">
+      <c r="O48" s="55">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
-      <c r="P48" s="113" t="s">
+      <c r="P48" s="109" t="s">
         <v>144</v>
       </c>
-      <c r="Q48" s="114" t="s">
+      <c r="Q48" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="R48" s="114" t="s">
+      <c r="R48" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="S48" s="114" t="s">
+      <c r="S48" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="T48" s="114" t="s">
+      <c r="T48" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="U48" s="117" t="s">
+      <c r="U48" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="V48" s="201"/>
-      <c r="W48" s="118"/>
+      <c r="V48" s="113"/>
+      <c r="W48" s="114"/>
       <c r="X48" s="11"/>
     </row>
     <row r="49" spans="1:24" ht="26.25" thickBot="1">
       <c r="A49" s="6">
         <v>47</v>
       </c>
-      <c r="B49" s="273" t="s">
+      <c r="B49" s="281" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="169" t="s">
-        <v>251</v>
-      </c>
-      <c r="D49" s="170" t="s">
+      <c r="C49" s="246" t="s">
+        <v>249</v>
+      </c>
+      <c r="D49" s="247" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="170" t="s">
+      <c r="E49" s="247" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="170" t="s">
-        <v>250</v>
-      </c>
-      <c r="G49" s="170" t="s">
+      <c r="F49" s="247" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="H49" s="170" t="s">
+      <c r="H49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="I49" s="170" t="s">
+      <c r="I49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="J49" s="170" t="s">
+      <c r="J49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="K49" s="170" t="s">
+      <c r="K49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="170" t="s">
+      <c r="L49" s="247" t="s">
         <v>144</v>
       </c>
-      <c r="M49" s="168">
+      <c r="M49" s="59">
         <v>1</v>
       </c>
-      <c r="N49" s="44">
+      <c r="N49" s="37">
         <f>M49*5</f>
         <v>5</v>
       </c>
-      <c r="O49" s="44">
+      <c r="O49" s="37">
         <f>M49*20</f>
         <v>20</v>
       </c>
-      <c r="P49" s="171" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q49" s="172">
+      <c r="P49" s="248" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q49" s="249">
         <v>0.2</v>
       </c>
-      <c r="R49" s="173">
+      <c r="R49" s="250">
         <f>Q49*N49</f>
         <v>1</v>
       </c>
-      <c r="S49" s="172">
+      <c r="S49" s="249">
         <v>0.2</v>
       </c>
-      <c r="T49" s="46">
+      <c r="T49" s="39">
         <f>S49*O49</f>
         <v>4</v>
       </c>
-      <c r="U49" s="174"/>
-      <c r="V49" s="202"/>
-      <c r="W49" s="176"/>
+      <c r="U49" s="251"/>
+      <c r="V49" s="251"/>
+      <c r="W49" s="252"/>
       <c r="X49" s="11"/>
     </row>
     <row r="50" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A50" s="6">
+      <c r="A50" s="259">
         <v>48</v>
       </c>
-      <c r="B50" s="274"/>
-      <c r="C50" s="129" t="s">
+      <c r="B50" s="282"/>
+      <c r="C50" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="130" t="s">
+      <c r="D50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="E50" s="130" t="s">
+      <c r="E50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="131" t="s">
+      <c r="F50" s="126" t="s">
         <v>152</v>
       </c>
-      <c r="G50" s="130" t="s">
+      <c r="G50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="H50" s="130" t="s">
+      <c r="H50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="I50" s="130" t="s">
+      <c r="I50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="130" t="s">
+      <c r="J50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="K50" s="130" t="s">
+      <c r="K50" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="L50" s="130" t="s">
+      <c r="L50" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="122">
+      <c r="M50" s="117">
         <v>1</v>
       </c>
-      <c r="N50" s="122">
+      <c r="N50" s="117">
         <f t="shared" ref="N50" si="4">M50*5</f>
         <v>5</v>
       </c>
-      <c r="O50" s="57">
+      <c r="O50" s="55">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="P50" s="139" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q50" s="123">
+      <c r="P50" s="132" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q50" s="118">
         <v>3.35</v>
       </c>
-      <c r="R50" s="124">
+      <c r="R50" s="119">
         <f>Q50*N50</f>
         <v>16.75</v>
       </c>
-      <c r="S50" s="124">
+      <c r="S50" s="119">
         <v>3.35</v>
       </c>
-      <c r="T50" s="105">
+      <c r="T50" s="102">
         <f>S50*O50</f>
         <v>67</v>
       </c>
-      <c r="U50" s="117" t="s">
+      <c r="U50" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="V50" s="201"/>
-      <c r="W50" s="132"/>
+      <c r="V50" s="113"/>
+      <c r="W50" s="127"/>
       <c r="X50" s="11"/>
     </row>
     <row r="51" spans="1:24" ht="15.75">
       <c r="A51" s="1"/>
-      <c r="C51" s="23"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="8"/>
       <c r="E51" s="7"/>
       <c r="G51" s="7"/>
@@ -6225,21 +6246,21 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
-      <c r="M51" s="261" t="s">
+      <c r="M51" s="269" t="s">
         <v>37</v>
       </c>
-      <c r="N51" s="262"/>
-      <c r="O51" s="262"/>
-      <c r="P51" s="262"/>
+      <c r="N51" s="270"/>
+      <c r="O51" s="270"/>
+      <c r="P51" s="270"/>
       <c r="Q51" s="19"/>
-      <c r="R51" s="141">
-        <f>SUM(R3:R49)</f>
-        <v>317.21379999999999</v>
-      </c>
-      <c r="S51" s="141"/>
-      <c r="T51" s="98">
-        <f>SUM(T3:T49)</f>
-        <v>1161.0529000000004</v>
+      <c r="R51" s="134">
+        <f>SUM(R3:R50)</f>
+        <v>334.07325999999995</v>
+      </c>
+      <c r="S51" s="134"/>
+      <c r="T51" s="95">
+        <f>SUM(T3:T50)</f>
+        <v>1226.0483999999999</v>
       </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -6254,21 +6275,21 @@
       <c r="I52" s="2"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="263" t="s">
+      <c r="M52" s="271" t="s">
         <v>38</v>
       </c>
-      <c r="N52" s="264"/>
-      <c r="O52" s="264"/>
-      <c r="P52" s="264"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="144">
+      <c r="N52" s="272"/>
+      <c r="O52" s="272"/>
+      <c r="P52" s="272"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="137">
         <f>R51/5</f>
-        <v>63.44276</v>
-      </c>
-      <c r="S52" s="144"/>
-      <c r="T52" s="33">
+        <v>66.814651999999995</v>
+      </c>
+      <c r="S52" s="137"/>
+      <c r="T52" s="32">
         <f>T51/20</f>
-        <v>58.05264500000002</v>
+        <v>61.302419999999998</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
@@ -6283,18 +6304,18 @@
       <c r="I53" s="2"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="252" t="s">
+      <c r="M53" s="29"/>
+      <c r="N53" s="260" t="s">
         <v>147</v>
       </c>
-      <c r="O53" s="253"/>
-      <c r="P53" s="254"/>
-      <c r="Q53" s="140"/>
-      <c r="R53" s="142">
+      <c r="O53" s="261"/>
+      <c r="P53" s="262"/>
+      <c r="Q53" s="133"/>
+      <c r="R53" s="135">
         <v>3</v>
       </c>
-      <c r="S53" s="142"/>
-      <c r="T53" s="143">
+      <c r="S53" s="135"/>
+      <c r="T53" s="136">
         <v>3</v>
       </c>
       <c r="U53" s="7"/>
@@ -6310,18 +6331,18 @@
       <c r="I54" s="2"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="270" t="s">
-        <v>252</v>
-      </c>
-      <c r="O54" s="271"/>
-      <c r="P54" s="272"/>
-      <c r="Q54" s="138"/>
-      <c r="R54" s="137">
+      <c r="M54" s="29"/>
+      <c r="N54" s="278" t="s">
+        <v>250</v>
+      </c>
+      <c r="O54" s="279"/>
+      <c r="P54" s="280"/>
+      <c r="Q54" s="131"/>
+      <c r="R54" s="130">
         <v>22.78</v>
       </c>
-      <c r="S54" s="137"/>
-      <c r="T54" s="145">
+      <c r="S54" s="130"/>
+      <c r="T54" s="138">
         <v>90.99</v>
       </c>
       <c r="U54" s="7"/>
@@ -6335,20 +6356,20 @@
       <c r="D55" s="2"/>
       <c r="G55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="N55" s="255" t="s">
+      <c r="N55" s="263" t="s">
         <v>43</v>
       </c>
-      <c r="O55" s="256"/>
-      <c r="P55" s="257"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="146">
+      <c r="O55" s="264"/>
+      <c r="P55" s="265"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="139">
         <f>SUM(R52:R54)</f>
-        <v>89.222759999999994</v>
-      </c>
-      <c r="S55" s="146"/>
-      <c r="T55" s="32">
+        <v>92.594651999999996</v>
+      </c>
+      <c r="S55" s="139"/>
+      <c r="T55" s="31">
         <f>SUM(T52:T54)</f>
-        <v>152.04264500000002</v>
+        <v>155.29241999999999</v>
       </c>
       <c r="W55" s="11"/>
       <c r="X55" s="11"/>
@@ -6643,20 +6664,20 @@
     <hyperlink ref="P39" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
     <hyperlink ref="P14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="P15" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="P21" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="P22" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="P32" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="P50" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="P49" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="P16" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="P17" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="P23" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="P30" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="P46" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="P41" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="P47" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="P19" r:id="rId43" display="LCSC" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="P40" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="P22" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="P50" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="P49" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="P16" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="P17" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="P30" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="P46" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="P41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="P47" r:id="rId40" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="P19" r:id="rId41" display="LCSC" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="P40" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="P23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="P21" r:id="rId44" xr:uid="{AE5A2967-91AE-4EFF-8287-DFFFA2DC3CCB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId45"/>
